--- a/PPFAS_Equity_Analysis.xlsx
+++ b/PPFAS_Equity_Analysis.xlsx
@@ -9198,17 +9198,17 @@
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>Motilal Oswal Financial Services Limited</t>
+          <t>Zydus Wellness Limited</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>INE338I01027</t>
+          <t>INE768C01010</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>Capital Markets</t>
+          <t>Food Products</t>
         </is>
       </c>
       <c r="D40" s="8" t="n"/>
@@ -9258,86 +9258,64 @@
       <c r="AV40" s="8" t="n"/>
       <c r="AW40" s="9" t="n"/>
       <c r="AX40" s="10" t="n"/>
-      <c r="AY40" s="11" t="n"/>
-      <c r="AZ40" s="8" t="n"/>
-      <c r="BA40" s="9" t="n"/>
-      <c r="BB40" s="10" t="n"/>
-      <c r="BC40" s="11" t="n"/>
-      <c r="BD40" s="8" t="n"/>
-      <c r="BE40" s="9" t="n"/>
-      <c r="BF40" s="10" t="n"/>
+      <c r="AY40" s="11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AZ40" s="8" t="n">
+        <v>4400000</v>
+      </c>
+      <c r="BA40" s="9" t="n">
+        <v>88822.8</v>
+      </c>
+      <c r="BB40" s="10" t="n">
+        <v>0.0077</v>
+      </c>
+      <c r="BC40" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD40" s="8" t="n">
+        <v>4400000</v>
+      </c>
+      <c r="BE40" s="9" t="n">
+        <v>89280.39999999999</v>
+      </c>
+      <c r="BF40" s="10" t="n">
+        <v>0.007900000000000001</v>
+      </c>
       <c r="BG40" s="11" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="BH40" s="8" t="n">
-        <v>591805</v>
+        <v>4400000</v>
       </c>
       <c r="BI40" s="9" t="n">
-        <v>5149</v>
+        <v>89020.8</v>
       </c>
       <c r="BJ40" s="10" t="n">
-        <v>0.0005</v>
+        <v>0.0081</v>
       </c>
       <c r="BK40" s="11" t="n">
-        <v>-0.8902567225534253</v>
-      </c>
-      <c r="BL40" s="8" t="n">
-        <v>5392631</v>
-      </c>
-      <c r="BM40" s="9" t="n">
-        <v>43674.92</v>
-      </c>
-      <c r="BN40" s="10" t="n">
-        <v>0.0042</v>
-      </c>
-      <c r="BO40" s="11" t="n">
-        <v>-0.3719237093069153</v>
-      </c>
-      <c r="BP40" s="8" t="n">
-        <v>8585949</v>
-      </c>
-      <c r="BQ40" s="9" t="n">
-        <v>56044.78</v>
-      </c>
-      <c r="BR40" s="10" t="n">
-        <v>0.0057</v>
-      </c>
-      <c r="BS40" s="11" t="n">
-        <v>-0.2132577936597328</v>
-      </c>
-      <c r="BT40" s="8" t="n">
-        <v>10913294</v>
-      </c>
-      <c r="BU40" s="9" t="n">
-        <v>67154.95</v>
-      </c>
-      <c r="BV40" s="10" t="n">
-        <v>0.0072</v>
-      </c>
-      <c r="BW40" s="11" t="n">
-        <v>-0.09462389658963724</v>
-      </c>
-      <c r="BX40" s="8" t="n">
-        <v>12053879</v>
-      </c>
-      <c r="BY40" s="9" t="n">
-        <v>70937.08</v>
-      </c>
-      <c r="BZ40" s="10" t="n">
-        <v>0.0081</v>
-      </c>
-      <c r="CA40" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB40" s="8" t="n">
-        <v>12053879</v>
-      </c>
-      <c r="CC40" s="9" t="n">
-        <v>76801.28999999999</v>
-      </c>
-      <c r="CD40" s="10" t="n">
-        <v>0.0086</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="BL40" s="8" t="n"/>
+      <c r="BM40" s="9" t="n"/>
+      <c r="BN40" s="10" t="n"/>
+      <c r="BO40" s="11" t="n"/>
+      <c r="BP40" s="8" t="n"/>
+      <c r="BQ40" s="9" t="n"/>
+      <c r="BR40" s="10" t="n"/>
+      <c r="BS40" s="11" t="n"/>
+      <c r="BT40" s="8" t="n"/>
+      <c r="BU40" s="9" t="n"/>
+      <c r="BV40" s="10" t="n"/>
+      <c r="BW40" s="11" t="n"/>
+      <c r="BX40" s="8" t="n"/>
+      <c r="BY40" s="9" t="n"/>
+      <c r="BZ40" s="10" t="n"/>
+      <c r="CA40" s="11" t="n"/>
+      <c r="CB40" s="8" t="n"/>
+      <c r="CC40" s="9" t="n"/>
+      <c r="CD40" s="10" t="n"/>
       <c r="CE40" s="11" t="n"/>
     </row>
     <row r="41">
@@ -9697,17 +9675,17 @@
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>ITC Hotels Limited</t>
+          <t>Motilal Oswal Financial Services Limited</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>INE379A01028</t>
+          <t>INE338I01027</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>Leisure Services</t>
+          <t>Capital Markets</t>
         </is>
       </c>
       <c r="D43" s="8" t="n"/>
@@ -9765,70 +9743,94 @@
       <c r="BD43" s="8" t="n"/>
       <c r="BE43" s="9" t="n"/>
       <c r="BF43" s="10" t="n"/>
-      <c r="BG43" s="11" t="n"/>
-      <c r="BH43" s="8" t="n"/>
-      <c r="BI43" s="9" t="n"/>
-      <c r="BJ43" s="10" t="n"/>
-      <c r="BK43" s="11" t="n"/>
-      <c r="BL43" s="8" t="n"/>
-      <c r="BM43" s="9" t="n"/>
-      <c r="BN43" s="10" t="n"/>
-      <c r="BO43" s="11" t="n"/>
-      <c r="BP43" s="8" t="n"/>
-      <c r="BQ43" s="9" t="n"/>
-      <c r="BR43" s="10" t="n"/>
+      <c r="BG43" s="11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH43" s="8" t="n">
+        <v>591805</v>
+      </c>
+      <c r="BI43" s="9" t="n">
+        <v>5149</v>
+      </c>
+      <c r="BJ43" s="10" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="BK43" s="11" t="n">
+        <v>-0.8902567225534253</v>
+      </c>
+      <c r="BL43" s="8" t="n">
+        <v>5392631</v>
+      </c>
+      <c r="BM43" s="9" t="n">
+        <v>43674.92</v>
+      </c>
+      <c r="BN43" s="10" t="n">
+        <v>0.0042</v>
+      </c>
+      <c r="BO43" s="11" t="n">
+        <v>-0.3719237093069153</v>
+      </c>
+      <c r="BP43" s="8" t="n">
+        <v>8585949</v>
+      </c>
+      <c r="BQ43" s="9" t="n">
+        <v>56044.78</v>
+      </c>
+      <c r="BR43" s="10" t="n">
+        <v>0.0057</v>
+      </c>
       <c r="BS43" s="11" t="n">
-        <v>-1</v>
+        <v>-0.2132577936597328</v>
       </c>
       <c r="BT43" s="8" t="n">
-        <v>9899412</v>
+        <v>10913294</v>
       </c>
       <c r="BU43" s="9" t="n">
-        <v>19552.33</v>
+        <v>67154.95</v>
       </c>
       <c r="BV43" s="10" t="n">
-        <v>0.0021</v>
+        <v>0.0072</v>
       </c>
       <c r="BW43" s="11" t="n">
-        <v>0</v>
+        <v>-0.09462389658963724</v>
       </c>
       <c r="BX43" s="8" t="n">
-        <v>9899412</v>
+        <v>12053879</v>
       </c>
       <c r="BY43" s="9" t="n">
-        <v>16216.23</v>
+        <v>70937.08</v>
       </c>
       <c r="BZ43" s="10" t="n">
-        <v>0.0018</v>
+        <v>0.0081</v>
       </c>
       <c r="CA43" s="11" t="n">
         <v>0</v>
       </c>
       <c r="CB43" s="8" t="n">
-        <v>9899412</v>
+        <v>12053879</v>
       </c>
       <c r="CC43" s="9" t="n">
-        <v>16131.09</v>
+        <v>76801.28999999999</v>
       </c>
       <c r="CD43" s="10" t="n">
-        <v>0.0018</v>
+        <v>0.0086</v>
       </c>
       <c r="CE43" s="11" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>Zydus Wellness Limited</t>
+          <t>ITC Hotels Limited</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>INE768C01010</t>
+          <t>INE379A01028</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>Food Products</t>
+          <t>Leisure Services</t>
         </is>
       </c>
       <c r="D44" s="8" t="n"/>
@@ -9878,45 +9880,19 @@
       <c r="AV44" s="8" t="n"/>
       <c r="AW44" s="9" t="n"/>
       <c r="AX44" s="10" t="n"/>
-      <c r="AY44" s="11" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AZ44" s="8" t="n">
-        <v>4400000</v>
-      </c>
-      <c r="BA44" s="9" t="n">
-        <v>88822.8</v>
-      </c>
-      <c r="BB44" s="10" t="n">
-        <v>0.0077</v>
-      </c>
-      <c r="BC44" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD44" s="8" t="n">
-        <v>4400000</v>
-      </c>
-      <c r="BE44" s="9" t="n">
-        <v>89280.39999999999</v>
-      </c>
-      <c r="BF44" s="10" t="n">
-        <v>0.007900000000000001</v>
-      </c>
-      <c r="BG44" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH44" s="8" t="n">
-        <v>4400000</v>
-      </c>
-      <c r="BI44" s="9" t="n">
-        <v>89020.8</v>
-      </c>
-      <c r="BJ44" s="10" t="n">
-        <v>0.0081</v>
-      </c>
-      <c r="BK44" s="11" t="n">
-        <v>1</v>
-      </c>
+      <c r="AY44" s="11" t="n"/>
+      <c r="AZ44" s="8" t="n"/>
+      <c r="BA44" s="9" t="n"/>
+      <c r="BB44" s="10" t="n"/>
+      <c r="BC44" s="11" t="n"/>
+      <c r="BD44" s="8" t="n"/>
+      <c r="BE44" s="9" t="n"/>
+      <c r="BF44" s="10" t="n"/>
+      <c r="BG44" s="11" t="n"/>
+      <c r="BH44" s="8" t="n"/>
+      <c r="BI44" s="9" t="n"/>
+      <c r="BJ44" s="10" t="n"/>
+      <c r="BK44" s="11" t="n"/>
       <c r="BL44" s="8" t="n"/>
       <c r="BM44" s="9" t="n"/>
       <c r="BN44" s="10" t="n"/>
@@ -9924,18 +9900,42 @@
       <c r="BP44" s="8" t="n"/>
       <c r="BQ44" s="9" t="n"/>
       <c r="BR44" s="10" t="n"/>
-      <c r="BS44" s="11" t="n"/>
-      <c r="BT44" s="8" t="n"/>
-      <c r="BU44" s="9" t="n"/>
-      <c r="BV44" s="10" t="n"/>
-      <c r="BW44" s="11" t="n"/>
-      <c r="BX44" s="8" t="n"/>
-      <c r="BY44" s="9" t="n"/>
-      <c r="BZ44" s="10" t="n"/>
-      <c r="CA44" s="11" t="n"/>
-      <c r="CB44" s="8" t="n"/>
-      <c r="CC44" s="9" t="n"/>
-      <c r="CD44" s="10" t="n"/>
+      <c r="BS44" s="11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BT44" s="8" t="n">
+        <v>9899412</v>
+      </c>
+      <c r="BU44" s="9" t="n">
+        <v>19552.33</v>
+      </c>
+      <c r="BV44" s="10" t="n">
+        <v>0.0021</v>
+      </c>
+      <c r="BW44" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX44" s="8" t="n">
+        <v>9899412</v>
+      </c>
+      <c r="BY44" s="9" t="n">
+        <v>16216.23</v>
+      </c>
+      <c r="BZ44" s="10" t="n">
+        <v>0.0018</v>
+      </c>
+      <c r="CA44" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB44" s="8" t="n">
+        <v>9899412</v>
+      </c>
+      <c r="CC44" s="9" t="n">
+        <v>16131.09</v>
+      </c>
+      <c r="CD44" s="10" t="n">
+        <v>0.0018</v>
+      </c>
       <c r="CE44" s="11" t="n"/>
     </row>
     <row r="45">

--- a/PPFAS_Equity_Analysis.xlsx
+++ b/PPFAS_Equity_Analysis.xlsx
@@ -9198,17 +9198,17 @@
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>Zydus Wellness Limited</t>
+          <t>Motilal Oswal Financial Services Limited</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>INE768C01010</t>
+          <t>INE338I01027</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>Food Products</t>
+          <t>Capital Markets</t>
         </is>
       </c>
       <c r="D40" s="8" t="n"/>
@@ -9258,64 +9258,86 @@
       <c r="AV40" s="8" t="n"/>
       <c r="AW40" s="9" t="n"/>
       <c r="AX40" s="10" t="n"/>
-      <c r="AY40" s="11" t="n">
+      <c r="AY40" s="11" t="n"/>
+      <c r="AZ40" s="8" t="n"/>
+      <c r="BA40" s="9" t="n"/>
+      <c r="BB40" s="10" t="n"/>
+      <c r="BC40" s="11" t="n"/>
+      <c r="BD40" s="8" t="n"/>
+      <c r="BE40" s="9" t="n"/>
+      <c r="BF40" s="10" t="n"/>
+      <c r="BG40" s="11" t="n">
         <v>-1</v>
       </c>
-      <c r="AZ40" s="8" t="n">
-        <v>4400000</v>
-      </c>
-      <c r="BA40" s="9" t="n">
-        <v>88822.8</v>
-      </c>
-      <c r="BB40" s="10" t="n">
-        <v>0.0077</v>
-      </c>
-      <c r="BC40" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD40" s="8" t="n">
-        <v>4400000</v>
-      </c>
-      <c r="BE40" s="9" t="n">
-        <v>89280.39999999999</v>
-      </c>
-      <c r="BF40" s="10" t="n">
-        <v>0.007900000000000001</v>
-      </c>
-      <c r="BG40" s="11" t="n">
-        <v>0</v>
-      </c>
       <c r="BH40" s="8" t="n">
-        <v>4400000</v>
+        <v>591805</v>
       </c>
       <c r="BI40" s="9" t="n">
-        <v>89020.8</v>
+        <v>5149</v>
       </c>
       <c r="BJ40" s="10" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="BK40" s="11" t="n">
+        <v>-0.8902567225534253</v>
+      </c>
+      <c r="BL40" s="8" t="n">
+        <v>5392631</v>
+      </c>
+      <c r="BM40" s="9" t="n">
+        <v>43674.92</v>
+      </c>
+      <c r="BN40" s="10" t="n">
+        <v>0.0042</v>
+      </c>
+      <c r="BO40" s="11" t="n">
+        <v>-0.3719237093069153</v>
+      </c>
+      <c r="BP40" s="8" t="n">
+        <v>8585949</v>
+      </c>
+      <c r="BQ40" s="9" t="n">
+        <v>56044.78</v>
+      </c>
+      <c r="BR40" s="10" t="n">
+        <v>0.0057</v>
+      </c>
+      <c r="BS40" s="11" t="n">
+        <v>-0.2132577936597328</v>
+      </c>
+      <c r="BT40" s="8" t="n">
+        <v>10913294</v>
+      </c>
+      <c r="BU40" s="9" t="n">
+        <v>67154.95</v>
+      </c>
+      <c r="BV40" s="10" t="n">
+        <v>0.0072</v>
+      </c>
+      <c r="BW40" s="11" t="n">
+        <v>-0.09462389658963724</v>
+      </c>
+      <c r="BX40" s="8" t="n">
+        <v>12053879</v>
+      </c>
+      <c r="BY40" s="9" t="n">
+        <v>70937.08</v>
+      </c>
+      <c r="BZ40" s="10" t="n">
         <v>0.0081</v>
       </c>
-      <c r="BK40" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="BL40" s="8" t="n"/>
-      <c r="BM40" s="9" t="n"/>
-      <c r="BN40" s="10" t="n"/>
-      <c r="BO40" s="11" t="n"/>
-      <c r="BP40" s="8" t="n"/>
-      <c r="BQ40" s="9" t="n"/>
-      <c r="BR40" s="10" t="n"/>
-      <c r="BS40" s="11" t="n"/>
-      <c r="BT40" s="8" t="n"/>
-      <c r="BU40" s="9" t="n"/>
-      <c r="BV40" s="10" t="n"/>
-      <c r="BW40" s="11" t="n"/>
-      <c r="BX40" s="8" t="n"/>
-      <c r="BY40" s="9" t="n"/>
-      <c r="BZ40" s="10" t="n"/>
-      <c r="CA40" s="11" t="n"/>
-      <c r="CB40" s="8" t="n"/>
-      <c r="CC40" s="9" t="n"/>
-      <c r="CD40" s="10" t="n"/>
+      <c r="CA40" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB40" s="8" t="n">
+        <v>12053879</v>
+      </c>
+      <c r="CC40" s="9" t="n">
+        <v>76801.28999999999</v>
+      </c>
+      <c r="CD40" s="10" t="n">
+        <v>0.0086</v>
+      </c>
       <c r="CE40" s="11" t="n"/>
     </row>
     <row r="41">
@@ -9675,17 +9697,17 @@
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>Motilal Oswal Financial Services Limited</t>
+          <t>ITC Hotels Limited</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>INE338I01027</t>
+          <t>INE379A01028</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>Capital Markets</t>
+          <t>Leisure Services</t>
         </is>
       </c>
       <c r="D43" s="8" t="n"/>
@@ -9743,94 +9765,70 @@
       <c r="BD43" s="8" t="n"/>
       <c r="BE43" s="9" t="n"/>
       <c r="BF43" s="10" t="n"/>
-      <c r="BG43" s="11" t="n">
+      <c r="BG43" s="11" t="n"/>
+      <c r="BH43" s="8" t="n"/>
+      <c r="BI43" s="9" t="n"/>
+      <c r="BJ43" s="10" t="n"/>
+      <c r="BK43" s="11" t="n"/>
+      <c r="BL43" s="8" t="n"/>
+      <c r="BM43" s="9" t="n"/>
+      <c r="BN43" s="10" t="n"/>
+      <c r="BO43" s="11" t="n"/>
+      <c r="BP43" s="8" t="n"/>
+      <c r="BQ43" s="9" t="n"/>
+      <c r="BR43" s="10" t="n"/>
+      <c r="BS43" s="11" t="n">
         <v>-1</v>
       </c>
-      <c r="BH43" s="8" t="n">
-        <v>591805</v>
-      </c>
-      <c r="BI43" s="9" t="n">
-        <v>5149</v>
-      </c>
-      <c r="BJ43" s="10" t="n">
-        <v>0.0005</v>
-      </c>
-      <c r="BK43" s="11" t="n">
-        <v>-0.8902567225534253</v>
-      </c>
-      <c r="BL43" s="8" t="n">
-        <v>5392631</v>
-      </c>
-      <c r="BM43" s="9" t="n">
-        <v>43674.92</v>
-      </c>
-      <c r="BN43" s="10" t="n">
-        <v>0.0042</v>
-      </c>
-      <c r="BO43" s="11" t="n">
-        <v>-0.3719237093069153</v>
-      </c>
-      <c r="BP43" s="8" t="n">
-        <v>8585949</v>
-      </c>
-      <c r="BQ43" s="9" t="n">
-        <v>56044.78</v>
-      </c>
-      <c r="BR43" s="10" t="n">
-        <v>0.0057</v>
-      </c>
-      <c r="BS43" s="11" t="n">
-        <v>-0.2132577936597328</v>
-      </c>
       <c r="BT43" s="8" t="n">
-        <v>10913294</v>
+        <v>9899412</v>
       </c>
       <c r="BU43" s="9" t="n">
-        <v>67154.95</v>
+        <v>19552.33</v>
       </c>
       <c r="BV43" s="10" t="n">
-        <v>0.0072</v>
+        <v>0.0021</v>
       </c>
       <c r="BW43" s="11" t="n">
-        <v>-0.09462389658963724</v>
+        <v>0</v>
       </c>
       <c r="BX43" s="8" t="n">
-        <v>12053879</v>
+        <v>9899412</v>
       </c>
       <c r="BY43" s="9" t="n">
-        <v>70937.08</v>
+        <v>16216.23</v>
       </c>
       <c r="BZ43" s="10" t="n">
-        <v>0.0081</v>
+        <v>0.0018</v>
       </c>
       <c r="CA43" s="11" t="n">
         <v>0</v>
       </c>
       <c r="CB43" s="8" t="n">
-        <v>12053879</v>
+        <v>9899412</v>
       </c>
       <c r="CC43" s="9" t="n">
-        <v>76801.28999999999</v>
+        <v>16131.09</v>
       </c>
       <c r="CD43" s="10" t="n">
-        <v>0.0086</v>
+        <v>0.0018</v>
       </c>
       <c r="CE43" s="11" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>ITC Hotels Limited</t>
+          <t>Zydus Wellness Limited</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>INE379A01028</t>
+          <t>INE768C01010</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>Leisure Services</t>
+          <t>Food Products</t>
         </is>
       </c>
       <c r="D44" s="8" t="n"/>
@@ -9880,19 +9878,45 @@
       <c r="AV44" s="8" t="n"/>
       <c r="AW44" s="9" t="n"/>
       <c r="AX44" s="10" t="n"/>
-      <c r="AY44" s="11" t="n"/>
-      <c r="AZ44" s="8" t="n"/>
-      <c r="BA44" s="9" t="n"/>
-      <c r="BB44" s="10" t="n"/>
-      <c r="BC44" s="11" t="n"/>
-      <c r="BD44" s="8" t="n"/>
-      <c r="BE44" s="9" t="n"/>
-      <c r="BF44" s="10" t="n"/>
-      <c r="BG44" s="11" t="n"/>
-      <c r="BH44" s="8" t="n"/>
-      <c r="BI44" s="9" t="n"/>
-      <c r="BJ44" s="10" t="n"/>
-      <c r="BK44" s="11" t="n"/>
+      <c r="AY44" s="11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AZ44" s="8" t="n">
+        <v>4400000</v>
+      </c>
+      <c r="BA44" s="9" t="n">
+        <v>88822.8</v>
+      </c>
+      <c r="BB44" s="10" t="n">
+        <v>0.0077</v>
+      </c>
+      <c r="BC44" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD44" s="8" t="n">
+        <v>4400000</v>
+      </c>
+      <c r="BE44" s="9" t="n">
+        <v>89280.39999999999</v>
+      </c>
+      <c r="BF44" s="10" t="n">
+        <v>0.007900000000000001</v>
+      </c>
+      <c r="BG44" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH44" s="8" t="n">
+        <v>4400000</v>
+      </c>
+      <c r="BI44" s="9" t="n">
+        <v>89020.8</v>
+      </c>
+      <c r="BJ44" s="10" t="n">
+        <v>0.0081</v>
+      </c>
+      <c r="BK44" s="11" t="n">
+        <v>1</v>
+      </c>
       <c r="BL44" s="8" t="n"/>
       <c r="BM44" s="9" t="n"/>
       <c r="BN44" s="10" t="n"/>
@@ -9900,42 +9924,18 @@
       <c r="BP44" s="8" t="n"/>
       <c r="BQ44" s="9" t="n"/>
       <c r="BR44" s="10" t="n"/>
-      <c r="BS44" s="11" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BT44" s="8" t="n">
-        <v>9899412</v>
-      </c>
-      <c r="BU44" s="9" t="n">
-        <v>19552.33</v>
-      </c>
-      <c r="BV44" s="10" t="n">
-        <v>0.0021</v>
-      </c>
-      <c r="BW44" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX44" s="8" t="n">
-        <v>9899412</v>
-      </c>
-      <c r="BY44" s="9" t="n">
-        <v>16216.23</v>
-      </c>
-      <c r="BZ44" s="10" t="n">
-        <v>0.0018</v>
-      </c>
-      <c r="CA44" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB44" s="8" t="n">
-        <v>9899412</v>
-      </c>
-      <c r="CC44" s="9" t="n">
-        <v>16131.09</v>
-      </c>
-      <c r="CD44" s="10" t="n">
-        <v>0.0018</v>
-      </c>
+      <c r="BS44" s="11" t="n"/>
+      <c r="BT44" s="8" t="n"/>
+      <c r="BU44" s="9" t="n"/>
+      <c r="BV44" s="10" t="n"/>
+      <c r="BW44" s="11" t="n"/>
+      <c r="BX44" s="8" t="n"/>
+      <c r="BY44" s="9" t="n"/>
+      <c r="BZ44" s="10" t="n"/>
+      <c r="CA44" s="11" t="n"/>
+      <c r="CB44" s="8" t="n"/>
+      <c r="CC44" s="9" t="n"/>
+      <c r="CD44" s="10" t="n"/>
       <c r="CE44" s="11" t="n"/>
     </row>
     <row r="45">

--- a/PPFAS_Equity_Analysis.xlsx
+++ b/PPFAS_Equity_Analysis.xlsx
@@ -490,7 +490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CI46"/>
+  <dimension ref="A1:CE46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -519,39 +519,39 @@
     <col width="14" customWidth="1" min="24" max="24"/>
     <col width="26" customWidth="1" min="25" max="25"/>
     <col width="20" customWidth="1" min="26" max="26"/>
-    <col width="24" customWidth="1" min="27" max="27"/>
-    <col width="14" customWidth="1" min="28" max="28"/>
+    <col width="23" customWidth="1" min="27" max="27"/>
+    <col width="15" customWidth="1" min="28" max="28"/>
     <col width="26" customWidth="1" min="29" max="29"/>
-    <col width="14" customWidth="1" min="30" max="30"/>
-    <col width="23" customWidth="1" min="31" max="31"/>
-    <col width="15" customWidth="1" min="32" max="32"/>
+    <col width="20" customWidth="1" min="30" max="30"/>
+    <col width="24" customWidth="1" min="31" max="31"/>
+    <col width="14" customWidth="1" min="32" max="32"/>
     <col width="26" customWidth="1" min="33" max="33"/>
-    <col width="20" customWidth="1" min="34" max="34"/>
-    <col width="24" customWidth="1" min="35" max="35"/>
-    <col width="14" customWidth="1" min="36" max="36"/>
+    <col width="22" customWidth="1" min="34" max="34"/>
+    <col width="23" customWidth="1" min="35" max="35"/>
+    <col width="15" customWidth="1" min="36" max="36"/>
     <col width="26" customWidth="1" min="37" max="37"/>
-    <col width="22" customWidth="1" min="38" max="38"/>
-    <col width="23" customWidth="1" min="39" max="39"/>
+    <col width="20" customWidth="1" min="38" max="38"/>
+    <col width="22" customWidth="1" min="39" max="39"/>
     <col width="15" customWidth="1" min="40" max="40"/>
     <col width="26" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="22" customWidth="1" min="43" max="43"/>
-    <col width="15" customWidth="1" min="44" max="44"/>
+    <col width="14" customWidth="1" min="44" max="44"/>
     <col width="26" customWidth="1" min="45" max="45"/>
-    <col width="20" customWidth="1" min="46" max="46"/>
-    <col width="22" customWidth="1" min="47" max="47"/>
-    <col width="14" customWidth="1" min="48" max="48"/>
+    <col width="14" customWidth="1" min="46" max="46"/>
+    <col width="23" customWidth="1" min="47" max="47"/>
+    <col width="16" customWidth="1" min="48" max="48"/>
     <col width="26" customWidth="1" min="49" max="49"/>
-    <col width="14" customWidth="1" min="50" max="50"/>
-    <col width="23" customWidth="1" min="51" max="51"/>
-    <col width="16" customWidth="1" min="52" max="52"/>
+    <col width="20" customWidth="1" min="50" max="50"/>
+    <col width="22" customWidth="1" min="51" max="51"/>
+    <col width="13" customWidth="1" min="52" max="52"/>
     <col width="26" customWidth="1" min="53" max="53"/>
     <col width="20" customWidth="1" min="54" max="54"/>
-    <col width="22" customWidth="1" min="55" max="55"/>
+    <col width="23" customWidth="1" min="55" max="55"/>
     <col width="13" customWidth="1" min="56" max="56"/>
     <col width="26" customWidth="1" min="57" max="57"/>
     <col width="20" customWidth="1" min="58" max="58"/>
-    <col width="23" customWidth="1" min="59" max="59"/>
+    <col width="22" customWidth="1" min="59" max="59"/>
     <col width="13" customWidth="1" min="60" max="60"/>
     <col width="26" customWidth="1" min="61" max="61"/>
     <col width="20" customWidth="1" min="62" max="62"/>
@@ -559,27 +559,23 @@
     <col width="13" customWidth="1" min="64" max="64"/>
     <col width="26" customWidth="1" min="65" max="65"/>
     <col width="20" customWidth="1" min="66" max="66"/>
-    <col width="22" customWidth="1" min="67" max="67"/>
+    <col width="23" customWidth="1" min="67" max="67"/>
     <col width="13" customWidth="1" min="68" max="68"/>
     <col width="26" customWidth="1" min="69" max="69"/>
     <col width="20" customWidth="1" min="70" max="70"/>
-    <col width="23" customWidth="1" min="71" max="71"/>
+    <col width="22" customWidth="1" min="71" max="71"/>
     <col width="13" customWidth="1" min="72" max="72"/>
     <col width="26" customWidth="1" min="73" max="73"/>
     <col width="20" customWidth="1" min="74" max="74"/>
-    <col width="22" customWidth="1" min="75" max="75"/>
-    <col width="13" customWidth="1" min="76" max="76"/>
+    <col width="23" customWidth="1" min="75" max="75"/>
+    <col width="15" customWidth="1" min="76" max="76"/>
     <col width="26" customWidth="1" min="77" max="77"/>
     <col width="20" customWidth="1" min="78" max="78"/>
-    <col width="23" customWidth="1" min="79" max="79"/>
-    <col width="15" customWidth="1" min="80" max="80"/>
+    <col width="22" customWidth="1" min="79" max="79"/>
+    <col width="14" customWidth="1" min="80" max="80"/>
     <col width="26" customWidth="1" min="81" max="81"/>
     <col width="20" customWidth="1" min="82" max="82"/>
-    <col width="22" customWidth="1" min="83" max="83"/>
-    <col width="14" customWidth="1" min="84" max="84"/>
-    <col width="26" customWidth="1" min="85" max="85"/>
-    <col width="20" customWidth="1" min="86" max="86"/>
-    <col width="17" customWidth="1" min="87" max="87"/>
+    <col width="17" customWidth="1" min="83" max="83"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -670,10 +666,6 @@
       <c r="CC1" s="1" t="n"/>
       <c r="CD1" s="1" t="n"/>
       <c r="CE1" s="1" t="n"/>
-      <c r="CF1" s="1" t="n"/>
-      <c r="CG1" s="1" t="n"/>
-      <c r="CH1" s="1" t="n"/>
-      <c r="CI1" s="1" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -741,7 +733,7 @@
       <c r="AA2" s="3" t="n"/>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>March_2026</t>
+          <t>February_2026</t>
         </is>
       </c>
       <c r="AC2" s="2" t="n"/>
@@ -749,7 +741,7 @@
       <c r="AE2" s="3" t="n"/>
       <c r="AF2" s="2" t="inlineStr">
         <is>
-          <t>February_2026</t>
+          <t>January_2026</t>
         </is>
       </c>
       <c r="AG2" s="2" t="n"/>
@@ -757,7 +749,7 @@
       <c r="AI2" s="3" t="n"/>
       <c r="AJ2" s="2" t="inlineStr">
         <is>
-          <t>January_2026</t>
+          <t>December_2025</t>
         </is>
       </c>
       <c r="AK2" s="2" t="n"/>
@@ -765,7 +757,7 @@
       <c r="AM2" s="3" t="n"/>
       <c r="AN2" s="2" t="inlineStr">
         <is>
-          <t>December_2025</t>
+          <t>November_2025</t>
         </is>
       </c>
       <c r="AO2" s="2" t="n"/>
@@ -773,7 +765,7 @@
       <c r="AQ2" s="3" t="n"/>
       <c r="AR2" s="2" t="inlineStr">
         <is>
-          <t>November_2025</t>
+          <t>October_2025</t>
         </is>
       </c>
       <c r="AS2" s="2" t="n"/>
@@ -781,7 +773,7 @@
       <c r="AU2" s="3" t="n"/>
       <c r="AV2" s="2" t="inlineStr">
         <is>
-          <t>October_2025</t>
+          <t>September_2025</t>
         </is>
       </c>
       <c r="AW2" s="2" t="n"/>
@@ -789,7 +781,7 @@
       <c r="AY2" s="3" t="n"/>
       <c r="AZ2" s="2" t="inlineStr">
         <is>
-          <t>September_2025</t>
+          <t>August_2025</t>
         </is>
       </c>
       <c r="BA2" s="2" t="n"/>
@@ -797,7 +789,7 @@
       <c r="BC2" s="3" t="n"/>
       <c r="BD2" s="2" t="inlineStr">
         <is>
-          <t>August_2025</t>
+          <t>July_2025</t>
         </is>
       </c>
       <c r="BE2" s="2" t="n"/>
@@ -805,7 +797,7 @@
       <c r="BG2" s="3" t="n"/>
       <c r="BH2" s="2" t="inlineStr">
         <is>
-          <t>July_2025</t>
+          <t>June_2025</t>
         </is>
       </c>
       <c r="BI2" s="2" t="n"/>
@@ -813,7 +805,7 @@
       <c r="BK2" s="3" t="n"/>
       <c r="BL2" s="2" t="inlineStr">
         <is>
-          <t>June_2025</t>
+          <t>May_2025</t>
         </is>
       </c>
       <c r="BM2" s="2" t="n"/>
@@ -821,7 +813,7 @@
       <c r="BO2" s="3" t="n"/>
       <c r="BP2" s="2" t="inlineStr">
         <is>
-          <t>May_2025</t>
+          <t>April_2025</t>
         </is>
       </c>
       <c r="BQ2" s="2" t="n"/>
@@ -829,7 +821,7 @@
       <c r="BS2" s="3" t="n"/>
       <c r="BT2" s="2" t="inlineStr">
         <is>
-          <t>April_2025</t>
+          <t>March_2025</t>
         </is>
       </c>
       <c r="BU2" s="2" t="n"/>
@@ -837,7 +829,7 @@
       <c r="BW2" s="3" t="n"/>
       <c r="BX2" s="2" t="inlineStr">
         <is>
-          <t>March_2025</t>
+          <t>February_2025</t>
         </is>
       </c>
       <c r="BY2" s="2" t="n"/>
@@ -845,20 +837,12 @@
       <c r="CA2" s="3" t="n"/>
       <c r="CB2" s="2" t="inlineStr">
         <is>
-          <t>February_2025</t>
+          <t>January_2025</t>
         </is>
       </c>
       <c r="CC2" s="2" t="n"/>
       <c r="CD2" s="2" t="n"/>
       <c r="CE2" s="3" t="n"/>
-      <c r="CF2" s="2" t="inlineStr">
-        <is>
-          <t>January_2025</t>
-        </is>
-      </c>
-      <c r="CG2" s="2" t="n"/>
-      <c r="CH2" s="2" t="n"/>
-      <c r="CI2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n"/>
@@ -1264,26 +1248,6 @@
           <t>% Change in Qty</t>
         </is>
       </c>
-      <c r="CF3" s="4" t="inlineStr">
-        <is>
-          <t>Quantity</t>
-        </is>
-      </c>
-      <c r="CG3" s="4" t="inlineStr">
-        <is>
-          <t>Market Value (Rs. Lakhs)</t>
-        </is>
-      </c>
-      <c r="CH3" s="4" t="inlineStr">
-        <is>
-          <t>% Net Assets</t>
-        </is>
-      </c>
-      <c r="CI3" s="5" t="inlineStr">
-        <is>
-          <t>% Change in Qty</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -1371,148 +1335,148 @@
         <v>0.0794</v>
       </c>
       <c r="AA4" s="11" t="n">
-        <v>0.03394007080483452</v>
+        <v>0.2402727503134398</v>
       </c>
       <c r="AB4" s="8" t="n">
-        <v>140247203</v>
+        <v>116915576</v>
       </c>
       <c r="AC4" s="9" t="n">
-        <v>1025978.41</v>
+        <v>1037918.03</v>
       </c>
       <c r="AD4" s="10" t="n">
-        <v>0.0796</v>
+        <v>0.07729999999999999</v>
       </c>
       <c r="AE4" s="11" t="n">
-        <v>0.1995596121426969</v>
+        <v>0.008626968303207154</v>
       </c>
       <c r="AF4" s="8" t="n">
-        <v>116915576</v>
+        <v>115915576</v>
       </c>
       <c r="AG4" s="9" t="n">
-        <v>1037918.03</v>
+        <v>1077145.49</v>
       </c>
       <c r="AH4" s="10" t="n">
-        <v>0.07729999999999999</v>
+        <v>0.0804</v>
       </c>
       <c r="AI4" s="11" t="n">
-        <v>0.008626968303207154</v>
+        <v>0.06600587475157653</v>
       </c>
       <c r="AJ4" s="8" t="n">
-        <v>115915576</v>
+        <v>108738215</v>
       </c>
       <c r="AK4" s="9" t="n">
-        <v>1077145.49</v>
+        <v>1077813.19</v>
       </c>
       <c r="AL4" s="10" t="n">
-        <v>0.0804</v>
+        <v>0.0809</v>
       </c>
       <c r="AM4" s="11" t="n">
-        <v>0.06600587475157653</v>
+        <v>0.05075274131724232</v>
       </c>
       <c r="AN4" s="8" t="n">
-        <v>108738215</v>
+        <v>103486016</v>
       </c>
       <c r="AO4" s="9" t="n">
-        <v>1077813.19</v>
+        <v>1042725.1</v>
       </c>
       <c r="AP4" s="10" t="n">
-        <v>0.0809</v>
+        <v>0.0803</v>
       </c>
       <c r="AQ4" s="11" t="n">
-        <v>0.05075274131724232</v>
+        <v>0.01255042387516938</v>
       </c>
       <c r="AR4" s="8" t="n">
-        <v>103486016</v>
+        <v>102203321</v>
       </c>
       <c r="AS4" s="9" t="n">
-        <v>1042725.1</v>
+        <v>1009053.39</v>
       </c>
       <c r="AT4" s="10" t="n">
-        <v>0.0803</v>
+        <v>0.08019999999999999</v>
       </c>
       <c r="AU4" s="11" t="n">
-        <v>0.01255042387516938</v>
+        <v>0.005262209454604842</v>
       </c>
       <c r="AV4" s="8" t="n">
-        <v>102203321</v>
+        <v>101668321</v>
       </c>
       <c r="AW4" s="9" t="n">
-        <v>1009053.39</v>
+        <v>966865.73</v>
       </c>
       <c r="AX4" s="10" t="n">
-        <v>0.08019999999999999</v>
+        <v>0.0808</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.005262209454604842</v>
+        <v>0.06097375017638836</v>
       </c>
       <c r="AZ4" s="8" t="n">
-        <v>101668321</v>
+        <v>95825482</v>
       </c>
       <c r="BA4" s="9" t="n">
-        <v>966865.73</v>
+        <v>911875.29</v>
       </c>
       <c r="BB4" s="10" t="n">
-        <v>0.0808</v>
+        <v>0.0793</v>
       </c>
       <c r="BC4" s="11" t="n">
-        <v>0.06097375017638836</v>
+        <v>1.135602796681763</v>
       </c>
       <c r="BD4" s="8" t="n">
-        <v>95825482</v>
+        <v>44870461</v>
       </c>
       <c r="BE4" s="9" t="n">
-        <v>911875.29</v>
+        <v>905575.64</v>
       </c>
       <c r="BF4" s="10" t="n">
-        <v>0.0793</v>
+        <v>0.0799</v>
       </c>
       <c r="BG4" s="11" t="n">
-        <v>1.135602796681763</v>
+        <v>0.009203290657165424</v>
       </c>
       <c r="BH4" s="8" t="n">
-        <v>44870461</v>
+        <v>44461271</v>
       </c>
       <c r="BI4" s="9" t="n">
-        <v>905575.64</v>
+        <v>889892.34</v>
       </c>
       <c r="BJ4" s="10" t="n">
-        <v>0.0799</v>
+        <v>0.0806</v>
       </c>
       <c r="BK4" s="11" t="n">
-        <v>0.009203290657165424</v>
+        <v>0.026983580212343</v>
       </c>
       <c r="BL4" s="8" t="n">
-        <v>44461271</v>
+        <v>43293069</v>
       </c>
       <c r="BM4" s="9" t="n">
-        <v>889892.34</v>
+        <v>842006.9</v>
       </c>
       <c r="BN4" s="10" t="n">
-        <v>0.0806</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="BO4" s="11" t="n">
-        <v>0.026983580212343</v>
+        <v>0.01121152982515689</v>
       </c>
       <c r="BP4" s="8" t="n">
-        <v>43293069</v>
+        <v>42813069</v>
       </c>
       <c r="BQ4" s="9" t="n">
-        <v>842006.9</v>
+        <v>824151.58</v>
       </c>
       <c r="BR4" s="10" t="n">
-        <v>0.08110000000000001</v>
+        <v>0.08359999999999999</v>
       </c>
       <c r="BS4" s="11" t="n">
-        <v>0.01121152982515689</v>
+        <v>0</v>
       </c>
       <c r="BT4" s="8" t="n">
         <v>42813069</v>
       </c>
       <c r="BU4" s="9" t="n">
-        <v>824151.58</v>
+        <v>782708.53</v>
       </c>
       <c r="BV4" s="10" t="n">
-        <v>0.08359999999999999</v>
+        <v>0.0838</v>
       </c>
       <c r="BW4" s="11" t="n">
         <v>0</v>
@@ -1521,10 +1485,10 @@
         <v>42813069</v>
       </c>
       <c r="BY4" s="9" t="n">
-        <v>782708.53</v>
+        <v>741693.61</v>
       </c>
       <c r="BZ4" s="10" t="n">
-        <v>0.0838</v>
+        <v>0.0843</v>
       </c>
       <c r="CA4" s="11" t="n">
         <v>0</v>
@@ -1533,24 +1497,12 @@
         <v>42813069</v>
       </c>
       <c r="CC4" s="9" t="n">
-        <v>741693.61</v>
+        <v>727287.01</v>
       </c>
       <c r="CD4" s="10" t="n">
-        <v>0.0843</v>
-      </c>
-      <c r="CE4" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF4" s="8" t="n">
-        <v>42813069</v>
-      </c>
-      <c r="CG4" s="9" t="n">
-        <v>727287.01</v>
-      </c>
-      <c r="CH4" s="10" t="n">
         <v>0.08110000000000001</v>
       </c>
-      <c r="CI4" s="11" t="n"/>
+      <c r="CE4" s="11" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -1638,186 +1590,174 @@
         <v>0.0699</v>
       </c>
       <c r="AA5" s="11" t="n">
-        <v>-0.00842648029250833</v>
+        <v>-0.005398666515228007</v>
       </c>
       <c r="AB5" s="8" t="n">
-        <v>312063864</v>
+        <v>311113864</v>
       </c>
       <c r="AC5" s="9" t="n">
-        <v>924021.1</v>
+        <v>929141.55</v>
       </c>
       <c r="AD5" s="10" t="n">
-        <v>0.0716</v>
+        <v>0.0692</v>
       </c>
       <c r="AE5" s="11" t="n">
-        <v>0.003053544409065615</v>
+        <v>-0.007185705380051316</v>
       </c>
       <c r="AF5" s="8" t="n">
-        <v>311113864</v>
+        <v>313365617</v>
       </c>
       <c r="AG5" s="9" t="n">
-        <v>929141.55</v>
+        <v>803782.8100000001</v>
       </c>
       <c r="AH5" s="10" t="n">
-        <v>0.0692</v>
+        <v>0.06</v>
       </c>
       <c r="AI5" s="11" t="n">
-        <v>-0.007185705380051316</v>
+        <v>0.02601784123854898</v>
       </c>
       <c r="AJ5" s="8" t="n">
-        <v>313365617</v>
+        <v>305419267</v>
       </c>
       <c r="AK5" s="9" t="n">
-        <v>803782.8100000001</v>
+        <v>808139.38</v>
       </c>
       <c r="AL5" s="10" t="n">
+        <v>0.0606</v>
+      </c>
+      <c r="AM5" s="11" t="n">
+        <v>0.07483622732268541</v>
+      </c>
+      <c r="AN5" s="8" t="n">
+        <v>284154236</v>
+      </c>
+      <c r="AO5" s="9" t="n">
+        <v>767074.36</v>
+      </c>
+      <c r="AP5" s="10" t="n">
+        <v>0.0591</v>
+      </c>
+      <c r="AQ5" s="11" t="n">
+        <v>0.08544209611432535</v>
+      </c>
+      <c r="AR5" s="8" t="n">
+        <v>261786637</v>
+      </c>
+      <c r="AS5" s="9" t="n">
+        <v>754338.1899999999</v>
+      </c>
+      <c r="AT5" s="10" t="n">
         <v>0.06</v>
       </c>
-      <c r="AM5" s="11" t="n">
-        <v>0.02601784123854898</v>
-      </c>
-      <c r="AN5" s="8" t="n">
-        <v>305419267</v>
-      </c>
-      <c r="AO5" s="9" t="n">
-        <v>808139.38</v>
-      </c>
-      <c r="AP5" s="10" t="n">
-        <v>0.0606</v>
-      </c>
-      <c r="AQ5" s="11" t="n">
-        <v>0.07483622732268541</v>
-      </c>
-      <c r="AR5" s="8" t="n">
-        <v>284154236</v>
-      </c>
-      <c r="AS5" s="9" t="n">
-        <v>767074.36</v>
-      </c>
-      <c r="AT5" s="10" t="n">
-        <v>0.0591</v>
-      </c>
       <c r="AU5" s="11" t="n">
-        <v>0.08544209611432535</v>
+        <v>0.02291281861384987</v>
       </c>
       <c r="AV5" s="8" t="n">
-        <v>261786637</v>
+        <v>255922726</v>
       </c>
       <c r="AW5" s="9" t="n">
-        <v>754338.1899999999</v>
+        <v>717223.4399999999</v>
       </c>
       <c r="AX5" s="10" t="n">
-        <v>0.06</v>
+        <v>0.0599</v>
       </c>
       <c r="AY5" s="11" t="n">
-        <v>0.02291281861384987</v>
+        <v>0.04012490664854439</v>
       </c>
       <c r="AZ5" s="8" t="n">
-        <v>255922726</v>
+        <v>246049993</v>
       </c>
       <c r="BA5" s="9" t="n">
-        <v>717223.4399999999</v>
+        <v>677252.61</v>
       </c>
       <c r="BB5" s="10" t="n">
+        <v>0.0589</v>
+      </c>
+      <c r="BC5" s="11" t="n">
+        <v>0.06613218800272164</v>
+      </c>
+      <c r="BD5" s="8" t="n">
+        <v>230787510</v>
+      </c>
+      <c r="BE5" s="9" t="n">
+        <v>671591.65</v>
+      </c>
+      <c r="BF5" s="10" t="n">
+        <v>0.0593</v>
+      </c>
+      <c r="BG5" s="11" t="n">
+        <v>0.02930647191621902</v>
+      </c>
+      <c r="BH5" s="8" t="n">
+        <v>224216515</v>
+      </c>
+      <c r="BI5" s="9" t="n">
+        <v>672425.33</v>
+      </c>
+      <c r="BJ5" s="10" t="n">
+        <v>0.0609</v>
+      </c>
+      <c r="BK5" s="11" t="n">
+        <v>0.07348663585077284</v>
+      </c>
+      <c r="BL5" s="8" t="n">
+        <v>208867542</v>
+      </c>
+      <c r="BM5" s="9" t="n">
+        <v>605193.7</v>
+      </c>
+      <c r="BN5" s="10" t="n">
+        <v>0.0583</v>
+      </c>
+      <c r="BO5" s="11" t="n">
+        <v>0.0787685054851275</v>
+      </c>
+      <c r="BP5" s="8" t="n">
+        <v>193616648</v>
+      </c>
+      <c r="BQ5" s="9" t="n">
+        <v>595274.38</v>
+      </c>
+      <c r="BR5" s="10" t="n">
+        <v>0.0604</v>
+      </c>
+      <c r="BS5" s="11" t="n">
+        <v>0.004416437745811861</v>
+      </c>
+      <c r="BT5" s="8" t="n">
+        <v>192765312</v>
+      </c>
+      <c r="BU5" s="9" t="n">
+        <v>559694.08</v>
+      </c>
+      <c r="BV5" s="10" t="n">
         <v>0.0599</v>
       </c>
-      <c r="BC5" s="11" t="n">
-        <v>0.04012490664854439</v>
-      </c>
-      <c r="BD5" s="8" t="n">
-        <v>246049993</v>
-      </c>
-      <c r="BE5" s="9" t="n">
-        <v>677252.61</v>
-      </c>
-      <c r="BF5" s="10" t="n">
-        <v>0.0589</v>
-      </c>
-      <c r="BG5" s="11" t="n">
-        <v>0.06613218800272164</v>
-      </c>
-      <c r="BH5" s="8" t="n">
-        <v>230787510</v>
-      </c>
-      <c r="BI5" s="9" t="n">
-        <v>671591.65</v>
-      </c>
-      <c r="BJ5" s="10" t="n">
-        <v>0.0593</v>
-      </c>
-      <c r="BK5" s="11" t="n">
-        <v>0.02930647191621902</v>
-      </c>
-      <c r="BL5" s="8" t="n">
-        <v>224216515</v>
-      </c>
-      <c r="BM5" s="9" t="n">
-        <v>672425.33</v>
-      </c>
-      <c r="BN5" s="10" t="n">
-        <v>0.0609</v>
-      </c>
-      <c r="BO5" s="11" t="n">
-        <v>0.07348663585077284</v>
-      </c>
-      <c r="BP5" s="8" t="n">
-        <v>208867542</v>
-      </c>
-      <c r="BQ5" s="9" t="n">
-        <v>605193.7</v>
-      </c>
-      <c r="BR5" s="10" t="n">
-        <v>0.0583</v>
-      </c>
-      <c r="BS5" s="11" t="n">
-        <v>0.0787685054851275</v>
-      </c>
-      <c r="BT5" s="8" t="n">
-        <v>193616648</v>
-      </c>
-      <c r="BU5" s="9" t="n">
-        <v>595274.38</v>
-      </c>
-      <c r="BV5" s="10" t="n">
-        <v>0.0604</v>
-      </c>
       <c r="BW5" s="11" t="n">
-        <v>0.004416437745811861</v>
+        <v>-0.003790710650882039</v>
       </c>
       <c r="BX5" s="8" t="n">
-        <v>192765312</v>
+        <v>193498810</v>
       </c>
       <c r="BY5" s="9" t="n">
-        <v>559694.08</v>
+        <v>485391.76</v>
       </c>
       <c r="BZ5" s="10" t="n">
-        <v>0.0599</v>
+        <v>0.0552</v>
       </c>
       <c r="CA5" s="11" t="n">
-        <v>-0.003790710650882039</v>
+        <v>0.04268662994371823</v>
       </c>
       <c r="CB5" s="8" t="n">
-        <v>193498810</v>
+        <v>185577147</v>
       </c>
       <c r="CC5" s="9" t="n">
-        <v>485391.76</v>
+        <v>559793.46</v>
       </c>
       <c r="CD5" s="10" t="n">
-        <v>0.0552</v>
-      </c>
-      <c r="CE5" s="11" t="n">
-        <v>0.04268662994371823</v>
-      </c>
-      <c r="CF5" s="8" t="n">
-        <v>185577147</v>
-      </c>
-      <c r="CG5" s="9" t="n">
-        <v>559793.46</v>
-      </c>
-      <c r="CH5" s="10" t="n">
         <v>0.0624</v>
       </c>
-      <c r="CI5" s="11" t="n"/>
+      <c r="CE5" s="11" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -1905,186 +1845,174 @@
         <v>0.0543</v>
       </c>
       <c r="AA6" s="11" t="n">
-        <v>0.08526303507031635</v>
+        <v>0.1280505783005292</v>
       </c>
       <c r="AB6" s="8" t="n">
-        <v>224093958</v>
+        <v>215593958</v>
       </c>
       <c r="AC6" s="9" t="n">
-        <v>644718.3199999999</v>
+        <v>676102.65</v>
       </c>
       <c r="AD6" s="10" t="n">
-        <v>0.05</v>
+        <v>0.0504</v>
       </c>
       <c r="AE6" s="11" t="n">
-        <v>0.03942596573137731</v>
+        <v>0.02712213930725835</v>
       </c>
       <c r="AF6" s="8" t="n">
-        <v>215593958</v>
+        <v>209900994</v>
       </c>
       <c r="AG6" s="9" t="n">
-        <v>676102.65</v>
+        <v>676196.05</v>
       </c>
       <c r="AH6" s="10" t="n">
-        <v>0.0504</v>
+        <v>0.0505</v>
       </c>
       <c r="AI6" s="11" t="n">
-        <v>0.02712213930725835</v>
+        <v>0.4118991702128273</v>
       </c>
       <c r="AJ6" s="8" t="n">
-        <v>209900994</v>
+        <v>148665711</v>
       </c>
       <c r="AK6" s="9" t="n">
-        <v>676196.05</v>
+        <v>599122.8199999999</v>
       </c>
       <c r="AL6" s="10" t="n">
-        <v>0.0505</v>
+        <v>0.0449</v>
       </c>
       <c r="AM6" s="11" t="n">
-        <v>0.4118991702128273</v>
+        <v>0.02714259251540287</v>
       </c>
       <c r="AN6" s="8" t="n">
-        <v>148665711</v>
+        <v>144737169</v>
       </c>
       <c r="AO6" s="9" t="n">
-        <v>599122.8199999999</v>
+        <v>585100.01</v>
       </c>
       <c r="AP6" s="10" t="n">
-        <v>0.0449</v>
+        <v>0.0451</v>
       </c>
       <c r="AQ6" s="11" t="n">
-        <v>0.02714259251540287</v>
+        <v>0.04299272879906111</v>
       </c>
       <c r="AR6" s="8" t="n">
-        <v>144737169</v>
+        <v>138771024</v>
       </c>
       <c r="AS6" s="9" t="n">
-        <v>585100.01</v>
+        <v>583324</v>
       </c>
       <c r="AT6" s="10" t="n">
-        <v>0.0451</v>
+        <v>0.0464</v>
       </c>
       <c r="AU6" s="11" t="n">
-        <v>0.04299272879906111</v>
+        <v>0.02247256843567582</v>
       </c>
       <c r="AV6" s="8" t="n">
-        <v>138771024</v>
+        <v>135721024</v>
       </c>
       <c r="AW6" s="9" t="n">
-        <v>583324</v>
+        <v>544987.77</v>
       </c>
       <c r="AX6" s="10" t="n">
-        <v>0.0464</v>
+        <v>0.0455</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>0.02247256843567582</v>
+        <v>0.04867833529118113</v>
       </c>
       <c r="AZ6" s="8" t="n">
-        <v>135721024</v>
+        <v>129421024</v>
       </c>
       <c r="BA6" s="9" t="n">
-        <v>544987.77</v>
+        <v>530302.65</v>
       </c>
       <c r="BB6" s="10" t="n">
+        <v>0.0461</v>
+      </c>
+      <c r="BC6" s="11" t="n">
+        <v>0.05933146465642036</v>
+      </c>
+      <c r="BD6" s="8" t="n">
+        <v>122172359</v>
+      </c>
+      <c r="BE6" s="9" t="n">
+        <v>503289.03</v>
+      </c>
+      <c r="BF6" s="10" t="n">
+        <v>0.0444</v>
+      </c>
+      <c r="BG6" s="11" t="n">
+        <v>0.04045226173662547</v>
+      </c>
+      <c r="BH6" s="8" t="n">
+        <v>117422359</v>
+      </c>
+      <c r="BI6" s="9" t="n">
+        <v>489005.41</v>
+      </c>
+      <c r="BJ6" s="10" t="n">
+        <v>0.0443</v>
+      </c>
+      <c r="BK6" s="11" t="n">
+        <v>0.07460089770293252</v>
+      </c>
+      <c r="BL6" s="8" t="n">
+        <v>109270669</v>
+      </c>
+      <c r="BM6" s="9" t="n">
+        <v>456806.03</v>
+      </c>
+      <c r="BN6" s="10" t="n">
+        <v>0.044</v>
+      </c>
+      <c r="BO6" s="11" t="n">
+        <v>0.03799307836597426</v>
+      </c>
+      <c r="BP6" s="8" t="n">
+        <v>105271096</v>
+      </c>
+      <c r="BQ6" s="9" t="n">
+        <v>448244.33</v>
+      </c>
+      <c r="BR6" s="10" t="n">
         <v>0.0455</v>
       </c>
-      <c r="BC6" s="11" t="n">
-        <v>0.04867833529118113</v>
-      </c>
-      <c r="BD6" s="8" t="n">
-        <v>129421024</v>
-      </c>
-      <c r="BE6" s="9" t="n">
-        <v>530302.65</v>
-      </c>
-      <c r="BF6" s="10" t="n">
-        <v>0.0461</v>
-      </c>
-      <c r="BG6" s="11" t="n">
-        <v>0.05933146465642036</v>
-      </c>
-      <c r="BH6" s="8" t="n">
-        <v>122172359</v>
-      </c>
-      <c r="BI6" s="9" t="n">
-        <v>503289.03</v>
-      </c>
-      <c r="BJ6" s="10" t="n">
+      <c r="BS6" s="11" t="n">
+        <v>0.04028866499357868</v>
+      </c>
+      <c r="BT6" s="8" t="n">
+        <v>101194120</v>
+      </c>
+      <c r="BU6" s="9" t="n">
+        <v>414642.91</v>
+      </c>
+      <c r="BV6" s="10" t="n">
         <v>0.0444</v>
       </c>
-      <c r="BK6" s="11" t="n">
-        <v>0.04045226173662547</v>
-      </c>
-      <c r="BL6" s="8" t="n">
-        <v>117422359</v>
-      </c>
-      <c r="BM6" s="9" t="n">
-        <v>489005.41</v>
-      </c>
-      <c r="BN6" s="10" t="n">
-        <v>0.0443</v>
-      </c>
-      <c r="BO6" s="11" t="n">
-        <v>0.07460089770293252</v>
-      </c>
-      <c r="BP6" s="8" t="n">
-        <v>109270669</v>
-      </c>
-      <c r="BQ6" s="9" t="n">
-        <v>456806.03</v>
-      </c>
-      <c r="BR6" s="10" t="n">
-        <v>0.044</v>
-      </c>
-      <c r="BS6" s="11" t="n">
-        <v>0.03799307836597426</v>
-      </c>
-      <c r="BT6" s="8" t="n">
-        <v>105271096</v>
-      </c>
-      <c r="BU6" s="9" t="n">
-        <v>448244.33</v>
-      </c>
-      <c r="BV6" s="10" t="n">
-        <v>0.0455</v>
-      </c>
       <c r="BW6" s="11" t="n">
-        <v>0.04028866499357868</v>
+        <v>0</v>
       </c>
       <c r="BX6" s="8" t="n">
         <v>101194120</v>
       </c>
       <c r="BY6" s="9" t="n">
-        <v>414642.91</v>
+        <v>399716.77</v>
       </c>
       <c r="BZ6" s="10" t="n">
-        <v>0.0444</v>
+        <v>0.0454</v>
       </c>
       <c r="CA6" s="11" t="n">
-        <v>0</v>
+        <v>0.02222354216593874</v>
       </c>
       <c r="CB6" s="8" t="n">
-        <v>101194120</v>
+        <v>98994120</v>
       </c>
       <c r="CC6" s="9" t="n">
-        <v>399716.77</v>
+        <v>442998.69</v>
       </c>
       <c r="CD6" s="10" t="n">
-        <v>0.0454</v>
-      </c>
-      <c r="CE6" s="11" t="n">
-        <v>0.02222354216593874</v>
-      </c>
-      <c r="CF6" s="8" t="n">
-        <v>98994120</v>
-      </c>
-      <c r="CG6" s="9" t="n">
-        <v>442998.69</v>
-      </c>
-      <c r="CH6" s="10" t="n">
         <v>0.0494</v>
       </c>
-      <c r="CI6" s="11" t="n"/>
+      <c r="CE6" s="11" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -2172,52 +2100,52 @@
         <v>0.0595</v>
       </c>
       <c r="AA7" s="11" t="n">
-        <v>-0.003861171338551467</v>
+        <v>0.07879048239992377</v>
       </c>
       <c r="AB7" s="8" t="n">
-        <v>174817417</v>
+        <v>161423761</v>
       </c>
       <c r="AC7" s="9" t="n">
-        <v>787465.05</v>
+        <v>695171.4300000001</v>
       </c>
       <c r="AD7" s="10" t="n">
-        <v>0.0611</v>
+        <v>0.0518</v>
       </c>
       <c r="AE7" s="11" t="n">
-        <v>0.08297202293533477</v>
+        <v>0.009957016950540437</v>
       </c>
       <c r="AF7" s="8" t="n">
-        <v>161423761</v>
+        <v>159832308</v>
       </c>
       <c r="AG7" s="9" t="n">
-        <v>695171.4300000001</v>
+        <v>704460.9</v>
       </c>
       <c r="AH7" s="10" t="n">
-        <v>0.0518</v>
+        <v>0.0526</v>
       </c>
       <c r="AI7" s="11" t="n">
-        <v>0.009957016950540437</v>
+        <v>-0.01362167378906329</v>
       </c>
       <c r="AJ7" s="8" t="n">
-        <v>159832308</v>
+        <v>162039558</v>
       </c>
       <c r="AK7" s="9" t="n">
-        <v>704460.9</v>
+        <v>646537.84</v>
       </c>
       <c r="AL7" s="10" t="n">
-        <v>0.0526</v>
+        <v>0.0485</v>
       </c>
       <c r="AM7" s="11" t="n">
-        <v>-0.01362167378906329</v>
+        <v>0</v>
       </c>
       <c r="AN7" s="8" t="n">
         <v>162039558</v>
       </c>
       <c r="AO7" s="9" t="n">
-        <v>646537.84</v>
+        <v>609511.8</v>
       </c>
       <c r="AP7" s="10" t="n">
-        <v>0.0485</v>
+        <v>0.047</v>
       </c>
       <c r="AQ7" s="11" t="n">
         <v>0</v>
@@ -2226,10 +2154,10 @@
         <v>162039558</v>
       </c>
       <c r="AS7" s="9" t="n">
-        <v>609511.8</v>
+        <v>629766.74</v>
       </c>
       <c r="AT7" s="10" t="n">
-        <v>0.047</v>
+        <v>0.0501</v>
       </c>
       <c r="AU7" s="11" t="n">
         <v>0</v>
@@ -2238,10 +2166,10 @@
         <v>162039558</v>
       </c>
       <c r="AW7" s="9" t="n">
-        <v>629766.74</v>
+        <v>631873.26</v>
       </c>
       <c r="AX7" s="10" t="n">
-        <v>0.0501</v>
+        <v>0.0528</v>
       </c>
       <c r="AY7" s="11" t="n">
         <v>0</v>
@@ -2250,7 +2178,7 @@
         <v>162039558</v>
       </c>
       <c r="BA7" s="9" t="n">
-        <v>631873.26</v>
+        <v>607324.26</v>
       </c>
       <c r="BB7" s="10" t="n">
         <v>0.0528</v>
@@ -2262,10 +2190,10 @@
         <v>162039558</v>
       </c>
       <c r="BE7" s="9" t="n">
-        <v>607324.26</v>
+        <v>609835.88</v>
       </c>
       <c r="BF7" s="10" t="n">
-        <v>0.0528</v>
+        <v>0.0538</v>
       </c>
       <c r="BG7" s="11" t="n">
         <v>0</v>
@@ -2274,84 +2202,72 @@
         <v>162039558</v>
       </c>
       <c r="BI7" s="9" t="n">
-        <v>609835.88</v>
+        <v>635114.05</v>
       </c>
       <c r="BJ7" s="10" t="n">
-        <v>0.0538</v>
+        <v>0.0575</v>
       </c>
       <c r="BK7" s="11" t="n">
-        <v>0</v>
+        <v>0.0408396826825464</v>
       </c>
       <c r="BL7" s="8" t="n">
-        <v>162039558</v>
+        <v>155681572</v>
       </c>
       <c r="BM7" s="9" t="n">
-        <v>635114.05</v>
+        <v>618522.89</v>
       </c>
       <c r="BN7" s="10" t="n">
-        <v>0.0575</v>
+        <v>0.0595</v>
       </c>
       <c r="BO7" s="11" t="n">
-        <v>0.0408396826825464</v>
+        <v>0.04960632238493121</v>
       </c>
       <c r="BP7" s="8" t="n">
-        <v>155681572</v>
+        <v>148323775</v>
       </c>
       <c r="BQ7" s="9" t="n">
-        <v>618522.89</v>
+        <v>571491.51</v>
       </c>
       <c r="BR7" s="10" t="n">
-        <v>0.0595</v>
+        <v>0.058</v>
       </c>
       <c r="BS7" s="11" t="n">
-        <v>0.04960632238493121</v>
+        <v>0.05138982123049783</v>
       </c>
       <c r="BT7" s="8" t="n">
-        <v>148323775</v>
+        <v>141074007</v>
       </c>
       <c r="BU7" s="9" t="n">
-        <v>571491.51</v>
+        <v>561756.7</v>
       </c>
       <c r="BV7" s="10" t="n">
-        <v>0.058</v>
+        <v>0.0601</v>
       </c>
       <c r="BW7" s="11" t="n">
-        <v>0.05138982123049783</v>
+        <v>-0.01095372515938375</v>
       </c>
       <c r="BX7" s="8" t="n">
-        <v>141074007</v>
+        <v>142636407</v>
       </c>
       <c r="BY7" s="9" t="n">
-        <v>561756.7</v>
+        <v>526827.5699999999</v>
       </c>
       <c r="BZ7" s="10" t="n">
-        <v>0.0601</v>
+        <v>0.0599</v>
       </c>
       <c r="CA7" s="11" t="n">
-        <v>-0.01095372515938375</v>
+        <v>0.02369256314048828</v>
       </c>
       <c r="CB7" s="8" t="n">
-        <v>142636407</v>
+        <v>139335199</v>
       </c>
       <c r="CC7" s="9" t="n">
-        <v>526827.5699999999</v>
+        <v>551628.05</v>
       </c>
       <c r="CD7" s="10" t="n">
-        <v>0.0599</v>
-      </c>
-      <c r="CE7" s="11" t="n">
-        <v>0.02369256314048828</v>
-      </c>
-      <c r="CF7" s="8" t="n">
-        <v>139335199</v>
-      </c>
-      <c r="CG7" s="9" t="n">
-        <v>551628.05</v>
-      </c>
-      <c r="CH7" s="10" t="n">
         <v>0.0615</v>
       </c>
-      <c r="CI7" s="11" t="n"/>
+      <c r="CE7" s="11" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -2439,28 +2355,28 @@
         <v>0.0492</v>
       </c>
       <c r="AA8" s="11" t="n">
-        <v>0.01857141851633198</v>
+        <v>0.1119295044804045</v>
       </c>
       <c r="AB8" s="8" t="n">
-        <v>53846183</v>
+        <v>49325234</v>
       </c>
       <c r="AC8" s="9" t="n">
-        <v>649331.12</v>
+        <v>680145.65</v>
       </c>
       <c r="AD8" s="10" t="n">
-        <v>0.0503</v>
+        <v>0.0507</v>
       </c>
       <c r="AE8" s="11" t="n">
-        <v>0.09165590577836893</v>
+        <v>0</v>
       </c>
       <c r="AF8" s="8" t="n">
         <v>49325234</v>
       </c>
       <c r="AG8" s="9" t="n">
-        <v>680145.65</v>
+        <v>668356.92</v>
       </c>
       <c r="AH8" s="10" t="n">
-        <v>0.0507</v>
+        <v>0.0499</v>
       </c>
       <c r="AI8" s="11" t="n">
         <v>0</v>
@@ -2469,106 +2385,106 @@
         <v>49325234</v>
       </c>
       <c r="AK8" s="9" t="n">
-        <v>668356.92</v>
+        <v>662388.5699999999</v>
       </c>
       <c r="AL8" s="10" t="n">
-        <v>0.0499</v>
+        <v>0.0497</v>
       </c>
       <c r="AM8" s="11" t="n">
-        <v>0</v>
+        <v>0.08865063536064391</v>
       </c>
       <c r="AN8" s="8" t="n">
-        <v>49325234</v>
+        <v>45308598</v>
       </c>
       <c r="AO8" s="9" t="n">
-        <v>662388.5699999999</v>
+        <v>629245.8100000001</v>
       </c>
       <c r="AP8" s="10" t="n">
-        <v>0.0497</v>
+        <v>0.0485</v>
       </c>
       <c r="AQ8" s="11" t="n">
-        <v>0.08865063536064391</v>
+        <v>0.04649493840859896</v>
       </c>
       <c r="AR8" s="8" t="n">
-        <v>45308598</v>
+        <v>43295573</v>
       </c>
       <c r="AS8" s="9" t="n">
-        <v>629245.8100000001</v>
+        <v>582455.34</v>
       </c>
       <c r="AT8" s="10" t="n">
-        <v>0.0485</v>
+        <v>0.0463</v>
       </c>
       <c r="AU8" s="11" t="n">
-        <v>0.04649493840859896</v>
+        <v>0.02558297621590971</v>
       </c>
       <c r="AV8" s="8" t="n">
-        <v>43295573</v>
+        <v>42215573</v>
       </c>
       <c r="AW8" s="9" t="n">
-        <v>582455.34</v>
+        <v>569065.92</v>
       </c>
       <c r="AX8" s="10" t="n">
-        <v>0.0463</v>
+        <v>0.0475</v>
       </c>
       <c r="AY8" s="11" t="n">
-        <v>0.02558297621590971</v>
+        <v>0.03671439253646495</v>
       </c>
       <c r="AZ8" s="8" t="n">
-        <v>42215573</v>
+        <v>40720543</v>
       </c>
       <c r="BA8" s="9" t="n">
-        <v>569065.92</v>
+        <v>569191.75</v>
       </c>
       <c r="BB8" s="10" t="n">
-        <v>0.0475</v>
+        <v>0.0495</v>
       </c>
       <c r="BC8" s="11" t="n">
-        <v>0.03671439253646495</v>
+        <v>0.02815262499999053</v>
       </c>
       <c r="BD8" s="8" t="n">
-        <v>40720543</v>
+        <v>39605543</v>
       </c>
       <c r="BE8" s="9" t="n">
-        <v>569191.75</v>
+        <v>586716.51</v>
       </c>
       <c r="BF8" s="10" t="n">
-        <v>0.0495</v>
+        <v>0.0518</v>
       </c>
       <c r="BG8" s="11" t="n">
-        <v>0.02815262499999053</v>
+        <v>0.08540125861519442</v>
       </c>
       <c r="BH8" s="8" t="n">
-        <v>39605543</v>
+        <v>36489310</v>
       </c>
       <c r="BI8" s="9" t="n">
-        <v>586716.51</v>
+        <v>527562.4399999999</v>
       </c>
       <c r="BJ8" s="10" t="n">
-        <v>0.0518</v>
+        <v>0.0478</v>
       </c>
       <c r="BK8" s="11" t="n">
-        <v>0.08540125861519442</v>
+        <v>0.04294684214648178</v>
       </c>
       <c r="BL8" s="8" t="n">
-        <v>36489310</v>
+        <v>34986740</v>
       </c>
       <c r="BM8" s="9" t="n">
-        <v>527562.4399999999</v>
+        <v>505838.29</v>
       </c>
       <c r="BN8" s="10" t="n">
-        <v>0.0478</v>
+        <v>0.0487</v>
       </c>
       <c r="BO8" s="11" t="n">
-        <v>0.04294684214648178</v>
+        <v>0</v>
       </c>
       <c r="BP8" s="8" t="n">
         <v>34986740</v>
       </c>
       <c r="BQ8" s="9" t="n">
-        <v>505838.29</v>
+        <v>499260.78</v>
       </c>
       <c r="BR8" s="10" t="n">
-        <v>0.0487</v>
+        <v>0.0507</v>
       </c>
       <c r="BS8" s="11" t="n">
         <v>0</v>
@@ -2577,10 +2493,10 @@
         <v>34986740</v>
       </c>
       <c r="BU8" s="9" t="n">
-        <v>499260.78</v>
+        <v>471743.71</v>
       </c>
       <c r="BV8" s="10" t="n">
-        <v>0.0507</v>
+        <v>0.0505</v>
       </c>
       <c r="BW8" s="11" t="n">
         <v>0</v>
@@ -2589,10 +2505,10 @@
         <v>34986740</v>
       </c>
       <c r="BY8" s="9" t="n">
-        <v>471743.71</v>
+        <v>421275.34</v>
       </c>
       <c r="BZ8" s="10" t="n">
-        <v>0.0505</v>
+        <v>0.0479</v>
       </c>
       <c r="CA8" s="11" t="n">
         <v>0</v>
@@ -2601,24 +2517,12 @@
         <v>34986740</v>
       </c>
       <c r="CC8" s="9" t="n">
-        <v>421275.34</v>
+        <v>438313.88</v>
       </c>
       <c r="CD8" s="10" t="n">
-        <v>0.0479</v>
-      </c>
-      <c r="CE8" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF8" s="8" t="n">
-        <v>34986740</v>
-      </c>
-      <c r="CG8" s="9" t="n">
-        <v>438313.88</v>
-      </c>
-      <c r="CH8" s="10" t="n">
         <v>0.0489</v>
       </c>
-      <c r="CI8" s="11" t="n"/>
+      <c r="CE8" s="11" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -2712,46 +2616,46 @@
         <v>6026828</v>
       </c>
       <c r="AC9" s="9" t="n">
-        <v>527106.38</v>
+        <v>651138.5</v>
       </c>
       <c r="AD9" s="10" t="n">
-        <v>0.0409</v>
+        <v>0.0485</v>
       </c>
       <c r="AE9" s="11" t="n">
-        <v>0</v>
+        <v>0.007956679538397187</v>
       </c>
       <c r="AF9" s="8" t="n">
-        <v>6026828</v>
+        <v>5979253</v>
       </c>
       <c r="AG9" s="9" t="n">
-        <v>651138.5</v>
+        <v>645759.3199999999</v>
       </c>
       <c r="AH9" s="10" t="n">
-        <v>0.0485</v>
+        <v>0.0482</v>
       </c>
       <c r="AI9" s="11" t="n">
-        <v>0.007956679538397187</v>
+        <v>0.124148370025633</v>
       </c>
       <c r="AJ9" s="8" t="n">
-        <v>5979253</v>
+        <v>5318918</v>
       </c>
       <c r="AK9" s="9" t="n">
-        <v>645759.3199999999</v>
+        <v>602527.03</v>
       </c>
       <c r="AL9" s="10" t="n">
-        <v>0.0482</v>
+        <v>0.0452</v>
       </c>
       <c r="AM9" s="11" t="n">
-        <v>0.124148370025633</v>
+        <v>0</v>
       </c>
       <c r="AN9" s="8" t="n">
         <v>5318918</v>
       </c>
       <c r="AO9" s="9" t="n">
-        <v>602527.03</v>
+        <v>611622.38</v>
       </c>
       <c r="AP9" s="10" t="n">
-        <v>0.0452</v>
+        <v>0.0471</v>
       </c>
       <c r="AQ9" s="11" t="n">
         <v>0</v>
@@ -2760,10 +2664,10 @@
         <v>5318918</v>
       </c>
       <c r="AS9" s="9" t="n">
-        <v>611622.38</v>
+        <v>654386.48</v>
       </c>
       <c r="AT9" s="10" t="n">
-        <v>0.0471</v>
+        <v>0.052</v>
       </c>
       <c r="AU9" s="11" t="n">
         <v>0</v>
@@ -2772,10 +2676,10 @@
         <v>5318918</v>
       </c>
       <c r="AW9" s="9" t="n">
-        <v>654386.48</v>
+        <v>651407.89</v>
       </c>
       <c r="AX9" s="10" t="n">
-        <v>0.052</v>
+        <v>0.0544</v>
       </c>
       <c r="AY9" s="11" t="n">
         <v>0</v>
@@ -2784,10 +2688,10 @@
         <v>5318918</v>
       </c>
       <c r="BA9" s="9" t="n">
-        <v>651407.89</v>
+        <v>679225.83</v>
       </c>
       <c r="BB9" s="10" t="n">
-        <v>0.0544</v>
+        <v>0.059</v>
       </c>
       <c r="BC9" s="11" t="n">
         <v>0</v>
@@ -2796,10 +2700,10 @@
         <v>5318918</v>
       </c>
       <c r="BE9" s="9" t="n">
-        <v>679225.83</v>
+        <v>742680.52</v>
       </c>
       <c r="BF9" s="10" t="n">
-        <v>0.059</v>
+        <v>0.06560000000000001</v>
       </c>
       <c r="BG9" s="11" t="n">
         <v>0</v>
@@ -2808,10 +2712,10 @@
         <v>5318918</v>
       </c>
       <c r="BI9" s="9" t="n">
-        <v>742680.52</v>
+        <v>764807.22</v>
       </c>
       <c r="BJ9" s="10" t="n">
-        <v>0.06560000000000001</v>
+        <v>0.0693</v>
       </c>
       <c r="BK9" s="11" t="n">
         <v>0</v>
@@ -2820,10 +2724,10 @@
         <v>5318918</v>
       </c>
       <c r="BM9" s="9" t="n">
-        <v>764807.22</v>
+        <v>713479.66</v>
       </c>
       <c r="BN9" s="10" t="n">
-        <v>0.0693</v>
+        <v>0.0687</v>
       </c>
       <c r="BO9" s="11" t="n">
         <v>0</v>
@@ -2832,10 +2736,10 @@
         <v>5318918</v>
       </c>
       <c r="BQ9" s="9" t="n">
-        <v>713479.66</v>
+        <v>636834.05</v>
       </c>
       <c r="BR9" s="10" t="n">
-        <v>0.0687</v>
+        <v>0.0646</v>
       </c>
       <c r="BS9" s="11" t="n">
         <v>0</v>
@@ -2844,10 +2748,10 @@
         <v>5318918</v>
       </c>
       <c r="BU9" s="9" t="n">
-        <v>636834.05</v>
+        <v>663431.3</v>
       </c>
       <c r="BV9" s="10" t="n">
-        <v>0.0646</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="BW9" s="11" t="n">
         <v>0</v>
@@ -2856,10 +2760,10 @@
         <v>5318918</v>
       </c>
       <c r="BY9" s="9" t="n">
-        <v>663431.3</v>
+        <v>615630.1899999999</v>
       </c>
       <c r="BZ9" s="10" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="CA9" s="11" t="n">
         <v>0</v>
@@ -2868,24 +2772,12 @@
         <v>5318918</v>
       </c>
       <c r="CC9" s="9" t="n">
-        <v>615630.1899999999</v>
+        <v>614850.96</v>
       </c>
       <c r="CD9" s="10" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="CE9" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF9" s="8" t="n">
-        <v>5318918</v>
-      </c>
-      <c r="CG9" s="9" t="n">
-        <v>614850.96</v>
-      </c>
-      <c r="CH9" s="10" t="n">
         <v>0.06850000000000001</v>
       </c>
-      <c r="CI9" s="11" t="n"/>
+      <c r="CE9" s="11" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -2973,44 +2865,36 @@
         <v>0.0403</v>
       </c>
       <c r="AA10" s="11" t="n">
-        <v>0.01180948837975782</v>
+        <v>0.2049531565627438</v>
       </c>
       <c r="AB10" s="8" t="n">
-        <v>146607960</v>
+        <v>123107960</v>
       </c>
       <c r="AC10" s="9" t="n">
-        <v>518112.53</v>
+        <v>511144.25</v>
       </c>
       <c r="AD10" s="10" t="n">
-        <v>0.0402</v>
+        <v>0.0381</v>
       </c>
       <c r="AE10" s="11" t="n">
-        <v>0.1908893624750179</v>
+        <v>0</v>
       </c>
       <c r="AF10" s="8" t="n">
         <v>123107960</v>
       </c>
       <c r="AG10" s="9" t="n">
-        <v>511144.25</v>
+        <v>502280.48</v>
       </c>
       <c r="AH10" s="10" t="n">
-        <v>0.0381</v>
+        <v>0.0375</v>
       </c>
       <c r="AI10" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ10" s="8" t="n">
-        <v>123107960</v>
-      </c>
-      <c r="AK10" s="9" t="n">
-        <v>502280.48</v>
-      </c>
-      <c r="AL10" s="10" t="n">
-        <v>0.0375</v>
-      </c>
-      <c r="AM10" s="11" t="n">
         <v>1</v>
       </c>
+      <c r="AJ10" s="8" t="n"/>
+      <c r="AK10" s="9" t="n"/>
+      <c r="AL10" s="10" t="n"/>
+      <c r="AM10" s="11" t="n"/>
       <c r="AN10" s="8" t="n"/>
       <c r="AO10" s="9" t="n"/>
       <c r="AP10" s="10" t="n"/>
@@ -3055,10 +2939,6 @@
       <c r="CC10" s="9" t="n"/>
       <c r="CD10" s="10" t="n"/>
       <c r="CE10" s="11" t="n"/>
-      <c r="CF10" s="8" t="n"/>
-      <c r="CG10" s="9" t="n"/>
-      <c r="CH10" s="10" t="n"/>
-      <c r="CI10" s="11" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -3146,88 +3026,88 @@
         <v>0.0343</v>
       </c>
       <c r="AA11" s="11" t="n">
-        <v>0.3492279063625878</v>
+        <v>0.4511186421294715</v>
       </c>
       <c r="AB11" s="8" t="n">
-        <v>29868916</v>
+        <v>27771661</v>
       </c>
       <c r="AC11" s="9" t="n">
-        <v>400721.38</v>
+        <v>385776.14</v>
       </c>
       <c r="AD11" s="10" t="n">
-        <v>0.0311</v>
+        <v>0.0287</v>
       </c>
       <c r="AE11" s="11" t="n">
-        <v>0.07551780932368431</v>
+        <v>0.1837798947287478</v>
       </c>
       <c r="AF11" s="8" t="n">
-        <v>27771661</v>
+        <v>23460156</v>
       </c>
       <c r="AG11" s="9" t="n">
-        <v>385776.14</v>
+        <v>397790.41</v>
       </c>
       <c r="AH11" s="10" t="n">
-        <v>0.0287</v>
+        <v>0.0297</v>
       </c>
       <c r="AI11" s="11" t="n">
-        <v>0.1837798947287478</v>
+        <v>0.1005951337129751</v>
       </c>
       <c r="AJ11" s="8" t="n">
-        <v>23460156</v>
+        <v>21315882</v>
       </c>
       <c r="AK11" s="9" t="n">
-        <v>397790.41</v>
+        <v>346020.71</v>
       </c>
       <c r="AL11" s="10" t="n">
-        <v>0.0297</v>
+        <v>0.026</v>
       </c>
       <c r="AM11" s="11" t="n">
-        <v>0.1005951337129751</v>
+        <v>0.07485632112907131</v>
       </c>
       <c r="AN11" s="8" t="n">
-        <v>21315882</v>
+        <v>19831378</v>
       </c>
       <c r="AO11" s="9" t="n">
-        <v>346020.71</v>
+        <v>322101.24</v>
       </c>
       <c r="AP11" s="10" t="n">
-        <v>0.026</v>
+        <v>0.0248</v>
       </c>
       <c r="AQ11" s="11" t="n">
-        <v>0.07485632112907131</v>
+        <v>0.09330382775845011</v>
       </c>
       <c r="AR11" s="8" t="n">
-        <v>19831378</v>
+        <v>18138945</v>
       </c>
       <c r="AS11" s="9" t="n">
-        <v>322101.24</v>
+        <v>279611.84</v>
       </c>
       <c r="AT11" s="10" t="n">
-        <v>0.0248</v>
+        <v>0.0222</v>
       </c>
       <c r="AU11" s="11" t="n">
-        <v>0.09330382775845011</v>
+        <v>-0.0303656466471499</v>
       </c>
       <c r="AV11" s="8" t="n">
-        <v>18138945</v>
+        <v>18706995</v>
       </c>
       <c r="AW11" s="9" t="n">
-        <v>279611.84</v>
+        <v>259110.59</v>
       </c>
       <c r="AX11" s="10" t="n">
-        <v>0.0222</v>
+        <v>0.0216</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>-0.0303656466471499</v>
+        <v>0</v>
       </c>
       <c r="AZ11" s="8" t="n">
         <v>18706995</v>
       </c>
       <c r="BA11" s="9" t="n">
-        <v>259110.59</v>
+        <v>272149.36</v>
       </c>
       <c r="BB11" s="10" t="n">
-        <v>0.0216</v>
+        <v>0.0237</v>
       </c>
       <c r="BC11" s="11" t="n">
         <v>0</v>
@@ -3236,58 +3116,58 @@
         <v>18706995</v>
       </c>
       <c r="BE11" s="9" t="n">
-        <v>272149.36</v>
+        <v>274599.98</v>
       </c>
       <c r="BF11" s="10" t="n">
-        <v>0.0237</v>
+        <v>0.0242</v>
       </c>
       <c r="BG11" s="11" t="n">
-        <v>0</v>
+        <v>0.00797456974367416</v>
       </c>
       <c r="BH11" s="8" t="n">
-        <v>18706995</v>
+        <v>18558995</v>
       </c>
       <c r="BI11" s="9" t="n">
-        <v>274599.98</v>
+        <v>320810.79</v>
       </c>
       <c r="BJ11" s="10" t="n">
-        <v>0.0242</v>
+        <v>0.0291</v>
       </c>
       <c r="BK11" s="11" t="n">
-        <v>0.00797456974367416</v>
+        <v>0.01185405417517898</v>
       </c>
       <c r="BL11" s="8" t="n">
-        <v>18558995</v>
+        <v>18341573</v>
       </c>
       <c r="BM11" s="9" t="n">
-        <v>320810.79</v>
+        <v>300178.18</v>
       </c>
       <c r="BN11" s="10" t="n">
-        <v>0.0291</v>
+        <v>0.0289</v>
       </c>
       <c r="BO11" s="11" t="n">
-        <v>0.01185405417517898</v>
+        <v>-0.01953282340226823</v>
       </c>
       <c r="BP11" s="8" t="n">
-        <v>18341573</v>
+        <v>18706973</v>
       </c>
       <c r="BQ11" s="9" t="n">
-        <v>300178.18</v>
+        <v>293231.8</v>
       </c>
       <c r="BR11" s="10" t="n">
-        <v>0.0289</v>
+        <v>0.0298</v>
       </c>
       <c r="BS11" s="11" t="n">
-        <v>-0.01953282340226823</v>
+        <v>0</v>
       </c>
       <c r="BT11" s="8" t="n">
         <v>18706973</v>
       </c>
       <c r="BU11" s="9" t="n">
-        <v>293231.8</v>
+        <v>297908.55</v>
       </c>
       <c r="BV11" s="10" t="n">
-        <v>0.0298</v>
+        <v>0.0319</v>
       </c>
       <c r="BW11" s="11" t="n">
         <v>0</v>
@@ -3296,10 +3176,10 @@
         <v>18706973</v>
       </c>
       <c r="BY11" s="9" t="n">
-        <v>297908.55</v>
+        <v>294644.18</v>
       </c>
       <c r="BZ11" s="10" t="n">
-        <v>0.0319</v>
+        <v>0.0335</v>
       </c>
       <c r="CA11" s="11" t="n">
         <v>0</v>
@@ -3308,24 +3188,12 @@
         <v>18706973</v>
       </c>
       <c r="CC11" s="9" t="n">
-        <v>294644.18</v>
+        <v>322779.47</v>
       </c>
       <c r="CD11" s="10" t="n">
-        <v>0.0335</v>
-      </c>
-      <c r="CE11" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF11" s="8" t="n">
-        <v>18706973</v>
-      </c>
-      <c r="CG11" s="9" t="n">
-        <v>322779.47</v>
-      </c>
-      <c r="CH11" s="10" t="n">
         <v>0.036</v>
       </c>
-      <c r="CI11" s="11" t="n"/>
+      <c r="CE11" s="11" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -3413,88 +3281,88 @@
         <v>0.0352</v>
       </c>
       <c r="AA12" s="11" t="n">
-        <v>0.0942516216104385</v>
+        <v>0.1467846415582418</v>
       </c>
       <c r="AB12" s="8" t="n">
-        <v>14645626</v>
+        <v>13974725</v>
       </c>
       <c r="AC12" s="9" t="n">
-        <v>432734.31</v>
+        <v>474777.31</v>
       </c>
       <c r="AD12" s="10" t="n">
-        <v>0.0336</v>
+        <v>0.0354</v>
       </c>
       <c r="AE12" s="11" t="n">
-        <v>0.04800817189604804</v>
+        <v>0</v>
       </c>
       <c r="AF12" s="8" t="n">
         <v>13974725</v>
       </c>
       <c r="AG12" s="9" t="n">
-        <v>474777.31</v>
+        <v>479584.61</v>
       </c>
       <c r="AH12" s="10" t="n">
-        <v>0.0354</v>
+        <v>0.0358</v>
       </c>
       <c r="AI12" s="11" t="n">
-        <v>0</v>
+        <v>0.07221829643218575</v>
       </c>
       <c r="AJ12" s="8" t="n">
-        <v>13974725</v>
+        <v>13033470</v>
       </c>
       <c r="AK12" s="9" t="n">
-        <v>479584.61</v>
+        <v>483437.47</v>
       </c>
       <c r="AL12" s="10" t="n">
-        <v>0.0358</v>
+        <v>0.0363</v>
       </c>
       <c r="AM12" s="11" t="n">
-        <v>0.07221829643218575</v>
+        <v>0.0480713103458591</v>
       </c>
       <c r="AN12" s="8" t="n">
-        <v>13033470</v>
+        <v>12435671</v>
       </c>
       <c r="AO12" s="9" t="n">
-        <v>483437.47</v>
+        <v>467245.47</v>
       </c>
       <c r="AP12" s="10" t="n">
-        <v>0.0363</v>
+        <v>0.036</v>
       </c>
       <c r="AQ12" s="11" t="n">
-        <v>0.0480713103458591</v>
+        <v>0</v>
       </c>
       <c r="AR12" s="8" t="n">
         <v>12435671</v>
       </c>
       <c r="AS12" s="9" t="n">
-        <v>467245.47</v>
+        <v>433656.72</v>
       </c>
       <c r="AT12" s="10" t="n">
-        <v>0.036</v>
+        <v>0.0345</v>
       </c>
       <c r="AU12" s="11" t="n">
-        <v>0</v>
+        <v>0.008106571584148119</v>
       </c>
       <c r="AV12" s="8" t="n">
-        <v>12435671</v>
+        <v>12335671</v>
       </c>
       <c r="AW12" s="9" t="n">
-        <v>433656.72</v>
+        <v>422743.45</v>
       </c>
       <c r="AX12" s="10" t="n">
-        <v>0.0345</v>
+        <v>0.0353</v>
       </c>
       <c r="AY12" s="11" t="n">
-        <v>0.008106571584148119</v>
+        <v>0</v>
       </c>
       <c r="AZ12" s="8" t="n">
         <v>12335671</v>
       </c>
       <c r="BA12" s="9" t="n">
-        <v>422743.45</v>
+        <v>394679.79</v>
       </c>
       <c r="BB12" s="10" t="n">
-        <v>0.0353</v>
+        <v>0.0343</v>
       </c>
       <c r="BC12" s="11" t="n">
         <v>0</v>
@@ -3503,10 +3371,10 @@
         <v>12335671</v>
       </c>
       <c r="BE12" s="9" t="n">
-        <v>394679.79</v>
+        <v>395123.88</v>
       </c>
       <c r="BF12" s="10" t="n">
-        <v>0.0343</v>
+        <v>0.0349</v>
       </c>
       <c r="BG12" s="11" t="n">
         <v>0</v>
@@ -3515,84 +3383,72 @@
         <v>12335671</v>
       </c>
       <c r="BI12" s="9" t="n">
-        <v>395123.88</v>
+        <v>392669.08</v>
       </c>
       <c r="BJ12" s="10" t="n">
-        <v>0.0349</v>
+        <v>0.0356</v>
       </c>
       <c r="BK12" s="11" t="n">
-        <v>0</v>
+        <v>0.00852700604200313</v>
       </c>
       <c r="BL12" s="8" t="n">
-        <v>12335671</v>
+        <v>12231374</v>
       </c>
       <c r="BM12" s="9" t="n">
-        <v>392669.08</v>
+        <v>364103.54</v>
       </c>
       <c r="BN12" s="10" t="n">
-        <v>0.0356</v>
+        <v>0.0351</v>
       </c>
       <c r="BO12" s="11" t="n">
-        <v>0.00852700604200313</v>
+        <v>0.1078930368366115</v>
       </c>
       <c r="BP12" s="8" t="n">
-        <v>12231374</v>
+        <v>11040212</v>
       </c>
       <c r="BQ12" s="9" t="n">
-        <v>364103.54</v>
+        <v>323345.73</v>
       </c>
       <c r="BR12" s="10" t="n">
-        <v>0.0351</v>
+        <v>0.0328</v>
       </c>
       <c r="BS12" s="11" t="n">
-        <v>0.1078930368366115</v>
+        <v>0.06163142499453569</v>
       </c>
       <c r="BT12" s="8" t="n">
-        <v>11040212</v>
+        <v>10399289</v>
       </c>
       <c r="BU12" s="9" t="n">
-        <v>323345.73</v>
+        <v>277224.25</v>
       </c>
       <c r="BV12" s="10" t="n">
-        <v>0.0328</v>
+        <v>0.0297</v>
       </c>
       <c r="BW12" s="11" t="n">
-        <v>0.06163142499453569</v>
+        <v>0.03283692525275198</v>
       </c>
       <c r="BX12" s="8" t="n">
-        <v>10399289</v>
+        <v>10068665</v>
       </c>
       <c r="BY12" s="9" t="n">
-        <v>277224.25</v>
+        <v>260285.06</v>
       </c>
       <c r="BZ12" s="10" t="n">
-        <v>0.0297</v>
+        <v>0.0296</v>
       </c>
       <c r="CA12" s="11" t="n">
-        <v>0.03283692525275198</v>
+        <v>0.07897007813229198</v>
       </c>
       <c r="CB12" s="8" t="n">
-        <v>10068665</v>
+        <v>9331737</v>
       </c>
       <c r="CC12" s="9" t="n">
-        <v>260285.06</v>
+        <v>279004.94</v>
       </c>
       <c r="CD12" s="10" t="n">
-        <v>0.0296</v>
-      </c>
-      <c r="CE12" s="11" t="n">
-        <v>0.07897007813229198</v>
-      </c>
-      <c r="CF12" s="8" t="n">
-        <v>9331737</v>
-      </c>
-      <c r="CG12" s="9" t="n">
-        <v>279004.94</v>
-      </c>
-      <c r="CH12" s="10" t="n">
         <v>0.0311</v>
       </c>
-      <c r="CI12" s="11" t="n"/>
+      <c r="CE12" s="11" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -3680,76 +3536,76 @@
         <v>0.0303</v>
       </c>
       <c r="AA13" s="11" t="n">
-        <v>0.342400003741088</v>
+        <v>0.7478605305716015</v>
       </c>
       <c r="AB13" s="8" t="n">
-        <v>26944033</v>
+        <v>20693682</v>
       </c>
       <c r="AC13" s="9" t="n">
-        <v>336962.08</v>
+        <v>269038.56</v>
       </c>
       <c r="AD13" s="10" t="n">
-        <v>0.0261</v>
+        <v>0.02</v>
       </c>
       <c r="AE13" s="11" t="n">
-        <v>0.302041511993854</v>
+        <v>0.2534377545687067</v>
       </c>
       <c r="AF13" s="8" t="n">
-        <v>20693682</v>
+        <v>16509541</v>
       </c>
       <c r="AG13" s="9" t="n">
-        <v>269038.56</v>
+        <v>270921.57</v>
       </c>
       <c r="AH13" s="10" t="n">
-        <v>0.02</v>
+        <v>0.0202</v>
       </c>
       <c r="AI13" s="11" t="n">
-        <v>0.2534377545687067</v>
+        <v>0.005579568588889614</v>
       </c>
       <c r="AJ13" s="8" t="n">
-        <v>16509541</v>
+        <v>16417936</v>
       </c>
       <c r="AK13" s="9" t="n">
-        <v>270921.57</v>
+        <v>265215.34</v>
       </c>
       <c r="AL13" s="10" t="n">
-        <v>0.0202</v>
+        <v>0.0199</v>
       </c>
       <c r="AM13" s="11" t="n">
-        <v>0.005579568588889614</v>
+        <v>-0.06831357175852101</v>
       </c>
       <c r="AN13" s="8" t="n">
-        <v>16417936</v>
+        <v>17621740</v>
       </c>
       <c r="AO13" s="9" t="n">
-        <v>265215.34</v>
+        <v>274916.77</v>
       </c>
       <c r="AP13" s="10" t="n">
-        <v>0.0199</v>
+        <v>0.0212</v>
       </c>
       <c r="AQ13" s="11" t="n">
-        <v>-0.06831357175852101</v>
+        <v>0.8934928409505942</v>
       </c>
       <c r="AR13" s="8" t="n">
-        <v>17621740</v>
+        <v>9306473</v>
       </c>
       <c r="AS13" s="9" t="n">
-        <v>274916.77</v>
+        <v>137949.85</v>
       </c>
       <c r="AT13" s="10" t="n">
-        <v>0.0212</v>
+        <v>0.011</v>
       </c>
       <c r="AU13" s="11" t="n">
-        <v>0.8934928409505942</v>
+        <v>0</v>
       </c>
       <c r="AV13" s="8" t="n">
         <v>9306473</v>
       </c>
       <c r="AW13" s="9" t="n">
-        <v>137949.85</v>
+        <v>134180.73</v>
       </c>
       <c r="AX13" s="10" t="n">
-        <v>0.011</v>
+        <v>0.0112</v>
       </c>
       <c r="AY13" s="11" t="n">
         <v>0</v>
@@ -3758,10 +3614,10 @@
         <v>9306473</v>
       </c>
       <c r="BA13" s="9" t="n">
-        <v>134180.73</v>
+        <v>136767.93</v>
       </c>
       <c r="BB13" s="10" t="n">
-        <v>0.0112</v>
+        <v>0.0119</v>
       </c>
       <c r="BC13" s="11" t="n">
         <v>0</v>
@@ -3770,10 +3626,10 @@
         <v>9306473</v>
       </c>
       <c r="BE13" s="9" t="n">
-        <v>136767.93</v>
+        <v>140434.68</v>
       </c>
       <c r="BF13" s="10" t="n">
-        <v>0.0119</v>
+        <v>0.0124</v>
       </c>
       <c r="BG13" s="11" t="n">
         <v>0</v>
@@ -3782,10 +3638,10 @@
         <v>9306473</v>
       </c>
       <c r="BI13" s="9" t="n">
-        <v>140434.68</v>
+        <v>149071.08</v>
       </c>
       <c r="BJ13" s="10" t="n">
-        <v>0.0124</v>
+        <v>0.0135</v>
       </c>
       <c r="BK13" s="11" t="n">
         <v>0</v>
@@ -3794,10 +3650,10 @@
         <v>9306473</v>
       </c>
       <c r="BM13" s="9" t="n">
-        <v>149071.08</v>
+        <v>145432.25</v>
       </c>
       <c r="BN13" s="10" t="n">
-        <v>0.0135</v>
+        <v>0.014</v>
       </c>
       <c r="BO13" s="11" t="n">
         <v>0</v>
@@ -3806,10 +3662,10 @@
         <v>9306473</v>
       </c>
       <c r="BQ13" s="9" t="n">
-        <v>145432.25</v>
+        <v>139606.4</v>
       </c>
       <c r="BR13" s="10" t="n">
-        <v>0.014</v>
+        <v>0.0142</v>
       </c>
       <c r="BS13" s="11" t="n">
         <v>0</v>
@@ -3818,10 +3674,10 @@
         <v>9306473</v>
       </c>
       <c r="BU13" s="9" t="n">
-        <v>139606.4</v>
+        <v>146172.12</v>
       </c>
       <c r="BV13" s="10" t="n">
-        <v>0.0142</v>
+        <v>0.0156</v>
       </c>
       <c r="BW13" s="11" t="n">
         <v>0</v>
@@ -3830,10 +3686,10 @@
         <v>9306473</v>
       </c>
       <c r="BY13" s="9" t="n">
-        <v>146172.12</v>
+        <v>157065.34</v>
       </c>
       <c r="BZ13" s="10" t="n">
-        <v>0.0156</v>
+        <v>0.0178</v>
       </c>
       <c r="CA13" s="11" t="n">
         <v>0</v>
@@ -3842,24 +3698,12 @@
         <v>9306473</v>
       </c>
       <c r="CC13" s="9" t="n">
-        <v>157065.34</v>
+        <v>174943.08</v>
       </c>
       <c r="CD13" s="10" t="n">
-        <v>0.0178</v>
-      </c>
-      <c r="CE13" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF13" s="8" t="n">
-        <v>9306473</v>
-      </c>
-      <c r="CG13" s="9" t="n">
-        <v>174943.08</v>
-      </c>
-      <c r="CH13" s="10" t="n">
         <v>0.0195</v>
       </c>
-      <c r="CI13" s="11" t="n"/>
+      <c r="CE13" s="11" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -3953,10 +3797,10 @@
         <v>21167034</v>
       </c>
       <c r="AC14" s="9" t="n">
-        <v>377281.21</v>
+        <v>397792.07</v>
       </c>
       <c r="AD14" s="10" t="n">
-        <v>0.0293</v>
+        <v>0.0296</v>
       </c>
       <c r="AE14" s="11" t="n">
         <v>0</v>
@@ -3965,10 +3809,10 @@
         <v>21167034</v>
       </c>
       <c r="AG14" s="9" t="n">
-        <v>397792.07</v>
+        <v>416715.398358</v>
       </c>
       <c r="AH14" s="10" t="n">
-        <v>0.0296</v>
+        <v>0.0311051731198606</v>
       </c>
       <c r="AI14" s="11" t="n">
         <v>0</v>
@@ -3977,10 +3821,10 @@
         <v>21167034</v>
       </c>
       <c r="AK14" s="9" t="n">
-        <v>416715.398358</v>
+        <v>445693.07</v>
       </c>
       <c r="AL14" s="10" t="n">
-        <v>0.0311051731198606</v>
+        <v>0.0334</v>
       </c>
       <c r="AM14" s="11" t="n">
         <v>0</v>
@@ -3989,10 +3833,10 @@
         <v>21167034</v>
       </c>
       <c r="AO14" s="9" t="n">
-        <v>445693.07</v>
+        <v>444846.39</v>
       </c>
       <c r="AP14" s="10" t="n">
-        <v>0.0334</v>
+        <v>0.0343</v>
       </c>
       <c r="AQ14" s="11" t="n">
         <v>0</v>
@@ -4001,10 +3845,10 @@
         <v>21167034</v>
       </c>
       <c r="AS14" s="9" t="n">
-        <v>444846.39</v>
+        <v>434876.71</v>
       </c>
       <c r="AT14" s="10" t="n">
-        <v>0.0343</v>
+        <v>0.0346</v>
       </c>
       <c r="AU14" s="11" t="n">
         <v>0</v>
@@ -4013,10 +3857,10 @@
         <v>21167034</v>
       </c>
       <c r="AW14" s="9" t="n">
-        <v>434876.71</v>
+        <v>397601.57</v>
       </c>
       <c r="AX14" s="10" t="n">
-        <v>0.0346</v>
+        <v>0.0332</v>
       </c>
       <c r="AY14" s="11" t="n">
         <v>0</v>
@@ -4025,10 +3869,10 @@
         <v>21167034</v>
       </c>
       <c r="BA14" s="9" t="n">
-        <v>397601.57</v>
+        <v>399802.94</v>
       </c>
       <c r="BB14" s="10" t="n">
-        <v>0.0332</v>
+        <v>0.0348</v>
       </c>
       <c r="BC14" s="11" t="n">
         <v>0</v>
@@ -4037,50 +3881,42 @@
         <v>21167034</v>
       </c>
       <c r="BE14" s="9" t="n">
-        <v>399802.94</v>
+        <v>405200.53</v>
       </c>
       <c r="BF14" s="10" t="n">
-        <v>0.0348</v>
+        <v>0.0358</v>
       </c>
       <c r="BG14" s="11" t="n">
-        <v>0</v>
+        <v>0.01098531912399817</v>
       </c>
       <c r="BH14" s="8" t="n">
-        <v>21167034</v>
+        <v>20937034</v>
       </c>
       <c r="BI14" s="9" t="n">
-        <v>405200.53</v>
+        <v>420750.64</v>
       </c>
       <c r="BJ14" s="10" t="n">
-        <v>0.0358</v>
+        <v>0.0381</v>
       </c>
       <c r="BK14" s="11" t="n">
-        <v>0.01098531912399817</v>
+        <v>0.7744638647975486</v>
       </c>
       <c r="BL14" s="8" t="n">
-        <v>20937034</v>
+        <v>11799076</v>
       </c>
       <c r="BM14" s="9" t="n">
-        <v>420750.64</v>
+        <v>219014.45</v>
       </c>
       <c r="BN14" s="10" t="n">
-        <v>0.0381</v>
+        <v>0.0211</v>
       </c>
       <c r="BO14" s="11" t="n">
-        <v>0.7744638647975486</v>
-      </c>
-      <c r="BP14" s="8" t="n">
-        <v>11799076</v>
-      </c>
-      <c r="BQ14" s="9" t="n">
-        <v>219014.45</v>
-      </c>
-      <c r="BR14" s="10" t="n">
-        <v>0.0211</v>
-      </c>
-      <c r="BS14" s="11" t="n">
         <v>1</v>
       </c>
+      <c r="BP14" s="8" t="n"/>
+      <c r="BQ14" s="9" t="n"/>
+      <c r="BR14" s="10" t="n"/>
+      <c r="BS14" s="11" t="n"/>
       <c r="BT14" s="8" t="n"/>
       <c r="BU14" s="9" t="n"/>
       <c r="BV14" s="10" t="n"/>
@@ -4093,10 +3929,6 @@
       <c r="CC14" s="9" t="n"/>
       <c r="CD14" s="10" t="n"/>
       <c r="CE14" s="11" t="n"/>
-      <c r="CF14" s="8" t="n"/>
-      <c r="CG14" s="9" t="n"/>
-      <c r="CH14" s="10" t="n"/>
-      <c r="CI14" s="11" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -4190,10 +4022,10 @@
         <v>33244875</v>
       </c>
       <c r="AC15" s="9" t="n">
-        <v>386072.73</v>
+        <v>460075.83</v>
       </c>
       <c r="AD15" s="10" t="n">
-        <v>0.0299</v>
+        <v>0.0343</v>
       </c>
       <c r="AE15" s="11" t="n">
         <v>0</v>
@@ -4202,10 +4034,10 @@
         <v>33244875</v>
       </c>
       <c r="AG15" s="9" t="n">
-        <v>460075.83</v>
+        <v>455587.77</v>
       </c>
       <c r="AH15" s="10" t="n">
-        <v>0.0343</v>
+        <v>0.034</v>
       </c>
       <c r="AI15" s="11" t="n">
         <v>0</v>
@@ -4214,10 +4046,10 @@
         <v>33244875</v>
       </c>
       <c r="AK15" s="9" t="n">
-        <v>455587.77</v>
+        <v>422010.44</v>
       </c>
       <c r="AL15" s="10" t="n">
-        <v>0.034</v>
+        <v>0.0317</v>
       </c>
       <c r="AM15" s="11" t="n">
         <v>0</v>
@@ -4226,10 +4058,10 @@
         <v>33244875</v>
       </c>
       <c r="AO15" s="9" t="n">
-        <v>422010.44</v>
+        <v>425434.67</v>
       </c>
       <c r="AP15" s="10" t="n">
-        <v>0.0317</v>
+        <v>0.0328</v>
       </c>
       <c r="AQ15" s="11" t="n">
         <v>0</v>
@@ -4238,10 +4070,10 @@
         <v>33244875</v>
       </c>
       <c r="AS15" s="9" t="n">
-        <v>425434.67</v>
+        <v>409842.82</v>
       </c>
       <c r="AT15" s="10" t="n">
-        <v>0.0328</v>
+        <v>0.0326</v>
       </c>
       <c r="AU15" s="11" t="n">
         <v>0</v>
@@ -4250,58 +4082,58 @@
         <v>33244875</v>
       </c>
       <c r="AW15" s="9" t="n">
-        <v>409842.82</v>
+        <v>376199.01</v>
       </c>
       <c r="AX15" s="10" t="n">
-        <v>0.0326</v>
+        <v>0.0314</v>
       </c>
       <c r="AY15" s="11" t="n">
-        <v>0</v>
+        <v>0.01837960782511803</v>
       </c>
       <c r="AZ15" s="8" t="n">
-        <v>33244875</v>
+        <v>32644875</v>
       </c>
       <c r="BA15" s="9" t="n">
-        <v>376199.01</v>
+        <v>341204.23</v>
       </c>
       <c r="BB15" s="10" t="n">
-        <v>0.0314</v>
+        <v>0.0297</v>
       </c>
       <c r="BC15" s="11" t="n">
-        <v>0.01837960782511803</v>
+        <v>0.0842854566355568</v>
       </c>
       <c r="BD15" s="8" t="n">
-        <v>32644875</v>
+        <v>30107270</v>
       </c>
       <c r="BE15" s="9" t="n">
-        <v>341204.23</v>
+        <v>321666.07</v>
       </c>
       <c r="BF15" s="10" t="n">
-        <v>0.0297</v>
+        <v>0.0284</v>
       </c>
       <c r="BG15" s="11" t="n">
-        <v>0.0842854566355568</v>
+        <v>0.1045592607036581</v>
       </c>
       <c r="BH15" s="8" t="n">
-        <v>30107270</v>
+        <v>27257270</v>
       </c>
       <c r="BI15" s="9" t="n">
-        <v>321666.07</v>
+        <v>326869.18</v>
       </c>
       <c r="BJ15" s="10" t="n">
-        <v>0.0284</v>
+        <v>0.0296</v>
       </c>
       <c r="BK15" s="11" t="n">
-        <v>0.1045592607036581</v>
+        <v>0</v>
       </c>
       <c r="BL15" s="8" t="n">
         <v>27257270</v>
       </c>
       <c r="BM15" s="9" t="n">
-        <v>326869.18</v>
+        <v>324961.17</v>
       </c>
       <c r="BN15" s="10" t="n">
-        <v>0.0296</v>
+        <v>0.0313</v>
       </c>
       <c r="BO15" s="11" t="n">
         <v>0</v>
@@ -4310,10 +4142,10 @@
         <v>27257270</v>
       </c>
       <c r="BQ15" s="9" t="n">
-        <v>324961.17</v>
+        <v>322998.65</v>
       </c>
       <c r="BR15" s="10" t="n">
-        <v>0.0313</v>
+        <v>0.0328</v>
       </c>
       <c r="BS15" s="11" t="n">
         <v>0</v>
@@ -4322,10 +4154,10 @@
         <v>27257270</v>
       </c>
       <c r="BU15" s="9" t="n">
-        <v>322998.65</v>
+        <v>300375.12</v>
       </c>
       <c r="BV15" s="10" t="n">
-        <v>0.0328</v>
+        <v>0.0321</v>
       </c>
       <c r="BW15" s="11" t="n">
         <v>0</v>
@@ -4334,10 +4166,10 @@
         <v>27257270</v>
       </c>
       <c r="BY15" s="9" t="n">
-        <v>300375.12</v>
+        <v>276811.21</v>
       </c>
       <c r="BZ15" s="10" t="n">
-        <v>0.0321</v>
+        <v>0.0315</v>
       </c>
       <c r="CA15" s="11" t="n">
         <v>0</v>
@@ -4346,24 +4178,12 @@
         <v>27257270</v>
       </c>
       <c r="CC15" s="9" t="n">
-        <v>276811.21</v>
+        <v>268783.94</v>
       </c>
       <c r="CD15" s="10" t="n">
-        <v>0.0315</v>
-      </c>
-      <c r="CE15" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF15" s="8" t="n">
-        <v>27257270</v>
-      </c>
-      <c r="CG15" s="9" t="n">
-        <v>268783.94</v>
-      </c>
-      <c r="CH15" s="10" t="n">
         <v>0.03</v>
       </c>
-      <c r="CI15" s="11" t="n"/>
+      <c r="CE15" s="11" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -4451,68 +4271,60 @@
         <v>0.0279</v>
       </c>
       <c r="AA16" s="11" t="n">
-        <v>0.2789485718226543</v>
+        <v>0.5296260686972589</v>
       </c>
       <c r="AB16" s="8" t="n">
-        <v>12412184</v>
+        <v>10378056</v>
       </c>
       <c r="AC16" s="9" t="n">
-        <v>292791.01</v>
+        <v>273710.85</v>
       </c>
       <c r="AD16" s="10" t="n">
-        <v>0.0227</v>
+        <v>0.0204</v>
       </c>
       <c r="AE16" s="11" t="n">
-        <v>0.1960027966702049</v>
+        <v>0.2259018504190464</v>
       </c>
       <c r="AF16" s="8" t="n">
-        <v>10378056</v>
+        <v>8465650</v>
       </c>
       <c r="AG16" s="9" t="n">
-        <v>273710.85</v>
+        <v>264458.44</v>
       </c>
       <c r="AH16" s="10" t="n">
-        <v>0.0204</v>
+        <v>0.0197</v>
       </c>
       <c r="AI16" s="11" t="n">
-        <v>0.2259018504190464</v>
+        <v>0.8187749766950423</v>
       </c>
       <c r="AJ16" s="8" t="n">
-        <v>8465650</v>
+        <v>4654589</v>
       </c>
       <c r="AK16" s="9" t="n">
-        <v>264458.44</v>
+        <v>149235.43</v>
       </c>
       <c r="AL16" s="10" t="n">
-        <v>0.0197</v>
+        <v>0.0112</v>
       </c>
       <c r="AM16" s="11" t="n">
-        <v>0.8187749766950423</v>
+        <v>0.6557662214497397</v>
       </c>
       <c r="AN16" s="8" t="n">
-        <v>4654589</v>
+        <v>2811139</v>
       </c>
       <c r="AO16" s="9" t="n">
-        <v>149235.43</v>
+        <v>88199.49000000001</v>
       </c>
       <c r="AP16" s="10" t="n">
-        <v>0.0112</v>
+        <v>0.0068</v>
       </c>
       <c r="AQ16" s="11" t="n">
-        <v>0.6557662214497397</v>
-      </c>
-      <c r="AR16" s="8" t="n">
-        <v>2811139</v>
-      </c>
-      <c r="AS16" s="9" t="n">
-        <v>88199.49000000001</v>
-      </c>
-      <c r="AT16" s="10" t="n">
-        <v>0.0068</v>
-      </c>
-      <c r="AU16" s="11" t="n">
         <v>1</v>
       </c>
+      <c r="AR16" s="8" t="n"/>
+      <c r="AS16" s="9" t="n"/>
+      <c r="AT16" s="10" t="n"/>
+      <c r="AU16" s="11" t="n"/>
       <c r="AV16" s="8" t="n"/>
       <c r="AW16" s="9" t="n"/>
       <c r="AX16" s="10" t="n"/>
@@ -4549,10 +4361,6 @@
       <c r="CC16" s="9" t="n"/>
       <c r="CD16" s="10" t="n"/>
       <c r="CE16" s="11" t="n"/>
-      <c r="CF16" s="8" t="n"/>
-      <c r="CG16" s="9" t="n"/>
-      <c r="CH16" s="10" t="n"/>
-      <c r="CI16" s="11" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -4666,10 +4474,6 @@
       <c r="CC17" s="9" t="n"/>
       <c r="CD17" s="10" t="n"/>
       <c r="CE17" s="11" t="n"/>
-      <c r="CF17" s="8" t="n"/>
-      <c r="CG17" s="9" t="n"/>
-      <c r="CH17" s="10" t="n"/>
-      <c r="CI17" s="11" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -4757,112 +4561,112 @@
         <v>0.0287</v>
       </c>
       <c r="AA18" s="11" t="n">
-        <v>0</v>
+        <v>0.06253145709252579</v>
       </c>
       <c r="AB18" s="8" t="n">
-        <v>3039945</v>
+        <v>2861040</v>
       </c>
       <c r="AC18" s="9" t="n">
-        <v>374095.63</v>
+        <v>425064.71</v>
       </c>
       <c r="AD18" s="10" t="n">
-        <v>0.029</v>
+        <v>0.0317</v>
       </c>
       <c r="AE18" s="11" t="n">
-        <v>0.06253145709252579</v>
+        <v>0.02897415480359852</v>
       </c>
       <c r="AF18" s="8" t="n">
-        <v>2861040</v>
+        <v>2780478</v>
       </c>
       <c r="AG18" s="9" t="n">
-        <v>425064.71</v>
+        <v>405921.98</v>
       </c>
       <c r="AH18" s="10" t="n">
-        <v>0.0317</v>
+        <v>0.0303</v>
       </c>
       <c r="AI18" s="11" t="n">
-        <v>0.02897415480359852</v>
+        <v>0.01230872292630713</v>
       </c>
       <c r="AJ18" s="8" t="n">
-        <v>2780478</v>
+        <v>2746670</v>
       </c>
       <c r="AK18" s="9" t="n">
-        <v>405921.98</v>
+        <v>458611.49</v>
       </c>
       <c r="AL18" s="10" t="n">
-        <v>0.0303</v>
+        <v>0.0344</v>
       </c>
       <c r="AM18" s="11" t="n">
-        <v>0.01230872292630713</v>
+        <v>0</v>
       </c>
       <c r="AN18" s="8" t="n">
         <v>2746670</v>
       </c>
       <c r="AO18" s="9" t="n">
-        <v>458611.49</v>
+        <v>436720.53</v>
       </c>
       <c r="AP18" s="10" t="n">
-        <v>0.0344</v>
+        <v>0.0337</v>
       </c>
       <c r="AQ18" s="11" t="n">
-        <v>0</v>
+        <v>0.01854138622819997</v>
       </c>
       <c r="AR18" s="8" t="n">
-        <v>2746670</v>
+        <v>2696670</v>
       </c>
       <c r="AS18" s="9" t="n">
-        <v>436720.53</v>
+        <v>436483.01</v>
       </c>
       <c r="AT18" s="10" t="n">
-        <v>0.0337</v>
+        <v>0.0347</v>
       </c>
       <c r="AU18" s="11" t="n">
-        <v>0.01854138622819997</v>
+        <v>0</v>
       </c>
       <c r="AV18" s="8" t="n">
         <v>2696670</v>
       </c>
       <c r="AW18" s="9" t="n">
-        <v>436483.01</v>
+        <v>432249.23</v>
       </c>
       <c r="AX18" s="10" t="n">
-        <v>0.0347</v>
+        <v>0.0361</v>
       </c>
       <c r="AY18" s="11" t="n">
-        <v>0</v>
+        <v>-0.01820386140308082</v>
       </c>
       <c r="AZ18" s="8" t="n">
-        <v>2696670</v>
+        <v>2746670</v>
       </c>
       <c r="BA18" s="9" t="n">
-        <v>432249.23</v>
+        <v>406259.96</v>
       </c>
       <c r="BB18" s="10" t="n">
-        <v>0.0361</v>
+        <v>0.0353</v>
       </c>
       <c r="BC18" s="11" t="n">
-        <v>-0.01820386140308082</v>
+        <v>-0.09100927632732893</v>
       </c>
       <c r="BD18" s="8" t="n">
-        <v>2746670</v>
+        <v>3021670</v>
       </c>
       <c r="BE18" s="9" t="n">
-        <v>406259.96</v>
+        <v>380972.15</v>
       </c>
       <c r="BF18" s="10" t="n">
-        <v>0.0353</v>
+        <v>0.0336</v>
       </c>
       <c r="BG18" s="11" t="n">
-        <v>-0.09100927632732893</v>
+        <v>0</v>
       </c>
       <c r="BH18" s="8" t="n">
         <v>3021670</v>
       </c>
       <c r="BI18" s="9" t="n">
-        <v>380972.15</v>
+        <v>374687.08</v>
       </c>
       <c r="BJ18" s="10" t="n">
-        <v>0.0336</v>
+        <v>0.0339</v>
       </c>
       <c r="BK18" s="11" t="n">
         <v>0</v>
@@ -4871,10 +4675,10 @@
         <v>3021670</v>
       </c>
       <c r="BM18" s="9" t="n">
-        <v>374687.08</v>
+        <v>372239.53</v>
       </c>
       <c r="BN18" s="10" t="n">
-        <v>0.0339</v>
+        <v>0.0358</v>
       </c>
       <c r="BO18" s="11" t="n">
         <v>0</v>
@@ -4883,34 +4687,34 @@
         <v>3021670</v>
       </c>
       <c r="BQ18" s="9" t="n">
-        <v>372239.53</v>
+        <v>370366.09</v>
       </c>
       <c r="BR18" s="10" t="n">
-        <v>0.0358</v>
+        <v>0.0376</v>
       </c>
       <c r="BS18" s="11" t="n">
-        <v>0</v>
+        <v>0.001190161420612721</v>
       </c>
       <c r="BT18" s="8" t="n">
-        <v>3021670</v>
+        <v>3018078</v>
       </c>
       <c r="BU18" s="9" t="n">
-        <v>370366.09</v>
+        <v>347747.47</v>
       </c>
       <c r="BV18" s="10" t="n">
-        <v>0.0376</v>
+        <v>0.0372</v>
       </c>
       <c r="BW18" s="11" t="n">
-        <v>0.001190161420612721</v>
+        <v>0</v>
       </c>
       <c r="BX18" s="8" t="n">
         <v>3018078</v>
       </c>
       <c r="BY18" s="9" t="n">
-        <v>347747.47</v>
+        <v>360535.07</v>
       </c>
       <c r="BZ18" s="10" t="n">
-        <v>0.0372</v>
+        <v>0.041</v>
       </c>
       <c r="CA18" s="11" t="n">
         <v>0</v>
@@ -4919,24 +4723,12 @@
         <v>3018078</v>
       </c>
       <c r="CC18" s="9" t="n">
-        <v>360535.07</v>
+        <v>371545.02</v>
       </c>
       <c r="CD18" s="10" t="n">
-        <v>0.041</v>
-      </c>
-      <c r="CE18" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF18" s="8" t="n">
-        <v>3018078</v>
-      </c>
-      <c r="CG18" s="9" t="n">
-        <v>371545.02</v>
-      </c>
-      <c r="CH18" s="10" t="n">
         <v>0.0414</v>
       </c>
-      <c r="CI18" s="11" t="n"/>
+      <c r="CE18" s="11" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -5030,180 +4822,168 @@
         <v>18853686</v>
       </c>
       <c r="AC19" s="9" t="n">
-        <v>164253.31</v>
+        <v>173774.42</v>
       </c>
       <c r="AD19" s="10" t="n">
-        <v>0.0127</v>
+        <v>0.0129</v>
       </c>
       <c r="AE19" s="11" t="n">
-        <v>0</v>
+        <v>0.00550299933303119</v>
       </c>
       <c r="AF19" s="8" t="n">
-        <v>18853686</v>
+        <v>18750502</v>
       </c>
       <c r="AG19" s="9" t="n">
-        <v>173774.42</v>
+        <v>165998.19</v>
       </c>
       <c r="AH19" s="10" t="n">
-        <v>0.0129</v>
+        <v>0.0124</v>
       </c>
       <c r="AI19" s="11" t="n">
-        <v>0.00550299933303119</v>
+        <v>0.04733304757267096</v>
       </c>
       <c r="AJ19" s="8" t="n">
-        <v>18750502</v>
+        <v>17903094</v>
       </c>
       <c r="AK19" s="9" t="n">
-        <v>165998.19</v>
+        <v>163696.94</v>
       </c>
       <c r="AL19" s="10" t="n">
+        <v>0.0123</v>
+      </c>
+      <c r="AM19" s="11" t="n">
+        <v>0.02860906275493533</v>
+      </c>
+      <c r="AN19" s="8" t="n">
+        <v>17405149</v>
+      </c>
+      <c r="AO19" s="9" t="n">
+        <v>164043.53</v>
+      </c>
+      <c r="AP19" s="10" t="n">
+        <v>0.0126</v>
+      </c>
+      <c r="AQ19" s="11" t="n">
+        <v>0.1044024130018492</v>
+      </c>
+      <c r="AR19" s="8" t="n">
+        <v>15759789</v>
+      </c>
+      <c r="AS19" s="9" t="n">
+        <v>153571.26</v>
+      </c>
+      <c r="AT19" s="10" t="n">
+        <v>0.0122</v>
+      </c>
+      <c r="AU19" s="11" t="n">
+        <v>0.04036608437732761</v>
+      </c>
+      <c r="AV19" s="8" t="n">
+        <v>15148311</v>
+      </c>
+      <c r="AW19" s="9" t="n">
+        <v>148741.27</v>
+      </c>
+      <c r="AX19" s="10" t="n">
         <v>0.0124</v>
       </c>
-      <c r="AM19" s="11" t="n">
-        <v>0.04733304757267096</v>
-      </c>
-      <c r="AN19" s="8" t="n">
-        <v>17903094</v>
-      </c>
-      <c r="AO19" s="9" t="n">
-        <v>163696.94</v>
-      </c>
-      <c r="AP19" s="10" t="n">
-        <v>0.0123</v>
-      </c>
-      <c r="AQ19" s="11" t="n">
-        <v>0.02860906275493533</v>
-      </c>
-      <c r="AR19" s="8" t="n">
-        <v>17405149</v>
-      </c>
-      <c r="AS19" s="9" t="n">
-        <v>164043.53</v>
-      </c>
-      <c r="AT19" s="10" t="n">
+      <c r="AY19" s="11" t="n">
+        <v>0.02447981732333564</v>
+      </c>
+      <c r="AZ19" s="8" t="n">
+        <v>14786344</v>
+      </c>
+      <c r="BA19" s="9" t="n">
+        <v>145061.43</v>
+      </c>
+      <c r="BB19" s="10" t="n">
         <v>0.0126</v>
       </c>
-      <c r="AU19" s="11" t="n">
-        <v>0.1044024130018492</v>
-      </c>
-      <c r="AV19" s="8" t="n">
-        <v>15759789</v>
-      </c>
-      <c r="AW19" s="9" t="n">
-        <v>153571.26</v>
-      </c>
-      <c r="AX19" s="10" t="n">
-        <v>0.0122</v>
-      </c>
-      <c r="AY19" s="11" t="n">
-        <v>0.04036608437732761</v>
-      </c>
-      <c r="AZ19" s="8" t="n">
-        <v>15148311</v>
-      </c>
-      <c r="BA19" s="9" t="n">
-        <v>148741.27</v>
-      </c>
-      <c r="BB19" s="10" t="n">
+      <c r="BC19" s="11" t="n">
+        <v>0.02183487170521033</v>
+      </c>
+      <c r="BD19" s="8" t="n">
+        <v>14470385</v>
+      </c>
+      <c r="BE19" s="9" t="n">
+        <v>140333.79</v>
+      </c>
+      <c r="BF19" s="10" t="n">
         <v>0.0124</v>
       </c>
-      <c r="BC19" s="11" t="n">
-        <v>0.02447981732333564</v>
-      </c>
-      <c r="BD19" s="8" t="n">
-        <v>14786344</v>
-      </c>
-      <c r="BE19" s="9" t="n">
-        <v>145061.43</v>
-      </c>
-      <c r="BF19" s="10" t="n">
-        <v>0.0126</v>
-      </c>
       <c r="BG19" s="11" t="n">
-        <v>0.02183487170521033</v>
+        <v>0.01486488524161312</v>
       </c>
       <c r="BH19" s="8" t="n">
-        <v>14470385</v>
+        <v>14258435</v>
       </c>
       <c r="BI19" s="9" t="n">
-        <v>140333.79</v>
+        <v>141151.38</v>
       </c>
       <c r="BJ19" s="10" t="n">
-        <v>0.0124</v>
+        <v>0.0128</v>
       </c>
       <c r="BK19" s="11" t="n">
-        <v>0.01486488524161312</v>
+        <v>0</v>
       </c>
       <c r="BL19" s="8" t="n">
         <v>14258435</v>
       </c>
       <c r="BM19" s="9" t="n">
-        <v>141151.38</v>
+        <v>132603.45</v>
       </c>
       <c r="BN19" s="10" t="n">
         <v>0.0128</v>
       </c>
       <c r="BO19" s="11" t="n">
-        <v>0</v>
+        <v>0.0231160633003793</v>
       </c>
       <c r="BP19" s="8" t="n">
-        <v>14258435</v>
+        <v>13936283</v>
       </c>
       <c r="BQ19" s="9" t="n">
-        <v>132603.45</v>
+        <v>123789.03</v>
       </c>
       <c r="BR19" s="10" t="n">
-        <v>0.0128</v>
+        <v>0.0126</v>
       </c>
       <c r="BS19" s="11" t="n">
-        <v>0.0231160633003793</v>
+        <v>0.07172012123664578</v>
       </c>
       <c r="BT19" s="8" t="n">
-        <v>13936283</v>
+        <v>13003659</v>
       </c>
       <c r="BU19" s="9" t="n">
-        <v>123789.03</v>
+        <v>115264.43</v>
       </c>
       <c r="BV19" s="10" t="n">
-        <v>0.0126</v>
+        <v>0.0123</v>
       </c>
       <c r="BW19" s="11" t="n">
-        <v>0.07172012123664578</v>
+        <v>0.132761983775747</v>
       </c>
       <c r="BX19" s="8" t="n">
-        <v>13003659</v>
+        <v>11479604</v>
       </c>
       <c r="BY19" s="9" t="n">
-        <v>115264.43</v>
+        <v>100630.21</v>
       </c>
       <c r="BZ19" s="10" t="n">
-        <v>0.0123</v>
+        <v>0.0114</v>
       </c>
       <c r="CA19" s="11" t="n">
-        <v>0.132761983775747</v>
+        <v>0.2957940438149267</v>
       </c>
       <c r="CB19" s="8" t="n">
-        <v>11479604</v>
+        <v>8859127</v>
       </c>
       <c r="CC19" s="9" t="n">
-        <v>100630.21</v>
+        <v>85955.67999999999</v>
       </c>
       <c r="CD19" s="10" t="n">
-        <v>0.0114</v>
-      </c>
-      <c r="CE19" s="11" t="n">
-        <v>0.2957940438149267</v>
-      </c>
-      <c r="CF19" s="8" t="n">
-        <v>8859127</v>
-      </c>
-      <c r="CG19" s="9" t="n">
-        <v>85955.67999999999</v>
-      </c>
-      <c r="CH19" s="10" t="n">
         <v>0.009599999999999999</v>
       </c>
-      <c r="CI19" s="11" t="n"/>
+      <c r="CE19" s="11" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -5291,186 +5071,174 @@
         <v>0.0133</v>
       </c>
       <c r="AA20" s="11" t="n">
-        <v>0.08087039879149707</v>
+        <v>0.1135898782108316</v>
       </c>
       <c r="AB20" s="8" t="n">
-        <v>13271296</v>
+        <v>12881359</v>
       </c>
       <c r="AC20" s="9" t="n">
-        <v>162467.21</v>
+        <v>173666.48</v>
       </c>
       <c r="AD20" s="10" t="n">
-        <v>0.0126</v>
+        <v>0.0129</v>
       </c>
       <c r="AE20" s="11" t="n">
-        <v>0.03027141779062287</v>
+        <v>0.02043991688728315</v>
       </c>
       <c r="AF20" s="8" t="n">
-        <v>12881359</v>
+        <v>12623339</v>
       </c>
       <c r="AG20" s="9" t="n">
-        <v>173666.48</v>
+        <v>167133.01</v>
       </c>
       <c r="AH20" s="10" t="n">
-        <v>0.0129</v>
+        <v>0.0125</v>
       </c>
       <c r="AI20" s="11" t="n">
-        <v>0.02043991688728315</v>
+        <v>0.1486639530668313</v>
       </c>
       <c r="AJ20" s="8" t="n">
-        <v>12623339</v>
+        <v>10989584</v>
       </c>
       <c r="AK20" s="9" t="n">
-        <v>167133.01</v>
+        <v>166085.58</v>
       </c>
       <c r="AL20" s="10" t="n">
         <v>0.0125</v>
       </c>
       <c r="AM20" s="11" t="n">
-        <v>0.1486639530668313</v>
+        <v>0.02078030694418823</v>
       </c>
       <c r="AN20" s="8" t="n">
-        <v>10989584</v>
+        <v>10765866</v>
       </c>
       <c r="AO20" s="9" t="n">
-        <v>166085.58</v>
+        <v>164857.71</v>
       </c>
       <c r="AP20" s="10" t="n">
+        <v>0.0127</v>
+      </c>
+      <c r="AQ20" s="11" t="n">
+        <v>0.05823053317160534</v>
+      </c>
+      <c r="AR20" s="8" t="n">
+        <v>10173460</v>
+      </c>
+      <c r="AS20" s="9" t="n">
+        <v>152734.15</v>
+      </c>
+      <c r="AT20" s="10" t="n">
+        <v>0.0121</v>
+      </c>
+      <c r="AU20" s="11" t="n">
+        <v>0.01848262661129821</v>
+      </c>
+      <c r="AV20" s="8" t="n">
+        <v>9988840</v>
+      </c>
+      <c r="AW20" s="9" t="n">
+        <v>150162.23</v>
+      </c>
+      <c r="AX20" s="10" t="n">
         <v>0.0125</v>
       </c>
-      <c r="AQ20" s="11" t="n">
-        <v>0.02078030694418823</v>
-      </c>
-      <c r="AR20" s="8" t="n">
-        <v>10765866</v>
-      </c>
-      <c r="AS20" s="9" t="n">
-        <v>164857.71</v>
-      </c>
-      <c r="AT20" s="10" t="n">
-        <v>0.0127</v>
-      </c>
-      <c r="AU20" s="11" t="n">
-        <v>0.05823053317160534</v>
-      </c>
-      <c r="AV20" s="8" t="n">
-        <v>10173460</v>
-      </c>
-      <c r="AW20" s="9" t="n">
-        <v>152734.15</v>
-      </c>
-      <c r="AX20" s="10" t="n">
-        <v>0.0121</v>
-      </c>
       <c r="AY20" s="11" t="n">
-        <v>0.01848262661129821</v>
+        <v>0.11089473889663</v>
       </c>
       <c r="AZ20" s="8" t="n">
-        <v>9988840</v>
+        <v>8991707</v>
       </c>
       <c r="BA20" s="9" t="n">
-        <v>150162.23</v>
+        <v>142914.19</v>
       </c>
       <c r="BB20" s="10" t="n">
+        <v>0.0124</v>
+      </c>
+      <c r="BC20" s="11" t="n">
+        <v>-0.04856779498084111</v>
+      </c>
+      <c r="BD20" s="8" t="n">
+        <v>9450707</v>
+      </c>
+      <c r="BE20" s="9" t="n">
+        <v>146920.69</v>
+      </c>
+      <c r="BF20" s="10" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="BG20" s="11" t="n">
+        <v>0.03318890177940083</v>
+      </c>
+      <c r="BH20" s="8" t="n">
+        <v>9147124</v>
+      </c>
+      <c r="BI20" s="9" t="n">
+        <v>137746.54</v>
+      </c>
+      <c r="BJ20" s="10" t="n">
         <v>0.0125</v>
       </c>
-      <c r="BC20" s="11" t="n">
-        <v>0.11089473889663</v>
-      </c>
-      <c r="BD20" s="8" t="n">
-        <v>8991707</v>
-      </c>
-      <c r="BE20" s="9" t="n">
-        <v>142914.19</v>
-      </c>
-      <c r="BF20" s="10" t="n">
-        <v>0.0124</v>
-      </c>
-      <c r="BG20" s="11" t="n">
-        <v>-0.04856779498084111</v>
-      </c>
-      <c r="BH20" s="8" t="n">
-        <v>9450707</v>
-      </c>
-      <c r="BI20" s="9" t="n">
-        <v>146920.69</v>
-      </c>
-      <c r="BJ20" s="10" t="n">
-        <v>0.013</v>
-      </c>
       <c r="BK20" s="11" t="n">
-        <v>0.03318890177940083</v>
+        <v>0.0298589752957666</v>
       </c>
       <c r="BL20" s="8" t="n">
-        <v>9147124</v>
+        <v>8881919</v>
       </c>
       <c r="BM20" s="9" t="n">
-        <v>137746.54</v>
+        <v>130182.29</v>
       </c>
       <c r="BN20" s="10" t="n">
         <v>0.0125</v>
       </c>
       <c r="BO20" s="11" t="n">
-        <v>0.0298589752957666</v>
+        <v>0.1110462167918367</v>
       </c>
       <c r="BP20" s="8" t="n">
-        <v>8881919</v>
+        <v>7994194</v>
       </c>
       <c r="BQ20" s="9" t="n">
-        <v>130182.29</v>
+        <v>123918</v>
       </c>
       <c r="BR20" s="10" t="n">
-        <v>0.0125</v>
+        <v>0.0126</v>
       </c>
       <c r="BS20" s="11" t="n">
-        <v>0.1110462167918367</v>
+        <v>0</v>
       </c>
       <c r="BT20" s="8" t="n">
         <v>7994194</v>
       </c>
       <c r="BU20" s="9" t="n">
-        <v>123918</v>
+        <v>115292.27</v>
       </c>
       <c r="BV20" s="10" t="n">
-        <v>0.0126</v>
+        <v>0.0123</v>
       </c>
       <c r="BW20" s="11" t="n">
-        <v>0</v>
+        <v>0.03077033965211765</v>
       </c>
       <c r="BX20" s="8" t="n">
-        <v>7994194</v>
+        <v>7755553</v>
       </c>
       <c r="BY20" s="9" t="n">
-        <v>115292.27</v>
+        <v>109159.41</v>
       </c>
       <c r="BZ20" s="10" t="n">
-        <v>0.0123</v>
+        <v>0.0124</v>
       </c>
       <c r="CA20" s="11" t="n">
-        <v>0.03077033965211765</v>
+        <v>0.2461624388271065</v>
       </c>
       <c r="CB20" s="8" t="n">
-        <v>7755553</v>
+        <v>6223549</v>
       </c>
       <c r="CC20" s="9" t="n">
-        <v>109159.41</v>
+        <v>92071.17999999999</v>
       </c>
       <c r="CD20" s="10" t="n">
-        <v>0.0124</v>
-      </c>
-      <c r="CE20" s="11" t="n">
-        <v>0.2461624388271065</v>
-      </c>
-      <c r="CF20" s="8" t="n">
-        <v>6223549</v>
-      </c>
-      <c r="CG20" s="9" t="n">
-        <v>92071.17999999999</v>
-      </c>
-      <c r="CH20" s="10" t="n">
         <v>0.0103</v>
       </c>
-      <c r="CI20" s="11" t="n"/>
+      <c r="CE20" s="11" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
@@ -5564,180 +5332,168 @@
         <v>13769904</v>
       </c>
       <c r="AC21" s="9" t="n">
-        <v>172798.53</v>
+        <v>177122.28</v>
       </c>
       <c r="AD21" s="10" t="n">
-        <v>0.0134</v>
+        <v>0.0132</v>
       </c>
       <c r="AE21" s="11" t="n">
-        <v>0</v>
+        <v>-0.02223420828005112</v>
       </c>
       <c r="AF21" s="8" t="n">
-        <v>13769904</v>
+        <v>14083029</v>
       </c>
       <c r="AG21" s="9" t="n">
-        <v>177122.28</v>
+        <v>171545.38</v>
       </c>
       <c r="AH21" s="10" t="n">
-        <v>0.0132</v>
+        <v>0.0128</v>
       </c>
       <c r="AI21" s="11" t="n">
-        <v>-0.02223420828005112</v>
+        <v>0.07294813282038955</v>
       </c>
       <c r="AJ21" s="8" t="n">
-        <v>14083029</v>
+        <v>13125545</v>
       </c>
       <c r="AK21" s="9" t="n">
-        <v>171545.38</v>
+        <v>166878.18</v>
       </c>
       <c r="AL21" s="10" t="n">
-        <v>0.0128</v>
+        <v>0.0125</v>
       </c>
       <c r="AM21" s="11" t="n">
-        <v>0.07294813282038955</v>
+        <v>0</v>
       </c>
       <c r="AN21" s="8" t="n">
         <v>13125545</v>
       </c>
       <c r="AO21" s="9" t="n">
-        <v>166878.18</v>
+        <v>165224.36</v>
       </c>
       <c r="AP21" s="10" t="n">
-        <v>0.0125</v>
+        <v>0.0127</v>
       </c>
       <c r="AQ21" s="11" t="n">
-        <v>0</v>
+        <v>0.02739609151703509</v>
       </c>
       <c r="AR21" s="8" t="n">
-        <v>13125545</v>
+        <v>12775545</v>
       </c>
       <c r="AS21" s="9" t="n">
-        <v>165224.36</v>
+        <v>152999.93</v>
       </c>
       <c r="AT21" s="10" t="n">
+        <v>0.0122</v>
+      </c>
+      <c r="AU21" s="11" t="n">
+        <v>0.05513752418556975</v>
+      </c>
+      <c r="AV21" s="8" t="n">
+        <v>12107943</v>
+      </c>
+      <c r="AW21" s="9" t="n">
+        <v>148164.9</v>
+      </c>
+      <c r="AX21" s="10" t="n">
+        <v>0.0124</v>
+      </c>
+      <c r="AY21" s="11" t="n">
+        <v>0.04083231560577577</v>
+      </c>
+      <c r="AZ21" s="8" t="n">
+        <v>11632943</v>
+      </c>
+      <c r="BA21" s="9" t="n">
+        <v>146586.71</v>
+      </c>
+      <c r="BB21" s="10" t="n">
         <v>0.0127</v>
       </c>
-      <c r="AU21" s="11" t="n">
-        <v>0.02739609151703509</v>
-      </c>
-      <c r="AV21" s="8" t="n">
-        <v>12775545</v>
-      </c>
-      <c r="AW21" s="9" t="n">
-        <v>152999.93</v>
-      </c>
-      <c r="AX21" s="10" t="n">
-        <v>0.0122</v>
-      </c>
-      <c r="AY21" s="11" t="n">
-        <v>0.05513752418556975</v>
-      </c>
-      <c r="AZ21" s="8" t="n">
-        <v>12107943</v>
-      </c>
-      <c r="BA21" s="9" t="n">
-        <v>148164.9</v>
-      </c>
-      <c r="BB21" s="10" t="n">
-        <v>0.0124</v>
-      </c>
       <c r="BC21" s="11" t="n">
-        <v>0.04083231560577577</v>
+        <v>0.037023978878946</v>
       </c>
       <c r="BD21" s="8" t="n">
-        <v>11632943</v>
+        <v>11217622</v>
       </c>
       <c r="BE21" s="9" t="n">
-        <v>146586.71</v>
+        <v>142497.45</v>
       </c>
       <c r="BF21" s="10" t="n">
-        <v>0.0127</v>
+        <v>0.0126</v>
       </c>
       <c r="BG21" s="11" t="n">
-        <v>0.037023978878946</v>
+        <v>0.08471904462602137</v>
       </c>
       <c r="BH21" s="8" t="n">
-        <v>11217622</v>
+        <v>10341500</v>
       </c>
       <c r="BI21" s="9" t="n">
-        <v>142497.45</v>
+        <v>132712.47</v>
       </c>
       <c r="BJ21" s="10" t="n">
-        <v>0.0126</v>
+        <v>0.012</v>
       </c>
       <c r="BK21" s="11" t="n">
-        <v>0.08471904462602137</v>
+        <v>0</v>
       </c>
       <c r="BL21" s="8" t="n">
         <v>10341500</v>
       </c>
       <c r="BM21" s="9" t="n">
-        <v>132712.47</v>
+        <v>129392.85</v>
       </c>
       <c r="BN21" s="10" t="n">
-        <v>0.012</v>
+        <v>0.0125</v>
       </c>
       <c r="BO21" s="11" t="n">
-        <v>0</v>
+        <v>-0.005975775856020039</v>
       </c>
       <c r="BP21" s="8" t="n">
-        <v>10341500</v>
+        <v>10403670</v>
       </c>
       <c r="BQ21" s="9" t="n">
-        <v>129392.85</v>
+        <v>123169.05</v>
       </c>
       <c r="BR21" s="10" t="n">
         <v>0.0125</v>
       </c>
       <c r="BS21" s="11" t="n">
-        <v>-0.005975775856020039</v>
+        <v>0.02666147990782253</v>
       </c>
       <c r="BT21" s="8" t="n">
-        <v>10403670</v>
+        <v>10133496</v>
       </c>
       <c r="BU21" s="9" t="n">
-        <v>123169.05</v>
+        <v>115947.46</v>
       </c>
       <c r="BV21" s="10" t="n">
-        <v>0.0125</v>
+        <v>0.0124</v>
       </c>
       <c r="BW21" s="11" t="n">
-        <v>0.02666147990782253</v>
+        <v>0.02236244056730923</v>
       </c>
       <c r="BX21" s="8" t="n">
-        <v>10133496</v>
+        <v>9911843</v>
       </c>
       <c r="BY21" s="9" t="n">
-        <v>115947.46</v>
+        <v>110665.73</v>
       </c>
       <c r="BZ21" s="10" t="n">
-        <v>0.0124</v>
+        <v>0.0126</v>
       </c>
       <c r="CA21" s="11" t="n">
-        <v>0.02236244056730923</v>
+        <v>0.3415700706027321</v>
       </c>
       <c r="CB21" s="8" t="n">
-        <v>9911843</v>
+        <v>7388241</v>
       </c>
       <c r="CC21" s="9" t="n">
-        <v>110665.73</v>
+        <v>89940.75</v>
       </c>
       <c r="CD21" s="10" t="n">
-        <v>0.0126</v>
-      </c>
-      <c r="CE21" s="11" t="n">
-        <v>0.3415700706027321</v>
-      </c>
-      <c r="CF21" s="8" t="n">
-        <v>7388241</v>
-      </c>
-      <c r="CG21" s="9" t="n">
-        <v>89940.75</v>
-      </c>
-      <c r="CH21" s="10" t="n">
         <v>0.01</v>
       </c>
-      <c r="CI21" s="11" t="n"/>
+      <c r="CE21" s="11" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -5825,32 +5581,24 @@
         <v>0.0045</v>
       </c>
       <c r="AA22" s="11" t="n">
-        <v>77.70472532588454</v>
+        <v>131.346858464915</v>
       </c>
       <c r="AB22" s="8" t="n">
-        <v>481152</v>
+        <v>286134</v>
       </c>
       <c r="AC22" s="9" t="n">
-        <v>700.65</v>
+        <v>488.89</v>
       </c>
       <c r="AD22" s="10" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="AE22" s="11" t="n">
-        <v>0.6815617857367527</v>
-      </c>
-      <c r="AF22" s="8" t="n">
-        <v>286134</v>
-      </c>
-      <c r="AG22" s="9" t="n">
-        <v>488.89</v>
-      </c>
-      <c r="AH22" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI22" s="11" t="n">
         <v>1</v>
       </c>
+      <c r="AF22" s="8" t="n"/>
+      <c r="AG22" s="9" t="n"/>
+      <c r="AH22" s="10" t="n"/>
+      <c r="AI22" s="11" t="n"/>
       <c r="AJ22" s="8" t="n"/>
       <c r="AK22" s="9" t="n"/>
       <c r="AL22" s="10" t="n"/>
@@ -5899,10 +5647,6 @@
       <c r="CC22" s="9" t="n"/>
       <c r="CD22" s="10" t="n"/>
       <c r="CE22" s="11" t="n"/>
-      <c r="CF22" s="8" t="n"/>
-      <c r="CG22" s="9" t="n"/>
-      <c r="CH22" s="10" t="n"/>
-      <c r="CI22" s="11" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -5990,40 +5734,40 @@
         <v>0.008</v>
       </c>
       <c r="AA23" s="11" t="n">
-        <v>0</v>
+        <v>0.003718720983944644</v>
       </c>
       <c r="AB23" s="8" t="n">
-        <v>22157154</v>
+        <v>22075063</v>
       </c>
       <c r="AC23" s="9" t="n">
-        <v>94467.03</v>
+        <v>84966.92</v>
       </c>
       <c r="AD23" s="10" t="n">
-        <v>0.0073</v>
+        <v>0.0063</v>
       </c>
       <c r="AE23" s="11" t="n">
-        <v>0.003718720983944644</v>
+        <v>0.003411954545454545</v>
       </c>
       <c r="AF23" s="8" t="n">
-        <v>22075063</v>
+        <v>22000000</v>
       </c>
       <c r="AG23" s="9" t="n">
-        <v>84966.92</v>
+        <v>98626</v>
       </c>
       <c r="AH23" s="10" t="n">
-        <v>0.0063</v>
+        <v>0.0074</v>
       </c>
       <c r="AI23" s="11" t="n">
-        <v>0.003411954545454545</v>
+        <v>0</v>
       </c>
       <c r="AJ23" s="8" t="n">
         <v>22000000</v>
       </c>
       <c r="AK23" s="9" t="n">
-        <v>98626</v>
+        <v>100012</v>
       </c>
       <c r="AL23" s="10" t="n">
-        <v>0.0074</v>
+        <v>0.0075</v>
       </c>
       <c r="AM23" s="11" t="n">
         <v>0</v>
@@ -6032,10 +5776,10 @@
         <v>22000000</v>
       </c>
       <c r="AO23" s="9" t="n">
-        <v>100012</v>
+        <v>94699</v>
       </c>
       <c r="AP23" s="10" t="n">
-        <v>0.0075</v>
+        <v>0.0073</v>
       </c>
       <c r="AQ23" s="11" t="n">
         <v>0</v>
@@ -6044,10 +5788,10 @@
         <v>22000000</v>
       </c>
       <c r="AS23" s="9" t="n">
-        <v>94699</v>
+        <v>104852</v>
       </c>
       <c r="AT23" s="10" t="n">
-        <v>0.0073</v>
+        <v>0.0083</v>
       </c>
       <c r="AU23" s="11" t="n">
         <v>0</v>
@@ -6056,26 +5800,18 @@
         <v>22000000</v>
       </c>
       <c r="AW23" s="9" t="n">
-        <v>104852</v>
+        <v>100584</v>
       </c>
       <c r="AX23" s="10" t="n">
-        <v>0.0083</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ23" s="8" t="n">
-        <v>22000000</v>
-      </c>
-      <c r="BA23" s="9" t="n">
-        <v>100584</v>
-      </c>
-      <c r="BB23" s="10" t="n">
-        <v>0.008399999999999999</v>
-      </c>
-      <c r="BC23" s="11" t="n">
         <v>1</v>
       </c>
+      <c r="AZ23" s="8" t="n"/>
+      <c r="BA23" s="9" t="n"/>
+      <c r="BB23" s="10" t="n"/>
+      <c r="BC23" s="11" t="n"/>
       <c r="BD23" s="8" t="n"/>
       <c r="BE23" s="9" t="n"/>
       <c r="BF23" s="10" t="n"/>
@@ -6104,10 +5840,6 @@
       <c r="CC23" s="9" t="n"/>
       <c r="CD23" s="10" t="n"/>
       <c r="CE23" s="11" t="n"/>
-      <c r="CF23" s="8" t="n"/>
-      <c r="CG23" s="9" t="n"/>
-      <c r="CH23" s="10" t="n"/>
-      <c r="CI23" s="11" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -6201,10 +5933,10 @@
         <v>80755676</v>
       </c>
       <c r="AC24" s="9" t="n">
-        <v>92667.14</v>
+        <v>101461.43</v>
       </c>
       <c r="AD24" s="10" t="n">
-        <v>0.0072</v>
+        <v>0.0076</v>
       </c>
       <c r="AE24" s="11" t="n">
         <v>0</v>
@@ -6213,7 +5945,7 @@
         <v>80755676</v>
       </c>
       <c r="AG24" s="9" t="n">
-        <v>101461.43</v>
+        <v>102390.12</v>
       </c>
       <c r="AH24" s="10" t="n">
         <v>0.0076</v>
@@ -6225,10 +5957,10 @@
         <v>80755676</v>
       </c>
       <c r="AK24" s="9" t="n">
-        <v>102390.12</v>
+        <v>108390.27</v>
       </c>
       <c r="AL24" s="10" t="n">
-        <v>0.0076</v>
+        <v>0.0081</v>
       </c>
       <c r="AM24" s="11" t="n">
         <v>0</v>
@@ -6237,10 +5969,10 @@
         <v>80755676</v>
       </c>
       <c r="AO24" s="9" t="n">
-        <v>108390.27</v>
+        <v>112484.58</v>
       </c>
       <c r="AP24" s="10" t="n">
-        <v>0.0081</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="AQ24" s="11" t="n">
         <v>0</v>
@@ -6249,10 +5981,10 @@
         <v>80755676</v>
       </c>
       <c r="AS24" s="9" t="n">
-        <v>112484.58</v>
+        <v>112298.84</v>
       </c>
       <c r="AT24" s="10" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.0089</v>
       </c>
       <c r="AU24" s="11" t="n">
         <v>0</v>
@@ -6261,46 +5993,46 @@
         <v>80755676</v>
       </c>
       <c r="AW24" s="9" t="n">
-        <v>112298.84</v>
+        <v>112403.83</v>
       </c>
       <c r="AX24" s="10" t="n">
+        <v>0.0094</v>
+      </c>
+      <c r="AY24" s="11" t="n">
+        <v>0.09854178046374168</v>
+      </c>
+      <c r="AZ24" s="8" t="n">
+        <v>73511702</v>
+      </c>
+      <c r="BA24" s="9" t="n">
+        <v>102769.36</v>
+      </c>
+      <c r="BB24" s="10" t="n">
         <v>0.0089</v>
       </c>
-      <c r="AY24" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ24" s="8" t="n">
-        <v>80755676</v>
-      </c>
-      <c r="BA24" s="9" t="n">
-        <v>112403.83</v>
-      </c>
-      <c r="BB24" s="10" t="n">
-        <v>0.0094</v>
-      </c>
       <c r="BC24" s="11" t="n">
-        <v>0.09854178046374168</v>
+        <v>0.6629129724205788</v>
       </c>
       <c r="BD24" s="8" t="n">
-        <v>73511702</v>
+        <v>44206584</v>
       </c>
       <c r="BE24" s="9" t="n">
-        <v>102769.36</v>
+        <v>59811.51</v>
       </c>
       <c r="BF24" s="10" t="n">
-        <v>0.0089</v>
+        <v>0.0053</v>
       </c>
       <c r="BG24" s="11" t="n">
-        <v>0.6629129724205788</v>
+        <v>0</v>
       </c>
       <c r="BH24" s="8" t="n">
         <v>44206584</v>
       </c>
       <c r="BI24" s="9" t="n">
-        <v>59811.51</v>
+        <v>85367.33</v>
       </c>
       <c r="BJ24" s="10" t="n">
-        <v>0.0053</v>
+        <v>0.0077</v>
       </c>
       <c r="BK24" s="11" t="n">
         <v>0</v>
@@ -6309,10 +6041,10 @@
         <v>44206584</v>
       </c>
       <c r="BM24" s="9" t="n">
-        <v>85367.33</v>
+        <v>88656.3</v>
       </c>
       <c r="BN24" s="10" t="n">
-        <v>0.0077</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="BO24" s="11" t="n">
         <v>0</v>
@@ -6321,7 +6053,7 @@
         <v>44206584</v>
       </c>
       <c r="BQ24" s="9" t="n">
-        <v>88656.3</v>
+        <v>84147.23</v>
       </c>
       <c r="BR24" s="10" t="n">
         <v>0.008500000000000001</v>
@@ -6333,10 +6065,10 @@
         <v>44206584</v>
       </c>
       <c r="BU24" s="9" t="n">
-        <v>84147.23</v>
+        <v>77701.91</v>
       </c>
       <c r="BV24" s="10" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.0083</v>
       </c>
       <c r="BW24" s="11" t="n">
         <v>0</v>
@@ -6345,10 +6077,10 @@
         <v>44206584</v>
       </c>
       <c r="BY24" s="9" t="n">
-        <v>77701.91</v>
+        <v>68931.33</v>
       </c>
       <c r="BZ24" s="10" t="n">
-        <v>0.0083</v>
+        <v>0.0078</v>
       </c>
       <c r="CA24" s="11" t="n">
         <v>0</v>
@@ -6357,24 +6089,12 @@
         <v>44206584</v>
       </c>
       <c r="CC24" s="9" t="n">
-        <v>68931.33</v>
+        <v>77184.7</v>
       </c>
       <c r="CD24" s="10" t="n">
-        <v>0.0078</v>
-      </c>
-      <c r="CE24" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF24" s="8" t="n">
-        <v>44206584</v>
-      </c>
-      <c r="CG24" s="9" t="n">
-        <v>77184.7</v>
-      </c>
-      <c r="CH24" s="10" t="n">
         <v>0.0086</v>
       </c>
-      <c r="CI24" s="11" t="n"/>
+      <c r="CE24" s="11" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
@@ -6504,10 +6224,6 @@
       <c r="CC25" s="9" t="n"/>
       <c r="CD25" s="10" t="n"/>
       <c r="CE25" s="11" t="n"/>
-      <c r="CF25" s="8" t="n"/>
-      <c r="CG25" s="9" t="n"/>
-      <c r="CH25" s="10" t="n"/>
-      <c r="CI25" s="11" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
@@ -6601,180 +6317,168 @@
         <v>7394472</v>
       </c>
       <c r="AC26" s="9" t="n">
-        <v>57344.13</v>
+        <v>63976.97</v>
       </c>
       <c r="AD26" s="10" t="n">
-        <v>0.0044</v>
+        <v>0.0048</v>
       </c>
       <c r="AE26" s="11" t="n">
-        <v>0</v>
+        <v>0.004287575158874156</v>
       </c>
       <c r="AF26" s="8" t="n">
-        <v>7394472</v>
+        <v>7362903</v>
       </c>
       <c r="AG26" s="9" t="n">
-        <v>63976.97</v>
+        <v>67966.96000000001</v>
       </c>
       <c r="AH26" s="10" t="n">
+        <v>0.0051</v>
+      </c>
+      <c r="AI26" s="11" t="n">
+        <v>0.1913802993295465</v>
+      </c>
+      <c r="AJ26" s="8" t="n">
+        <v>6180145</v>
+      </c>
+      <c r="AK26" s="9" t="n">
+        <v>63945.96</v>
+      </c>
+      <c r="AL26" s="10" t="n">
         <v>0.0048</v>
       </c>
-      <c r="AI26" s="11" t="n">
-        <v>0.004287575158874156</v>
-      </c>
-      <c r="AJ26" s="8" t="n">
-        <v>7362903</v>
-      </c>
-      <c r="AK26" s="9" t="n">
-        <v>67966.96000000001</v>
-      </c>
-      <c r="AL26" s="10" t="n">
-        <v>0.0051</v>
-      </c>
       <c r="AM26" s="11" t="n">
-        <v>0.1913802993295465</v>
+        <v>0.05773144178420389</v>
       </c>
       <c r="AN26" s="8" t="n">
-        <v>6180145</v>
+        <v>5842830</v>
       </c>
       <c r="AO26" s="9" t="n">
-        <v>63945.96</v>
+        <v>60233.73</v>
       </c>
       <c r="AP26" s="10" t="n">
-        <v>0.0048</v>
+        <v>0.0046</v>
       </c>
       <c r="AQ26" s="11" t="n">
-        <v>0.05773144178420389</v>
+        <v>0.05688668625904227</v>
       </c>
       <c r="AR26" s="8" t="n">
-        <v>5842830</v>
+        <v>5528341</v>
       </c>
       <c r="AS26" s="9" t="n">
-        <v>60233.73</v>
+        <v>59285.93</v>
       </c>
       <c r="AT26" s="10" t="n">
-        <v>0.0046</v>
+        <v>0.0047</v>
       </c>
       <c r="AU26" s="11" t="n">
-        <v>0.05688668625904227</v>
+        <v>0.1065051605034048</v>
       </c>
       <c r="AV26" s="8" t="n">
-        <v>5528341</v>
+        <v>4996218</v>
       </c>
       <c r="AW26" s="9" t="n">
-        <v>59285.93</v>
+        <v>51236.22</v>
       </c>
       <c r="AX26" s="10" t="n">
-        <v>0.0047</v>
+        <v>0.0043</v>
       </c>
       <c r="AY26" s="11" t="n">
-        <v>0.1065051605034048</v>
+        <v>0.1269063080091213</v>
       </c>
       <c r="AZ26" s="8" t="n">
-        <v>4996218</v>
+        <v>4433570</v>
       </c>
       <c r="BA26" s="9" t="n">
-        <v>51236.22</v>
+        <v>49913.13</v>
       </c>
       <c r="BB26" s="10" t="n">
         <v>0.0043</v>
       </c>
       <c r="BC26" s="11" t="n">
-        <v>0.1269063080091213</v>
+        <v>0.1091786303542636</v>
       </c>
       <c r="BD26" s="8" t="n">
-        <v>4433570</v>
+        <v>3997165</v>
       </c>
       <c r="BE26" s="9" t="n">
-        <v>49913.13</v>
+        <v>49305.03</v>
       </c>
       <c r="BF26" s="10" t="n">
-        <v>0.0043</v>
+        <v>0.0044</v>
       </c>
       <c r="BG26" s="11" t="n">
-        <v>0.1091786303542636</v>
+        <v>0.136585363079533</v>
       </c>
       <c r="BH26" s="8" t="n">
-        <v>3997165</v>
+        <v>3516819</v>
       </c>
       <c r="BI26" s="9" t="n">
-        <v>49305.03</v>
+        <v>39036.69</v>
       </c>
       <c r="BJ26" s="10" t="n">
-        <v>0.0044</v>
+        <v>0.0035</v>
       </c>
       <c r="BK26" s="11" t="n">
-        <v>0.136585363079533</v>
+        <v>0.08443118240843069</v>
       </c>
       <c r="BL26" s="8" t="n">
-        <v>3516819</v>
+        <v>3243008</v>
       </c>
       <c r="BM26" s="9" t="n">
-        <v>39036.69</v>
+        <v>30813.44</v>
       </c>
       <c r="BN26" s="10" t="n">
-        <v>0.0035</v>
+        <v>0.003</v>
       </c>
       <c r="BO26" s="11" t="n">
-        <v>0.08443118240843069</v>
+        <v>0.08526813218218672</v>
       </c>
       <c r="BP26" s="8" t="n">
-        <v>3243008</v>
+        <v>2988209</v>
       </c>
       <c r="BQ26" s="9" t="n">
-        <v>30813.44</v>
+        <v>24424.13</v>
       </c>
       <c r="BR26" s="10" t="n">
-        <v>0.003</v>
+        <v>0.0025</v>
       </c>
       <c r="BS26" s="11" t="n">
-        <v>0.08526813218218672</v>
+        <v>0.05097801295341799</v>
       </c>
       <c r="BT26" s="8" t="n">
-        <v>2988209</v>
+        <v>2843265</v>
       </c>
       <c r="BU26" s="9" t="n">
-        <v>24424.13</v>
+        <v>22336.69</v>
       </c>
       <c r="BV26" s="10" t="n">
-        <v>0.0025</v>
+        <v>0.0024</v>
       </c>
       <c r="BW26" s="11" t="n">
-        <v>0.05097801295341799</v>
+        <v>0.08976771675272589</v>
       </c>
       <c r="BX26" s="8" t="n">
-        <v>2843265</v>
+        <v>2609056</v>
       </c>
       <c r="BY26" s="9" t="n">
-        <v>22336.69</v>
+        <v>17326.74</v>
       </c>
       <c r="BZ26" s="10" t="n">
-        <v>0.0024</v>
+        <v>0.002</v>
       </c>
       <c r="CA26" s="11" t="n">
-        <v>0.08976771675272589</v>
+        <v>0.1546891810734174</v>
       </c>
       <c r="CB26" s="8" t="n">
-        <v>2609056</v>
+        <v>2259531</v>
       </c>
       <c r="CC26" s="9" t="n">
-        <v>17326.74</v>
+        <v>18525.89</v>
       </c>
       <c r="CD26" s="10" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="CE26" s="11" t="n">
-        <v>0.1546891810734174</v>
-      </c>
-      <c r="CF26" s="8" t="n">
-        <v>2259531</v>
-      </c>
-      <c r="CG26" s="9" t="n">
-        <v>18525.89</v>
-      </c>
-      <c r="CH26" s="10" t="n">
         <v>0.0021</v>
       </c>
-      <c r="CI26" s="11" t="n"/>
+      <c r="CE26" s="11" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
@@ -6862,32 +6566,24 @@
         <v>0.0003</v>
       </c>
       <c r="AA27" s="11" t="n">
-        <v>6.08421151852201</v>
+        <v>122.4095238095238</v>
       </c>
       <c r="AB27" s="8" t="n">
-        <v>53045</v>
+        <v>3045</v>
       </c>
       <c r="AC27" s="9" t="n">
-        <v>492.1</v>
+        <v>37.14</v>
       </c>
       <c r="AD27" s="10" t="n">
         <v>0</v>
       </c>
       <c r="AE27" s="11" t="n">
-        <v>16.42036124794745</v>
-      </c>
-      <c r="AF27" s="8" t="n">
-        <v>3045</v>
-      </c>
-      <c r="AG27" s="9" t="n">
-        <v>37.14</v>
-      </c>
-      <c r="AH27" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI27" s="11" t="n">
         <v>1</v>
       </c>
+      <c r="AF27" s="8" t="n"/>
+      <c r="AG27" s="9" t="n"/>
+      <c r="AH27" s="10" t="n"/>
+      <c r="AI27" s="11" t="n"/>
       <c r="AJ27" s="8" t="n"/>
       <c r="AK27" s="9" t="n"/>
       <c r="AL27" s="10" t="n"/>
@@ -6936,10 +6632,6 @@
       <c r="CC27" s="9" t="n"/>
       <c r="CD27" s="10" t="n"/>
       <c r="CE27" s="11" t="n"/>
-      <c r="CF27" s="8" t="n"/>
-      <c r="CG27" s="9" t="n"/>
-      <c r="CH27" s="10" t="n"/>
-      <c r="CI27" s="11" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -7033,10 +6725,10 @@
         <v>1995914</v>
       </c>
       <c r="AC28" s="9" t="n">
-        <v>32040.41</v>
+        <v>36543.19</v>
       </c>
       <c r="AD28" s="10" t="n">
-        <v>0.0025</v>
+        <v>0.0027</v>
       </c>
       <c r="AE28" s="11" t="n">
         <v>0</v>
@@ -7045,10 +6737,10 @@
         <v>1995914</v>
       </c>
       <c r="AG28" s="9" t="n">
-        <v>36543.19</v>
+        <v>35285.76</v>
       </c>
       <c r="AH28" s="10" t="n">
-        <v>0.0027</v>
+        <v>0.0026</v>
       </c>
       <c r="AI28" s="11" t="n">
         <v>0</v>
@@ -7057,10 +6749,10 @@
         <v>1995914</v>
       </c>
       <c r="AK28" s="9" t="n">
-        <v>35285.76</v>
+        <v>37762.69</v>
       </c>
       <c r="AL28" s="10" t="n">
-        <v>0.0026</v>
+        <v>0.0028</v>
       </c>
       <c r="AM28" s="11" t="n">
         <v>0</v>
@@ -7069,10 +6761,10 @@
         <v>1995914</v>
       </c>
       <c r="AO28" s="9" t="n">
-        <v>37762.69</v>
+        <v>38830.51</v>
       </c>
       <c r="AP28" s="10" t="n">
-        <v>0.0028</v>
+        <v>0.003</v>
       </c>
       <c r="AQ28" s="11" t="n">
         <v>0</v>
@@ -7081,10 +6773,10 @@
         <v>1995914</v>
       </c>
       <c r="AS28" s="9" t="n">
-        <v>38830.51</v>
+        <v>35076.19</v>
       </c>
       <c r="AT28" s="10" t="n">
-        <v>0.003</v>
+        <v>0.0028</v>
       </c>
       <c r="AU28" s="11" t="n">
         <v>0</v>
@@ -7093,10 +6785,10 @@
         <v>1995914</v>
       </c>
       <c r="AW28" s="9" t="n">
-        <v>35076.19</v>
+        <v>34681</v>
       </c>
       <c r="AX28" s="10" t="n">
-        <v>0.0028</v>
+        <v>0.0029</v>
       </c>
       <c r="AY28" s="11" t="n">
         <v>0</v>
@@ -7105,10 +6797,10 @@
         <v>1995914</v>
       </c>
       <c r="BA28" s="9" t="n">
-        <v>34681</v>
+        <v>35004.34</v>
       </c>
       <c r="BB28" s="10" t="n">
-        <v>0.0029</v>
+        <v>0.003</v>
       </c>
       <c r="BC28" s="11" t="n">
         <v>0</v>
@@ -7117,10 +6809,10 @@
         <v>1995914</v>
       </c>
       <c r="BE28" s="9" t="n">
-        <v>35004.34</v>
+        <v>38225.74</v>
       </c>
       <c r="BF28" s="10" t="n">
-        <v>0.003</v>
+        <v>0.0034</v>
       </c>
       <c r="BG28" s="11" t="n">
         <v>0</v>
@@ -7129,10 +6821,10 @@
         <v>1995914</v>
       </c>
       <c r="BI28" s="9" t="n">
-        <v>38225.74</v>
+        <v>43319.32</v>
       </c>
       <c r="BJ28" s="10" t="n">
-        <v>0.0034</v>
+        <v>0.0039</v>
       </c>
       <c r="BK28" s="11" t="n">
         <v>0</v>
@@ -7141,10 +6833,10 @@
         <v>1995914</v>
       </c>
       <c r="BM28" s="9" t="n">
-        <v>43319.32</v>
+        <v>34806.74</v>
       </c>
       <c r="BN28" s="10" t="n">
-        <v>0.0039</v>
+        <v>0.0034</v>
       </c>
       <c r="BO28" s="11" t="n">
         <v>0</v>
@@ -7153,10 +6845,10 @@
         <v>1995914</v>
       </c>
       <c r="BQ28" s="9" t="n">
-        <v>34806.74</v>
+        <v>35138.07</v>
       </c>
       <c r="BR28" s="10" t="n">
-        <v>0.0034</v>
+        <v>0.0036</v>
       </c>
       <c r="BS28" s="11" t="n">
         <v>0</v>
@@ -7165,7 +6857,7 @@
         <v>1995914</v>
       </c>
       <c r="BU28" s="9" t="n">
-        <v>35138.07</v>
+        <v>33771.86</v>
       </c>
       <c r="BV28" s="10" t="n">
         <v>0.0036</v>
@@ -7177,10 +6869,10 @@
         <v>1995914</v>
       </c>
       <c r="BY28" s="9" t="n">
-        <v>33771.86</v>
+        <v>28830.98</v>
       </c>
       <c r="BZ28" s="10" t="n">
-        <v>0.0036</v>
+        <v>0.0033</v>
       </c>
       <c r="CA28" s="11" t="n">
         <v>0</v>
@@ -7189,24 +6881,12 @@
         <v>1995914</v>
       </c>
       <c r="CC28" s="9" t="n">
-        <v>28830.98</v>
+        <v>27686.32</v>
       </c>
       <c r="CD28" s="10" t="n">
-        <v>0.0033</v>
-      </c>
-      <c r="CE28" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF28" s="8" t="n">
-        <v>1995914</v>
-      </c>
-      <c r="CG28" s="9" t="n">
-        <v>27686.32</v>
-      </c>
-      <c r="CH28" s="10" t="n">
         <v>0.0031</v>
       </c>
-      <c r="CI28" s="11" t="n"/>
+      <c r="CE28" s="11" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -7300,10 +6980,10 @@
         <v>2264603</v>
       </c>
       <c r="AC29" s="9" t="n">
-        <v>25349.97</v>
+        <v>28810.28</v>
       </c>
       <c r="AD29" s="10" t="n">
-        <v>0.002</v>
+        <v>0.0021</v>
       </c>
       <c r="AE29" s="11" t="n">
         <v>0</v>
@@ -7312,10 +6992,10 @@
         <v>2264603</v>
       </c>
       <c r="AG29" s="9" t="n">
-        <v>28810.28</v>
+        <v>29897.29</v>
       </c>
       <c r="AH29" s="10" t="n">
-        <v>0.0021</v>
+        <v>0.0022</v>
       </c>
       <c r="AI29" s="11" t="n">
         <v>0</v>
@@ -7324,10 +7004,10 @@
         <v>2264603</v>
       </c>
       <c r="AK29" s="9" t="n">
-        <v>29897.29</v>
+        <v>32691.81</v>
       </c>
       <c r="AL29" s="10" t="n">
-        <v>0.0022</v>
+        <v>0.0025</v>
       </c>
       <c r="AM29" s="11" t="n">
         <v>0</v>
@@ -7336,10 +7016,10 @@
         <v>2264603</v>
       </c>
       <c r="AO29" s="9" t="n">
-        <v>32691.81</v>
+        <v>36623.16</v>
       </c>
       <c r="AP29" s="10" t="n">
-        <v>0.0025</v>
+        <v>0.0028</v>
       </c>
       <c r="AQ29" s="11" t="n">
         <v>0</v>
@@ -7348,10 +7028,10 @@
         <v>2264603</v>
       </c>
       <c r="AS29" s="9" t="n">
-        <v>36623.16</v>
+        <v>35943.78</v>
       </c>
       <c r="AT29" s="10" t="n">
-        <v>0.0028</v>
+        <v>0.0029</v>
       </c>
       <c r="AU29" s="11" t="n">
         <v>0</v>
@@ -7360,10 +7040,10 @@
         <v>2264603</v>
       </c>
       <c r="AW29" s="9" t="n">
-        <v>35943.78</v>
+        <v>33031.5</v>
       </c>
       <c r="AX29" s="10" t="n">
-        <v>0.0029</v>
+        <v>0.0028</v>
       </c>
       <c r="AY29" s="11" t="n">
         <v>0</v>
@@ -7372,7 +7052,7 @@
         <v>2264603</v>
       </c>
       <c r="BA29" s="9" t="n">
-        <v>33031.5</v>
+        <v>32257.01</v>
       </c>
       <c r="BB29" s="10" t="n">
         <v>0.0028</v>
@@ -7384,10 +7064,10 @@
         <v>2264603</v>
       </c>
       <c r="BE29" s="9" t="n">
-        <v>32257.01</v>
+        <v>33534.24</v>
       </c>
       <c r="BF29" s="10" t="n">
-        <v>0.0028</v>
+        <v>0.003</v>
       </c>
       <c r="BG29" s="11" t="n">
         <v>0</v>
@@ -7396,10 +7076,10 @@
         <v>2264603</v>
       </c>
       <c r="BI29" s="9" t="n">
-        <v>33534.24</v>
+        <v>40626.98</v>
       </c>
       <c r="BJ29" s="10" t="n">
-        <v>0.003</v>
+        <v>0.0037</v>
       </c>
       <c r="BK29" s="11" t="n">
         <v>0</v>
@@ -7408,10 +7088,10 @@
         <v>2264603</v>
       </c>
       <c r="BM29" s="9" t="n">
-        <v>40626.98</v>
+        <v>34641.63</v>
       </c>
       <c r="BN29" s="10" t="n">
-        <v>0.0037</v>
+        <v>0.0033</v>
       </c>
       <c r="BO29" s="11" t="n">
         <v>0</v>
@@ -7420,10 +7100,10 @@
         <v>2264603</v>
       </c>
       <c r="BQ29" s="9" t="n">
-        <v>34641.63</v>
+        <v>29892.76</v>
       </c>
       <c r="BR29" s="10" t="n">
-        <v>0.0033</v>
+        <v>0.003</v>
       </c>
       <c r="BS29" s="11" t="n">
         <v>0</v>
@@ -7432,7 +7112,7 @@
         <v>2264603</v>
       </c>
       <c r="BU29" s="9" t="n">
-        <v>29892.76</v>
+        <v>27629.29</v>
       </c>
       <c r="BV29" s="10" t="n">
         <v>0.003</v>
@@ -7444,10 +7124,10 @@
         <v>2264603</v>
       </c>
       <c r="BY29" s="9" t="n">
-        <v>27629.29</v>
+        <v>25089.54</v>
       </c>
       <c r="BZ29" s="10" t="n">
-        <v>0.003</v>
+        <v>0.0029</v>
       </c>
       <c r="CA29" s="11" t="n">
         <v>0</v>
@@ -7456,24 +7136,12 @@
         <v>2264603</v>
       </c>
       <c r="CC29" s="9" t="n">
-        <v>25089.54</v>
+        <v>29659.51</v>
       </c>
       <c r="CD29" s="10" t="n">
-        <v>0.0029</v>
-      </c>
-      <c r="CE29" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF29" s="8" t="n">
-        <v>2264603</v>
-      </c>
-      <c r="CG29" s="9" t="n">
-        <v>29659.51</v>
-      </c>
-      <c r="CH29" s="10" t="n">
         <v>0.0033</v>
       </c>
-      <c r="CI29" s="11" t="n"/>
+      <c r="CE29" s="11" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
@@ -7567,7 +7235,7 @@
         <v>710855</v>
       </c>
       <c r="AC30" s="9" t="n">
-        <v>2972.44</v>
+        <v>3234.03</v>
       </c>
       <c r="AD30" s="10" t="n">
         <v>0.0002</v>
@@ -7579,7 +7247,7 @@
         <v>710855</v>
       </c>
       <c r="AG30" s="9" t="n">
-        <v>3234.03</v>
+        <v>3158.33</v>
       </c>
       <c r="AH30" s="10" t="n">
         <v>0.0002</v>
@@ -7591,7 +7259,7 @@
         <v>710855</v>
       </c>
       <c r="AK30" s="9" t="n">
-        <v>3158.33</v>
+        <v>2976.71</v>
       </c>
       <c r="AL30" s="10" t="n">
         <v>0.0002</v>
@@ -7603,26 +7271,18 @@
         <v>710855</v>
       </c>
       <c r="AO30" s="9" t="n">
-        <v>2976.71</v>
+        <v>2850.8839775</v>
       </c>
       <c r="AP30" s="10" t="n">
         <v>0.0002</v>
       </c>
       <c r="AQ30" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR30" s="8" t="n">
-        <v>710855</v>
-      </c>
-      <c r="AS30" s="9" t="n">
-        <v>2850.8839775</v>
-      </c>
-      <c r="AT30" s="10" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="AU30" s="11" t="n">
         <v>1</v>
       </c>
+      <c r="AR30" s="8" t="n"/>
+      <c r="AS30" s="9" t="n"/>
+      <c r="AT30" s="10" t="n"/>
+      <c r="AU30" s="11" t="n"/>
       <c r="AV30" s="8" t="n"/>
       <c r="AW30" s="9" t="n"/>
       <c r="AX30" s="10" t="n"/>
@@ -7659,10 +7319,6 @@
       <c r="CC30" s="9" t="n"/>
       <c r="CD30" s="10" t="n"/>
       <c r="CE30" s="11" t="n"/>
-      <c r="CF30" s="8" t="n"/>
-      <c r="CG30" s="9" t="n"/>
-      <c r="CH30" s="10" t="n"/>
-      <c r="CI30" s="11" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
@@ -7756,38 +7412,30 @@
         <v>464063</v>
       </c>
       <c r="AC31" s="9" t="n">
-        <v>2065.08</v>
+        <v>2188.75</v>
       </c>
       <c r="AD31" s="10" t="n">
         <v>0.0002</v>
       </c>
       <c r="AE31" s="11" t="n">
-        <v>0</v>
+        <v>0.004302331872531515</v>
       </c>
       <c r="AF31" s="8" t="n">
-        <v>464063</v>
+        <v>462075</v>
       </c>
       <c r="AG31" s="9" t="n">
-        <v>2188.75</v>
+        <v>1932.4</v>
       </c>
       <c r="AH31" s="10" t="n">
-        <v>0.0002</v>
+        <v>0.0001</v>
       </c>
       <c r="AI31" s="11" t="n">
-        <v>0.004302331872531515</v>
-      </c>
-      <c r="AJ31" s="8" t="n">
-        <v>462075</v>
-      </c>
-      <c r="AK31" s="9" t="n">
-        <v>1932.4</v>
-      </c>
-      <c r="AL31" s="10" t="n">
-        <v>0.0001</v>
-      </c>
-      <c r="AM31" s="11" t="n">
         <v>1</v>
       </c>
+      <c r="AJ31" s="8" t="n"/>
+      <c r="AK31" s="9" t="n"/>
+      <c r="AL31" s="10" t="n"/>
+      <c r="AM31" s="11" t="n"/>
       <c r="AN31" s="8" t="n"/>
       <c r="AO31" s="9" t="n"/>
       <c r="AP31" s="10" t="n"/>
@@ -7832,10 +7480,6 @@
       <c r="CC31" s="9" t="n"/>
       <c r="CD31" s="10" t="n"/>
       <c r="CE31" s="11" t="n"/>
-      <c r="CF31" s="8" t="n"/>
-      <c r="CG31" s="9" t="n"/>
-      <c r="CH31" s="10" t="n"/>
-      <c r="CI31" s="11" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
@@ -7923,44 +7567,36 @@
         <v>0.0014</v>
       </c>
       <c r="AA32" s="11" t="n">
-        <v>0</v>
+        <v>0.3678192645926667</v>
       </c>
       <c r="AB32" s="8" t="n">
-        <v>6957544</v>
+        <v>5086596</v>
       </c>
       <c r="AC32" s="9" t="n">
-        <v>18479.24</v>
+        <v>15442.91</v>
       </c>
       <c r="AD32" s="10" t="n">
-        <v>0.0014</v>
+        <v>0.0012</v>
       </c>
       <c r="AE32" s="11" t="n">
-        <v>0.3678192645926667</v>
+        <v>24.46379118733668</v>
       </c>
       <c r="AF32" s="8" t="n">
-        <v>5086596</v>
+        <v>199758</v>
       </c>
       <c r="AG32" s="9" t="n">
-        <v>15442.91</v>
+        <v>629.9400000000001</v>
       </c>
       <c r="AH32" s="10" t="n">
-        <v>0.0012</v>
+        <v>0</v>
       </c>
       <c r="AI32" s="11" t="n">
-        <v>24.46379118733668</v>
-      </c>
-      <c r="AJ32" s="8" t="n">
-        <v>199758</v>
-      </c>
-      <c r="AK32" s="9" t="n">
-        <v>629.9400000000001</v>
-      </c>
-      <c r="AL32" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM32" s="11" t="n">
         <v>1</v>
       </c>
+      <c r="AJ32" s="8" t="n"/>
+      <c r="AK32" s="9" t="n"/>
+      <c r="AL32" s="10" t="n"/>
+      <c r="AM32" s="11" t="n"/>
       <c r="AN32" s="8" t="n"/>
       <c r="AO32" s="9" t="n"/>
       <c r="AP32" s="10" t="n"/>
@@ -8005,10 +7641,6 @@
       <c r="CC32" s="9" t="n"/>
       <c r="CD32" s="10" t="n"/>
       <c r="CE32" s="11" t="n"/>
-      <c r="CF32" s="8" t="n"/>
-      <c r="CG32" s="9" t="n"/>
-      <c r="CH32" s="10" t="n"/>
-      <c r="CI32" s="11" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
@@ -8102,43 +7734,43 @@
         <v>80565</v>
       </c>
       <c r="AC33" s="9" t="n">
-        <v>8949.969999999999</v>
+        <v>10682.11</v>
       </c>
       <c r="AD33" s="10" t="n">
-        <v>0.0007</v>
+        <v>0.0008</v>
       </c>
       <c r="AE33" s="11" t="n">
-        <v>0</v>
+        <v>0.0001613864336081041</v>
       </c>
       <c r="AF33" s="8" t="n">
-        <v>80565</v>
+        <v>80552</v>
       </c>
       <c r="AG33" s="9" t="n">
-        <v>10682.11</v>
+        <v>10825.38</v>
       </c>
       <c r="AH33" s="10" t="n">
         <v>0.0008</v>
       </c>
       <c r="AI33" s="11" t="n">
-        <v>0.0001613864336081041</v>
+        <v>0.004902755772901358</v>
       </c>
       <c r="AJ33" s="8" t="n">
-        <v>80552</v>
+        <v>80159</v>
       </c>
       <c r="AK33" s="9" t="n">
-        <v>10825.38</v>
+        <v>11401.01</v>
       </c>
       <c r="AL33" s="10" t="n">
-        <v>0.0008</v>
+        <v>0.0009</v>
       </c>
       <c r="AM33" s="11" t="n">
-        <v>0.004902755772901358</v>
+        <v>0</v>
       </c>
       <c r="AN33" s="8" t="n">
         <v>80159</v>
       </c>
       <c r="AO33" s="9" t="n">
-        <v>11401.01</v>
+        <v>11787.38</v>
       </c>
       <c r="AP33" s="10" t="n">
         <v>0.0009</v>
@@ -8150,10 +7782,10 @@
         <v>80159</v>
       </c>
       <c r="AS33" s="9" t="n">
-        <v>11787.38</v>
+        <v>12110.42</v>
       </c>
       <c r="AT33" s="10" t="n">
-        <v>0.0009</v>
+        <v>0.001</v>
       </c>
       <c r="AU33" s="11" t="n">
         <v>0</v>
@@ -8162,10 +7794,10 @@
         <v>80159</v>
       </c>
       <c r="AW33" s="9" t="n">
-        <v>12110.42</v>
+        <v>13825.82</v>
       </c>
       <c r="AX33" s="10" t="n">
-        <v>0.001</v>
+        <v>0.0012</v>
       </c>
       <c r="AY33" s="11" t="n">
         <v>0</v>
@@ -8174,10 +7806,10 @@
         <v>80159</v>
       </c>
       <c r="BA33" s="9" t="n">
-        <v>13825.82</v>
+        <v>12726.04</v>
       </c>
       <c r="BB33" s="10" t="n">
-        <v>0.0012</v>
+        <v>0.0011</v>
       </c>
       <c r="BC33" s="11" t="n">
         <v>0</v>
@@ -8186,7 +7818,7 @@
         <v>80159</v>
       </c>
       <c r="BE33" s="9" t="n">
-        <v>12726.04</v>
+        <v>12868.73</v>
       </c>
       <c r="BF33" s="10" t="n">
         <v>0.0011</v>
@@ -8198,7 +7830,7 @@
         <v>80159</v>
       </c>
       <c r="BI33" s="9" t="n">
-        <v>12868.73</v>
+        <v>11621.45</v>
       </c>
       <c r="BJ33" s="10" t="n">
         <v>0.0011</v>
@@ -8210,10 +7842,10 @@
         <v>80159</v>
       </c>
       <c r="BM33" s="9" t="n">
-        <v>11621.45</v>
+        <v>10722.07</v>
       </c>
       <c r="BN33" s="10" t="n">
-        <v>0.0011</v>
+        <v>0.001</v>
       </c>
       <c r="BO33" s="11" t="n">
         <v>0</v>
@@ -8222,10 +7854,10 @@
         <v>80159</v>
       </c>
       <c r="BQ33" s="9" t="n">
-        <v>10722.07</v>
+        <v>9198.25</v>
       </c>
       <c r="BR33" s="10" t="n">
-        <v>0.001</v>
+        <v>0.0009</v>
       </c>
       <c r="BS33" s="11" t="n">
         <v>0</v>
@@ -8234,10 +7866,10 @@
         <v>80159</v>
       </c>
       <c r="BU33" s="9" t="n">
-        <v>9198.25</v>
+        <v>8997.450000000001</v>
       </c>
       <c r="BV33" s="10" t="n">
-        <v>0.0009</v>
+        <v>0.001</v>
       </c>
       <c r="BW33" s="11" t="n">
         <v>0</v>
@@ -8246,10 +7878,10 @@
         <v>80159</v>
       </c>
       <c r="BY33" s="9" t="n">
-        <v>8997.450000000001</v>
+        <v>7401.52</v>
       </c>
       <c r="BZ33" s="10" t="n">
-        <v>0.001</v>
+        <v>0.0008</v>
       </c>
       <c r="CA33" s="11" t="n">
         <v>0</v>
@@ -8258,24 +7890,12 @@
         <v>80159</v>
       </c>
       <c r="CC33" s="9" t="n">
-        <v>7401.52</v>
+        <v>7463.48</v>
       </c>
       <c r="CD33" s="10" t="n">
         <v>0.0008</v>
       </c>
-      <c r="CE33" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF33" s="8" t="n">
-        <v>80159</v>
-      </c>
-      <c r="CG33" s="9" t="n">
-        <v>7463.48</v>
-      </c>
-      <c r="CH33" s="10" t="n">
-        <v>0.0008</v>
-      </c>
-      <c r="CI33" s="11" t="n"/>
+      <c r="CE33" s="11" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
@@ -8369,10 +7989,10 @@
         <v>287393</v>
       </c>
       <c r="AC34" s="9" t="n">
-        <v>14378.27</v>
+        <v>15895.71</v>
       </c>
       <c r="AD34" s="10" t="n">
-        <v>0.0011</v>
+        <v>0.0012</v>
       </c>
       <c r="AE34" s="11" t="n">
         <v>0</v>
@@ -8381,10 +8001,10 @@
         <v>287393</v>
       </c>
       <c r="AG34" s="9" t="n">
-        <v>15895.71</v>
+        <v>18124.44</v>
       </c>
       <c r="AH34" s="10" t="n">
-        <v>0.0012</v>
+        <v>0.0014</v>
       </c>
       <c r="AI34" s="11" t="n">
         <v>0</v>
@@ -8393,10 +8013,10 @@
         <v>287393</v>
       </c>
       <c r="AK34" s="9" t="n">
-        <v>18124.44</v>
+        <v>17460.56</v>
       </c>
       <c r="AL34" s="10" t="n">
-        <v>0.0014</v>
+        <v>0.0013</v>
       </c>
       <c r="AM34" s="11" t="n">
         <v>0</v>
@@ -8405,10 +8025,10 @@
         <v>287393</v>
       </c>
       <c r="AO34" s="9" t="n">
-        <v>17460.56</v>
+        <v>17812.62</v>
       </c>
       <c r="AP34" s="10" t="n">
-        <v>0.0013</v>
+        <v>0.0014</v>
       </c>
       <c r="AQ34" s="11" t="n">
         <v>0</v>
@@ -8417,10 +8037,10 @@
         <v>287393</v>
       </c>
       <c r="AS34" s="9" t="n">
-        <v>17812.62</v>
+        <v>18463.56</v>
       </c>
       <c r="AT34" s="10" t="n">
-        <v>0.0014</v>
+        <v>0.0015</v>
       </c>
       <c r="AU34" s="11" t="n">
         <v>0</v>
@@ -8429,7 +8049,7 @@
         <v>287393</v>
       </c>
       <c r="AW34" s="9" t="n">
-        <v>18463.56</v>
+        <v>18243.71</v>
       </c>
       <c r="AX34" s="10" t="n">
         <v>0.0015</v>
@@ -8441,10 +8061,10 @@
         <v>287393</v>
       </c>
       <c r="BA34" s="9" t="n">
-        <v>18243.71</v>
+        <v>17962.06</v>
       </c>
       <c r="BB34" s="10" t="n">
-        <v>0.0015</v>
+        <v>0.0016</v>
       </c>
       <c r="BC34" s="11" t="n">
         <v>0</v>
@@ -8453,10 +8073,10 @@
         <v>287393</v>
       </c>
       <c r="BE34" s="9" t="n">
-        <v>17962.06</v>
+        <v>19048.41</v>
       </c>
       <c r="BF34" s="10" t="n">
-        <v>0.0016</v>
+        <v>0.0017</v>
       </c>
       <c r="BG34" s="11" t="n">
         <v>0</v>
@@ -8465,10 +8085,10 @@
         <v>287393</v>
       </c>
       <c r="BI34" s="9" t="n">
-        <v>19048.41</v>
+        <v>19453.63</v>
       </c>
       <c r="BJ34" s="10" t="n">
-        <v>0.0017</v>
+        <v>0.0018</v>
       </c>
       <c r="BK34" s="11" t="n">
         <v>0</v>
@@ -8477,10 +8097,10 @@
         <v>287393</v>
       </c>
       <c r="BM34" s="9" t="n">
-        <v>19453.63</v>
+        <v>19370.29</v>
       </c>
       <c r="BN34" s="10" t="n">
-        <v>0.0018</v>
+        <v>0.0019</v>
       </c>
       <c r="BO34" s="11" t="n">
         <v>0</v>
@@ -8489,10 +8109,10 @@
         <v>287393</v>
       </c>
       <c r="BQ34" s="9" t="n">
-        <v>19370.29</v>
+        <v>15976.18</v>
       </c>
       <c r="BR34" s="10" t="n">
-        <v>0.0019</v>
+        <v>0.0016</v>
       </c>
       <c r="BS34" s="11" t="n">
         <v>0</v>
@@ -8501,10 +8121,10 @@
         <v>287393</v>
       </c>
       <c r="BU34" s="9" t="n">
-        <v>15976.18</v>
+        <v>15821.13</v>
       </c>
       <c r="BV34" s="10" t="n">
-        <v>0.0016</v>
+        <v>0.0017</v>
       </c>
       <c r="BW34" s="11" t="n">
         <v>0</v>
@@ -8513,36 +8133,24 @@
         <v>287393</v>
       </c>
       <c r="BY34" s="9" t="n">
-        <v>15821.13</v>
+        <v>15273.64</v>
       </c>
       <c r="BZ34" s="10" t="n">
         <v>0.0017</v>
       </c>
       <c r="CA34" s="11" t="n">
-        <v>0</v>
+        <v>-0.03505968069568721</v>
       </c>
       <c r="CB34" s="8" t="n">
-        <v>287393</v>
+        <v>297835</v>
       </c>
       <c r="CC34" s="9" t="n">
-        <v>15273.64</v>
+        <v>18529.51</v>
       </c>
       <c r="CD34" s="10" t="n">
-        <v>0.0017</v>
-      </c>
-      <c r="CE34" s="11" t="n">
-        <v>-0.03505968069568721</v>
-      </c>
-      <c r="CF34" s="8" t="n">
-        <v>297835</v>
-      </c>
-      <c r="CG34" s="9" t="n">
-        <v>18529.51</v>
-      </c>
-      <c r="CH34" s="10" t="n">
         <v>0.0021</v>
       </c>
-      <c r="CI34" s="11" t="n"/>
+      <c r="CE34" s="11" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
@@ -8636,7 +8244,7 @@
         <v>151687</v>
       </c>
       <c r="AC35" s="9" t="n">
-        <v>1538.11</v>
+        <v>1704.36</v>
       </c>
       <c r="AD35" s="10" t="n">
         <v>0.0001</v>
@@ -8648,7 +8256,7 @@
         <v>151687</v>
       </c>
       <c r="AG35" s="9" t="n">
-        <v>1704.36</v>
+        <v>1728.63</v>
       </c>
       <c r="AH35" s="10" t="n">
         <v>0.0001</v>
@@ -8660,7 +8268,7 @@
         <v>151687</v>
       </c>
       <c r="AK35" s="9" t="n">
-        <v>1728.63</v>
+        <v>1858.32</v>
       </c>
       <c r="AL35" s="10" t="n">
         <v>0.0001</v>
@@ -8672,10 +8280,10 @@
         <v>151687</v>
       </c>
       <c r="AO35" s="9" t="n">
-        <v>1858.32</v>
+        <v>1947.66</v>
       </c>
       <c r="AP35" s="10" t="n">
-        <v>0.0001</v>
+        <v>0.0002</v>
       </c>
       <c r="AQ35" s="11" t="n">
         <v>0</v>
@@ -8684,7 +8292,7 @@
         <v>151687</v>
       </c>
       <c r="AS35" s="9" t="n">
-        <v>1947.66</v>
+        <v>2076.6</v>
       </c>
       <c r="AT35" s="10" t="n">
         <v>0.0002</v>
@@ -8696,7 +8304,7 @@
         <v>151687</v>
       </c>
       <c r="AW35" s="9" t="n">
-        <v>2076.6</v>
+        <v>1987.1</v>
       </c>
       <c r="AX35" s="10" t="n">
         <v>0.0002</v>
@@ -8708,7 +8316,7 @@
         <v>151687</v>
       </c>
       <c r="BA35" s="9" t="n">
-        <v>1987.1</v>
+        <v>2130.6</v>
       </c>
       <c r="BB35" s="10" t="n">
         <v>0.0002</v>
@@ -8720,7 +8328,7 @@
         <v>151687</v>
       </c>
       <c r="BE35" s="9" t="n">
-        <v>2130.6</v>
+        <v>2091.16</v>
       </c>
       <c r="BF35" s="10" t="n">
         <v>0.0002</v>
@@ -8732,38 +8340,30 @@
         <v>151687</v>
       </c>
       <c r="BI35" s="9" t="n">
-        <v>2091.16</v>
+        <v>1766.62</v>
       </c>
       <c r="BJ35" s="10" t="n">
         <v>0.0002</v>
       </c>
       <c r="BK35" s="11" t="n">
-        <v>0</v>
+        <v>0.6954140540298874</v>
       </c>
       <c r="BL35" s="8" t="n">
-        <v>151687</v>
+        <v>89469</v>
       </c>
       <c r="BM35" s="9" t="n">
-        <v>1766.62</v>
+        <v>828.48</v>
       </c>
       <c r="BN35" s="10" t="n">
-        <v>0.0002</v>
+        <v>0.0001</v>
       </c>
       <c r="BO35" s="11" t="n">
-        <v>0.6954140540298874</v>
-      </c>
-      <c r="BP35" s="8" t="n">
-        <v>89469</v>
-      </c>
-      <c r="BQ35" s="9" t="n">
-        <v>828.48</v>
-      </c>
-      <c r="BR35" s="10" t="n">
-        <v>0.0001</v>
-      </c>
-      <c r="BS35" s="11" t="n">
         <v>1</v>
       </c>
+      <c r="BP35" s="8" t="n"/>
+      <c r="BQ35" s="9" t="n"/>
+      <c r="BR35" s="10" t="n"/>
+      <c r="BS35" s="11" t="n"/>
       <c r="BT35" s="8" t="n"/>
       <c r="BU35" s="9" t="n"/>
       <c r="BV35" s="10" t="n"/>
@@ -8776,10 +8376,6 @@
       <c r="CC35" s="9" t="n"/>
       <c r="CD35" s="10" t="n"/>
       <c r="CE35" s="11" t="n"/>
-      <c r="CF35" s="8" t="n"/>
-      <c r="CG35" s="9" t="n"/>
-      <c r="CH35" s="10" t="n"/>
-      <c r="CI35" s="11" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
@@ -8873,7 +8469,7 @@
         <v>47293</v>
       </c>
       <c r="AC36" s="9" t="n">
-        <v>1564.88</v>
+        <v>1700.33</v>
       </c>
       <c r="AD36" s="10" t="n">
         <v>0.0001</v>
@@ -8885,7 +8481,7 @@
         <v>47293</v>
       </c>
       <c r="AG36" s="9" t="n">
-        <v>1700.33</v>
+        <v>1637.61</v>
       </c>
       <c r="AH36" s="10" t="n">
         <v>0.0001</v>
@@ -8897,7 +8493,7 @@
         <v>47293</v>
       </c>
       <c r="AK36" s="9" t="n">
-        <v>1637.61</v>
+        <v>1691.91</v>
       </c>
       <c r="AL36" s="10" t="n">
         <v>0.0001</v>
@@ -8909,7 +8505,7 @@
         <v>47293</v>
       </c>
       <c r="AO36" s="9" t="n">
-        <v>1691.91</v>
+        <v>1764.08</v>
       </c>
       <c r="AP36" s="10" t="n">
         <v>0.0001</v>
@@ -8921,10 +8517,10 @@
         <v>47293</v>
       </c>
       <c r="AS36" s="9" t="n">
-        <v>1764.08</v>
+        <v>1892.15</v>
       </c>
       <c r="AT36" s="10" t="n">
-        <v>0.0001</v>
+        <v>0.0002</v>
       </c>
       <c r="AU36" s="11" t="n">
         <v>0</v>
@@ -8933,7 +8529,7 @@
         <v>47293</v>
       </c>
       <c r="AW36" s="9" t="n">
-        <v>1892.15</v>
+        <v>1955.38</v>
       </c>
       <c r="AX36" s="10" t="n">
         <v>0.0002</v>
@@ -8945,7 +8541,7 @@
         <v>47293</v>
       </c>
       <c r="BA36" s="9" t="n">
-        <v>1955.38</v>
+        <v>1897.21</v>
       </c>
       <c r="BB36" s="10" t="n">
         <v>0.0002</v>
@@ -8957,7 +8553,7 @@
         <v>47293</v>
       </c>
       <c r="BE36" s="9" t="n">
-        <v>1897.21</v>
+        <v>1983.66</v>
       </c>
       <c r="BF36" s="10" t="n">
         <v>0.0002</v>
@@ -8969,7 +8565,7 @@
         <v>47293</v>
       </c>
       <c r="BI36" s="9" t="n">
-        <v>1983.66</v>
+        <v>1867.41</v>
       </c>
       <c r="BJ36" s="10" t="n">
         <v>0.0002</v>
@@ -8981,7 +8577,7 @@
         <v>47293</v>
       </c>
       <c r="BM36" s="9" t="n">
-        <v>1867.41</v>
+        <v>1857.76</v>
       </c>
       <c r="BN36" s="10" t="n">
         <v>0.0002</v>
@@ -8993,7 +8589,7 @@
         <v>47293</v>
       </c>
       <c r="BQ36" s="9" t="n">
-        <v>1857.76</v>
+        <v>1925.39</v>
       </c>
       <c r="BR36" s="10" t="n">
         <v>0.0002</v>
@@ -9005,7 +8601,7 @@
         <v>47293</v>
       </c>
       <c r="BU36" s="9" t="n">
-        <v>1925.39</v>
+        <v>1844.17</v>
       </c>
       <c r="BV36" s="10" t="n">
         <v>0.0002</v>
@@ -9017,10 +8613,10 @@
         <v>47293</v>
       </c>
       <c r="BY36" s="9" t="n">
-        <v>1844.17</v>
+        <v>1236.83</v>
       </c>
       <c r="BZ36" s="10" t="n">
-        <v>0.0002</v>
+        <v>0.0001</v>
       </c>
       <c r="CA36" s="11" t="n">
         <v>0</v>
@@ -9029,24 +8625,12 @@
         <v>47293</v>
       </c>
       <c r="CC36" s="9" t="n">
-        <v>1236.83</v>
+        <v>1612.64</v>
       </c>
       <c r="CD36" s="10" t="n">
-        <v>0.0001</v>
-      </c>
-      <c r="CE36" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF36" s="8" t="n">
-        <v>47293</v>
-      </c>
-      <c r="CG36" s="9" t="n">
-        <v>1612.64</v>
-      </c>
-      <c r="CH36" s="10" t="n">
         <v>0.0002</v>
       </c>
-      <c r="CI36" s="11" t="n"/>
+      <c r="CE36" s="11" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
@@ -9095,105 +8679,113 @@
       <c r="AF37" s="8" t="n"/>
       <c r="AG37" s="9" t="n"/>
       <c r="AH37" s="10" t="n"/>
-      <c r="AI37" s="11" t="n"/>
-      <c r="AJ37" s="8" t="n"/>
-      <c r="AK37" s="9" t="n"/>
-      <c r="AL37" s="10" t="n"/>
+      <c r="AI37" s="11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AJ37" s="8" t="n">
+        <v>24621592</v>
+      </c>
+      <c r="AK37" s="9" t="n">
+        <v>541945.86</v>
+      </c>
+      <c r="AL37" s="10" t="n">
+        <v>0.0407</v>
+      </c>
       <c r="AM37" s="11" t="n">
-        <v>-1</v>
+        <v>0.01296144774839237</v>
       </c>
       <c r="AN37" s="8" t="n">
-        <v>24621592</v>
+        <v>24306544</v>
       </c>
       <c r="AO37" s="9" t="n">
-        <v>541945.86</v>
+        <v>516368.22</v>
       </c>
       <c r="AP37" s="10" t="n">
-        <v>0.0407</v>
+        <v>0.0398</v>
       </c>
       <c r="AQ37" s="11" t="n">
-        <v>0.01296144774839237</v>
+        <v>0.004192884502844551</v>
       </c>
       <c r="AR37" s="8" t="n">
-        <v>24306544</v>
+        <v>24205055</v>
       </c>
       <c r="AS37" s="9" t="n">
-        <v>516368.22</v>
+        <v>508838.67</v>
       </c>
       <c r="AT37" s="10" t="n">
-        <v>0.0398</v>
+        <v>0.0404</v>
       </c>
       <c r="AU37" s="11" t="n">
-        <v>0.004192884502844551</v>
+        <v>0</v>
       </c>
       <c r="AV37" s="8" t="n">
         <v>24205055</v>
       </c>
       <c r="AW37" s="9" t="n">
-        <v>508838.67</v>
+        <v>482334.13</v>
       </c>
       <c r="AX37" s="10" t="n">
-        <v>0.0404</v>
+        <v>0.0403</v>
       </c>
       <c r="AY37" s="11" t="n">
-        <v>0</v>
+        <v>0.03407788338216907</v>
       </c>
       <c r="AZ37" s="8" t="n">
-        <v>24205055</v>
+        <v>23407381</v>
       </c>
       <c r="BA37" s="9" t="n">
-        <v>482334.13</v>
+        <v>458854.89</v>
       </c>
       <c r="BB37" s="10" t="n">
-        <v>0.0403</v>
+        <v>0.0399</v>
       </c>
       <c r="BC37" s="11" t="n">
-        <v>0.03407788338216907</v>
+        <v>0.06425892329321918</v>
       </c>
       <c r="BD37" s="8" t="n">
-        <v>23407381</v>
+        <v>21994066</v>
       </c>
       <c r="BE37" s="9" t="n">
-        <v>458854.89</v>
+        <v>435174.59</v>
       </c>
       <c r="BF37" s="10" t="n">
-        <v>0.0399</v>
+        <v>0.0384</v>
       </c>
       <c r="BG37" s="11" t="n">
-        <v>0.06425892329321918</v>
+        <v>0.07428402120388222</v>
       </c>
       <c r="BH37" s="8" t="n">
-        <v>21994066</v>
+        <v>20473232</v>
       </c>
       <c r="BI37" s="9" t="n">
-        <v>435174.59</v>
+        <v>442938.37</v>
       </c>
       <c r="BJ37" s="10" t="n">
-        <v>0.0384</v>
+        <v>0.0401</v>
       </c>
       <c r="BK37" s="11" t="n">
-        <v>0.07428402120388222</v>
+        <v>0.03644973136547983</v>
       </c>
       <c r="BL37" s="8" t="n">
-        <v>20473232</v>
+        <v>19753232</v>
       </c>
       <c r="BM37" s="9" t="n">
-        <v>442938.37</v>
+        <v>409820.3</v>
       </c>
       <c r="BN37" s="10" t="n">
-        <v>0.0401</v>
+        <v>0.0395</v>
       </c>
       <c r="BO37" s="11" t="n">
-        <v>0.03644973136547983</v>
+        <v>0</v>
       </c>
       <c r="BP37" s="8" t="n">
         <v>19753232</v>
       </c>
       <c r="BQ37" s="9" t="n">
-        <v>409820.3</v>
+        <v>436171.12</v>
       </c>
       <c r="BR37" s="10" t="n">
-        <v>0.0395</v>
+        <v>0.0443</v>
       </c>
       <c r="BS37" s="11" t="n">
         <v>0</v>
@@ -9202,10 +8794,10 @@
         <v>19753232</v>
       </c>
       <c r="BU37" s="9" t="n">
-        <v>436171.12</v>
+        <v>428882.17</v>
       </c>
       <c r="BV37" s="10" t="n">
-        <v>0.0443</v>
+        <v>0.0459</v>
       </c>
       <c r="BW37" s="11" t="n">
         <v>0</v>
@@ -9214,10 +8806,10 @@
         <v>19753232</v>
       </c>
       <c r="BY37" s="9" t="n">
-        <v>428882.17</v>
+        <v>375894.13</v>
       </c>
       <c r="BZ37" s="10" t="n">
-        <v>0.0459</v>
+        <v>0.0427</v>
       </c>
       <c r="CA37" s="11" t="n">
         <v>0</v>
@@ -9226,24 +8818,12 @@
         <v>19753232</v>
       </c>
       <c r="CC37" s="9" t="n">
-        <v>375894.13</v>
+        <v>375568.2</v>
       </c>
       <c r="CD37" s="10" t="n">
-        <v>0.0427</v>
-      </c>
-      <c r="CE37" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF37" s="8" t="n">
-        <v>19753232</v>
-      </c>
-      <c r="CG37" s="9" t="n">
-        <v>375568.2</v>
-      </c>
-      <c r="CH37" s="10" t="n">
         <v>0.0419</v>
       </c>
-      <c r="CI37" s="11" t="n"/>
+      <c r="CE37" s="11" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
@@ -9288,37 +8868,37 @@
         <v>-1</v>
       </c>
       <c r="AB38" s="8" t="n">
-        <v>2274074</v>
+        <v>2906065</v>
       </c>
       <c r="AC38" s="9" t="n">
-        <v>47368.96</v>
+        <v>69277.67999999999</v>
       </c>
       <c r="AD38" s="10" t="n">
-        <v>0.0037</v>
+        <v>0.0052</v>
       </c>
       <c r="AE38" s="11" t="n">
-        <v>-0.2174731122669314</v>
+        <v>-0.3062750860930125</v>
       </c>
       <c r="AF38" s="8" t="n">
-        <v>2906065</v>
+        <v>4189074</v>
       </c>
       <c r="AG38" s="9" t="n">
-        <v>69277.67999999999</v>
+        <v>96591.67</v>
       </c>
       <c r="AH38" s="10" t="n">
-        <v>0.0052</v>
+        <v>0.0072</v>
       </c>
       <c r="AI38" s="11" t="n">
-        <v>-0.3062750860930125</v>
+        <v>0</v>
       </c>
       <c r="AJ38" s="8" t="n">
         <v>4189074</v>
       </c>
       <c r="AK38" s="9" t="n">
-        <v>96591.67</v>
+        <v>97173.95</v>
       </c>
       <c r="AL38" s="10" t="n">
-        <v>0.0072</v>
+        <v>0.0073</v>
       </c>
       <c r="AM38" s="11" t="n">
         <v>0</v>
@@ -9327,10 +8907,10 @@
         <v>4189074</v>
       </c>
       <c r="AO38" s="9" t="n">
-        <v>97173.95</v>
+        <v>96721.53</v>
       </c>
       <c r="AP38" s="10" t="n">
-        <v>0.0073</v>
+        <v>0.0075</v>
       </c>
       <c r="AQ38" s="11" t="n">
         <v>0</v>
@@ -9339,10 +8919,10 @@
         <v>4189074</v>
       </c>
       <c r="AS38" s="9" t="n">
-        <v>96721.53</v>
+        <v>95502.50999999999</v>
       </c>
       <c r="AT38" s="10" t="n">
-        <v>0.0075</v>
+        <v>0.0076</v>
       </c>
       <c r="AU38" s="11" t="n">
         <v>0</v>
@@ -9351,10 +8931,10 @@
         <v>4189074</v>
       </c>
       <c r="AW38" s="9" t="n">
-        <v>95502.50999999999</v>
+        <v>96130.87</v>
       </c>
       <c r="AX38" s="10" t="n">
-        <v>0.0076</v>
+        <v>0.008</v>
       </c>
       <c r="AY38" s="11" t="n">
         <v>0</v>
@@ -9363,10 +8943,10 @@
         <v>4189074</v>
       </c>
       <c r="BA38" s="9" t="n">
-        <v>96130.87</v>
+        <v>95904.66</v>
       </c>
       <c r="BB38" s="10" t="n">
-        <v>0.008</v>
+        <v>0.0083</v>
       </c>
       <c r="BC38" s="11" t="n">
         <v>0</v>
@@ -9375,10 +8955,10 @@
         <v>4189074</v>
       </c>
       <c r="BE38" s="9" t="n">
-        <v>95904.66</v>
+        <v>112108</v>
       </c>
       <c r="BF38" s="10" t="n">
-        <v>0.0083</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="BG38" s="11" t="n">
         <v>0</v>
@@ -9387,10 +8967,10 @@
         <v>4189074</v>
       </c>
       <c r="BI38" s="9" t="n">
-        <v>112108</v>
+        <v>102435.43</v>
       </c>
       <c r="BJ38" s="10" t="n">
-        <v>0.009900000000000001</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="BK38" s="11" t="n">
         <v>0</v>
@@ -9399,10 +8979,10 @@
         <v>4189074</v>
       </c>
       <c r="BM38" s="9" t="n">
-        <v>102435.43</v>
+        <v>103562.29</v>
       </c>
       <c r="BN38" s="10" t="n">
-        <v>0.009299999999999999</v>
+        <v>0.01</v>
       </c>
       <c r="BO38" s="11" t="n">
         <v>0</v>
@@ -9411,10 +8991,10 @@
         <v>4189074</v>
       </c>
       <c r="BQ38" s="9" t="n">
-        <v>103562.29</v>
+        <v>112061.92</v>
       </c>
       <c r="BR38" s="10" t="n">
-        <v>0.01</v>
+        <v>0.0114</v>
       </c>
       <c r="BS38" s="11" t="n">
         <v>0</v>
@@ -9423,10 +9003,10 @@
         <v>4189074</v>
       </c>
       <c r="BU38" s="9" t="n">
-        <v>112061.92</v>
+        <v>107022.46</v>
       </c>
       <c r="BV38" s="10" t="n">
-        <v>0.0114</v>
+        <v>0.0115</v>
       </c>
       <c r="BW38" s="11" t="n">
         <v>0</v>
@@ -9435,10 +9015,10 @@
         <v>4189074</v>
       </c>
       <c r="BY38" s="9" t="n">
-        <v>107022.46</v>
+        <v>109571.51</v>
       </c>
       <c r="BZ38" s="10" t="n">
-        <v>0.0115</v>
+        <v>0.0125</v>
       </c>
       <c r="CA38" s="11" t="n">
         <v>0</v>
@@ -9447,24 +9027,12 @@
         <v>4189074</v>
       </c>
       <c r="CC38" s="9" t="n">
-        <v>109571.51</v>
+        <v>116089.71</v>
       </c>
       <c r="CD38" s="10" t="n">
-        <v>0.0125</v>
-      </c>
-      <c r="CE38" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF38" s="8" t="n">
-        <v>4189074</v>
-      </c>
-      <c r="CG38" s="9" t="n">
-        <v>116089.71</v>
-      </c>
-      <c r="CH38" s="10" t="n">
         <v>0.0129</v>
       </c>
-      <c r="CI38" s="11" t="n"/>
+      <c r="CE38" s="11" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
@@ -9529,21 +9097,29 @@
       <c r="AV39" s="8" t="n"/>
       <c r="AW39" s="9" t="n"/>
       <c r="AX39" s="10" t="n"/>
-      <c r="AY39" s="11" t="n"/>
-      <c r="AZ39" s="8" t="n"/>
-      <c r="BA39" s="9" t="n"/>
-      <c r="BB39" s="10" t="n"/>
+      <c r="AY39" s="11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AZ39" s="8" t="n">
+        <v>4400000</v>
+      </c>
+      <c r="BA39" s="9" t="n">
+        <v>88822.8</v>
+      </c>
+      <c r="BB39" s="10" t="n">
+        <v>0.0077</v>
+      </c>
       <c r="BC39" s="11" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="BD39" s="8" t="n">
         <v>4400000</v>
       </c>
       <c r="BE39" s="9" t="n">
-        <v>88822.8</v>
+        <v>89280.39999999999</v>
       </c>
       <c r="BF39" s="10" t="n">
-        <v>0.0077</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="BG39" s="11" t="n">
         <v>0</v>
@@ -9552,26 +9128,18 @@
         <v>4400000</v>
       </c>
       <c r="BI39" s="9" t="n">
-        <v>89280.39999999999</v>
+        <v>89020.8</v>
       </c>
       <c r="BJ39" s="10" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.0081</v>
       </c>
       <c r="BK39" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL39" s="8" t="n">
-        <v>4400000</v>
-      </c>
-      <c r="BM39" s="9" t="n">
-        <v>89020.8</v>
-      </c>
-      <c r="BN39" s="10" t="n">
-        <v>0.0081</v>
-      </c>
-      <c r="BO39" s="11" t="n">
         <v>1</v>
       </c>
+      <c r="BL39" s="8" t="n"/>
+      <c r="BM39" s="9" t="n"/>
+      <c r="BN39" s="10" t="n"/>
+      <c r="BO39" s="11" t="n"/>
       <c r="BP39" s="8" t="n"/>
       <c r="BQ39" s="9" t="n"/>
       <c r="BR39" s="10" t="n"/>
@@ -9588,10 +9156,6 @@
       <c r="CC39" s="9" t="n"/>
       <c r="CD39" s="10" t="n"/>
       <c r="CE39" s="11" t="n"/>
-      <c r="CF39" s="8" t="n"/>
-      <c r="CG39" s="9" t="n"/>
-      <c r="CH39" s="10" t="n"/>
-      <c r="CI39" s="11" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
@@ -9640,21 +9204,29 @@
       <c r="AF40" s="8" t="n"/>
       <c r="AG40" s="9" t="n"/>
       <c r="AH40" s="10" t="n"/>
-      <c r="AI40" s="11" t="n"/>
-      <c r="AJ40" s="8" t="n"/>
-      <c r="AK40" s="9" t="n"/>
-      <c r="AL40" s="10" t="n"/>
+      <c r="AI40" s="11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AJ40" s="8" t="n">
+        <v>797719</v>
+      </c>
+      <c r="AK40" s="9" t="n">
+        <v>88833.99000000001</v>
+      </c>
+      <c r="AL40" s="10" t="n">
+        <v>0.0067</v>
+      </c>
       <c r="AM40" s="11" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AN40" s="8" t="n">
         <v>797719</v>
       </c>
       <c r="AO40" s="9" t="n">
-        <v>88833.99000000001</v>
+        <v>80358.22</v>
       </c>
       <c r="AP40" s="10" t="n">
-        <v>0.0067</v>
+        <v>0.0062</v>
       </c>
       <c r="AQ40" s="11" t="n">
         <v>0</v>
@@ -9663,10 +9235,10 @@
         <v>797719</v>
       </c>
       <c r="AS40" s="9" t="n">
-        <v>80358.22</v>
+        <v>73737.16</v>
       </c>
       <c r="AT40" s="10" t="n">
-        <v>0.0062</v>
+        <v>0.0059</v>
       </c>
       <c r="AU40" s="11" t="n">
         <v>0</v>
@@ -9675,10 +9247,10 @@
         <v>797719</v>
       </c>
       <c r="AW40" s="9" t="n">
-        <v>73737.16</v>
+        <v>62190.17</v>
       </c>
       <c r="AX40" s="10" t="n">
-        <v>0.0059</v>
+        <v>0.0052</v>
       </c>
       <c r="AY40" s="11" t="n">
         <v>0</v>
@@ -9687,10 +9259,10 @@
         <v>797719</v>
       </c>
       <c r="BA40" s="9" t="n">
-        <v>62190.17</v>
+        <v>58951.43</v>
       </c>
       <c r="BB40" s="10" t="n">
-        <v>0.0052</v>
+        <v>0.0051</v>
       </c>
       <c r="BC40" s="11" t="n">
         <v>0</v>
@@ -9699,10 +9271,10 @@
         <v>797719</v>
       </c>
       <c r="BE40" s="9" t="n">
-        <v>58951.43</v>
+        <v>61368.52</v>
       </c>
       <c r="BF40" s="10" t="n">
-        <v>0.0051</v>
+        <v>0.0054</v>
       </c>
       <c r="BG40" s="11" t="n">
         <v>0</v>
@@ -9711,10 +9283,10 @@
         <v>797719</v>
       </c>
       <c r="BI40" s="9" t="n">
-        <v>61368.52</v>
+        <v>71347.99000000001</v>
       </c>
       <c r="BJ40" s="10" t="n">
-        <v>0.0054</v>
+        <v>0.0065</v>
       </c>
       <c r="BK40" s="11" t="n">
         <v>0</v>
@@ -9723,10 +9295,10 @@
         <v>797719</v>
       </c>
       <c r="BM40" s="9" t="n">
-        <v>71347.99000000001</v>
+        <v>52665.41</v>
       </c>
       <c r="BN40" s="10" t="n">
-        <v>0.0065</v>
+        <v>0.0051</v>
       </c>
       <c r="BO40" s="11" t="n">
         <v>0</v>
@@ -9735,10 +9307,10 @@
         <v>797719</v>
       </c>
       <c r="BQ40" s="9" t="n">
-        <v>52665.41</v>
+        <v>48884.22</v>
       </c>
       <c r="BR40" s="10" t="n">
-        <v>0.0051</v>
+        <v>0.005</v>
       </c>
       <c r="BS40" s="11" t="n">
         <v>0</v>
@@ -9747,10 +9319,10 @@
         <v>797719</v>
       </c>
       <c r="BU40" s="9" t="n">
-        <v>48884.22</v>
+        <v>42372.84</v>
       </c>
       <c r="BV40" s="10" t="n">
-        <v>0.005</v>
+        <v>0.0045</v>
       </c>
       <c r="BW40" s="11" t="n">
         <v>0</v>
@@ -9759,36 +9331,24 @@
         <v>797719</v>
       </c>
       <c r="BY40" s="9" t="n">
-        <v>42372.84</v>
+        <v>39819.34</v>
       </c>
       <c r="BZ40" s="10" t="n">
         <v>0.0045</v>
       </c>
       <c r="CA40" s="11" t="n">
-        <v>0</v>
+        <v>-0.09569612848812428</v>
       </c>
       <c r="CB40" s="8" t="n">
-        <v>797719</v>
+        <v>882136</v>
       </c>
       <c r="CC40" s="9" t="n">
-        <v>39819.34</v>
+        <v>50572.42</v>
       </c>
       <c r="CD40" s="10" t="n">
-        <v>0.0045</v>
-      </c>
-      <c r="CE40" s="11" t="n">
-        <v>-0.09569612848812428</v>
-      </c>
-      <c r="CF40" s="8" t="n">
-        <v>882136</v>
-      </c>
-      <c r="CG40" s="9" t="n">
-        <v>50572.42</v>
-      </c>
-      <c r="CH40" s="10" t="n">
         <v>0.0056</v>
       </c>
-      <c r="CI40" s="11" t="n"/>
+      <c r="CE40" s="11" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
@@ -9853,107 +9413,103 @@
       <c r="AV41" s="8" t="n"/>
       <c r="AW41" s="9" t="n"/>
       <c r="AX41" s="10" t="n"/>
-      <c r="AY41" s="11" t="n"/>
-      <c r="AZ41" s="8" t="n"/>
-      <c r="BA41" s="9" t="n"/>
-      <c r="BB41" s="10" t="n"/>
+      <c r="AY41" s="11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AZ41" s="8" t="n">
+        <v>218075</v>
+      </c>
+      <c r="BA41" s="9" t="n">
+        <v>3019.03</v>
+      </c>
+      <c r="BB41" s="10" t="n">
+        <v>0.0003</v>
+      </c>
       <c r="BC41" s="11" t="n">
-        <v>-1</v>
+        <v>-0.6148554615199853</v>
       </c>
       <c r="BD41" s="8" t="n">
-        <v>218075</v>
+        <v>566216</v>
       </c>
       <c r="BE41" s="9" t="n">
-        <v>3019.03</v>
+        <v>8345.459999999999</v>
       </c>
       <c r="BF41" s="10" t="n">
-        <v>0.0003</v>
+        <v>0.0007</v>
       </c>
       <c r="BG41" s="11" t="n">
-        <v>-0.6148554615199853</v>
+        <v>-0.5682871579351869</v>
       </c>
       <c r="BH41" s="8" t="n">
-        <v>566216</v>
+        <v>1311557</v>
       </c>
       <c r="BI41" s="9" t="n">
-        <v>8345.459999999999</v>
+        <v>18228.02</v>
       </c>
       <c r="BJ41" s="10" t="n">
-        <v>0.0007</v>
+        <v>0.0017</v>
       </c>
       <c r="BK41" s="11" t="n">
-        <v>-0.5682871579351869</v>
+        <v>-0.2008037316547793</v>
       </c>
       <c r="BL41" s="8" t="n">
-        <v>1311557</v>
+        <v>1641095</v>
       </c>
       <c r="BM41" s="9" t="n">
-        <v>18228.02</v>
+        <v>23382.32</v>
       </c>
       <c r="BN41" s="10" t="n">
-        <v>0.0017</v>
+        <v>0.0023</v>
       </c>
       <c r="BO41" s="11" t="n">
-        <v>-0.2008037316547793</v>
+        <v>-0.1163687388172734</v>
       </c>
       <c r="BP41" s="8" t="n">
-        <v>1641095</v>
+        <v>1857217</v>
       </c>
       <c r="BQ41" s="9" t="n">
-        <v>23382.32</v>
+        <v>26023.32</v>
       </c>
       <c r="BR41" s="10" t="n">
-        <v>0.0023</v>
+        <v>0.0026</v>
       </c>
       <c r="BS41" s="11" t="n">
-        <v>-0.1163687388172734</v>
+        <v>-0.03620728307597141</v>
       </c>
       <c r="BT41" s="8" t="n">
-        <v>1857217</v>
+        <v>1926988</v>
       </c>
       <c r="BU41" s="9" t="n">
-        <v>26023.32</v>
+        <v>28941.43</v>
       </c>
       <c r="BV41" s="10" t="n">
-        <v>0.0026</v>
+        <v>0.0031</v>
       </c>
       <c r="BW41" s="11" t="n">
-        <v>-0.03620728307597141</v>
+        <v>0</v>
       </c>
       <c r="BX41" s="8" t="n">
         <v>1926988</v>
       </c>
       <c r="BY41" s="9" t="n">
-        <v>28941.43</v>
+        <v>26117.43</v>
       </c>
       <c r="BZ41" s="10" t="n">
-        <v>0.0031</v>
+        <v>0.003</v>
       </c>
       <c r="CA41" s="11" t="n">
-        <v>0</v>
+        <v>-0.1421734974921662</v>
       </c>
       <c r="CB41" s="8" t="n">
-        <v>1926988</v>
+        <v>2246361</v>
       </c>
       <c r="CC41" s="9" t="n">
-        <v>26117.43</v>
+        <v>32421.73</v>
       </c>
       <c r="CD41" s="10" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="CE41" s="11" t="n">
-        <v>-0.1421734974921662</v>
-      </c>
-      <c r="CF41" s="8" t="n">
-        <v>2246361</v>
-      </c>
-      <c r="CG41" s="9" t="n">
-        <v>32421.73</v>
-      </c>
-      <c r="CH41" s="10" t="n">
         <v>0.0036</v>
       </c>
-      <c r="CI41" s="11" t="n"/>
+      <c r="CE41" s="11" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
@@ -10026,83 +9582,79 @@
       <c r="BD42" s="8" t="n"/>
       <c r="BE42" s="9" t="n"/>
       <c r="BF42" s="10" t="n"/>
-      <c r="BG42" s="11" t="n"/>
-      <c r="BH42" s="8" t="n"/>
-      <c r="BI42" s="9" t="n"/>
-      <c r="BJ42" s="10" t="n"/>
+      <c r="BG42" s="11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH42" s="8" t="n">
+        <v>591805</v>
+      </c>
+      <c r="BI42" s="9" t="n">
+        <v>5149</v>
+      </c>
+      <c r="BJ42" s="10" t="n">
+        <v>0.0005</v>
+      </c>
       <c r="BK42" s="11" t="n">
-        <v>-1</v>
+        <v>-0.8902567225534253</v>
       </c>
       <c r="BL42" s="8" t="n">
-        <v>591805</v>
+        <v>5392631</v>
       </c>
       <c r="BM42" s="9" t="n">
-        <v>5149</v>
+        <v>43674.92</v>
       </c>
       <c r="BN42" s="10" t="n">
-        <v>0.0005</v>
+        <v>0.0042</v>
       </c>
       <c r="BO42" s="11" t="n">
-        <v>-0.8902567225534253</v>
+        <v>-0.3719237093069153</v>
       </c>
       <c r="BP42" s="8" t="n">
-        <v>5392631</v>
+        <v>8585949</v>
       </c>
       <c r="BQ42" s="9" t="n">
-        <v>43674.92</v>
+        <v>56044.78</v>
       </c>
       <c r="BR42" s="10" t="n">
-        <v>0.0042</v>
+        <v>0.0057</v>
       </c>
       <c r="BS42" s="11" t="n">
-        <v>-0.3719237093069153</v>
+        <v>-0.2132577936597328</v>
       </c>
       <c r="BT42" s="8" t="n">
-        <v>8585949</v>
+        <v>10913294</v>
       </c>
       <c r="BU42" s="9" t="n">
-        <v>56044.78</v>
+        <v>67154.95</v>
       </c>
       <c r="BV42" s="10" t="n">
-        <v>0.0057</v>
+        <v>0.0072</v>
       </c>
       <c r="BW42" s="11" t="n">
-        <v>-0.2132577936597328</v>
+        <v>-0.09462389658963724</v>
       </c>
       <c r="BX42" s="8" t="n">
-        <v>10913294</v>
+        <v>12053879</v>
       </c>
       <c r="BY42" s="9" t="n">
-        <v>67154.95</v>
+        <v>70937.08</v>
       </c>
       <c r="BZ42" s="10" t="n">
-        <v>0.0072</v>
+        <v>0.0081</v>
       </c>
       <c r="CA42" s="11" t="n">
-        <v>-0.09462389658963724</v>
+        <v>0</v>
       </c>
       <c r="CB42" s="8" t="n">
         <v>12053879</v>
       </c>
       <c r="CC42" s="9" t="n">
-        <v>70937.08</v>
+        <v>76801.28999999999</v>
       </c>
       <c r="CD42" s="10" t="n">
-        <v>0.0081</v>
-      </c>
-      <c r="CE42" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF42" s="8" t="n">
-        <v>12053879</v>
-      </c>
-      <c r="CG42" s="9" t="n">
-        <v>76801.28999999999</v>
-      </c>
-      <c r="CH42" s="10" t="n">
         <v>0.0086</v>
       </c>
-      <c r="CI42" s="11" t="n"/>
+      <c r="CE42" s="11" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
@@ -10190,10 +9742,10 @@
         <v>2205298</v>
       </c>
       <c r="AC43" s="9" t="n">
-        <v>31198.35</v>
+        <v>29526.73</v>
       </c>
       <c r="AD43" s="10" t="n">
-        <v>0.0024</v>
+        <v>0.0022</v>
       </c>
       <c r="AE43" s="11" t="n">
         <v>0</v>
@@ -10202,38 +9754,30 @@
         <v>2205298</v>
       </c>
       <c r="AG43" s="9" t="n">
-        <v>29526.73</v>
+        <v>26516.5</v>
       </c>
       <c r="AH43" s="10" t="n">
-        <v>0.0022</v>
+        <v>0.002</v>
       </c>
       <c r="AI43" s="11" t="n">
-        <v>0</v>
+        <v>0.3305575398932319</v>
       </c>
       <c r="AJ43" s="8" t="n">
-        <v>2205298</v>
+        <v>1657424</v>
       </c>
       <c r="AK43" s="9" t="n">
-        <v>26516.5</v>
+        <v>18712.32</v>
       </c>
       <c r="AL43" s="10" t="n">
-        <v>0.002</v>
+        <v>0.0014</v>
       </c>
       <c r="AM43" s="11" t="n">
-        <v>0.3305575398932319</v>
-      </c>
-      <c r="AN43" s="8" t="n">
-        <v>1657424</v>
-      </c>
-      <c r="AO43" s="9" t="n">
-        <v>18712.32</v>
-      </c>
-      <c r="AP43" s="10" t="n">
-        <v>0.0014</v>
-      </c>
-      <c r="AQ43" s="11" t="n">
         <v>1</v>
       </c>
+      <c r="AN43" s="8" t="n"/>
+      <c r="AO43" s="9" t="n"/>
+      <c r="AP43" s="10" t="n"/>
+      <c r="AQ43" s="11" t="n"/>
       <c r="AR43" s="8" t="n"/>
       <c r="AS43" s="9" t="n"/>
       <c r="AT43" s="10" t="n"/>
@@ -10274,10 +9818,6 @@
       <c r="CC43" s="9" t="n"/>
       <c r="CD43" s="10" t="n"/>
       <c r="CE43" s="11" t="n"/>
-      <c r="CF43" s="8" t="n"/>
-      <c r="CG43" s="9" t="n"/>
-      <c r="CH43" s="10" t="n"/>
-      <c r="CI43" s="11" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
@@ -10362,21 +9902,29 @@
       <c r="BP44" s="8" t="n"/>
       <c r="BQ44" s="9" t="n"/>
       <c r="BR44" s="10" t="n"/>
-      <c r="BS44" s="11" t="n"/>
-      <c r="BT44" s="8" t="n"/>
-      <c r="BU44" s="9" t="n"/>
-      <c r="BV44" s="10" t="n"/>
+      <c r="BS44" s="11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BT44" s="8" t="n">
+        <v>9899412</v>
+      </c>
+      <c r="BU44" s="9" t="n">
+        <v>19552.33</v>
+      </c>
+      <c r="BV44" s="10" t="n">
+        <v>0.0021</v>
+      </c>
       <c r="BW44" s="11" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="BX44" s="8" t="n">
         <v>9899412</v>
       </c>
       <c r="BY44" s="9" t="n">
-        <v>19552.33</v>
+        <v>16216.23</v>
       </c>
       <c r="BZ44" s="10" t="n">
-        <v>0.0021</v>
+        <v>0.0018</v>
       </c>
       <c r="CA44" s="11" t="n">
         <v>0</v>
@@ -10385,24 +9933,12 @@
         <v>9899412</v>
       </c>
       <c r="CC44" s="9" t="n">
-        <v>16216.23</v>
+        <v>16131.09</v>
       </c>
       <c r="CD44" s="10" t="n">
         <v>0.0018</v>
       </c>
-      <c r="CE44" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF44" s="8" t="n">
-        <v>9899412</v>
-      </c>
-      <c r="CG44" s="9" t="n">
-        <v>16131.09</v>
-      </c>
-      <c r="CH44" s="10" t="n">
-        <v>0.0018</v>
-      </c>
-      <c r="CI44" s="11" t="n"/>
+      <c r="CE44" s="11" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
@@ -10447,25 +9983,25 @@
       <c r="AB45" s="8" t="n"/>
       <c r="AC45" s="9" t="n"/>
       <c r="AD45" s="10" t="n"/>
-      <c r="AE45" s="11" t="n"/>
-      <c r="AF45" s="8" t="n"/>
-      <c r="AG45" s="9" t="n"/>
-      <c r="AH45" s="10" t="n"/>
+      <c r="AE45" s="11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AF45" s="8" t="n">
+        <v>795472</v>
+      </c>
+      <c r="AG45" s="9" t="n">
+        <v>20109.53</v>
+      </c>
+      <c r="AH45" s="10" t="n">
+        <v>0.0015</v>
+      </c>
       <c r="AI45" s="11" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AJ45" s="8" t="n">
-        <v>795472</v>
-      </c>
-      <c r="AK45" s="9" t="n">
-        <v>20109.53</v>
-      </c>
-      <c r="AL45" s="10" t="n">
-        <v>0.0015</v>
-      </c>
-      <c r="AM45" s="11" t="n">
         <v>1</v>
       </c>
+      <c r="AJ45" s="8" t="n"/>
+      <c r="AK45" s="9" t="n"/>
+      <c r="AL45" s="10" t="n"/>
+      <c r="AM45" s="11" t="n"/>
       <c r="AN45" s="8" t="n"/>
       <c r="AO45" s="9" t="n"/>
       <c r="AP45" s="10" t="n"/>
@@ -10510,10 +10046,6 @@
       <c r="CC45" s="9" t="n"/>
       <c r="CD45" s="10" t="n"/>
       <c r="CE45" s="11" t="n"/>
-      <c r="CF45" s="8" t="n"/>
-      <c r="CG45" s="9" t="n"/>
-      <c r="CH45" s="10" t="n"/>
-      <c r="CI45" s="11" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="12" t="inlineStr">
@@ -10584,168 +10116,157 @@
       </c>
       <c r="AA46" s="17" t="n"/>
       <c r="AB46" s="14" t="n">
-        <v>1373201700</v>
+        <v>1285817925</v>
       </c>
       <c r="AC46" s="15" t="n">
-        <v>8608487.040000001</v>
+        <v>8857498.139999999</v>
       </c>
       <c r="AD46" s="16" t="n">
-        <v>0.6675</v>
+        <v>0.6597999999999999</v>
       </c>
       <c r="AE46" s="17" t="n"/>
       <c r="AF46" s="14" t="n">
-        <v>1285817925</v>
+        <v>1265994824</v>
       </c>
       <c r="AG46" s="15" t="n">
-        <v>8857498.139999999</v>
+        <v>8789059.288358001</v>
       </c>
       <c r="AH46" s="16" t="n">
-        <v>0.6597999999999999</v>
+        <v>0.6559051731198605</v>
       </c>
       <c r="AI46" s="17" t="n"/>
       <c r="AJ46" s="14" t="n">
-        <v>1265994824</v>
+        <v>1079845116</v>
       </c>
       <c r="AK46" s="15" t="n">
-        <v>8789059.288358001</v>
+        <v>8588270.84</v>
       </c>
       <c r="AL46" s="16" t="n">
-        <v>0.6559051731198605</v>
+        <v>0.6443999999999998</v>
       </c>
       <c r="AM46" s="17" t="n"/>
       <c r="AN46" s="14" t="n">
-        <v>1079845116</v>
+        <v>1039629309</v>
       </c>
       <c r="AO46" s="15" t="n">
-        <v>8588270.84</v>
+        <v>8271351.1939775</v>
       </c>
       <c r="AP46" s="16" t="n">
-        <v>0.6443999999999998</v>
+        <v>0.6373999999999999</v>
       </c>
       <c r="AQ46" s="17" t="n"/>
       <c r="AR46" s="14" t="n">
-        <v>1039629309</v>
+        <v>991416407</v>
       </c>
       <c r="AS46" s="15" t="n">
-        <v>8271351.1939775</v>
+        <v>7865128.239999999</v>
       </c>
       <c r="AT46" s="16" t="n">
-        <v>0.6373999999999999</v>
+        <v>0.6254999999999999</v>
       </c>
       <c r="AU46" s="17" t="n"/>
       <c r="AV46" s="14" t="n">
-        <v>991416407</v>
+        <v>979359723</v>
       </c>
       <c r="AW46" s="15" t="n">
-        <v>7865128.239999999</v>
+        <v>7559180.720000002</v>
       </c>
       <c r="AX46" s="16" t="n">
-        <v>0.6254999999999999</v>
+        <v>0.6313999999999996</v>
       </c>
       <c r="AY46" s="17" t="n"/>
       <c r="AZ46" s="14" t="n">
-        <v>979359723</v>
+        <v>927478800</v>
       </c>
       <c r="BA46" s="15" t="n">
-        <v>7559180.720000002</v>
+        <v>7320811.489999999</v>
       </c>
       <c r="BB46" s="16" t="n">
-        <v>0.6313999999999996</v>
+        <v>0.6364000000000001</v>
       </c>
       <c r="BC46" s="17" t="n"/>
       <c r="BD46" s="14" t="n">
-        <v>927478800</v>
+        <v>819556049</v>
       </c>
       <c r="BE46" s="15" t="n">
-        <v>7320811.489999999</v>
+        <v>7290583.900000002</v>
       </c>
       <c r="BF46" s="16" t="n">
-        <v>0.6364000000000001</v>
+        <v>0.6436999999999999</v>
       </c>
       <c r="BG46" s="17" t="n"/>
       <c r="BH46" s="14" t="n">
-        <v>819556049</v>
+        <v>799425942</v>
       </c>
       <c r="BI46" s="15" t="n">
-        <v>7290583.900000002</v>
+        <v>7347454.07</v>
       </c>
       <c r="BJ46" s="16" t="n">
-        <v>0.6436999999999999</v>
+        <v>0.6658000000000001</v>
       </c>
       <c r="BK46" s="17" t="n"/>
       <c r="BL46" s="14" t="n">
-        <v>799425942</v>
+        <v>756845974</v>
       </c>
       <c r="BM46" s="15" t="n">
-        <v>7347454.07</v>
+        <v>6714757.130000002</v>
       </c>
       <c r="BN46" s="16" t="n">
-        <v>0.6658000000000001</v>
+        <v>0.6467999999999997</v>
       </c>
       <c r="BO46" s="17" t="n"/>
       <c r="BP46" s="14" t="n">
-        <v>756845974</v>
+        <v>719050337</v>
       </c>
       <c r="BQ46" s="15" t="n">
-        <v>6714757.130000002</v>
+        <v>6275568.75</v>
       </c>
       <c r="BR46" s="16" t="n">
-        <v>0.6467999999999997</v>
+        <v>0.6369999999999999</v>
       </c>
       <c r="BS46" s="17" t="n"/>
       <c r="BT46" s="14" t="n">
-        <v>719050337</v>
+        <v>717176528</v>
       </c>
       <c r="BU46" s="15" t="n">
-        <v>6275568.75</v>
+        <v>6051937.579999999</v>
       </c>
       <c r="BV46" s="16" t="n">
-        <v>0.6369999999999999</v>
+        <v>0.6476999999999998</v>
       </c>
       <c r="BW46" s="17" t="n"/>
       <c r="BX46" s="14" t="n">
-        <v>717176528</v>
+        <v>718063829</v>
       </c>
       <c r="BY46" s="15" t="n">
-        <v>6051937.579999999</v>
+        <v>5662977.75</v>
       </c>
       <c r="BZ46" s="16" t="n">
-        <v>0.6476999999999998</v>
+        <v>0.6436999999999999</v>
       </c>
       <c r="CA46" s="17" t="n"/>
       <c r="CB46" s="14" t="n">
-        <v>718063829</v>
+        <v>697292654</v>
       </c>
       <c r="CC46" s="15" t="n">
-        <v>5662977.75</v>
+        <v>5868142.6</v>
       </c>
       <c r="CD46" s="16" t="n">
-        <v>0.6436999999999999</v>
+        <v>0.6543000000000003</v>
       </c>
       <c r="CE46" s="17" t="n"/>
-      <c r="CF46" s="14" t="n">
-        <v>697292654</v>
-      </c>
-      <c r="CG46" s="15" t="n">
-        <v>5868142.6</v>
-      </c>
-      <c r="CH46" s="16" t="n">
-        <v>0.6543000000000003</v>
-      </c>
-      <c r="CI46" s="17" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="22">
+  <mergeCells count="21">
     <mergeCell ref="BX2:CA2"/>
     <mergeCell ref="AR2:AU2"/>
     <mergeCell ref="AZ2:BC2"/>
     <mergeCell ref="BL2:BO2"/>
-    <mergeCell ref="A1:CI1"/>
     <mergeCell ref="L2:O2"/>
     <mergeCell ref="X2:AA2"/>
     <mergeCell ref="AJ2:AM2"/>
     <mergeCell ref="CB2:CE2"/>
-    <mergeCell ref="CF2:CI2"/>
+    <mergeCell ref="A1:CE1"/>
     <mergeCell ref="AV2:AY2"/>
     <mergeCell ref="D2:G2"/>
     <mergeCell ref="P2:S2"/>

--- a/PPFAS_Equity_Analysis.xlsx
+++ b/PPFAS_Equity_Analysis.xlsx
@@ -490,7 +490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CE46"/>
+  <dimension ref="A1:CI46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -519,39 +519,39 @@
     <col width="14" customWidth="1" min="24" max="24"/>
     <col width="26" customWidth="1" min="25" max="25"/>
     <col width="20" customWidth="1" min="26" max="26"/>
-    <col width="23" customWidth="1" min="27" max="27"/>
-    <col width="15" customWidth="1" min="28" max="28"/>
+    <col width="24" customWidth="1" min="27" max="27"/>
+    <col width="14" customWidth="1" min="28" max="28"/>
     <col width="26" customWidth="1" min="29" max="29"/>
-    <col width="20" customWidth="1" min="30" max="30"/>
-    <col width="24" customWidth="1" min="31" max="31"/>
-    <col width="14" customWidth="1" min="32" max="32"/>
+    <col width="14" customWidth="1" min="30" max="30"/>
+    <col width="23" customWidth="1" min="31" max="31"/>
+    <col width="15" customWidth="1" min="32" max="32"/>
     <col width="26" customWidth="1" min="33" max="33"/>
-    <col width="22" customWidth="1" min="34" max="34"/>
-    <col width="23" customWidth="1" min="35" max="35"/>
-    <col width="15" customWidth="1" min="36" max="36"/>
+    <col width="20" customWidth="1" min="34" max="34"/>
+    <col width="24" customWidth="1" min="35" max="35"/>
+    <col width="14" customWidth="1" min="36" max="36"/>
     <col width="26" customWidth="1" min="37" max="37"/>
-    <col width="20" customWidth="1" min="38" max="38"/>
-    <col width="22" customWidth="1" min="39" max="39"/>
+    <col width="22" customWidth="1" min="38" max="38"/>
+    <col width="23" customWidth="1" min="39" max="39"/>
     <col width="15" customWidth="1" min="40" max="40"/>
     <col width="26" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="22" customWidth="1" min="43" max="43"/>
-    <col width="14" customWidth="1" min="44" max="44"/>
+    <col width="15" customWidth="1" min="44" max="44"/>
     <col width="26" customWidth="1" min="45" max="45"/>
-    <col width="14" customWidth="1" min="46" max="46"/>
-    <col width="23" customWidth="1" min="47" max="47"/>
-    <col width="16" customWidth="1" min="48" max="48"/>
+    <col width="20" customWidth="1" min="46" max="46"/>
+    <col width="22" customWidth="1" min="47" max="47"/>
+    <col width="14" customWidth="1" min="48" max="48"/>
     <col width="26" customWidth="1" min="49" max="49"/>
-    <col width="20" customWidth="1" min="50" max="50"/>
-    <col width="22" customWidth="1" min="51" max="51"/>
-    <col width="13" customWidth="1" min="52" max="52"/>
+    <col width="14" customWidth="1" min="50" max="50"/>
+    <col width="23" customWidth="1" min="51" max="51"/>
+    <col width="16" customWidth="1" min="52" max="52"/>
     <col width="26" customWidth="1" min="53" max="53"/>
     <col width="20" customWidth="1" min="54" max="54"/>
-    <col width="23" customWidth="1" min="55" max="55"/>
+    <col width="22" customWidth="1" min="55" max="55"/>
     <col width="13" customWidth="1" min="56" max="56"/>
     <col width="26" customWidth="1" min="57" max="57"/>
     <col width="20" customWidth="1" min="58" max="58"/>
-    <col width="22" customWidth="1" min="59" max="59"/>
+    <col width="23" customWidth="1" min="59" max="59"/>
     <col width="13" customWidth="1" min="60" max="60"/>
     <col width="26" customWidth="1" min="61" max="61"/>
     <col width="20" customWidth="1" min="62" max="62"/>
@@ -559,23 +559,27 @@
     <col width="13" customWidth="1" min="64" max="64"/>
     <col width="26" customWidth="1" min="65" max="65"/>
     <col width="20" customWidth="1" min="66" max="66"/>
-    <col width="23" customWidth="1" min="67" max="67"/>
+    <col width="22" customWidth="1" min="67" max="67"/>
     <col width="13" customWidth="1" min="68" max="68"/>
     <col width="26" customWidth="1" min="69" max="69"/>
     <col width="20" customWidth="1" min="70" max="70"/>
-    <col width="22" customWidth="1" min="71" max="71"/>
+    <col width="23" customWidth="1" min="71" max="71"/>
     <col width="13" customWidth="1" min="72" max="72"/>
     <col width="26" customWidth="1" min="73" max="73"/>
     <col width="20" customWidth="1" min="74" max="74"/>
-    <col width="23" customWidth="1" min="75" max="75"/>
-    <col width="15" customWidth="1" min="76" max="76"/>
+    <col width="22" customWidth="1" min="75" max="75"/>
+    <col width="13" customWidth="1" min="76" max="76"/>
     <col width="26" customWidth="1" min="77" max="77"/>
     <col width="20" customWidth="1" min="78" max="78"/>
-    <col width="22" customWidth="1" min="79" max="79"/>
-    <col width="14" customWidth="1" min="80" max="80"/>
+    <col width="23" customWidth="1" min="79" max="79"/>
+    <col width="15" customWidth="1" min="80" max="80"/>
     <col width="26" customWidth="1" min="81" max="81"/>
     <col width="20" customWidth="1" min="82" max="82"/>
-    <col width="17" customWidth="1" min="83" max="83"/>
+    <col width="22" customWidth="1" min="83" max="83"/>
+    <col width="14" customWidth="1" min="84" max="84"/>
+    <col width="26" customWidth="1" min="85" max="85"/>
+    <col width="20" customWidth="1" min="86" max="86"/>
+    <col width="17" customWidth="1" min="87" max="87"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -666,6 +670,10 @@
       <c r="CC1" s="1" t="n"/>
       <c r="CD1" s="1" t="n"/>
       <c r="CE1" s="1" t="n"/>
+      <c r="CF1" s="1" t="n"/>
+      <c r="CG1" s="1" t="n"/>
+      <c r="CH1" s="1" t="n"/>
+      <c r="CI1" s="1" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -733,7 +741,7 @@
       <c r="AA2" s="3" t="n"/>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>February_2026</t>
+          <t>March_2026</t>
         </is>
       </c>
       <c r="AC2" s="2" t="n"/>
@@ -741,7 +749,7 @@
       <c r="AE2" s="3" t="n"/>
       <c r="AF2" s="2" t="inlineStr">
         <is>
-          <t>January_2026</t>
+          <t>February_2026</t>
         </is>
       </c>
       <c r="AG2" s="2" t="n"/>
@@ -749,7 +757,7 @@
       <c r="AI2" s="3" t="n"/>
       <c r="AJ2" s="2" t="inlineStr">
         <is>
-          <t>December_2025</t>
+          <t>January_2026</t>
         </is>
       </c>
       <c r="AK2" s="2" t="n"/>
@@ -757,7 +765,7 @@
       <c r="AM2" s="3" t="n"/>
       <c r="AN2" s="2" t="inlineStr">
         <is>
-          <t>November_2025</t>
+          <t>December_2025</t>
         </is>
       </c>
       <c r="AO2" s="2" t="n"/>
@@ -765,7 +773,7 @@
       <c r="AQ2" s="3" t="n"/>
       <c r="AR2" s="2" t="inlineStr">
         <is>
-          <t>October_2025</t>
+          <t>November_2025</t>
         </is>
       </c>
       <c r="AS2" s="2" t="n"/>
@@ -773,7 +781,7 @@
       <c r="AU2" s="3" t="n"/>
       <c r="AV2" s="2" t="inlineStr">
         <is>
-          <t>September_2025</t>
+          <t>October_2025</t>
         </is>
       </c>
       <c r="AW2" s="2" t="n"/>
@@ -781,7 +789,7 @@
       <c r="AY2" s="3" t="n"/>
       <c r="AZ2" s="2" t="inlineStr">
         <is>
-          <t>August_2025</t>
+          <t>September_2025</t>
         </is>
       </c>
       <c r="BA2" s="2" t="n"/>
@@ -789,7 +797,7 @@
       <c r="BC2" s="3" t="n"/>
       <c r="BD2" s="2" t="inlineStr">
         <is>
-          <t>July_2025</t>
+          <t>August_2025</t>
         </is>
       </c>
       <c r="BE2" s="2" t="n"/>
@@ -797,7 +805,7 @@
       <c r="BG2" s="3" t="n"/>
       <c r="BH2" s="2" t="inlineStr">
         <is>
-          <t>June_2025</t>
+          <t>July_2025</t>
         </is>
       </c>
       <c r="BI2" s="2" t="n"/>
@@ -805,7 +813,7 @@
       <c r="BK2" s="3" t="n"/>
       <c r="BL2" s="2" t="inlineStr">
         <is>
-          <t>May_2025</t>
+          <t>June_2025</t>
         </is>
       </c>
       <c r="BM2" s="2" t="n"/>
@@ -813,7 +821,7 @@
       <c r="BO2" s="3" t="n"/>
       <c r="BP2" s="2" t="inlineStr">
         <is>
-          <t>April_2025</t>
+          <t>May_2025</t>
         </is>
       </c>
       <c r="BQ2" s="2" t="n"/>
@@ -821,7 +829,7 @@
       <c r="BS2" s="3" t="n"/>
       <c r="BT2" s="2" t="inlineStr">
         <is>
-          <t>March_2025</t>
+          <t>April_2025</t>
         </is>
       </c>
       <c r="BU2" s="2" t="n"/>
@@ -829,7 +837,7 @@
       <c r="BW2" s="3" t="n"/>
       <c r="BX2" s="2" t="inlineStr">
         <is>
-          <t>February_2025</t>
+          <t>March_2025</t>
         </is>
       </c>
       <c r="BY2" s="2" t="n"/>
@@ -837,12 +845,20 @@
       <c r="CA2" s="3" t="n"/>
       <c r="CB2" s="2" t="inlineStr">
         <is>
-          <t>January_2025</t>
+          <t>February_2025</t>
         </is>
       </c>
       <c r="CC2" s="2" t="n"/>
       <c r="CD2" s="2" t="n"/>
       <c r="CE2" s="3" t="n"/>
+      <c r="CF2" s="2" t="inlineStr">
+        <is>
+          <t>January_2025</t>
+        </is>
+      </c>
+      <c r="CG2" s="2" t="n"/>
+      <c r="CH2" s="2" t="n"/>
+      <c r="CI2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n"/>
@@ -1248,6 +1264,26 @@
           <t>% Change in Qty</t>
         </is>
       </c>
+      <c r="CF3" s="4" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="CG3" s="4" t="inlineStr">
+        <is>
+          <t>Market Value (Rs. Lakhs)</t>
+        </is>
+      </c>
+      <c r="CH3" s="4" t="inlineStr">
+        <is>
+          <t>% Net Assets</t>
+        </is>
+      </c>
+      <c r="CI3" s="5" t="inlineStr">
+        <is>
+          <t>% Change in Qty</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -1335,148 +1371,148 @@
         <v>0.0794</v>
       </c>
       <c r="AA4" s="11" t="n">
-        <v>0.2402727503134398</v>
+        <v>0.03394007080483452</v>
       </c>
       <c r="AB4" s="8" t="n">
+        <v>140247203</v>
+      </c>
+      <c r="AC4" s="9" t="n">
+        <v>1025978.41</v>
+      </c>
+      <c r="AD4" s="10" t="n">
+        <v>0.0796</v>
+      </c>
+      <c r="AE4" s="11" t="n">
+        <v>0.1995596121426969</v>
+      </c>
+      <c r="AF4" s="8" t="n">
         <v>116915576</v>
       </c>
-      <c r="AC4" s="9" t="n">
+      <c r="AG4" s="9" t="n">
         <v>1037918.03</v>
       </c>
-      <c r="AD4" s="10" t="n">
+      <c r="AH4" s="10" t="n">
         <v>0.07729999999999999</v>
       </c>
-      <c r="AE4" s="11" t="n">
+      <c r="AI4" s="11" t="n">
         <v>0.008626968303207154</v>
       </c>
-      <c r="AF4" s="8" t="n">
+      <c r="AJ4" s="8" t="n">
         <v>115915576</v>
       </c>
-      <c r="AG4" s="9" t="n">
+      <c r="AK4" s="9" t="n">
         <v>1077145.49</v>
       </c>
-      <c r="AH4" s="10" t="n">
+      <c r="AL4" s="10" t="n">
         <v>0.0804</v>
       </c>
-      <c r="AI4" s="11" t="n">
+      <c r="AM4" s="11" t="n">
         <v>0.06600587475157653</v>
       </c>
-      <c r="AJ4" s="8" t="n">
+      <c r="AN4" s="8" t="n">
         <v>108738215</v>
       </c>
-      <c r="AK4" s="9" t="n">
+      <c r="AO4" s="9" t="n">
         <v>1077813.19</v>
       </c>
-      <c r="AL4" s="10" t="n">
+      <c r="AP4" s="10" t="n">
         <v>0.0809</v>
       </c>
-      <c r="AM4" s="11" t="n">
+      <c r="AQ4" s="11" t="n">
         <v>0.05075274131724232</v>
       </c>
-      <c r="AN4" s="8" t="n">
+      <c r="AR4" s="8" t="n">
         <v>103486016</v>
       </c>
-      <c r="AO4" s="9" t="n">
+      <c r="AS4" s="9" t="n">
         <v>1042725.1</v>
       </c>
-      <c r="AP4" s="10" t="n">
+      <c r="AT4" s="10" t="n">
         <v>0.0803</v>
       </c>
-      <c r="AQ4" s="11" t="n">
+      <c r="AU4" s="11" t="n">
         <v>0.01255042387516938</v>
       </c>
-      <c r="AR4" s="8" t="n">
+      <c r="AV4" s="8" t="n">
         <v>102203321</v>
       </c>
-      <c r="AS4" s="9" t="n">
+      <c r="AW4" s="9" t="n">
         <v>1009053.39</v>
       </c>
-      <c r="AT4" s="10" t="n">
+      <c r="AX4" s="10" t="n">
         <v>0.08019999999999999</v>
       </c>
-      <c r="AU4" s="11" t="n">
+      <c r="AY4" s="11" t="n">
         <v>0.005262209454604842</v>
       </c>
-      <c r="AV4" s="8" t="n">
+      <c r="AZ4" s="8" t="n">
         <v>101668321</v>
       </c>
-      <c r="AW4" s="9" t="n">
+      <c r="BA4" s="9" t="n">
         <v>966865.73</v>
       </c>
-      <c r="AX4" s="10" t="n">
+      <c r="BB4" s="10" t="n">
         <v>0.0808</v>
       </c>
-      <c r="AY4" s="11" t="n">
+      <c r="BC4" s="11" t="n">
         <v>0.06097375017638836</v>
       </c>
-      <c r="AZ4" s="8" t="n">
+      <c r="BD4" s="8" t="n">
         <v>95825482</v>
       </c>
-      <c r="BA4" s="9" t="n">
+      <c r="BE4" s="9" t="n">
         <v>911875.29</v>
       </c>
-      <c r="BB4" s="10" t="n">
+      <c r="BF4" s="10" t="n">
         <v>0.0793</v>
       </c>
-      <c r="BC4" s="11" t="n">
+      <c r="BG4" s="11" t="n">
         <v>1.135602796681763</v>
       </c>
-      <c r="BD4" s="8" t="n">
+      <c r="BH4" s="8" t="n">
         <v>44870461</v>
       </c>
-      <c r="BE4" s="9" t="n">
+      <c r="BI4" s="9" t="n">
         <v>905575.64</v>
       </c>
-      <c r="BF4" s="10" t="n">
+      <c r="BJ4" s="10" t="n">
         <v>0.0799</v>
       </c>
-      <c r="BG4" s="11" t="n">
+      <c r="BK4" s="11" t="n">
         <v>0.009203290657165424</v>
       </c>
-      <c r="BH4" s="8" t="n">
+      <c r="BL4" s="8" t="n">
         <v>44461271</v>
       </c>
-      <c r="BI4" s="9" t="n">
+      <c r="BM4" s="9" t="n">
         <v>889892.34</v>
       </c>
-      <c r="BJ4" s="10" t="n">
+      <c r="BN4" s="10" t="n">
         <v>0.0806</v>
       </c>
-      <c r="BK4" s="11" t="n">
+      <c r="BO4" s="11" t="n">
         <v>0.026983580212343</v>
       </c>
-      <c r="BL4" s="8" t="n">
+      <c r="BP4" s="8" t="n">
         <v>43293069</v>
       </c>
-      <c r="BM4" s="9" t="n">
+      <c r="BQ4" s="9" t="n">
         <v>842006.9</v>
       </c>
-      <c r="BN4" s="10" t="n">
+      <c r="BR4" s="10" t="n">
         <v>0.08110000000000001</v>
       </c>
-      <c r="BO4" s="11" t="n">
+      <c r="BS4" s="11" t="n">
         <v>0.01121152982515689</v>
-      </c>
-      <c r="BP4" s="8" t="n">
-        <v>42813069</v>
-      </c>
-      <c r="BQ4" s="9" t="n">
-        <v>824151.58</v>
-      </c>
-      <c r="BR4" s="10" t="n">
-        <v>0.08359999999999999</v>
-      </c>
-      <c r="BS4" s="11" t="n">
-        <v>0</v>
       </c>
       <c r="BT4" s="8" t="n">
         <v>42813069</v>
       </c>
       <c r="BU4" s="9" t="n">
-        <v>782708.53</v>
+        <v>824151.58</v>
       </c>
       <c r="BV4" s="10" t="n">
-        <v>0.0838</v>
+        <v>0.08359999999999999</v>
       </c>
       <c r="BW4" s="11" t="n">
         <v>0</v>
@@ -1485,10 +1521,10 @@
         <v>42813069</v>
       </c>
       <c r="BY4" s="9" t="n">
-        <v>741693.61</v>
+        <v>782708.53</v>
       </c>
       <c r="BZ4" s="10" t="n">
-        <v>0.0843</v>
+        <v>0.0838</v>
       </c>
       <c r="CA4" s="11" t="n">
         <v>0</v>
@@ -1497,12 +1533,24 @@
         <v>42813069</v>
       </c>
       <c r="CC4" s="9" t="n">
+        <v>741693.61</v>
+      </c>
+      <c r="CD4" s="10" t="n">
+        <v>0.0843</v>
+      </c>
+      <c r="CE4" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF4" s="8" t="n">
+        <v>42813069</v>
+      </c>
+      <c r="CG4" s="9" t="n">
         <v>727287.01</v>
       </c>
-      <c r="CD4" s="10" t="n">
+      <c r="CH4" s="10" t="n">
         <v>0.08110000000000001</v>
       </c>
-      <c r="CE4" s="11" t="n"/>
+      <c r="CI4" s="11" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -1590,174 +1638,186 @@
         <v>0.0699</v>
       </c>
       <c r="AA5" s="11" t="n">
-        <v>-0.005398666515228007</v>
+        <v>-0.00842648029250833</v>
       </c>
       <c r="AB5" s="8" t="n">
+        <v>312063864</v>
+      </c>
+      <c r="AC5" s="9" t="n">
+        <v>924021.1</v>
+      </c>
+      <c r="AD5" s="10" t="n">
+        <v>0.0716</v>
+      </c>
+      <c r="AE5" s="11" t="n">
+        <v>0.003053544409065615</v>
+      </c>
+      <c r="AF5" s="8" t="n">
         <v>311113864</v>
       </c>
-      <c r="AC5" s="9" t="n">
+      <c r="AG5" s="9" t="n">
         <v>929141.55</v>
       </c>
-      <c r="AD5" s="10" t="n">
+      <c r="AH5" s="10" t="n">
         <v>0.0692</v>
       </c>
-      <c r="AE5" s="11" t="n">
+      <c r="AI5" s="11" t="n">
         <v>-0.007185705380051316</v>
       </c>
-      <c r="AF5" s="8" t="n">
+      <c r="AJ5" s="8" t="n">
         <v>313365617</v>
       </c>
-      <c r="AG5" s="9" t="n">
+      <c r="AK5" s="9" t="n">
         <v>803782.8100000001</v>
       </c>
-      <c r="AH5" s="10" t="n">
+      <c r="AL5" s="10" t="n">
         <v>0.06</v>
       </c>
-      <c r="AI5" s="11" t="n">
+      <c r="AM5" s="11" t="n">
         <v>0.02601784123854898</v>
       </c>
-      <c r="AJ5" s="8" t="n">
+      <c r="AN5" s="8" t="n">
         <v>305419267</v>
       </c>
-      <c r="AK5" s="9" t="n">
+      <c r="AO5" s="9" t="n">
         <v>808139.38</v>
       </c>
-      <c r="AL5" s="10" t="n">
+      <c r="AP5" s="10" t="n">
         <v>0.0606</v>
       </c>
-      <c r="AM5" s="11" t="n">
+      <c r="AQ5" s="11" t="n">
         <v>0.07483622732268541</v>
       </c>
-      <c r="AN5" s="8" t="n">
+      <c r="AR5" s="8" t="n">
         <v>284154236</v>
       </c>
-      <c r="AO5" s="9" t="n">
+      <c r="AS5" s="9" t="n">
         <v>767074.36</v>
       </c>
-      <c r="AP5" s="10" t="n">
+      <c r="AT5" s="10" t="n">
         <v>0.0591</v>
       </c>
-      <c r="AQ5" s="11" t="n">
+      <c r="AU5" s="11" t="n">
         <v>0.08544209611432535</v>
       </c>
-      <c r="AR5" s="8" t="n">
+      <c r="AV5" s="8" t="n">
         <v>261786637</v>
       </c>
-      <c r="AS5" s="9" t="n">
+      <c r="AW5" s="9" t="n">
         <v>754338.1899999999</v>
       </c>
-      <c r="AT5" s="10" t="n">
+      <c r="AX5" s="10" t="n">
         <v>0.06</v>
       </c>
-      <c r="AU5" s="11" t="n">
+      <c r="AY5" s="11" t="n">
         <v>0.02291281861384987</v>
       </c>
-      <c r="AV5" s="8" t="n">
+      <c r="AZ5" s="8" t="n">
         <v>255922726</v>
       </c>
-      <c r="AW5" s="9" t="n">
+      <c r="BA5" s="9" t="n">
         <v>717223.4399999999</v>
       </c>
-      <c r="AX5" s="10" t="n">
+      <c r="BB5" s="10" t="n">
         <v>0.0599</v>
       </c>
-      <c r="AY5" s="11" t="n">
+      <c r="BC5" s="11" t="n">
         <v>0.04012490664854439</v>
       </c>
-      <c r="AZ5" s="8" t="n">
+      <c r="BD5" s="8" t="n">
         <v>246049993</v>
       </c>
-      <c r="BA5" s="9" t="n">
+      <c r="BE5" s="9" t="n">
         <v>677252.61</v>
       </c>
-      <c r="BB5" s="10" t="n">
+      <c r="BF5" s="10" t="n">
         <v>0.0589</v>
       </c>
-      <c r="BC5" s="11" t="n">
+      <c r="BG5" s="11" t="n">
         <v>0.06613218800272164</v>
       </c>
-      <c r="BD5" s="8" t="n">
+      <c r="BH5" s="8" t="n">
         <v>230787510</v>
       </c>
-      <c r="BE5" s="9" t="n">
+      <c r="BI5" s="9" t="n">
         <v>671591.65</v>
       </c>
-      <c r="BF5" s="10" t="n">
+      <c r="BJ5" s="10" t="n">
         <v>0.0593</v>
       </c>
-      <c r="BG5" s="11" t="n">
+      <c r="BK5" s="11" t="n">
         <v>0.02930647191621902</v>
       </c>
-      <c r="BH5" s="8" t="n">
+      <c r="BL5" s="8" t="n">
         <v>224216515</v>
       </c>
-      <c r="BI5" s="9" t="n">
+      <c r="BM5" s="9" t="n">
         <v>672425.33</v>
       </c>
-      <c r="BJ5" s="10" t="n">
+      <c r="BN5" s="10" t="n">
         <v>0.0609</v>
       </c>
-      <c r="BK5" s="11" t="n">
+      <c r="BO5" s="11" t="n">
         <v>0.07348663585077284</v>
       </c>
-      <c r="BL5" s="8" t="n">
+      <c r="BP5" s="8" t="n">
         <v>208867542</v>
       </c>
-      <c r="BM5" s="9" t="n">
+      <c r="BQ5" s="9" t="n">
         <v>605193.7</v>
       </c>
-      <c r="BN5" s="10" t="n">
+      <c r="BR5" s="10" t="n">
         <v>0.0583</v>
       </c>
-      <c r="BO5" s="11" t="n">
+      <c r="BS5" s="11" t="n">
         <v>0.0787685054851275</v>
       </c>
-      <c r="BP5" s="8" t="n">
+      <c r="BT5" s="8" t="n">
         <v>193616648</v>
       </c>
-      <c r="BQ5" s="9" t="n">
+      <c r="BU5" s="9" t="n">
         <v>595274.38</v>
       </c>
-      <c r="BR5" s="10" t="n">
+      <c r="BV5" s="10" t="n">
         <v>0.0604</v>
       </c>
-      <c r="BS5" s="11" t="n">
+      <c r="BW5" s="11" t="n">
         <v>0.004416437745811861</v>
       </c>
-      <c r="BT5" s="8" t="n">
+      <c r="BX5" s="8" t="n">
         <v>192765312</v>
       </c>
-      <c r="BU5" s="9" t="n">
+      <c r="BY5" s="9" t="n">
         <v>559694.08</v>
       </c>
-      <c r="BV5" s="10" t="n">
+      <c r="BZ5" s="10" t="n">
         <v>0.0599</v>
       </c>
-      <c r="BW5" s="11" t="n">
+      <c r="CA5" s="11" t="n">
         <v>-0.003790710650882039</v>
       </c>
-      <c r="BX5" s="8" t="n">
+      <c r="CB5" s="8" t="n">
         <v>193498810</v>
       </c>
-      <c r="BY5" s="9" t="n">
+      <c r="CC5" s="9" t="n">
         <v>485391.76</v>
       </c>
-      <c r="BZ5" s="10" t="n">
+      <c r="CD5" s="10" t="n">
         <v>0.0552</v>
       </c>
-      <c r="CA5" s="11" t="n">
+      <c r="CE5" s="11" t="n">
         <v>0.04268662994371823</v>
       </c>
-      <c r="CB5" s="8" t="n">
+      <c r="CF5" s="8" t="n">
         <v>185577147</v>
       </c>
-      <c r="CC5" s="9" t="n">
+      <c r="CG5" s="9" t="n">
         <v>559793.46</v>
       </c>
-      <c r="CD5" s="10" t="n">
+      <c r="CH5" s="10" t="n">
         <v>0.0624</v>
       </c>
-      <c r="CE5" s="11" t="n"/>
+      <c r="CI5" s="11" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -1845,174 +1905,186 @@
         <v>0.0543</v>
       </c>
       <c r="AA6" s="11" t="n">
-        <v>0.1280505783005292</v>
+        <v>0.08526303507031635</v>
       </c>
       <c r="AB6" s="8" t="n">
+        <v>224093958</v>
+      </c>
+      <c r="AC6" s="9" t="n">
+        <v>644718.3199999999</v>
+      </c>
+      <c r="AD6" s="10" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AE6" s="11" t="n">
+        <v>0.03942596573137731</v>
+      </c>
+      <c r="AF6" s="8" t="n">
         <v>215593958</v>
       </c>
-      <c r="AC6" s="9" t="n">
+      <c r="AG6" s="9" t="n">
         <v>676102.65</v>
       </c>
-      <c r="AD6" s="10" t="n">
+      <c r="AH6" s="10" t="n">
         <v>0.0504</v>
       </c>
-      <c r="AE6" s="11" t="n">
+      <c r="AI6" s="11" t="n">
         <v>0.02712213930725835</v>
       </c>
-      <c r="AF6" s="8" t="n">
+      <c r="AJ6" s="8" t="n">
         <v>209900994</v>
       </c>
-      <c r="AG6" s="9" t="n">
+      <c r="AK6" s="9" t="n">
         <v>676196.05</v>
       </c>
-      <c r="AH6" s="10" t="n">
+      <c r="AL6" s="10" t="n">
         <v>0.0505</v>
       </c>
-      <c r="AI6" s="11" t="n">
+      <c r="AM6" s="11" t="n">
         <v>0.4118991702128273</v>
       </c>
-      <c r="AJ6" s="8" t="n">
+      <c r="AN6" s="8" t="n">
         <v>148665711</v>
       </c>
-      <c r="AK6" s="9" t="n">
+      <c r="AO6" s="9" t="n">
         <v>599122.8199999999</v>
       </c>
-      <c r="AL6" s="10" t="n">
+      <c r="AP6" s="10" t="n">
         <v>0.0449</v>
       </c>
-      <c r="AM6" s="11" t="n">
+      <c r="AQ6" s="11" t="n">
         <v>0.02714259251540287</v>
       </c>
-      <c r="AN6" s="8" t="n">
+      <c r="AR6" s="8" t="n">
         <v>144737169</v>
       </c>
-      <c r="AO6" s="9" t="n">
+      <c r="AS6" s="9" t="n">
         <v>585100.01</v>
       </c>
-      <c r="AP6" s="10" t="n">
+      <c r="AT6" s="10" t="n">
         <v>0.0451</v>
       </c>
-      <c r="AQ6" s="11" t="n">
+      <c r="AU6" s="11" t="n">
         <v>0.04299272879906111</v>
       </c>
-      <c r="AR6" s="8" t="n">
+      <c r="AV6" s="8" t="n">
         <v>138771024</v>
       </c>
-      <c r="AS6" s="9" t="n">
+      <c r="AW6" s="9" t="n">
         <v>583324</v>
       </c>
-      <c r="AT6" s="10" t="n">
+      <c r="AX6" s="10" t="n">
         <v>0.0464</v>
       </c>
-      <c r="AU6" s="11" t="n">
+      <c r="AY6" s="11" t="n">
         <v>0.02247256843567582</v>
       </c>
-      <c r="AV6" s="8" t="n">
+      <c r="AZ6" s="8" t="n">
         <v>135721024</v>
       </c>
-      <c r="AW6" s="9" t="n">
+      <c r="BA6" s="9" t="n">
         <v>544987.77</v>
       </c>
-      <c r="AX6" s="10" t="n">
+      <c r="BB6" s="10" t="n">
         <v>0.0455</v>
       </c>
-      <c r="AY6" s="11" t="n">
+      <c r="BC6" s="11" t="n">
         <v>0.04867833529118113</v>
       </c>
-      <c r="AZ6" s="8" t="n">
+      <c r="BD6" s="8" t="n">
         <v>129421024</v>
       </c>
-      <c r="BA6" s="9" t="n">
+      <c r="BE6" s="9" t="n">
         <v>530302.65</v>
       </c>
-      <c r="BB6" s="10" t="n">
+      <c r="BF6" s="10" t="n">
         <v>0.0461</v>
       </c>
-      <c r="BC6" s="11" t="n">
+      <c r="BG6" s="11" t="n">
         <v>0.05933146465642036</v>
       </c>
-      <c r="BD6" s="8" t="n">
+      <c r="BH6" s="8" t="n">
         <v>122172359</v>
       </c>
-      <c r="BE6" s="9" t="n">
+      <c r="BI6" s="9" t="n">
         <v>503289.03</v>
       </c>
-      <c r="BF6" s="10" t="n">
+      <c r="BJ6" s="10" t="n">
         <v>0.0444</v>
       </c>
-      <c r="BG6" s="11" t="n">
+      <c r="BK6" s="11" t="n">
         <v>0.04045226173662547</v>
       </c>
-      <c r="BH6" s="8" t="n">
+      <c r="BL6" s="8" t="n">
         <v>117422359</v>
       </c>
-      <c r="BI6" s="9" t="n">
+      <c r="BM6" s="9" t="n">
         <v>489005.41</v>
       </c>
-      <c r="BJ6" s="10" t="n">
+      <c r="BN6" s="10" t="n">
         <v>0.0443</v>
       </c>
-      <c r="BK6" s="11" t="n">
+      <c r="BO6" s="11" t="n">
         <v>0.07460089770293252</v>
       </c>
-      <c r="BL6" s="8" t="n">
+      <c r="BP6" s="8" t="n">
         <v>109270669</v>
       </c>
-      <c r="BM6" s="9" t="n">
+      <c r="BQ6" s="9" t="n">
         <v>456806.03</v>
       </c>
-      <c r="BN6" s="10" t="n">
+      <c r="BR6" s="10" t="n">
         <v>0.044</v>
       </c>
-      <c r="BO6" s="11" t="n">
+      <c r="BS6" s="11" t="n">
         <v>0.03799307836597426</v>
       </c>
-      <c r="BP6" s="8" t="n">
+      <c r="BT6" s="8" t="n">
         <v>105271096</v>
       </c>
-      <c r="BQ6" s="9" t="n">
+      <c r="BU6" s="9" t="n">
         <v>448244.33</v>
       </c>
-      <c r="BR6" s="10" t="n">
+      <c r="BV6" s="10" t="n">
         <v>0.0455</v>
       </c>
-      <c r="BS6" s="11" t="n">
+      <c r="BW6" s="11" t="n">
         <v>0.04028866499357868</v>
-      </c>
-      <c r="BT6" s="8" t="n">
-        <v>101194120</v>
-      </c>
-      <c r="BU6" s="9" t="n">
-        <v>414642.91</v>
-      </c>
-      <c r="BV6" s="10" t="n">
-        <v>0.0444</v>
-      </c>
-      <c r="BW6" s="11" t="n">
-        <v>0</v>
       </c>
       <c r="BX6" s="8" t="n">
         <v>101194120</v>
       </c>
       <c r="BY6" s="9" t="n">
+        <v>414642.91</v>
+      </c>
+      <c r="BZ6" s="10" t="n">
+        <v>0.0444</v>
+      </c>
+      <c r="CA6" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB6" s="8" t="n">
+        <v>101194120</v>
+      </c>
+      <c r="CC6" s="9" t="n">
         <v>399716.77</v>
       </c>
-      <c r="BZ6" s="10" t="n">
+      <c r="CD6" s="10" t="n">
         <v>0.0454</v>
       </c>
-      <c r="CA6" s="11" t="n">
+      <c r="CE6" s="11" t="n">
         <v>0.02222354216593874</v>
       </c>
-      <c r="CB6" s="8" t="n">
+      <c r="CF6" s="8" t="n">
         <v>98994120</v>
       </c>
-      <c r="CC6" s="9" t="n">
+      <c r="CG6" s="9" t="n">
         <v>442998.69</v>
       </c>
-      <c r="CD6" s="10" t="n">
+      <c r="CH6" s="10" t="n">
         <v>0.0494</v>
       </c>
-      <c r="CE6" s="11" t="n"/>
+      <c r="CI6" s="11" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -2100,52 +2172,52 @@
         <v>0.0595</v>
       </c>
       <c r="AA7" s="11" t="n">
-        <v>0.07879048239992377</v>
+        <v>-0.003861171338551467</v>
       </c>
       <c r="AB7" s="8" t="n">
+        <v>174817417</v>
+      </c>
+      <c r="AC7" s="9" t="n">
+        <v>787465.05</v>
+      </c>
+      <c r="AD7" s="10" t="n">
+        <v>0.0611</v>
+      </c>
+      <c r="AE7" s="11" t="n">
+        <v>0.08297202293533477</v>
+      </c>
+      <c r="AF7" s="8" t="n">
         <v>161423761</v>
       </c>
-      <c r="AC7" s="9" t="n">
+      <c r="AG7" s="9" t="n">
         <v>695171.4300000001</v>
       </c>
-      <c r="AD7" s="10" t="n">
+      <c r="AH7" s="10" t="n">
         <v>0.0518</v>
       </c>
-      <c r="AE7" s="11" t="n">
+      <c r="AI7" s="11" t="n">
         <v>0.009957016950540437</v>
       </c>
-      <c r="AF7" s="8" t="n">
+      <c r="AJ7" s="8" t="n">
         <v>159832308</v>
       </c>
-      <c r="AG7" s="9" t="n">
+      <c r="AK7" s="9" t="n">
         <v>704460.9</v>
       </c>
-      <c r="AH7" s="10" t="n">
+      <c r="AL7" s="10" t="n">
         <v>0.0526</v>
       </c>
-      <c r="AI7" s="11" t="n">
+      <c r="AM7" s="11" t="n">
         <v>-0.01362167378906329</v>
-      </c>
-      <c r="AJ7" s="8" t="n">
-        <v>162039558</v>
-      </c>
-      <c r="AK7" s="9" t="n">
-        <v>646537.84</v>
-      </c>
-      <c r="AL7" s="10" t="n">
-        <v>0.0485</v>
-      </c>
-      <c r="AM7" s="11" t="n">
-        <v>0</v>
       </c>
       <c r="AN7" s="8" t="n">
         <v>162039558</v>
       </c>
       <c r="AO7" s="9" t="n">
-        <v>609511.8</v>
+        <v>646537.84</v>
       </c>
       <c r="AP7" s="10" t="n">
-        <v>0.047</v>
+        <v>0.0485</v>
       </c>
       <c r="AQ7" s="11" t="n">
         <v>0</v>
@@ -2154,10 +2226,10 @@
         <v>162039558</v>
       </c>
       <c r="AS7" s="9" t="n">
-        <v>629766.74</v>
+        <v>609511.8</v>
       </c>
       <c r="AT7" s="10" t="n">
-        <v>0.0501</v>
+        <v>0.047</v>
       </c>
       <c r="AU7" s="11" t="n">
         <v>0</v>
@@ -2166,10 +2238,10 @@
         <v>162039558</v>
       </c>
       <c r="AW7" s="9" t="n">
-        <v>631873.26</v>
+        <v>629766.74</v>
       </c>
       <c r="AX7" s="10" t="n">
-        <v>0.0528</v>
+        <v>0.0501</v>
       </c>
       <c r="AY7" s="11" t="n">
         <v>0</v>
@@ -2178,7 +2250,7 @@
         <v>162039558</v>
       </c>
       <c r="BA7" s="9" t="n">
-        <v>607324.26</v>
+        <v>631873.26</v>
       </c>
       <c r="BB7" s="10" t="n">
         <v>0.0528</v>
@@ -2190,10 +2262,10 @@
         <v>162039558</v>
       </c>
       <c r="BE7" s="9" t="n">
-        <v>609835.88</v>
+        <v>607324.26</v>
       </c>
       <c r="BF7" s="10" t="n">
-        <v>0.0538</v>
+        <v>0.0528</v>
       </c>
       <c r="BG7" s="11" t="n">
         <v>0</v>
@@ -2202,72 +2274,84 @@
         <v>162039558</v>
       </c>
       <c r="BI7" s="9" t="n">
+        <v>609835.88</v>
+      </c>
+      <c r="BJ7" s="10" t="n">
+        <v>0.0538</v>
+      </c>
+      <c r="BK7" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL7" s="8" t="n">
+        <v>162039558</v>
+      </c>
+      <c r="BM7" s="9" t="n">
         <v>635114.05</v>
       </c>
-      <c r="BJ7" s="10" t="n">
+      <c r="BN7" s="10" t="n">
         <v>0.0575</v>
       </c>
-      <c r="BK7" s="11" t="n">
+      <c r="BO7" s="11" t="n">
         <v>0.0408396826825464</v>
       </c>
-      <c r="BL7" s="8" t="n">
+      <c r="BP7" s="8" t="n">
         <v>155681572</v>
       </c>
-      <c r="BM7" s="9" t="n">
+      <c r="BQ7" s="9" t="n">
         <v>618522.89</v>
       </c>
-      <c r="BN7" s="10" t="n">
+      <c r="BR7" s="10" t="n">
         <v>0.0595</v>
       </c>
-      <c r="BO7" s="11" t="n">
+      <c r="BS7" s="11" t="n">
         <v>0.04960632238493121</v>
       </c>
-      <c r="BP7" s="8" t="n">
+      <c r="BT7" s="8" t="n">
         <v>148323775</v>
       </c>
-      <c r="BQ7" s="9" t="n">
+      <c r="BU7" s="9" t="n">
         <v>571491.51</v>
       </c>
-      <c r="BR7" s="10" t="n">
+      <c r="BV7" s="10" t="n">
         <v>0.058</v>
       </c>
-      <c r="BS7" s="11" t="n">
+      <c r="BW7" s="11" t="n">
         <v>0.05138982123049783</v>
       </c>
-      <c r="BT7" s="8" t="n">
+      <c r="BX7" s="8" t="n">
         <v>141074007</v>
       </c>
-      <c r="BU7" s="9" t="n">
+      <c r="BY7" s="9" t="n">
         <v>561756.7</v>
       </c>
-      <c r="BV7" s="10" t="n">
+      <c r="BZ7" s="10" t="n">
         <v>0.0601</v>
       </c>
-      <c r="BW7" s="11" t="n">
+      <c r="CA7" s="11" t="n">
         <v>-0.01095372515938375</v>
       </c>
-      <c r="BX7" s="8" t="n">
+      <c r="CB7" s="8" t="n">
         <v>142636407</v>
       </c>
-      <c r="BY7" s="9" t="n">
+      <c r="CC7" s="9" t="n">
         <v>526827.5699999999</v>
       </c>
-      <c r="BZ7" s="10" t="n">
+      <c r="CD7" s="10" t="n">
         <v>0.0599</v>
       </c>
-      <c r="CA7" s="11" t="n">
+      <c r="CE7" s="11" t="n">
         <v>0.02369256314048828</v>
       </c>
-      <c r="CB7" s="8" t="n">
+      <c r="CF7" s="8" t="n">
         <v>139335199</v>
       </c>
-      <c r="CC7" s="9" t="n">
+      <c r="CG7" s="9" t="n">
         <v>551628.05</v>
       </c>
-      <c r="CD7" s="10" t="n">
+      <c r="CH7" s="10" t="n">
         <v>0.0615</v>
       </c>
-      <c r="CE7" s="11" t="n"/>
+      <c r="CI7" s="11" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -2355,28 +2439,28 @@
         <v>0.0492</v>
       </c>
       <c r="AA8" s="11" t="n">
-        <v>0.1119295044804045</v>
+        <v>0.01857141851633198</v>
       </c>
       <c r="AB8" s="8" t="n">
-        <v>49325234</v>
+        <v>53846183</v>
       </c>
       <c r="AC8" s="9" t="n">
-        <v>680145.65</v>
+        <v>649331.12</v>
       </c>
       <c r="AD8" s="10" t="n">
-        <v>0.0507</v>
+        <v>0.0503</v>
       </c>
       <c r="AE8" s="11" t="n">
-        <v>0</v>
+        <v>0.09165590577836893</v>
       </c>
       <c r="AF8" s="8" t="n">
         <v>49325234</v>
       </c>
       <c r="AG8" s="9" t="n">
-        <v>668356.92</v>
+        <v>680145.65</v>
       </c>
       <c r="AH8" s="10" t="n">
-        <v>0.0499</v>
+        <v>0.0507</v>
       </c>
       <c r="AI8" s="11" t="n">
         <v>0</v>
@@ -2385,106 +2469,106 @@
         <v>49325234</v>
       </c>
       <c r="AK8" s="9" t="n">
+        <v>668356.92</v>
+      </c>
+      <c r="AL8" s="10" t="n">
+        <v>0.0499</v>
+      </c>
+      <c r="AM8" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN8" s="8" t="n">
+        <v>49325234</v>
+      </c>
+      <c r="AO8" s="9" t="n">
         <v>662388.5699999999</v>
       </c>
-      <c r="AL8" s="10" t="n">
+      <c r="AP8" s="10" t="n">
         <v>0.0497</v>
       </c>
-      <c r="AM8" s="11" t="n">
+      <c r="AQ8" s="11" t="n">
         <v>0.08865063536064391</v>
       </c>
-      <c r="AN8" s="8" t="n">
+      <c r="AR8" s="8" t="n">
         <v>45308598</v>
       </c>
-      <c r="AO8" s="9" t="n">
+      <c r="AS8" s="9" t="n">
         <v>629245.8100000001</v>
       </c>
-      <c r="AP8" s="10" t="n">
+      <c r="AT8" s="10" t="n">
         <v>0.0485</v>
       </c>
-      <c r="AQ8" s="11" t="n">
+      <c r="AU8" s="11" t="n">
         <v>0.04649493840859896</v>
       </c>
-      <c r="AR8" s="8" t="n">
+      <c r="AV8" s="8" t="n">
         <v>43295573</v>
       </c>
-      <c r="AS8" s="9" t="n">
+      <c r="AW8" s="9" t="n">
         <v>582455.34</v>
       </c>
-      <c r="AT8" s="10" t="n">
+      <c r="AX8" s="10" t="n">
         <v>0.0463</v>
       </c>
-      <c r="AU8" s="11" t="n">
+      <c r="AY8" s="11" t="n">
         <v>0.02558297621590971</v>
       </c>
-      <c r="AV8" s="8" t="n">
+      <c r="AZ8" s="8" t="n">
         <v>42215573</v>
       </c>
-      <c r="AW8" s="9" t="n">
+      <c r="BA8" s="9" t="n">
         <v>569065.92</v>
       </c>
-      <c r="AX8" s="10" t="n">
+      <c r="BB8" s="10" t="n">
         <v>0.0475</v>
       </c>
-      <c r="AY8" s="11" t="n">
+      <c r="BC8" s="11" t="n">
         <v>0.03671439253646495</v>
       </c>
-      <c r="AZ8" s="8" t="n">
+      <c r="BD8" s="8" t="n">
         <v>40720543</v>
       </c>
-      <c r="BA8" s="9" t="n">
+      <c r="BE8" s="9" t="n">
         <v>569191.75</v>
       </c>
-      <c r="BB8" s="10" t="n">
+      <c r="BF8" s="10" t="n">
         <v>0.0495</v>
       </c>
-      <c r="BC8" s="11" t="n">
+      <c r="BG8" s="11" t="n">
         <v>0.02815262499999053</v>
       </c>
-      <c r="BD8" s="8" t="n">
+      <c r="BH8" s="8" t="n">
         <v>39605543</v>
       </c>
-      <c r="BE8" s="9" t="n">
+      <c r="BI8" s="9" t="n">
         <v>586716.51</v>
       </c>
-      <c r="BF8" s="10" t="n">
+      <c r="BJ8" s="10" t="n">
         <v>0.0518</v>
       </c>
-      <c r="BG8" s="11" t="n">
+      <c r="BK8" s="11" t="n">
         <v>0.08540125861519442</v>
       </c>
-      <c r="BH8" s="8" t="n">
+      <c r="BL8" s="8" t="n">
         <v>36489310</v>
       </c>
-      <c r="BI8" s="9" t="n">
+      <c r="BM8" s="9" t="n">
         <v>527562.4399999999</v>
       </c>
-      <c r="BJ8" s="10" t="n">
+      <c r="BN8" s="10" t="n">
         <v>0.0478</v>
       </c>
-      <c r="BK8" s="11" t="n">
+      <c r="BO8" s="11" t="n">
         <v>0.04294684214648178</v>
-      </c>
-      <c r="BL8" s="8" t="n">
-        <v>34986740</v>
-      </c>
-      <c r="BM8" s="9" t="n">
-        <v>505838.29</v>
-      </c>
-      <c r="BN8" s="10" t="n">
-        <v>0.0487</v>
-      </c>
-      <c r="BO8" s="11" t="n">
-        <v>0</v>
       </c>
       <c r="BP8" s="8" t="n">
         <v>34986740</v>
       </c>
       <c r="BQ8" s="9" t="n">
-        <v>499260.78</v>
+        <v>505838.29</v>
       </c>
       <c r="BR8" s="10" t="n">
-        <v>0.0507</v>
+        <v>0.0487</v>
       </c>
       <c r="BS8" s="11" t="n">
         <v>0</v>
@@ -2493,10 +2577,10 @@
         <v>34986740</v>
       </c>
       <c r="BU8" s="9" t="n">
-        <v>471743.71</v>
+        <v>499260.78</v>
       </c>
       <c r="BV8" s="10" t="n">
-        <v>0.0505</v>
+        <v>0.0507</v>
       </c>
       <c r="BW8" s="11" t="n">
         <v>0</v>
@@ -2505,10 +2589,10 @@
         <v>34986740</v>
       </c>
       <c r="BY8" s="9" t="n">
-        <v>421275.34</v>
+        <v>471743.71</v>
       </c>
       <c r="BZ8" s="10" t="n">
-        <v>0.0479</v>
+        <v>0.0505</v>
       </c>
       <c r="CA8" s="11" t="n">
         <v>0</v>
@@ -2517,12 +2601,24 @@
         <v>34986740</v>
       </c>
       <c r="CC8" s="9" t="n">
+        <v>421275.34</v>
+      </c>
+      <c r="CD8" s="10" t="n">
+        <v>0.0479</v>
+      </c>
+      <c r="CE8" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF8" s="8" t="n">
+        <v>34986740</v>
+      </c>
+      <c r="CG8" s="9" t="n">
         <v>438313.88</v>
       </c>
-      <c r="CD8" s="10" t="n">
+      <c r="CH8" s="10" t="n">
         <v>0.0489</v>
       </c>
-      <c r="CE8" s="11" t="n"/>
+      <c r="CI8" s="11" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -2616,46 +2712,46 @@
         <v>6026828</v>
       </c>
       <c r="AC9" s="9" t="n">
+        <v>527106.38</v>
+      </c>
+      <c r="AD9" s="10" t="n">
+        <v>0.0409</v>
+      </c>
+      <c r="AE9" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" s="8" t="n">
+        <v>6026828</v>
+      </c>
+      <c r="AG9" s="9" t="n">
         <v>651138.5</v>
       </c>
-      <c r="AD9" s="10" t="n">
+      <c r="AH9" s="10" t="n">
         <v>0.0485</v>
       </c>
-      <c r="AE9" s="11" t="n">
+      <c r="AI9" s="11" t="n">
         <v>0.007956679538397187</v>
       </c>
-      <c r="AF9" s="8" t="n">
+      <c r="AJ9" s="8" t="n">
         <v>5979253</v>
       </c>
-      <c r="AG9" s="9" t="n">
+      <c r="AK9" s="9" t="n">
         <v>645759.3199999999</v>
       </c>
-      <c r="AH9" s="10" t="n">
+      <c r="AL9" s="10" t="n">
         <v>0.0482</v>
       </c>
-      <c r="AI9" s="11" t="n">
+      <c r="AM9" s="11" t="n">
         <v>0.124148370025633</v>
-      </c>
-      <c r="AJ9" s="8" t="n">
-        <v>5318918</v>
-      </c>
-      <c r="AK9" s="9" t="n">
-        <v>602527.03</v>
-      </c>
-      <c r="AL9" s="10" t="n">
-        <v>0.0452</v>
-      </c>
-      <c r="AM9" s="11" t="n">
-        <v>0</v>
       </c>
       <c r="AN9" s="8" t="n">
         <v>5318918</v>
       </c>
       <c r="AO9" s="9" t="n">
-        <v>611622.38</v>
+        <v>602527.03</v>
       </c>
       <c r="AP9" s="10" t="n">
-        <v>0.0471</v>
+        <v>0.0452</v>
       </c>
       <c r="AQ9" s="11" t="n">
         <v>0</v>
@@ -2664,10 +2760,10 @@
         <v>5318918</v>
       </c>
       <c r="AS9" s="9" t="n">
-        <v>654386.48</v>
+        <v>611622.38</v>
       </c>
       <c r="AT9" s="10" t="n">
-        <v>0.052</v>
+        <v>0.0471</v>
       </c>
       <c r="AU9" s="11" t="n">
         <v>0</v>
@@ -2676,10 +2772,10 @@
         <v>5318918</v>
       </c>
       <c r="AW9" s="9" t="n">
-        <v>651407.89</v>
+        <v>654386.48</v>
       </c>
       <c r="AX9" s="10" t="n">
-        <v>0.0544</v>
+        <v>0.052</v>
       </c>
       <c r="AY9" s="11" t="n">
         <v>0</v>
@@ -2688,10 +2784,10 @@
         <v>5318918</v>
       </c>
       <c r="BA9" s="9" t="n">
-        <v>679225.83</v>
+        <v>651407.89</v>
       </c>
       <c r="BB9" s="10" t="n">
-        <v>0.059</v>
+        <v>0.0544</v>
       </c>
       <c r="BC9" s="11" t="n">
         <v>0</v>
@@ -2700,10 +2796,10 @@
         <v>5318918</v>
       </c>
       <c r="BE9" s="9" t="n">
-        <v>742680.52</v>
+        <v>679225.83</v>
       </c>
       <c r="BF9" s="10" t="n">
-        <v>0.06560000000000001</v>
+        <v>0.059</v>
       </c>
       <c r="BG9" s="11" t="n">
         <v>0</v>
@@ -2712,10 +2808,10 @@
         <v>5318918</v>
       </c>
       <c r="BI9" s="9" t="n">
-        <v>764807.22</v>
+        <v>742680.52</v>
       </c>
       <c r="BJ9" s="10" t="n">
-        <v>0.0693</v>
+        <v>0.06560000000000001</v>
       </c>
       <c r="BK9" s="11" t="n">
         <v>0</v>
@@ -2724,10 +2820,10 @@
         <v>5318918</v>
       </c>
       <c r="BM9" s="9" t="n">
-        <v>713479.66</v>
+        <v>764807.22</v>
       </c>
       <c r="BN9" s="10" t="n">
-        <v>0.0687</v>
+        <v>0.0693</v>
       </c>
       <c r="BO9" s="11" t="n">
         <v>0</v>
@@ -2736,10 +2832,10 @@
         <v>5318918</v>
       </c>
       <c r="BQ9" s="9" t="n">
-        <v>636834.05</v>
+        <v>713479.66</v>
       </c>
       <c r="BR9" s="10" t="n">
-        <v>0.0646</v>
+        <v>0.0687</v>
       </c>
       <c r="BS9" s="11" t="n">
         <v>0</v>
@@ -2748,10 +2844,10 @@
         <v>5318918</v>
       </c>
       <c r="BU9" s="9" t="n">
-        <v>663431.3</v>
+        <v>636834.05</v>
       </c>
       <c r="BV9" s="10" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.0646</v>
       </c>
       <c r="BW9" s="11" t="n">
         <v>0</v>
@@ -2760,10 +2856,10 @@
         <v>5318918</v>
       </c>
       <c r="BY9" s="9" t="n">
-        <v>615630.1899999999</v>
+        <v>663431.3</v>
       </c>
       <c r="BZ9" s="10" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="CA9" s="11" t="n">
         <v>0</v>
@@ -2772,12 +2868,24 @@
         <v>5318918</v>
       </c>
       <c r="CC9" s="9" t="n">
+        <v>615630.1899999999</v>
+      </c>
+      <c r="CD9" s="10" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="CE9" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF9" s="8" t="n">
+        <v>5318918</v>
+      </c>
+      <c r="CG9" s="9" t="n">
         <v>614850.96</v>
       </c>
-      <c r="CD9" s="10" t="n">
+      <c r="CH9" s="10" t="n">
         <v>0.06850000000000001</v>
       </c>
-      <c r="CE9" s="11" t="n"/>
+      <c r="CI9" s="11" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -2865,36 +2973,44 @@
         <v>0.0403</v>
       </c>
       <c r="AA10" s="11" t="n">
-        <v>0.2049531565627438</v>
+        <v>0.01180948837975782</v>
       </c>
       <c r="AB10" s="8" t="n">
-        <v>123107960</v>
+        <v>146607960</v>
       </c>
       <c r="AC10" s="9" t="n">
-        <v>511144.25</v>
+        <v>518112.53</v>
       </c>
       <c r="AD10" s="10" t="n">
-        <v>0.0381</v>
+        <v>0.0402</v>
       </c>
       <c r="AE10" s="11" t="n">
-        <v>0</v>
+        <v>0.1908893624750179</v>
       </c>
       <c r="AF10" s="8" t="n">
         <v>123107960</v>
       </c>
       <c r="AG10" s="9" t="n">
+        <v>511144.25</v>
+      </c>
+      <c r="AH10" s="10" t="n">
+        <v>0.0381</v>
+      </c>
+      <c r="AI10" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" s="8" t="n">
+        <v>123107960</v>
+      </c>
+      <c r="AK10" s="9" t="n">
         <v>502280.48</v>
       </c>
-      <c r="AH10" s="10" t="n">
+      <c r="AL10" s="10" t="n">
         <v>0.0375</v>
       </c>
-      <c r="AI10" s="11" t="n">
+      <c r="AM10" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="AJ10" s="8" t="n"/>
-      <c r="AK10" s="9" t="n"/>
-      <c r="AL10" s="10" t="n"/>
-      <c r="AM10" s="11" t="n"/>
       <c r="AN10" s="8" t="n"/>
       <c r="AO10" s="9" t="n"/>
       <c r="AP10" s="10" t="n"/>
@@ -2939,6 +3055,10 @@
       <c r="CC10" s="9" t="n"/>
       <c r="CD10" s="10" t="n"/>
       <c r="CE10" s="11" t="n"/>
+      <c r="CF10" s="8" t="n"/>
+      <c r="CG10" s="9" t="n"/>
+      <c r="CH10" s="10" t="n"/>
+      <c r="CI10" s="11" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -3026,88 +3146,88 @@
         <v>0.0343</v>
       </c>
       <c r="AA11" s="11" t="n">
-        <v>0.4511186421294715</v>
+        <v>0.3492279063625878</v>
       </c>
       <c r="AB11" s="8" t="n">
+        <v>29868916</v>
+      </c>
+      <c r="AC11" s="9" t="n">
+        <v>400721.38</v>
+      </c>
+      <c r="AD11" s="10" t="n">
+        <v>0.0311</v>
+      </c>
+      <c r="AE11" s="11" t="n">
+        <v>0.07551780932368431</v>
+      </c>
+      <c r="AF11" s="8" t="n">
         <v>27771661</v>
       </c>
-      <c r="AC11" s="9" t="n">
+      <c r="AG11" s="9" t="n">
         <v>385776.14</v>
       </c>
-      <c r="AD11" s="10" t="n">
+      <c r="AH11" s="10" t="n">
         <v>0.0287</v>
       </c>
-      <c r="AE11" s="11" t="n">
+      <c r="AI11" s="11" t="n">
         <v>0.1837798947287478</v>
       </c>
-      <c r="AF11" s="8" t="n">
+      <c r="AJ11" s="8" t="n">
         <v>23460156</v>
       </c>
-      <c r="AG11" s="9" t="n">
+      <c r="AK11" s="9" t="n">
         <v>397790.41</v>
       </c>
-      <c r="AH11" s="10" t="n">
+      <c r="AL11" s="10" t="n">
         <v>0.0297</v>
       </c>
-      <c r="AI11" s="11" t="n">
+      <c r="AM11" s="11" t="n">
         <v>0.1005951337129751</v>
       </c>
-      <c r="AJ11" s="8" t="n">
+      <c r="AN11" s="8" t="n">
         <v>21315882</v>
       </c>
-      <c r="AK11" s="9" t="n">
+      <c r="AO11" s="9" t="n">
         <v>346020.71</v>
       </c>
-      <c r="AL11" s="10" t="n">
+      <c r="AP11" s="10" t="n">
         <v>0.026</v>
       </c>
-      <c r="AM11" s="11" t="n">
+      <c r="AQ11" s="11" t="n">
         <v>0.07485632112907131</v>
       </c>
-      <c r="AN11" s="8" t="n">
+      <c r="AR11" s="8" t="n">
         <v>19831378</v>
       </c>
-      <c r="AO11" s="9" t="n">
+      <c r="AS11" s="9" t="n">
         <v>322101.24</v>
       </c>
-      <c r="AP11" s="10" t="n">
+      <c r="AT11" s="10" t="n">
         <v>0.0248</v>
       </c>
-      <c r="AQ11" s="11" t="n">
+      <c r="AU11" s="11" t="n">
         <v>0.09330382775845011</v>
       </c>
-      <c r="AR11" s="8" t="n">
+      <c r="AV11" s="8" t="n">
         <v>18138945</v>
       </c>
-      <c r="AS11" s="9" t="n">
+      <c r="AW11" s="9" t="n">
         <v>279611.84</v>
       </c>
-      <c r="AT11" s="10" t="n">
+      <c r="AX11" s="10" t="n">
         <v>0.0222</v>
       </c>
-      <c r="AU11" s="11" t="n">
+      <c r="AY11" s="11" t="n">
         <v>-0.0303656466471499</v>
-      </c>
-      <c r="AV11" s="8" t="n">
-        <v>18706995</v>
-      </c>
-      <c r="AW11" s="9" t="n">
-        <v>259110.59</v>
-      </c>
-      <c r="AX11" s="10" t="n">
-        <v>0.0216</v>
-      </c>
-      <c r="AY11" s="11" t="n">
-        <v>0</v>
       </c>
       <c r="AZ11" s="8" t="n">
         <v>18706995</v>
       </c>
       <c r="BA11" s="9" t="n">
-        <v>272149.36</v>
+        <v>259110.59</v>
       </c>
       <c r="BB11" s="10" t="n">
-        <v>0.0237</v>
+        <v>0.0216</v>
       </c>
       <c r="BC11" s="11" t="n">
         <v>0</v>
@@ -3116,58 +3236,58 @@
         <v>18706995</v>
       </c>
       <c r="BE11" s="9" t="n">
+        <v>272149.36</v>
+      </c>
+      <c r="BF11" s="10" t="n">
+        <v>0.0237</v>
+      </c>
+      <c r="BG11" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH11" s="8" t="n">
+        <v>18706995</v>
+      </c>
+      <c r="BI11" s="9" t="n">
         <v>274599.98</v>
       </c>
-      <c r="BF11" s="10" t="n">
+      <c r="BJ11" s="10" t="n">
         <v>0.0242</v>
       </c>
-      <c r="BG11" s="11" t="n">
+      <c r="BK11" s="11" t="n">
         <v>0.00797456974367416</v>
       </c>
-      <c r="BH11" s="8" t="n">
+      <c r="BL11" s="8" t="n">
         <v>18558995</v>
       </c>
-      <c r="BI11" s="9" t="n">
+      <c r="BM11" s="9" t="n">
         <v>320810.79</v>
       </c>
-      <c r="BJ11" s="10" t="n">
+      <c r="BN11" s="10" t="n">
         <v>0.0291</v>
       </c>
-      <c r="BK11" s="11" t="n">
+      <c r="BO11" s="11" t="n">
         <v>0.01185405417517898</v>
       </c>
-      <c r="BL11" s="8" t="n">
+      <c r="BP11" s="8" t="n">
         <v>18341573</v>
       </c>
-      <c r="BM11" s="9" t="n">
+      <c r="BQ11" s="9" t="n">
         <v>300178.18</v>
       </c>
-      <c r="BN11" s="10" t="n">
+      <c r="BR11" s="10" t="n">
         <v>0.0289</v>
       </c>
-      <c r="BO11" s="11" t="n">
+      <c r="BS11" s="11" t="n">
         <v>-0.01953282340226823</v>
-      </c>
-      <c r="BP11" s="8" t="n">
-        <v>18706973</v>
-      </c>
-      <c r="BQ11" s="9" t="n">
-        <v>293231.8</v>
-      </c>
-      <c r="BR11" s="10" t="n">
-        <v>0.0298</v>
-      </c>
-      <c r="BS11" s="11" t="n">
-        <v>0</v>
       </c>
       <c r="BT11" s="8" t="n">
         <v>18706973</v>
       </c>
       <c r="BU11" s="9" t="n">
-        <v>297908.55</v>
+        <v>293231.8</v>
       </c>
       <c r="BV11" s="10" t="n">
-        <v>0.0319</v>
+        <v>0.0298</v>
       </c>
       <c r="BW11" s="11" t="n">
         <v>0</v>
@@ -3176,10 +3296,10 @@
         <v>18706973</v>
       </c>
       <c r="BY11" s="9" t="n">
-        <v>294644.18</v>
+        <v>297908.55</v>
       </c>
       <c r="BZ11" s="10" t="n">
-        <v>0.0335</v>
+        <v>0.0319</v>
       </c>
       <c r="CA11" s="11" t="n">
         <v>0</v>
@@ -3188,12 +3308,24 @@
         <v>18706973</v>
       </c>
       <c r="CC11" s="9" t="n">
+        <v>294644.18</v>
+      </c>
+      <c r="CD11" s="10" t="n">
+        <v>0.0335</v>
+      </c>
+      <c r="CE11" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF11" s="8" t="n">
+        <v>18706973</v>
+      </c>
+      <c r="CG11" s="9" t="n">
         <v>322779.47</v>
       </c>
-      <c r="CD11" s="10" t="n">
+      <c r="CH11" s="10" t="n">
         <v>0.036</v>
       </c>
-      <c r="CE11" s="11" t="n"/>
+      <c r="CI11" s="11" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -3281,88 +3413,88 @@
         <v>0.0352</v>
       </c>
       <c r="AA12" s="11" t="n">
-        <v>0.1467846415582418</v>
+        <v>0.0942516216104385</v>
       </c>
       <c r="AB12" s="8" t="n">
-        <v>13974725</v>
+        <v>14645626</v>
       </c>
       <c r="AC12" s="9" t="n">
-        <v>474777.31</v>
+        <v>432734.31</v>
       </c>
       <c r="AD12" s="10" t="n">
-        <v>0.0354</v>
+        <v>0.0336</v>
       </c>
       <c r="AE12" s="11" t="n">
-        <v>0</v>
+        <v>0.04800817189604804</v>
       </c>
       <c r="AF12" s="8" t="n">
         <v>13974725</v>
       </c>
       <c r="AG12" s="9" t="n">
+        <v>474777.31</v>
+      </c>
+      <c r="AH12" s="10" t="n">
+        <v>0.0354</v>
+      </c>
+      <c r="AI12" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ12" s="8" t="n">
+        <v>13974725</v>
+      </c>
+      <c r="AK12" s="9" t="n">
         <v>479584.61</v>
       </c>
-      <c r="AH12" s="10" t="n">
+      <c r="AL12" s="10" t="n">
         <v>0.0358</v>
       </c>
-      <c r="AI12" s="11" t="n">
+      <c r="AM12" s="11" t="n">
         <v>0.07221829643218575</v>
       </c>
-      <c r="AJ12" s="8" t="n">
+      <c r="AN12" s="8" t="n">
         <v>13033470</v>
       </c>
-      <c r="AK12" s="9" t="n">
+      <c r="AO12" s="9" t="n">
         <v>483437.47</v>
       </c>
-      <c r="AL12" s="10" t="n">
+      <c r="AP12" s="10" t="n">
         <v>0.0363</v>
       </c>
-      <c r="AM12" s="11" t="n">
+      <c r="AQ12" s="11" t="n">
         <v>0.0480713103458591</v>
-      </c>
-      <c r="AN12" s="8" t="n">
-        <v>12435671</v>
-      </c>
-      <c r="AO12" s="9" t="n">
-        <v>467245.47</v>
-      </c>
-      <c r="AP12" s="10" t="n">
-        <v>0.036</v>
-      </c>
-      <c r="AQ12" s="11" t="n">
-        <v>0</v>
       </c>
       <c r="AR12" s="8" t="n">
         <v>12435671</v>
       </c>
       <c r="AS12" s="9" t="n">
+        <v>467245.47</v>
+      </c>
+      <c r="AT12" s="10" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="AU12" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV12" s="8" t="n">
+        <v>12435671</v>
+      </c>
+      <c r="AW12" s="9" t="n">
         <v>433656.72</v>
       </c>
-      <c r="AT12" s="10" t="n">
+      <c r="AX12" s="10" t="n">
         <v>0.0345</v>
       </c>
-      <c r="AU12" s="11" t="n">
+      <c r="AY12" s="11" t="n">
         <v>0.008106571584148119</v>
-      </c>
-      <c r="AV12" s="8" t="n">
-        <v>12335671</v>
-      </c>
-      <c r="AW12" s="9" t="n">
-        <v>422743.45</v>
-      </c>
-      <c r="AX12" s="10" t="n">
-        <v>0.0353</v>
-      </c>
-      <c r="AY12" s="11" t="n">
-        <v>0</v>
       </c>
       <c r="AZ12" s="8" t="n">
         <v>12335671</v>
       </c>
       <c r="BA12" s="9" t="n">
-        <v>394679.79</v>
+        <v>422743.45</v>
       </c>
       <c r="BB12" s="10" t="n">
-        <v>0.0343</v>
+        <v>0.0353</v>
       </c>
       <c r="BC12" s="11" t="n">
         <v>0</v>
@@ -3371,10 +3503,10 @@
         <v>12335671</v>
       </c>
       <c r="BE12" s="9" t="n">
-        <v>395123.88</v>
+        <v>394679.79</v>
       </c>
       <c r="BF12" s="10" t="n">
-        <v>0.0349</v>
+        <v>0.0343</v>
       </c>
       <c r="BG12" s="11" t="n">
         <v>0</v>
@@ -3383,72 +3515,84 @@
         <v>12335671</v>
       </c>
       <c r="BI12" s="9" t="n">
+        <v>395123.88</v>
+      </c>
+      <c r="BJ12" s="10" t="n">
+        <v>0.0349</v>
+      </c>
+      <c r="BK12" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL12" s="8" t="n">
+        <v>12335671</v>
+      </c>
+      <c r="BM12" s="9" t="n">
         <v>392669.08</v>
       </c>
-      <c r="BJ12" s="10" t="n">
+      <c r="BN12" s="10" t="n">
         <v>0.0356</v>
       </c>
-      <c r="BK12" s="11" t="n">
+      <c r="BO12" s="11" t="n">
         <v>0.00852700604200313</v>
       </c>
-      <c r="BL12" s="8" t="n">
+      <c r="BP12" s="8" t="n">
         <v>12231374</v>
       </c>
-      <c r="BM12" s="9" t="n">
+      <c r="BQ12" s="9" t="n">
         <v>364103.54</v>
       </c>
-      <c r="BN12" s="10" t="n">
+      <c r="BR12" s="10" t="n">
         <v>0.0351</v>
       </c>
-      <c r="BO12" s="11" t="n">
+      <c r="BS12" s="11" t="n">
         <v>0.1078930368366115</v>
       </c>
-      <c r="BP12" s="8" t="n">
+      <c r="BT12" s="8" t="n">
         <v>11040212</v>
       </c>
-      <c r="BQ12" s="9" t="n">
+      <c r="BU12" s="9" t="n">
         <v>323345.73</v>
       </c>
-      <c r="BR12" s="10" t="n">
+      <c r="BV12" s="10" t="n">
         <v>0.0328</v>
       </c>
-      <c r="BS12" s="11" t="n">
+      <c r="BW12" s="11" t="n">
         <v>0.06163142499453569</v>
       </c>
-      <c r="BT12" s="8" t="n">
+      <c r="BX12" s="8" t="n">
         <v>10399289</v>
       </c>
-      <c r="BU12" s="9" t="n">
+      <c r="BY12" s="9" t="n">
         <v>277224.25</v>
       </c>
-      <c r="BV12" s="10" t="n">
+      <c r="BZ12" s="10" t="n">
         <v>0.0297</v>
       </c>
-      <c r="BW12" s="11" t="n">
+      <c r="CA12" s="11" t="n">
         <v>0.03283692525275198</v>
       </c>
-      <c r="BX12" s="8" t="n">
+      <c r="CB12" s="8" t="n">
         <v>10068665</v>
       </c>
-      <c r="BY12" s="9" t="n">
+      <c r="CC12" s="9" t="n">
         <v>260285.06</v>
       </c>
-      <c r="BZ12" s="10" t="n">
+      <c r="CD12" s="10" t="n">
         <v>0.0296</v>
       </c>
-      <c r="CA12" s="11" t="n">
+      <c r="CE12" s="11" t="n">
         <v>0.07897007813229198</v>
       </c>
-      <c r="CB12" s="8" t="n">
+      <c r="CF12" s="8" t="n">
         <v>9331737</v>
       </c>
-      <c r="CC12" s="9" t="n">
+      <c r="CG12" s="9" t="n">
         <v>279004.94</v>
       </c>
-      <c r="CD12" s="10" t="n">
+      <c r="CH12" s="10" t="n">
         <v>0.0311</v>
       </c>
-      <c r="CE12" s="11" t="n"/>
+      <c r="CI12" s="11" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -3536,76 +3680,76 @@
         <v>0.0303</v>
       </c>
       <c r="AA13" s="11" t="n">
-        <v>0.7478605305716015</v>
+        <v>0.342400003741088</v>
       </c>
       <c r="AB13" s="8" t="n">
+        <v>26944033</v>
+      </c>
+      <c r="AC13" s="9" t="n">
+        <v>336962.08</v>
+      </c>
+      <c r="AD13" s="10" t="n">
+        <v>0.0261</v>
+      </c>
+      <c r="AE13" s="11" t="n">
+        <v>0.302041511993854</v>
+      </c>
+      <c r="AF13" s="8" t="n">
         <v>20693682</v>
       </c>
-      <c r="AC13" s="9" t="n">
+      <c r="AG13" s="9" t="n">
         <v>269038.56</v>
       </c>
-      <c r="AD13" s="10" t="n">
+      <c r="AH13" s="10" t="n">
         <v>0.02</v>
       </c>
-      <c r="AE13" s="11" t="n">
+      <c r="AI13" s="11" t="n">
         <v>0.2534377545687067</v>
       </c>
-      <c r="AF13" s="8" t="n">
+      <c r="AJ13" s="8" t="n">
         <v>16509541</v>
       </c>
-      <c r="AG13" s="9" t="n">
+      <c r="AK13" s="9" t="n">
         <v>270921.57</v>
       </c>
-      <c r="AH13" s="10" t="n">
+      <c r="AL13" s="10" t="n">
         <v>0.0202</v>
       </c>
-      <c r="AI13" s="11" t="n">
+      <c r="AM13" s="11" t="n">
         <v>0.005579568588889614</v>
       </c>
-      <c r="AJ13" s="8" t="n">
+      <c r="AN13" s="8" t="n">
         <v>16417936</v>
       </c>
-      <c r="AK13" s="9" t="n">
+      <c r="AO13" s="9" t="n">
         <v>265215.34</v>
       </c>
-      <c r="AL13" s="10" t="n">
+      <c r="AP13" s="10" t="n">
         <v>0.0199</v>
       </c>
-      <c r="AM13" s="11" t="n">
+      <c r="AQ13" s="11" t="n">
         <v>-0.06831357175852101</v>
       </c>
-      <c r="AN13" s="8" t="n">
+      <c r="AR13" s="8" t="n">
         <v>17621740</v>
       </c>
-      <c r="AO13" s="9" t="n">
+      <c r="AS13" s="9" t="n">
         <v>274916.77</v>
       </c>
-      <c r="AP13" s="10" t="n">
+      <c r="AT13" s="10" t="n">
         <v>0.0212</v>
       </c>
-      <c r="AQ13" s="11" t="n">
+      <c r="AU13" s="11" t="n">
         <v>0.8934928409505942</v>
-      </c>
-      <c r="AR13" s="8" t="n">
-        <v>9306473</v>
-      </c>
-      <c r="AS13" s="9" t="n">
-        <v>137949.85</v>
-      </c>
-      <c r="AT13" s="10" t="n">
-        <v>0.011</v>
-      </c>
-      <c r="AU13" s="11" t="n">
-        <v>0</v>
       </c>
       <c r="AV13" s="8" t="n">
         <v>9306473</v>
       </c>
       <c r="AW13" s="9" t="n">
-        <v>134180.73</v>
+        <v>137949.85</v>
       </c>
       <c r="AX13" s="10" t="n">
-        <v>0.0112</v>
+        <v>0.011</v>
       </c>
       <c r="AY13" s="11" t="n">
         <v>0</v>
@@ -3614,10 +3758,10 @@
         <v>9306473</v>
       </c>
       <c r="BA13" s="9" t="n">
-        <v>136767.93</v>
+        <v>134180.73</v>
       </c>
       <c r="BB13" s="10" t="n">
-        <v>0.0119</v>
+        <v>0.0112</v>
       </c>
       <c r="BC13" s="11" t="n">
         <v>0</v>
@@ -3626,10 +3770,10 @@
         <v>9306473</v>
       </c>
       <c r="BE13" s="9" t="n">
-        <v>140434.68</v>
+        <v>136767.93</v>
       </c>
       <c r="BF13" s="10" t="n">
-        <v>0.0124</v>
+        <v>0.0119</v>
       </c>
       <c r="BG13" s="11" t="n">
         <v>0</v>
@@ -3638,10 +3782,10 @@
         <v>9306473</v>
       </c>
       <c r="BI13" s="9" t="n">
-        <v>149071.08</v>
+        <v>140434.68</v>
       </c>
       <c r="BJ13" s="10" t="n">
-        <v>0.0135</v>
+        <v>0.0124</v>
       </c>
       <c r="BK13" s="11" t="n">
         <v>0</v>
@@ -3650,10 +3794,10 @@
         <v>9306473</v>
       </c>
       <c r="BM13" s="9" t="n">
-        <v>145432.25</v>
+        <v>149071.08</v>
       </c>
       <c r="BN13" s="10" t="n">
-        <v>0.014</v>
+        <v>0.0135</v>
       </c>
       <c r="BO13" s="11" t="n">
         <v>0</v>
@@ -3662,10 +3806,10 @@
         <v>9306473</v>
       </c>
       <c r="BQ13" s="9" t="n">
-        <v>139606.4</v>
+        <v>145432.25</v>
       </c>
       <c r="BR13" s="10" t="n">
-        <v>0.0142</v>
+        <v>0.014</v>
       </c>
       <c r="BS13" s="11" t="n">
         <v>0</v>
@@ -3674,10 +3818,10 @@
         <v>9306473</v>
       </c>
       <c r="BU13" s="9" t="n">
-        <v>146172.12</v>
+        <v>139606.4</v>
       </c>
       <c r="BV13" s="10" t="n">
-        <v>0.0156</v>
+        <v>0.0142</v>
       </c>
       <c r="BW13" s="11" t="n">
         <v>0</v>
@@ -3686,10 +3830,10 @@
         <v>9306473</v>
       </c>
       <c r="BY13" s="9" t="n">
-        <v>157065.34</v>
+        <v>146172.12</v>
       </c>
       <c r="BZ13" s="10" t="n">
-        <v>0.0178</v>
+        <v>0.0156</v>
       </c>
       <c r="CA13" s="11" t="n">
         <v>0</v>
@@ -3698,12 +3842,24 @@
         <v>9306473</v>
       </c>
       <c r="CC13" s="9" t="n">
+        <v>157065.34</v>
+      </c>
+      <c r="CD13" s="10" t="n">
+        <v>0.0178</v>
+      </c>
+      <c r="CE13" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF13" s="8" t="n">
+        <v>9306473</v>
+      </c>
+      <c r="CG13" s="9" t="n">
         <v>174943.08</v>
       </c>
-      <c r="CD13" s="10" t="n">
+      <c r="CH13" s="10" t="n">
         <v>0.0195</v>
       </c>
-      <c r="CE13" s="11" t="n"/>
+      <c r="CI13" s="11" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -3797,10 +3953,10 @@
         <v>21167034</v>
       </c>
       <c r="AC14" s="9" t="n">
-        <v>397792.07</v>
+        <v>377281.21</v>
       </c>
       <c r="AD14" s="10" t="n">
-        <v>0.0296</v>
+        <v>0.0293</v>
       </c>
       <c r="AE14" s="11" t="n">
         <v>0</v>
@@ -3809,10 +3965,10 @@
         <v>21167034</v>
       </c>
       <c r="AG14" s="9" t="n">
-        <v>416715.398358</v>
+        <v>397792.07</v>
       </c>
       <c r="AH14" s="10" t="n">
-        <v>0.0311051731198606</v>
+        <v>0.0296</v>
       </c>
       <c r="AI14" s="11" t="n">
         <v>0</v>
@@ -3821,10 +3977,10 @@
         <v>21167034</v>
       </c>
       <c r="AK14" s="9" t="n">
-        <v>445693.07</v>
+        <v>416715.398358</v>
       </c>
       <c r="AL14" s="10" t="n">
-        <v>0.0334</v>
+        <v>0.0311051731198606</v>
       </c>
       <c r="AM14" s="11" t="n">
         <v>0</v>
@@ -3833,10 +3989,10 @@
         <v>21167034</v>
       </c>
       <c r="AO14" s="9" t="n">
-        <v>444846.39</v>
+        <v>445693.07</v>
       </c>
       <c r="AP14" s="10" t="n">
-        <v>0.0343</v>
+        <v>0.0334</v>
       </c>
       <c r="AQ14" s="11" t="n">
         <v>0</v>
@@ -3845,10 +4001,10 @@
         <v>21167034</v>
       </c>
       <c r="AS14" s="9" t="n">
-        <v>434876.71</v>
+        <v>444846.39</v>
       </c>
       <c r="AT14" s="10" t="n">
-        <v>0.0346</v>
+        <v>0.0343</v>
       </c>
       <c r="AU14" s="11" t="n">
         <v>0</v>
@@ -3857,10 +4013,10 @@
         <v>21167034</v>
       </c>
       <c r="AW14" s="9" t="n">
-        <v>397601.57</v>
+        <v>434876.71</v>
       </c>
       <c r="AX14" s="10" t="n">
-        <v>0.0332</v>
+        <v>0.0346</v>
       </c>
       <c r="AY14" s="11" t="n">
         <v>0</v>
@@ -3869,10 +4025,10 @@
         <v>21167034</v>
       </c>
       <c r="BA14" s="9" t="n">
-        <v>399802.94</v>
+        <v>397601.57</v>
       </c>
       <c r="BB14" s="10" t="n">
-        <v>0.0348</v>
+        <v>0.0332</v>
       </c>
       <c r="BC14" s="11" t="n">
         <v>0</v>
@@ -3881,42 +4037,50 @@
         <v>21167034</v>
       </c>
       <c r="BE14" s="9" t="n">
+        <v>399802.94</v>
+      </c>
+      <c r="BF14" s="10" t="n">
+        <v>0.0348</v>
+      </c>
+      <c r="BG14" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH14" s="8" t="n">
+        <v>21167034</v>
+      </c>
+      <c r="BI14" s="9" t="n">
         <v>405200.53</v>
       </c>
-      <c r="BF14" s="10" t="n">
+      <c r="BJ14" s="10" t="n">
         <v>0.0358</v>
       </c>
-      <c r="BG14" s="11" t="n">
+      <c r="BK14" s="11" t="n">
         <v>0.01098531912399817</v>
       </c>
-      <c r="BH14" s="8" t="n">
+      <c r="BL14" s="8" t="n">
         <v>20937034</v>
       </c>
-      <c r="BI14" s="9" t="n">
+      <c r="BM14" s="9" t="n">
         <v>420750.64</v>
       </c>
-      <c r="BJ14" s="10" t="n">
+      <c r="BN14" s="10" t="n">
         <v>0.0381</v>
       </c>
-      <c r="BK14" s="11" t="n">
+      <c r="BO14" s="11" t="n">
         <v>0.7744638647975486</v>
       </c>
-      <c r="BL14" s="8" t="n">
+      <c r="BP14" s="8" t="n">
         <v>11799076</v>
       </c>
-      <c r="BM14" s="9" t="n">
+      <c r="BQ14" s="9" t="n">
         <v>219014.45</v>
       </c>
-      <c r="BN14" s="10" t="n">
+      <c r="BR14" s="10" t="n">
         <v>0.0211</v>
       </c>
-      <c r="BO14" s="11" t="n">
+      <c r="BS14" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="BP14" s="8" t="n"/>
-      <c r="BQ14" s="9" t="n"/>
-      <c r="BR14" s="10" t="n"/>
-      <c r="BS14" s="11" t="n"/>
       <c r="BT14" s="8" t="n"/>
       <c r="BU14" s="9" t="n"/>
       <c r="BV14" s="10" t="n"/>
@@ -3929,6 +4093,10 @@
       <c r="CC14" s="9" t="n"/>
       <c r="CD14" s="10" t="n"/>
       <c r="CE14" s="11" t="n"/>
+      <c r="CF14" s="8" t="n"/>
+      <c r="CG14" s="9" t="n"/>
+      <c r="CH14" s="10" t="n"/>
+      <c r="CI14" s="11" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -4022,10 +4190,10 @@
         <v>33244875</v>
       </c>
       <c r="AC15" s="9" t="n">
-        <v>460075.83</v>
+        <v>386072.73</v>
       </c>
       <c r="AD15" s="10" t="n">
-        <v>0.0343</v>
+        <v>0.0299</v>
       </c>
       <c r="AE15" s="11" t="n">
         <v>0</v>
@@ -4034,10 +4202,10 @@
         <v>33244875</v>
       </c>
       <c r="AG15" s="9" t="n">
-        <v>455587.77</v>
+        <v>460075.83</v>
       </c>
       <c r="AH15" s="10" t="n">
-        <v>0.034</v>
+        <v>0.0343</v>
       </c>
       <c r="AI15" s="11" t="n">
         <v>0</v>
@@ -4046,10 +4214,10 @@
         <v>33244875</v>
       </c>
       <c r="AK15" s="9" t="n">
-        <v>422010.44</v>
+        <v>455587.77</v>
       </c>
       <c r="AL15" s="10" t="n">
-        <v>0.0317</v>
+        <v>0.034</v>
       </c>
       <c r="AM15" s="11" t="n">
         <v>0</v>
@@ -4058,10 +4226,10 @@
         <v>33244875</v>
       </c>
       <c r="AO15" s="9" t="n">
-        <v>425434.67</v>
+        <v>422010.44</v>
       </c>
       <c r="AP15" s="10" t="n">
-        <v>0.0328</v>
+        <v>0.0317</v>
       </c>
       <c r="AQ15" s="11" t="n">
         <v>0</v>
@@ -4070,10 +4238,10 @@
         <v>33244875</v>
       </c>
       <c r="AS15" s="9" t="n">
-        <v>409842.82</v>
+        <v>425434.67</v>
       </c>
       <c r="AT15" s="10" t="n">
-        <v>0.0326</v>
+        <v>0.0328</v>
       </c>
       <c r="AU15" s="11" t="n">
         <v>0</v>
@@ -4082,58 +4250,58 @@
         <v>33244875</v>
       </c>
       <c r="AW15" s="9" t="n">
+        <v>409842.82</v>
+      </c>
+      <c r="AX15" s="10" t="n">
+        <v>0.0326</v>
+      </c>
+      <c r="AY15" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ15" s="8" t="n">
+        <v>33244875</v>
+      </c>
+      <c r="BA15" s="9" t="n">
         <v>376199.01</v>
       </c>
-      <c r="AX15" s="10" t="n">
+      <c r="BB15" s="10" t="n">
         <v>0.0314</v>
       </c>
-      <c r="AY15" s="11" t="n">
+      <c r="BC15" s="11" t="n">
         <v>0.01837960782511803</v>
       </c>
-      <c r="AZ15" s="8" t="n">
+      <c r="BD15" s="8" t="n">
         <v>32644875</v>
       </c>
-      <c r="BA15" s="9" t="n">
+      <c r="BE15" s="9" t="n">
         <v>341204.23</v>
       </c>
-      <c r="BB15" s="10" t="n">
+      <c r="BF15" s="10" t="n">
         <v>0.0297</v>
       </c>
-      <c r="BC15" s="11" t="n">
+      <c r="BG15" s="11" t="n">
         <v>0.0842854566355568</v>
       </c>
-      <c r="BD15" s="8" t="n">
+      <c r="BH15" s="8" t="n">
         <v>30107270</v>
       </c>
-      <c r="BE15" s="9" t="n">
+      <c r="BI15" s="9" t="n">
         <v>321666.07</v>
       </c>
-      <c r="BF15" s="10" t="n">
+      <c r="BJ15" s="10" t="n">
         <v>0.0284</v>
       </c>
-      <c r="BG15" s="11" t="n">
+      <c r="BK15" s="11" t="n">
         <v>0.1045592607036581</v>
-      </c>
-      <c r="BH15" s="8" t="n">
-        <v>27257270</v>
-      </c>
-      <c r="BI15" s="9" t="n">
-        <v>326869.18</v>
-      </c>
-      <c r="BJ15" s="10" t="n">
-        <v>0.0296</v>
-      </c>
-      <c r="BK15" s="11" t="n">
-        <v>0</v>
       </c>
       <c r="BL15" s="8" t="n">
         <v>27257270</v>
       </c>
       <c r="BM15" s="9" t="n">
-        <v>324961.17</v>
+        <v>326869.18</v>
       </c>
       <c r="BN15" s="10" t="n">
-        <v>0.0313</v>
+        <v>0.0296</v>
       </c>
       <c r="BO15" s="11" t="n">
         <v>0</v>
@@ -4142,10 +4310,10 @@
         <v>27257270</v>
       </c>
       <c r="BQ15" s="9" t="n">
-        <v>322998.65</v>
+        <v>324961.17</v>
       </c>
       <c r="BR15" s="10" t="n">
-        <v>0.0328</v>
+        <v>0.0313</v>
       </c>
       <c r="BS15" s="11" t="n">
         <v>0</v>
@@ -4154,10 +4322,10 @@
         <v>27257270</v>
       </c>
       <c r="BU15" s="9" t="n">
-        <v>300375.12</v>
+        <v>322998.65</v>
       </c>
       <c r="BV15" s="10" t="n">
-        <v>0.0321</v>
+        <v>0.0328</v>
       </c>
       <c r="BW15" s="11" t="n">
         <v>0</v>
@@ -4166,10 +4334,10 @@
         <v>27257270</v>
       </c>
       <c r="BY15" s="9" t="n">
-        <v>276811.21</v>
+        <v>300375.12</v>
       </c>
       <c r="BZ15" s="10" t="n">
-        <v>0.0315</v>
+        <v>0.0321</v>
       </c>
       <c r="CA15" s="11" t="n">
         <v>0</v>
@@ -4178,12 +4346,24 @@
         <v>27257270</v>
       </c>
       <c r="CC15" s="9" t="n">
+        <v>276811.21</v>
+      </c>
+      <c r="CD15" s="10" t="n">
+        <v>0.0315</v>
+      </c>
+      <c r="CE15" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF15" s="8" t="n">
+        <v>27257270</v>
+      </c>
+      <c r="CG15" s="9" t="n">
         <v>268783.94</v>
       </c>
-      <c r="CD15" s="10" t="n">
+      <c r="CH15" s="10" t="n">
         <v>0.03</v>
       </c>
-      <c r="CE15" s="11" t="n"/>
+      <c r="CI15" s="11" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -4271,60 +4451,68 @@
         <v>0.0279</v>
       </c>
       <c r="AA16" s="11" t="n">
-        <v>0.5296260686972589</v>
+        <v>0.2789485718226543</v>
       </c>
       <c r="AB16" s="8" t="n">
+        <v>12412184</v>
+      </c>
+      <c r="AC16" s="9" t="n">
+        <v>292791.01</v>
+      </c>
+      <c r="AD16" s="10" t="n">
+        <v>0.0227</v>
+      </c>
+      <c r="AE16" s="11" t="n">
+        <v>0.1960027966702049</v>
+      </c>
+      <c r="AF16" s="8" t="n">
         <v>10378056</v>
       </c>
-      <c r="AC16" s="9" t="n">
+      <c r="AG16" s="9" t="n">
         <v>273710.85</v>
       </c>
-      <c r="AD16" s="10" t="n">
+      <c r="AH16" s="10" t="n">
         <v>0.0204</v>
       </c>
-      <c r="AE16" s="11" t="n">
+      <c r="AI16" s="11" t="n">
         <v>0.2259018504190464</v>
       </c>
-      <c r="AF16" s="8" t="n">
+      <c r="AJ16" s="8" t="n">
         <v>8465650</v>
       </c>
-      <c r="AG16" s="9" t="n">
+      <c r="AK16" s="9" t="n">
         <v>264458.44</v>
       </c>
-      <c r="AH16" s="10" t="n">
+      <c r="AL16" s="10" t="n">
         <v>0.0197</v>
       </c>
-      <c r="AI16" s="11" t="n">
+      <c r="AM16" s="11" t="n">
         <v>0.8187749766950423</v>
       </c>
-      <c r="AJ16" s="8" t="n">
+      <c r="AN16" s="8" t="n">
         <v>4654589</v>
       </c>
-      <c r="AK16" s="9" t="n">
+      <c r="AO16" s="9" t="n">
         <v>149235.43</v>
       </c>
-      <c r="AL16" s="10" t="n">
+      <c r="AP16" s="10" t="n">
         <v>0.0112</v>
       </c>
-      <c r="AM16" s="11" t="n">
+      <c r="AQ16" s="11" t="n">
         <v>0.6557662214497397</v>
       </c>
-      <c r="AN16" s="8" t="n">
+      <c r="AR16" s="8" t="n">
         <v>2811139</v>
       </c>
-      <c r="AO16" s="9" t="n">
+      <c r="AS16" s="9" t="n">
         <v>88199.49000000001</v>
       </c>
-      <c r="AP16" s="10" t="n">
+      <c r="AT16" s="10" t="n">
         <v>0.0068</v>
       </c>
-      <c r="AQ16" s="11" t="n">
+      <c r="AU16" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="AR16" s="8" t="n"/>
-      <c r="AS16" s="9" t="n"/>
-      <c r="AT16" s="10" t="n"/>
-      <c r="AU16" s="11" t="n"/>
       <c r="AV16" s="8" t="n"/>
       <c r="AW16" s="9" t="n"/>
       <c r="AX16" s="10" t="n"/>
@@ -4361,6 +4549,10 @@
       <c r="CC16" s="9" t="n"/>
       <c r="CD16" s="10" t="n"/>
       <c r="CE16" s="11" t="n"/>
+      <c r="CF16" s="8" t="n"/>
+      <c r="CG16" s="9" t="n"/>
+      <c r="CH16" s="10" t="n"/>
+      <c r="CI16" s="11" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -4474,6 +4666,10 @@
       <c r="CC17" s="9" t="n"/>
       <c r="CD17" s="10" t="n"/>
       <c r="CE17" s="11" t="n"/>
+      <c r="CF17" s="8" t="n"/>
+      <c r="CG17" s="9" t="n"/>
+      <c r="CH17" s="10" t="n"/>
+      <c r="CI17" s="11" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -4561,112 +4757,112 @@
         <v>0.0287</v>
       </c>
       <c r="AA18" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" s="8" t="n">
+        <v>3039945</v>
+      </c>
+      <c r="AC18" s="9" t="n">
+        <v>374095.63</v>
+      </c>
+      <c r="AD18" s="10" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="AE18" s="11" t="n">
         <v>0.06253145709252579</v>
       </c>
-      <c r="AB18" s="8" t="n">
+      <c r="AF18" s="8" t="n">
         <v>2861040</v>
       </c>
-      <c r="AC18" s="9" t="n">
+      <c r="AG18" s="9" t="n">
         <v>425064.71</v>
       </c>
-      <c r="AD18" s="10" t="n">
+      <c r="AH18" s="10" t="n">
         <v>0.0317</v>
       </c>
-      <c r="AE18" s="11" t="n">
+      <c r="AI18" s="11" t="n">
         <v>0.02897415480359852</v>
       </c>
-      <c r="AF18" s="8" t="n">
+      <c r="AJ18" s="8" t="n">
         <v>2780478</v>
       </c>
-      <c r="AG18" s="9" t="n">
+      <c r="AK18" s="9" t="n">
         <v>405921.98</v>
       </c>
-      <c r="AH18" s="10" t="n">
+      <c r="AL18" s="10" t="n">
         <v>0.0303</v>
       </c>
-      <c r="AI18" s="11" t="n">
+      <c r="AM18" s="11" t="n">
         <v>0.01230872292630713</v>
-      </c>
-      <c r="AJ18" s="8" t="n">
-        <v>2746670</v>
-      </c>
-      <c r="AK18" s="9" t="n">
-        <v>458611.49</v>
-      </c>
-      <c r="AL18" s="10" t="n">
-        <v>0.0344</v>
-      </c>
-      <c r="AM18" s="11" t="n">
-        <v>0</v>
       </c>
       <c r="AN18" s="8" t="n">
         <v>2746670</v>
       </c>
       <c r="AO18" s="9" t="n">
+        <v>458611.49</v>
+      </c>
+      <c r="AP18" s="10" t="n">
+        <v>0.0344</v>
+      </c>
+      <c r="AQ18" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR18" s="8" t="n">
+        <v>2746670</v>
+      </c>
+      <c r="AS18" s="9" t="n">
         <v>436720.53</v>
       </c>
-      <c r="AP18" s="10" t="n">
+      <c r="AT18" s="10" t="n">
         <v>0.0337</v>
       </c>
-      <c r="AQ18" s="11" t="n">
+      <c r="AU18" s="11" t="n">
         <v>0.01854138622819997</v>
-      </c>
-      <c r="AR18" s="8" t="n">
-        <v>2696670</v>
-      </c>
-      <c r="AS18" s="9" t="n">
-        <v>436483.01</v>
-      </c>
-      <c r="AT18" s="10" t="n">
-        <v>0.0347</v>
-      </c>
-      <c r="AU18" s="11" t="n">
-        <v>0</v>
       </c>
       <c r="AV18" s="8" t="n">
         <v>2696670</v>
       </c>
       <c r="AW18" s="9" t="n">
+        <v>436483.01</v>
+      </c>
+      <c r="AX18" s="10" t="n">
+        <v>0.0347</v>
+      </c>
+      <c r="AY18" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ18" s="8" t="n">
+        <v>2696670</v>
+      </c>
+      <c r="BA18" s="9" t="n">
         <v>432249.23</v>
       </c>
-      <c r="AX18" s="10" t="n">
+      <c r="BB18" s="10" t="n">
         <v>0.0361</v>
       </c>
-      <c r="AY18" s="11" t="n">
+      <c r="BC18" s="11" t="n">
         <v>-0.01820386140308082</v>
       </c>
-      <c r="AZ18" s="8" t="n">
+      <c r="BD18" s="8" t="n">
         <v>2746670</v>
       </c>
-      <c r="BA18" s="9" t="n">
+      <c r="BE18" s="9" t="n">
         <v>406259.96</v>
       </c>
-      <c r="BB18" s="10" t="n">
+      <c r="BF18" s="10" t="n">
         <v>0.0353</v>
       </c>
-      <c r="BC18" s="11" t="n">
+      <c r="BG18" s="11" t="n">
         <v>-0.09100927632732893</v>
-      </c>
-      <c r="BD18" s="8" t="n">
-        <v>3021670</v>
-      </c>
-      <c r="BE18" s="9" t="n">
-        <v>380972.15</v>
-      </c>
-      <c r="BF18" s="10" t="n">
-        <v>0.0336</v>
-      </c>
-      <c r="BG18" s="11" t="n">
-        <v>0</v>
       </c>
       <c r="BH18" s="8" t="n">
         <v>3021670</v>
       </c>
       <c r="BI18" s="9" t="n">
-        <v>374687.08</v>
+        <v>380972.15</v>
       </c>
       <c r="BJ18" s="10" t="n">
-        <v>0.0339</v>
+        <v>0.0336</v>
       </c>
       <c r="BK18" s="11" t="n">
         <v>0</v>
@@ -4675,10 +4871,10 @@
         <v>3021670</v>
       </c>
       <c r="BM18" s="9" t="n">
-        <v>372239.53</v>
+        <v>374687.08</v>
       </c>
       <c r="BN18" s="10" t="n">
-        <v>0.0358</v>
+        <v>0.0339</v>
       </c>
       <c r="BO18" s="11" t="n">
         <v>0</v>
@@ -4687,34 +4883,34 @@
         <v>3021670</v>
       </c>
       <c r="BQ18" s="9" t="n">
+        <v>372239.53</v>
+      </c>
+      <c r="BR18" s="10" t="n">
+        <v>0.0358</v>
+      </c>
+      <c r="BS18" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT18" s="8" t="n">
+        <v>3021670</v>
+      </c>
+      <c r="BU18" s="9" t="n">
         <v>370366.09</v>
       </c>
-      <c r="BR18" s="10" t="n">
+      <c r="BV18" s="10" t="n">
         <v>0.0376</v>
       </c>
-      <c r="BS18" s="11" t="n">
+      <c r="BW18" s="11" t="n">
         <v>0.001190161420612721</v>
-      </c>
-      <c r="BT18" s="8" t="n">
-        <v>3018078</v>
-      </c>
-      <c r="BU18" s="9" t="n">
-        <v>347747.47</v>
-      </c>
-      <c r="BV18" s="10" t="n">
-        <v>0.0372</v>
-      </c>
-      <c r="BW18" s="11" t="n">
-        <v>0</v>
       </c>
       <c r="BX18" s="8" t="n">
         <v>3018078</v>
       </c>
       <c r="BY18" s="9" t="n">
-        <v>360535.07</v>
+        <v>347747.47</v>
       </c>
       <c r="BZ18" s="10" t="n">
-        <v>0.041</v>
+        <v>0.0372</v>
       </c>
       <c r="CA18" s="11" t="n">
         <v>0</v>
@@ -4723,12 +4919,24 @@
         <v>3018078</v>
       </c>
       <c r="CC18" s="9" t="n">
+        <v>360535.07</v>
+      </c>
+      <c r="CD18" s="10" t="n">
+        <v>0.041</v>
+      </c>
+      <c r="CE18" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF18" s="8" t="n">
+        <v>3018078</v>
+      </c>
+      <c r="CG18" s="9" t="n">
         <v>371545.02</v>
       </c>
-      <c r="CD18" s="10" t="n">
+      <c r="CH18" s="10" t="n">
         <v>0.0414</v>
       </c>
-      <c r="CE18" s="11" t="n"/>
+      <c r="CI18" s="11" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -4822,168 +5030,180 @@
         <v>18853686</v>
       </c>
       <c r="AC19" s="9" t="n">
+        <v>164253.31</v>
+      </c>
+      <c r="AD19" s="10" t="n">
+        <v>0.0127</v>
+      </c>
+      <c r="AE19" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" s="8" t="n">
+        <v>18853686</v>
+      </c>
+      <c r="AG19" s="9" t="n">
         <v>173774.42</v>
       </c>
-      <c r="AD19" s="10" t="n">
+      <c r="AH19" s="10" t="n">
         <v>0.0129</v>
       </c>
-      <c r="AE19" s="11" t="n">
+      <c r="AI19" s="11" t="n">
         <v>0.00550299933303119</v>
       </c>
-      <c r="AF19" s="8" t="n">
+      <c r="AJ19" s="8" t="n">
         <v>18750502</v>
       </c>
-      <c r="AG19" s="9" t="n">
+      <c r="AK19" s="9" t="n">
         <v>165998.19</v>
       </c>
-      <c r="AH19" s="10" t="n">
+      <c r="AL19" s="10" t="n">
         <v>0.0124</v>
       </c>
-      <c r="AI19" s="11" t="n">
+      <c r="AM19" s="11" t="n">
         <v>0.04733304757267096</v>
       </c>
-      <c r="AJ19" s="8" t="n">
+      <c r="AN19" s="8" t="n">
         <v>17903094</v>
       </c>
-      <c r="AK19" s="9" t="n">
+      <c r="AO19" s="9" t="n">
         <v>163696.94</v>
       </c>
-      <c r="AL19" s="10" t="n">
+      <c r="AP19" s="10" t="n">
         <v>0.0123</v>
       </c>
-      <c r="AM19" s="11" t="n">
+      <c r="AQ19" s="11" t="n">
         <v>0.02860906275493533</v>
       </c>
-      <c r="AN19" s="8" t="n">
+      <c r="AR19" s="8" t="n">
         <v>17405149</v>
       </c>
-      <c r="AO19" s="9" t="n">
+      <c r="AS19" s="9" t="n">
         <v>164043.53</v>
       </c>
-      <c r="AP19" s="10" t="n">
+      <c r="AT19" s="10" t="n">
         <v>0.0126</v>
       </c>
-      <c r="AQ19" s="11" t="n">
+      <c r="AU19" s="11" t="n">
         <v>0.1044024130018492</v>
       </c>
-      <c r="AR19" s="8" t="n">
+      <c r="AV19" s="8" t="n">
         <v>15759789</v>
       </c>
-      <c r="AS19" s="9" t="n">
+      <c r="AW19" s="9" t="n">
         <v>153571.26</v>
       </c>
-      <c r="AT19" s="10" t="n">
+      <c r="AX19" s="10" t="n">
         <v>0.0122</v>
       </c>
-      <c r="AU19" s="11" t="n">
+      <c r="AY19" s="11" t="n">
         <v>0.04036608437732761</v>
       </c>
-      <c r="AV19" s="8" t="n">
+      <c r="AZ19" s="8" t="n">
         <v>15148311</v>
       </c>
-      <c r="AW19" s="9" t="n">
+      <c r="BA19" s="9" t="n">
         <v>148741.27</v>
       </c>
-      <c r="AX19" s="10" t="n">
+      <c r="BB19" s="10" t="n">
         <v>0.0124</v>
       </c>
-      <c r="AY19" s="11" t="n">
+      <c r="BC19" s="11" t="n">
         <v>0.02447981732333564</v>
       </c>
-      <c r="AZ19" s="8" t="n">
+      <c r="BD19" s="8" t="n">
         <v>14786344</v>
       </c>
-      <c r="BA19" s="9" t="n">
+      <c r="BE19" s="9" t="n">
         <v>145061.43</v>
       </c>
-      <c r="BB19" s="10" t="n">
+      <c r="BF19" s="10" t="n">
         <v>0.0126</v>
       </c>
-      <c r="BC19" s="11" t="n">
+      <c r="BG19" s="11" t="n">
         <v>0.02183487170521033</v>
       </c>
-      <c r="BD19" s="8" t="n">
+      <c r="BH19" s="8" t="n">
         <v>14470385</v>
       </c>
-      <c r="BE19" s="9" t="n">
+      <c r="BI19" s="9" t="n">
         <v>140333.79</v>
       </c>
-      <c r="BF19" s="10" t="n">
+      <c r="BJ19" s="10" t="n">
         <v>0.0124</v>
       </c>
-      <c r="BG19" s="11" t="n">
+      <c r="BK19" s="11" t="n">
         <v>0.01486488524161312</v>
-      </c>
-      <c r="BH19" s="8" t="n">
-        <v>14258435</v>
-      </c>
-      <c r="BI19" s="9" t="n">
-        <v>141151.38</v>
-      </c>
-      <c r="BJ19" s="10" t="n">
-        <v>0.0128</v>
-      </c>
-      <c r="BK19" s="11" t="n">
-        <v>0</v>
       </c>
       <c r="BL19" s="8" t="n">
         <v>14258435</v>
       </c>
       <c r="BM19" s="9" t="n">
-        <v>132603.45</v>
+        <v>141151.38</v>
       </c>
       <c r="BN19" s="10" t="n">
         <v>0.0128</v>
       </c>
       <c r="BO19" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP19" s="8" t="n">
+        <v>14258435</v>
+      </c>
+      <c r="BQ19" s="9" t="n">
+        <v>132603.45</v>
+      </c>
+      <c r="BR19" s="10" t="n">
+        <v>0.0128</v>
+      </c>
+      <c r="BS19" s="11" t="n">
         <v>0.0231160633003793</v>
       </c>
-      <c r="BP19" s="8" t="n">
+      <c r="BT19" s="8" t="n">
         <v>13936283</v>
       </c>
-      <c r="BQ19" s="9" t="n">
+      <c r="BU19" s="9" t="n">
         <v>123789.03</v>
       </c>
-      <c r="BR19" s="10" t="n">
+      <c r="BV19" s="10" t="n">
         <v>0.0126</v>
       </c>
-      <c r="BS19" s="11" t="n">
+      <c r="BW19" s="11" t="n">
         <v>0.07172012123664578</v>
       </c>
-      <c r="BT19" s="8" t="n">
+      <c r="BX19" s="8" t="n">
         <v>13003659</v>
       </c>
-      <c r="BU19" s="9" t="n">
+      <c r="BY19" s="9" t="n">
         <v>115264.43</v>
       </c>
-      <c r="BV19" s="10" t="n">
+      <c r="BZ19" s="10" t="n">
         <v>0.0123</v>
       </c>
-      <c r="BW19" s="11" t="n">
+      <c r="CA19" s="11" t="n">
         <v>0.132761983775747</v>
       </c>
-      <c r="BX19" s="8" t="n">
+      <c r="CB19" s="8" t="n">
         <v>11479604</v>
       </c>
-      <c r="BY19" s="9" t="n">
+      <c r="CC19" s="9" t="n">
         <v>100630.21</v>
       </c>
-      <c r="BZ19" s="10" t="n">
+      <c r="CD19" s="10" t="n">
         <v>0.0114</v>
       </c>
-      <c r="CA19" s="11" t="n">
+      <c r="CE19" s="11" t="n">
         <v>0.2957940438149267</v>
       </c>
-      <c r="CB19" s="8" t="n">
+      <c r="CF19" s="8" t="n">
         <v>8859127</v>
       </c>
-      <c r="CC19" s="9" t="n">
+      <c r="CG19" s="9" t="n">
         <v>85955.67999999999</v>
       </c>
-      <c r="CD19" s="10" t="n">
+      <c r="CH19" s="10" t="n">
         <v>0.009599999999999999</v>
       </c>
-      <c r="CE19" s="11" t="n"/>
+      <c r="CI19" s="11" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -5071,174 +5291,186 @@
         <v>0.0133</v>
       </c>
       <c r="AA20" s="11" t="n">
-        <v>0.1135898782108316</v>
+        <v>0.08087039879149707</v>
       </c>
       <c r="AB20" s="8" t="n">
+        <v>13271296</v>
+      </c>
+      <c r="AC20" s="9" t="n">
+        <v>162467.21</v>
+      </c>
+      <c r="AD20" s="10" t="n">
+        <v>0.0126</v>
+      </c>
+      <c r="AE20" s="11" t="n">
+        <v>0.03027141779062287</v>
+      </c>
+      <c r="AF20" s="8" t="n">
         <v>12881359</v>
       </c>
-      <c r="AC20" s="9" t="n">
+      <c r="AG20" s="9" t="n">
         <v>173666.48</v>
       </c>
-      <c r="AD20" s="10" t="n">
+      <c r="AH20" s="10" t="n">
         <v>0.0129</v>
       </c>
-      <c r="AE20" s="11" t="n">
+      <c r="AI20" s="11" t="n">
         <v>0.02043991688728315</v>
       </c>
-      <c r="AF20" s="8" t="n">
+      <c r="AJ20" s="8" t="n">
         <v>12623339</v>
       </c>
-      <c r="AG20" s="9" t="n">
+      <c r="AK20" s="9" t="n">
         <v>167133.01</v>
-      </c>
-      <c r="AH20" s="10" t="n">
-        <v>0.0125</v>
-      </c>
-      <c r="AI20" s="11" t="n">
-        <v>0.1486639530668313</v>
-      </c>
-      <c r="AJ20" s="8" t="n">
-        <v>10989584</v>
-      </c>
-      <c r="AK20" s="9" t="n">
-        <v>166085.58</v>
       </c>
       <c r="AL20" s="10" t="n">
         <v>0.0125</v>
       </c>
       <c r="AM20" s="11" t="n">
+        <v>0.1486639530668313</v>
+      </c>
+      <c r="AN20" s="8" t="n">
+        <v>10989584</v>
+      </c>
+      <c r="AO20" s="9" t="n">
+        <v>166085.58</v>
+      </c>
+      <c r="AP20" s="10" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="AQ20" s="11" t="n">
         <v>0.02078030694418823</v>
       </c>
-      <c r="AN20" s="8" t="n">
+      <c r="AR20" s="8" t="n">
         <v>10765866</v>
       </c>
-      <c r="AO20" s="9" t="n">
+      <c r="AS20" s="9" t="n">
         <v>164857.71</v>
       </c>
-      <c r="AP20" s="10" t="n">
+      <c r="AT20" s="10" t="n">
         <v>0.0127</v>
       </c>
-      <c r="AQ20" s="11" t="n">
+      <c r="AU20" s="11" t="n">
         <v>0.05823053317160534</v>
       </c>
-      <c r="AR20" s="8" t="n">
+      <c r="AV20" s="8" t="n">
         <v>10173460</v>
       </c>
-      <c r="AS20" s="9" t="n">
+      <c r="AW20" s="9" t="n">
         <v>152734.15</v>
       </c>
-      <c r="AT20" s="10" t="n">
+      <c r="AX20" s="10" t="n">
         <v>0.0121</v>
       </c>
-      <c r="AU20" s="11" t="n">
+      <c r="AY20" s="11" t="n">
         <v>0.01848262661129821</v>
       </c>
-      <c r="AV20" s="8" t="n">
+      <c r="AZ20" s="8" t="n">
         <v>9988840</v>
       </c>
-      <c r="AW20" s="9" t="n">
+      <c r="BA20" s="9" t="n">
         <v>150162.23</v>
       </c>
-      <c r="AX20" s="10" t="n">
+      <c r="BB20" s="10" t="n">
         <v>0.0125</v>
       </c>
-      <c r="AY20" s="11" t="n">
+      <c r="BC20" s="11" t="n">
         <v>0.11089473889663</v>
       </c>
-      <c r="AZ20" s="8" t="n">
+      <c r="BD20" s="8" t="n">
         <v>8991707</v>
       </c>
-      <c r="BA20" s="9" t="n">
+      <c r="BE20" s="9" t="n">
         <v>142914.19</v>
       </c>
-      <c r="BB20" s="10" t="n">
+      <c r="BF20" s="10" t="n">
         <v>0.0124</v>
       </c>
-      <c r="BC20" s="11" t="n">
+      <c r="BG20" s="11" t="n">
         <v>-0.04856779498084111</v>
       </c>
-      <c r="BD20" s="8" t="n">
+      <c r="BH20" s="8" t="n">
         <v>9450707</v>
       </c>
-      <c r="BE20" s="9" t="n">
+      <c r="BI20" s="9" t="n">
         <v>146920.69</v>
       </c>
-      <c r="BF20" s="10" t="n">
+      <c r="BJ20" s="10" t="n">
         <v>0.013</v>
       </c>
-      <c r="BG20" s="11" t="n">
+      <c r="BK20" s="11" t="n">
         <v>0.03318890177940083</v>
       </c>
-      <c r="BH20" s="8" t="n">
+      <c r="BL20" s="8" t="n">
         <v>9147124</v>
       </c>
-      <c r="BI20" s="9" t="n">
+      <c r="BM20" s="9" t="n">
         <v>137746.54</v>
-      </c>
-      <c r="BJ20" s="10" t="n">
-        <v>0.0125</v>
-      </c>
-      <c r="BK20" s="11" t="n">
-        <v>0.0298589752957666</v>
-      </c>
-      <c r="BL20" s="8" t="n">
-        <v>8881919</v>
-      </c>
-      <c r="BM20" s="9" t="n">
-        <v>130182.29</v>
       </c>
       <c r="BN20" s="10" t="n">
         <v>0.0125</v>
       </c>
       <c r="BO20" s="11" t="n">
+        <v>0.0298589752957666</v>
+      </c>
+      <c r="BP20" s="8" t="n">
+        <v>8881919</v>
+      </c>
+      <c r="BQ20" s="9" t="n">
+        <v>130182.29</v>
+      </c>
+      <c r="BR20" s="10" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="BS20" s="11" t="n">
         <v>0.1110462167918367</v>
-      </c>
-      <c r="BP20" s="8" t="n">
-        <v>7994194</v>
-      </c>
-      <c r="BQ20" s="9" t="n">
-        <v>123918</v>
-      </c>
-      <c r="BR20" s="10" t="n">
-        <v>0.0126</v>
-      </c>
-      <c r="BS20" s="11" t="n">
-        <v>0</v>
       </c>
       <c r="BT20" s="8" t="n">
         <v>7994194</v>
       </c>
       <c r="BU20" s="9" t="n">
+        <v>123918</v>
+      </c>
+      <c r="BV20" s="10" t="n">
+        <v>0.0126</v>
+      </c>
+      <c r="BW20" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX20" s="8" t="n">
+        <v>7994194</v>
+      </c>
+      <c r="BY20" s="9" t="n">
         <v>115292.27</v>
       </c>
-      <c r="BV20" s="10" t="n">
+      <c r="BZ20" s="10" t="n">
         <v>0.0123</v>
       </c>
-      <c r="BW20" s="11" t="n">
+      <c r="CA20" s="11" t="n">
         <v>0.03077033965211765</v>
       </c>
-      <c r="BX20" s="8" t="n">
+      <c r="CB20" s="8" t="n">
         <v>7755553</v>
       </c>
-      <c r="BY20" s="9" t="n">
+      <c r="CC20" s="9" t="n">
         <v>109159.41</v>
       </c>
-      <c r="BZ20" s="10" t="n">
+      <c r="CD20" s="10" t="n">
         <v>0.0124</v>
       </c>
-      <c r="CA20" s="11" t="n">
+      <c r="CE20" s="11" t="n">
         <v>0.2461624388271065</v>
       </c>
-      <c r="CB20" s="8" t="n">
+      <c r="CF20" s="8" t="n">
         <v>6223549</v>
       </c>
-      <c r="CC20" s="9" t="n">
+      <c r="CG20" s="9" t="n">
         <v>92071.17999999999</v>
       </c>
-      <c r="CD20" s="10" t="n">
+      <c r="CH20" s="10" t="n">
         <v>0.0103</v>
       </c>
-      <c r="CE20" s="11" t="n"/>
+      <c r="CI20" s="11" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
@@ -5332,168 +5564,180 @@
         <v>13769904</v>
       </c>
       <c r="AC21" s="9" t="n">
+        <v>172798.53</v>
+      </c>
+      <c r="AD21" s="10" t="n">
+        <v>0.0134</v>
+      </c>
+      <c r="AE21" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF21" s="8" t="n">
+        <v>13769904</v>
+      </c>
+      <c r="AG21" s="9" t="n">
         <v>177122.28</v>
       </c>
-      <c r="AD21" s="10" t="n">
+      <c r="AH21" s="10" t="n">
         <v>0.0132</v>
       </c>
-      <c r="AE21" s="11" t="n">
+      <c r="AI21" s="11" t="n">
         <v>-0.02223420828005112</v>
       </c>
-      <c r="AF21" s="8" t="n">
+      <c r="AJ21" s="8" t="n">
         <v>14083029</v>
       </c>
-      <c r="AG21" s="9" t="n">
+      <c r="AK21" s="9" t="n">
         <v>171545.38</v>
       </c>
-      <c r="AH21" s="10" t="n">
+      <c r="AL21" s="10" t="n">
         <v>0.0128</v>
       </c>
-      <c r="AI21" s="11" t="n">
+      <c r="AM21" s="11" t="n">
         <v>0.07294813282038955</v>
-      </c>
-      <c r="AJ21" s="8" t="n">
-        <v>13125545</v>
-      </c>
-      <c r="AK21" s="9" t="n">
-        <v>166878.18</v>
-      </c>
-      <c r="AL21" s="10" t="n">
-        <v>0.0125</v>
-      </c>
-      <c r="AM21" s="11" t="n">
-        <v>0</v>
       </c>
       <c r="AN21" s="8" t="n">
         <v>13125545</v>
       </c>
       <c r="AO21" s="9" t="n">
+        <v>166878.18</v>
+      </c>
+      <c r="AP21" s="10" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="AQ21" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR21" s="8" t="n">
+        <v>13125545</v>
+      </c>
+      <c r="AS21" s="9" t="n">
         <v>165224.36</v>
       </c>
-      <c r="AP21" s="10" t="n">
+      <c r="AT21" s="10" t="n">
         <v>0.0127</v>
       </c>
-      <c r="AQ21" s="11" t="n">
+      <c r="AU21" s="11" t="n">
         <v>0.02739609151703509</v>
       </c>
-      <c r="AR21" s="8" t="n">
+      <c r="AV21" s="8" t="n">
         <v>12775545</v>
       </c>
-      <c r="AS21" s="9" t="n">
+      <c r="AW21" s="9" t="n">
         <v>152999.93</v>
       </c>
-      <c r="AT21" s="10" t="n">
+      <c r="AX21" s="10" t="n">
         <v>0.0122</v>
       </c>
-      <c r="AU21" s="11" t="n">
+      <c r="AY21" s="11" t="n">
         <v>0.05513752418556975</v>
       </c>
-      <c r="AV21" s="8" t="n">
+      <c r="AZ21" s="8" t="n">
         <v>12107943</v>
       </c>
-      <c r="AW21" s="9" t="n">
+      <c r="BA21" s="9" t="n">
         <v>148164.9</v>
       </c>
-      <c r="AX21" s="10" t="n">
+      <c r="BB21" s="10" t="n">
         <v>0.0124</v>
       </c>
-      <c r="AY21" s="11" t="n">
+      <c r="BC21" s="11" t="n">
         <v>0.04083231560577577</v>
       </c>
-      <c r="AZ21" s="8" t="n">
+      <c r="BD21" s="8" t="n">
         <v>11632943</v>
       </c>
-      <c r="BA21" s="9" t="n">
+      <c r="BE21" s="9" t="n">
         <v>146586.71</v>
       </c>
-      <c r="BB21" s="10" t="n">
+      <c r="BF21" s="10" t="n">
         <v>0.0127</v>
       </c>
-      <c r="BC21" s="11" t="n">
+      <c r="BG21" s="11" t="n">
         <v>0.037023978878946</v>
       </c>
-      <c r="BD21" s="8" t="n">
+      <c r="BH21" s="8" t="n">
         <v>11217622</v>
       </c>
-      <c r="BE21" s="9" t="n">
+      <c r="BI21" s="9" t="n">
         <v>142497.45</v>
       </c>
-      <c r="BF21" s="10" t="n">
+      <c r="BJ21" s="10" t="n">
         <v>0.0126</v>
       </c>
-      <c r="BG21" s="11" t="n">
+      <c r="BK21" s="11" t="n">
         <v>0.08471904462602137</v>
-      </c>
-      <c r="BH21" s="8" t="n">
-        <v>10341500</v>
-      </c>
-      <c r="BI21" s="9" t="n">
-        <v>132712.47</v>
-      </c>
-      <c r="BJ21" s="10" t="n">
-        <v>0.012</v>
-      </c>
-      <c r="BK21" s="11" t="n">
-        <v>0</v>
       </c>
       <c r="BL21" s="8" t="n">
         <v>10341500</v>
       </c>
       <c r="BM21" s="9" t="n">
+        <v>132712.47</v>
+      </c>
+      <c r="BN21" s="10" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="BO21" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP21" s="8" t="n">
+        <v>10341500</v>
+      </c>
+      <c r="BQ21" s="9" t="n">
         <v>129392.85</v>
-      </c>
-      <c r="BN21" s="10" t="n">
-        <v>0.0125</v>
-      </c>
-      <c r="BO21" s="11" t="n">
-        <v>-0.005975775856020039</v>
-      </c>
-      <c r="BP21" s="8" t="n">
-        <v>10403670</v>
-      </c>
-      <c r="BQ21" s="9" t="n">
-        <v>123169.05</v>
       </c>
       <c r="BR21" s="10" t="n">
         <v>0.0125</v>
       </c>
       <c r="BS21" s="11" t="n">
+        <v>-0.005975775856020039</v>
+      </c>
+      <c r="BT21" s="8" t="n">
+        <v>10403670</v>
+      </c>
+      <c r="BU21" s="9" t="n">
+        <v>123169.05</v>
+      </c>
+      <c r="BV21" s="10" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="BW21" s="11" t="n">
         <v>0.02666147990782253</v>
       </c>
-      <c r="BT21" s="8" t="n">
+      <c r="BX21" s="8" t="n">
         <v>10133496</v>
       </c>
-      <c r="BU21" s="9" t="n">
+      <c r="BY21" s="9" t="n">
         <v>115947.46</v>
       </c>
-      <c r="BV21" s="10" t="n">
+      <c r="BZ21" s="10" t="n">
         <v>0.0124</v>
       </c>
-      <c r="BW21" s="11" t="n">
+      <c r="CA21" s="11" t="n">
         <v>0.02236244056730923</v>
       </c>
-      <c r="BX21" s="8" t="n">
+      <c r="CB21" s="8" t="n">
         <v>9911843</v>
       </c>
-      <c r="BY21" s="9" t="n">
+      <c r="CC21" s="9" t="n">
         <v>110665.73</v>
       </c>
-      <c r="BZ21" s="10" t="n">
+      <c r="CD21" s="10" t="n">
         <v>0.0126</v>
       </c>
-      <c r="CA21" s="11" t="n">
+      <c r="CE21" s="11" t="n">
         <v>0.3415700706027321</v>
       </c>
-      <c r="CB21" s="8" t="n">
+      <c r="CF21" s="8" t="n">
         <v>7388241</v>
       </c>
-      <c r="CC21" s="9" t="n">
+      <c r="CG21" s="9" t="n">
         <v>89940.75</v>
       </c>
-      <c r="CD21" s="10" t="n">
+      <c r="CH21" s="10" t="n">
         <v>0.01</v>
       </c>
-      <c r="CE21" s="11" t="n"/>
+      <c r="CI21" s="11" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -5581,24 +5825,32 @@
         <v>0.0045</v>
       </c>
       <c r="AA22" s="11" t="n">
-        <v>131.346858464915</v>
+        <v>77.70472532588454</v>
       </c>
       <c r="AB22" s="8" t="n">
+        <v>481152</v>
+      </c>
+      <c r="AC22" s="9" t="n">
+        <v>700.65</v>
+      </c>
+      <c r="AD22" s="10" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="AE22" s="11" t="n">
+        <v>0.6815617857367527</v>
+      </c>
+      <c r="AF22" s="8" t="n">
         <v>286134</v>
       </c>
-      <c r="AC22" s="9" t="n">
+      <c r="AG22" s="9" t="n">
         <v>488.89</v>
       </c>
-      <c r="AD22" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE22" s="11" t="n">
+      <c r="AH22" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI22" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="AF22" s="8" t="n"/>
-      <c r="AG22" s="9" t="n"/>
-      <c r="AH22" s="10" t="n"/>
-      <c r="AI22" s="11" t="n"/>
       <c r="AJ22" s="8" t="n"/>
       <c r="AK22" s="9" t="n"/>
       <c r="AL22" s="10" t="n"/>
@@ -5647,6 +5899,10 @@
       <c r="CC22" s="9" t="n"/>
       <c r="CD22" s="10" t="n"/>
       <c r="CE22" s="11" t="n"/>
+      <c r="CF22" s="8" t="n"/>
+      <c r="CG22" s="9" t="n"/>
+      <c r="CH22" s="10" t="n"/>
+      <c r="CI22" s="11" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -5734,40 +5990,40 @@
         <v>0.008</v>
       </c>
       <c r="AA23" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB23" s="8" t="n">
+        <v>22157154</v>
+      </c>
+      <c r="AC23" s="9" t="n">
+        <v>94467.03</v>
+      </c>
+      <c r="AD23" s="10" t="n">
+        <v>0.0073</v>
+      </c>
+      <c r="AE23" s="11" t="n">
         <v>0.003718720983944644</v>
       </c>
-      <c r="AB23" s="8" t="n">
+      <c r="AF23" s="8" t="n">
         <v>22075063</v>
       </c>
-      <c r="AC23" s="9" t="n">
+      <c r="AG23" s="9" t="n">
         <v>84966.92</v>
       </c>
-      <c r="AD23" s="10" t="n">
+      <c r="AH23" s="10" t="n">
         <v>0.0063</v>
       </c>
-      <c r="AE23" s="11" t="n">
+      <c r="AI23" s="11" t="n">
         <v>0.003411954545454545</v>
-      </c>
-      <c r="AF23" s="8" t="n">
-        <v>22000000</v>
-      </c>
-      <c r="AG23" s="9" t="n">
-        <v>98626</v>
-      </c>
-      <c r="AH23" s="10" t="n">
-        <v>0.0074</v>
-      </c>
-      <c r="AI23" s="11" t="n">
-        <v>0</v>
       </c>
       <c r="AJ23" s="8" t="n">
         <v>22000000</v>
       </c>
       <c r="AK23" s="9" t="n">
-        <v>100012</v>
+        <v>98626</v>
       </c>
       <c r="AL23" s="10" t="n">
-        <v>0.0075</v>
+        <v>0.0074</v>
       </c>
       <c r="AM23" s="11" t="n">
         <v>0</v>
@@ -5776,10 +6032,10 @@
         <v>22000000</v>
       </c>
       <c r="AO23" s="9" t="n">
-        <v>94699</v>
+        <v>100012</v>
       </c>
       <c r="AP23" s="10" t="n">
-        <v>0.0073</v>
+        <v>0.0075</v>
       </c>
       <c r="AQ23" s="11" t="n">
         <v>0</v>
@@ -5788,10 +6044,10 @@
         <v>22000000</v>
       </c>
       <c r="AS23" s="9" t="n">
-        <v>104852</v>
+        <v>94699</v>
       </c>
       <c r="AT23" s="10" t="n">
-        <v>0.0083</v>
+        <v>0.0073</v>
       </c>
       <c r="AU23" s="11" t="n">
         <v>0</v>
@@ -5800,18 +6056,26 @@
         <v>22000000</v>
       </c>
       <c r="AW23" s="9" t="n">
+        <v>104852</v>
+      </c>
+      <c r="AX23" s="10" t="n">
+        <v>0.0083</v>
+      </c>
+      <c r="AY23" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ23" s="8" t="n">
+        <v>22000000</v>
+      </c>
+      <c r="BA23" s="9" t="n">
         <v>100584</v>
       </c>
-      <c r="AX23" s="10" t="n">
+      <c r="BB23" s="10" t="n">
         <v>0.008399999999999999</v>
       </c>
-      <c r="AY23" s="11" t="n">
+      <c r="BC23" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="AZ23" s="8" t="n"/>
-      <c r="BA23" s="9" t="n"/>
-      <c r="BB23" s="10" t="n"/>
-      <c r="BC23" s="11" t="n"/>
       <c r="BD23" s="8" t="n"/>
       <c r="BE23" s="9" t="n"/>
       <c r="BF23" s="10" t="n"/>
@@ -5840,6 +6104,10 @@
       <c r="CC23" s="9" t="n"/>
       <c r="CD23" s="10" t="n"/>
       <c r="CE23" s="11" t="n"/>
+      <c r="CF23" s="8" t="n"/>
+      <c r="CG23" s="9" t="n"/>
+      <c r="CH23" s="10" t="n"/>
+      <c r="CI23" s="11" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -5933,10 +6201,10 @@
         <v>80755676</v>
       </c>
       <c r="AC24" s="9" t="n">
-        <v>101461.43</v>
+        <v>92667.14</v>
       </c>
       <c r="AD24" s="10" t="n">
-        <v>0.0076</v>
+        <v>0.0072</v>
       </c>
       <c r="AE24" s="11" t="n">
         <v>0</v>
@@ -5945,7 +6213,7 @@
         <v>80755676</v>
       </c>
       <c r="AG24" s="9" t="n">
-        <v>102390.12</v>
+        <v>101461.43</v>
       </c>
       <c r="AH24" s="10" t="n">
         <v>0.0076</v>
@@ -5957,10 +6225,10 @@
         <v>80755676</v>
       </c>
       <c r="AK24" s="9" t="n">
-        <v>108390.27</v>
+        <v>102390.12</v>
       </c>
       <c r="AL24" s="10" t="n">
-        <v>0.0081</v>
+        <v>0.0076</v>
       </c>
       <c r="AM24" s="11" t="n">
         <v>0</v>
@@ -5969,10 +6237,10 @@
         <v>80755676</v>
       </c>
       <c r="AO24" s="9" t="n">
-        <v>112484.58</v>
+        <v>108390.27</v>
       </c>
       <c r="AP24" s="10" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.0081</v>
       </c>
       <c r="AQ24" s="11" t="n">
         <v>0</v>
@@ -5981,10 +6249,10 @@
         <v>80755676</v>
       </c>
       <c r="AS24" s="9" t="n">
-        <v>112298.84</v>
+        <v>112484.58</v>
       </c>
       <c r="AT24" s="10" t="n">
-        <v>0.0089</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="AU24" s="11" t="n">
         <v>0</v>
@@ -5993,46 +6261,46 @@
         <v>80755676</v>
       </c>
       <c r="AW24" s="9" t="n">
+        <v>112298.84</v>
+      </c>
+      <c r="AX24" s="10" t="n">
+        <v>0.0089</v>
+      </c>
+      <c r="AY24" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ24" s="8" t="n">
+        <v>80755676</v>
+      </c>
+      <c r="BA24" s="9" t="n">
         <v>112403.83</v>
       </c>
-      <c r="AX24" s="10" t="n">
+      <c r="BB24" s="10" t="n">
         <v>0.0094</v>
       </c>
-      <c r="AY24" s="11" t="n">
+      <c r="BC24" s="11" t="n">
         <v>0.09854178046374168</v>
       </c>
-      <c r="AZ24" s="8" t="n">
+      <c r="BD24" s="8" t="n">
         <v>73511702</v>
       </c>
-      <c r="BA24" s="9" t="n">
+      <c r="BE24" s="9" t="n">
         <v>102769.36</v>
       </c>
-      <c r="BB24" s="10" t="n">
+      <c r="BF24" s="10" t="n">
         <v>0.0089</v>
       </c>
-      <c r="BC24" s="11" t="n">
+      <c r="BG24" s="11" t="n">
         <v>0.6629129724205788</v>
-      </c>
-      <c r="BD24" s="8" t="n">
-        <v>44206584</v>
-      </c>
-      <c r="BE24" s="9" t="n">
-        <v>59811.51</v>
-      </c>
-      <c r="BF24" s="10" t="n">
-        <v>0.0053</v>
-      </c>
-      <c r="BG24" s="11" t="n">
-        <v>0</v>
       </c>
       <c r="BH24" s="8" t="n">
         <v>44206584</v>
       </c>
       <c r="BI24" s="9" t="n">
-        <v>85367.33</v>
+        <v>59811.51</v>
       </c>
       <c r="BJ24" s="10" t="n">
-        <v>0.0077</v>
+        <v>0.0053</v>
       </c>
       <c r="BK24" s="11" t="n">
         <v>0</v>
@@ -6041,10 +6309,10 @@
         <v>44206584</v>
       </c>
       <c r="BM24" s="9" t="n">
-        <v>88656.3</v>
+        <v>85367.33</v>
       </c>
       <c r="BN24" s="10" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.0077</v>
       </c>
       <c r="BO24" s="11" t="n">
         <v>0</v>
@@ -6053,7 +6321,7 @@
         <v>44206584</v>
       </c>
       <c r="BQ24" s="9" t="n">
-        <v>84147.23</v>
+        <v>88656.3</v>
       </c>
       <c r="BR24" s="10" t="n">
         <v>0.008500000000000001</v>
@@ -6065,10 +6333,10 @@
         <v>44206584</v>
       </c>
       <c r="BU24" s="9" t="n">
-        <v>77701.91</v>
+        <v>84147.23</v>
       </c>
       <c r="BV24" s="10" t="n">
-        <v>0.0083</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="BW24" s="11" t="n">
         <v>0</v>
@@ -6077,10 +6345,10 @@
         <v>44206584</v>
       </c>
       <c r="BY24" s="9" t="n">
-        <v>68931.33</v>
+        <v>77701.91</v>
       </c>
       <c r="BZ24" s="10" t="n">
-        <v>0.0078</v>
+        <v>0.0083</v>
       </c>
       <c r="CA24" s="11" t="n">
         <v>0</v>
@@ -6089,12 +6357,24 @@
         <v>44206584</v>
       </c>
       <c r="CC24" s="9" t="n">
+        <v>68931.33</v>
+      </c>
+      <c r="CD24" s="10" t="n">
+        <v>0.0078</v>
+      </c>
+      <c r="CE24" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF24" s="8" t="n">
+        <v>44206584</v>
+      </c>
+      <c r="CG24" s="9" t="n">
         <v>77184.7</v>
       </c>
-      <c r="CD24" s="10" t="n">
+      <c r="CH24" s="10" t="n">
         <v>0.0086</v>
       </c>
-      <c r="CE24" s="11" t="n"/>
+      <c r="CI24" s="11" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
@@ -6224,6 +6504,10 @@
       <c r="CC25" s="9" t="n"/>
       <c r="CD25" s="10" t="n"/>
       <c r="CE25" s="11" t="n"/>
+      <c r="CF25" s="8" t="n"/>
+      <c r="CG25" s="9" t="n"/>
+      <c r="CH25" s="10" t="n"/>
+      <c r="CI25" s="11" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
@@ -6317,168 +6601,180 @@
         <v>7394472</v>
       </c>
       <c r="AC26" s="9" t="n">
+        <v>57344.13</v>
+      </c>
+      <c r="AD26" s="10" t="n">
+        <v>0.0044</v>
+      </c>
+      <c r="AE26" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF26" s="8" t="n">
+        <v>7394472</v>
+      </c>
+      <c r="AG26" s="9" t="n">
         <v>63976.97</v>
       </c>
-      <c r="AD26" s="10" t="n">
+      <c r="AH26" s="10" t="n">
         <v>0.0048</v>
       </c>
-      <c r="AE26" s="11" t="n">
+      <c r="AI26" s="11" t="n">
         <v>0.004287575158874156</v>
       </c>
-      <c r="AF26" s="8" t="n">
+      <c r="AJ26" s="8" t="n">
         <v>7362903</v>
       </c>
-      <c r="AG26" s="9" t="n">
+      <c r="AK26" s="9" t="n">
         <v>67966.96000000001</v>
       </c>
-      <c r="AH26" s="10" t="n">
+      <c r="AL26" s="10" t="n">
         <v>0.0051</v>
       </c>
-      <c r="AI26" s="11" t="n">
+      <c r="AM26" s="11" t="n">
         <v>0.1913802993295465</v>
       </c>
-      <c r="AJ26" s="8" t="n">
+      <c r="AN26" s="8" t="n">
         <v>6180145</v>
       </c>
-      <c r="AK26" s="9" t="n">
+      <c r="AO26" s="9" t="n">
         <v>63945.96</v>
       </c>
-      <c r="AL26" s="10" t="n">
+      <c r="AP26" s="10" t="n">
         <v>0.0048</v>
       </c>
-      <c r="AM26" s="11" t="n">
+      <c r="AQ26" s="11" t="n">
         <v>0.05773144178420389</v>
       </c>
-      <c r="AN26" s="8" t="n">
+      <c r="AR26" s="8" t="n">
         <v>5842830</v>
       </c>
-      <c r="AO26" s="9" t="n">
+      <c r="AS26" s="9" t="n">
         <v>60233.73</v>
       </c>
-      <c r="AP26" s="10" t="n">
+      <c r="AT26" s="10" t="n">
         <v>0.0046</v>
       </c>
-      <c r="AQ26" s="11" t="n">
+      <c r="AU26" s="11" t="n">
         <v>0.05688668625904227</v>
       </c>
-      <c r="AR26" s="8" t="n">
+      <c r="AV26" s="8" t="n">
         <v>5528341</v>
       </c>
-      <c r="AS26" s="9" t="n">
+      <c r="AW26" s="9" t="n">
         <v>59285.93</v>
       </c>
-      <c r="AT26" s="10" t="n">
+      <c r="AX26" s="10" t="n">
         <v>0.0047</v>
       </c>
-      <c r="AU26" s="11" t="n">
+      <c r="AY26" s="11" t="n">
         <v>0.1065051605034048</v>
       </c>
-      <c r="AV26" s="8" t="n">
+      <c r="AZ26" s="8" t="n">
         <v>4996218</v>
       </c>
-      <c r="AW26" s="9" t="n">
+      <c r="BA26" s="9" t="n">
         <v>51236.22</v>
-      </c>
-      <c r="AX26" s="10" t="n">
-        <v>0.0043</v>
-      </c>
-      <c r="AY26" s="11" t="n">
-        <v>0.1269063080091213</v>
-      </c>
-      <c r="AZ26" s="8" t="n">
-        <v>4433570</v>
-      </c>
-      <c r="BA26" s="9" t="n">
-        <v>49913.13</v>
       </c>
       <c r="BB26" s="10" t="n">
         <v>0.0043</v>
       </c>
       <c r="BC26" s="11" t="n">
+        <v>0.1269063080091213</v>
+      </c>
+      <c r="BD26" s="8" t="n">
+        <v>4433570</v>
+      </c>
+      <c r="BE26" s="9" t="n">
+        <v>49913.13</v>
+      </c>
+      <c r="BF26" s="10" t="n">
+        <v>0.0043</v>
+      </c>
+      <c r="BG26" s="11" t="n">
         <v>0.1091786303542636</v>
       </c>
-      <c r="BD26" s="8" t="n">
+      <c r="BH26" s="8" t="n">
         <v>3997165</v>
       </c>
-      <c r="BE26" s="9" t="n">
+      <c r="BI26" s="9" t="n">
         <v>49305.03</v>
       </c>
-      <c r="BF26" s="10" t="n">
+      <c r="BJ26" s="10" t="n">
         <v>0.0044</v>
       </c>
-      <c r="BG26" s="11" t="n">
+      <c r="BK26" s="11" t="n">
         <v>0.136585363079533</v>
       </c>
-      <c r="BH26" s="8" t="n">
+      <c r="BL26" s="8" t="n">
         <v>3516819</v>
       </c>
-      <c r="BI26" s="9" t="n">
+      <c r="BM26" s="9" t="n">
         <v>39036.69</v>
       </c>
-      <c r="BJ26" s="10" t="n">
+      <c r="BN26" s="10" t="n">
         <v>0.0035</v>
       </c>
-      <c r="BK26" s="11" t="n">
+      <c r="BO26" s="11" t="n">
         <v>0.08443118240843069</v>
       </c>
-      <c r="BL26" s="8" t="n">
+      <c r="BP26" s="8" t="n">
         <v>3243008</v>
       </c>
-      <c r="BM26" s="9" t="n">
+      <c r="BQ26" s="9" t="n">
         <v>30813.44</v>
       </c>
-      <c r="BN26" s="10" t="n">
+      <c r="BR26" s="10" t="n">
         <v>0.003</v>
       </c>
-      <c r="BO26" s="11" t="n">
+      <c r="BS26" s="11" t="n">
         <v>0.08526813218218672</v>
       </c>
-      <c r="BP26" s="8" t="n">
+      <c r="BT26" s="8" t="n">
         <v>2988209</v>
       </c>
-      <c r="BQ26" s="9" t="n">
+      <c r="BU26" s="9" t="n">
         <v>24424.13</v>
       </c>
-      <c r="BR26" s="10" t="n">
+      <c r="BV26" s="10" t="n">
         <v>0.0025</v>
       </c>
-      <c r="BS26" s="11" t="n">
+      <c r="BW26" s="11" t="n">
         <v>0.05097801295341799</v>
       </c>
-      <c r="BT26" s="8" t="n">
+      <c r="BX26" s="8" t="n">
         <v>2843265</v>
       </c>
-      <c r="BU26" s="9" t="n">
+      <c r="BY26" s="9" t="n">
         <v>22336.69</v>
       </c>
-      <c r="BV26" s="10" t="n">
+      <c r="BZ26" s="10" t="n">
         <v>0.0024</v>
       </c>
-      <c r="BW26" s="11" t="n">
+      <c r="CA26" s="11" t="n">
         <v>0.08976771675272589</v>
       </c>
-      <c r="BX26" s="8" t="n">
+      <c r="CB26" s="8" t="n">
         <v>2609056</v>
       </c>
-      <c r="BY26" s="9" t="n">
+      <c r="CC26" s="9" t="n">
         <v>17326.74</v>
       </c>
-      <c r="BZ26" s="10" t="n">
+      <c r="CD26" s="10" t="n">
         <v>0.002</v>
       </c>
-      <c r="CA26" s="11" t="n">
+      <c r="CE26" s="11" t="n">
         <v>0.1546891810734174</v>
       </c>
-      <c r="CB26" s="8" t="n">
+      <c r="CF26" s="8" t="n">
         <v>2259531</v>
       </c>
-      <c r="CC26" s="9" t="n">
+      <c r="CG26" s="9" t="n">
         <v>18525.89</v>
       </c>
-      <c r="CD26" s="10" t="n">
+      <c r="CH26" s="10" t="n">
         <v>0.0021</v>
       </c>
-      <c r="CE26" s="11" t="n"/>
+      <c r="CI26" s="11" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
@@ -6566,24 +6862,32 @@
         <v>0.0003</v>
       </c>
       <c r="AA27" s="11" t="n">
-        <v>122.4095238095238</v>
+        <v>6.08421151852201</v>
       </c>
       <c r="AB27" s="8" t="n">
+        <v>53045</v>
+      </c>
+      <c r="AC27" s="9" t="n">
+        <v>492.1</v>
+      </c>
+      <c r="AD27" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE27" s="11" t="n">
+        <v>16.42036124794745</v>
+      </c>
+      <c r="AF27" s="8" t="n">
         <v>3045</v>
       </c>
-      <c r="AC27" s="9" t="n">
+      <c r="AG27" s="9" t="n">
         <v>37.14</v>
       </c>
-      <c r="AD27" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE27" s="11" t="n">
+      <c r="AH27" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI27" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="AF27" s="8" t="n"/>
-      <c r="AG27" s="9" t="n"/>
-      <c r="AH27" s="10" t="n"/>
-      <c r="AI27" s="11" t="n"/>
       <c r="AJ27" s="8" t="n"/>
       <c r="AK27" s="9" t="n"/>
       <c r="AL27" s="10" t="n"/>
@@ -6632,6 +6936,10 @@
       <c r="CC27" s="9" t="n"/>
       <c r="CD27" s="10" t="n"/>
       <c r="CE27" s="11" t="n"/>
+      <c r="CF27" s="8" t="n"/>
+      <c r="CG27" s="9" t="n"/>
+      <c r="CH27" s="10" t="n"/>
+      <c r="CI27" s="11" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -6725,10 +7033,10 @@
         <v>1995914</v>
       </c>
       <c r="AC28" s="9" t="n">
-        <v>36543.19</v>
+        <v>32040.41</v>
       </c>
       <c r="AD28" s="10" t="n">
-        <v>0.0027</v>
+        <v>0.0025</v>
       </c>
       <c r="AE28" s="11" t="n">
         <v>0</v>
@@ -6737,10 +7045,10 @@
         <v>1995914</v>
       </c>
       <c r="AG28" s="9" t="n">
-        <v>35285.76</v>
+        <v>36543.19</v>
       </c>
       <c r="AH28" s="10" t="n">
-        <v>0.0026</v>
+        <v>0.0027</v>
       </c>
       <c r="AI28" s="11" t="n">
         <v>0</v>
@@ -6749,10 +7057,10 @@
         <v>1995914</v>
       </c>
       <c r="AK28" s="9" t="n">
-        <v>37762.69</v>
+        <v>35285.76</v>
       </c>
       <c r="AL28" s="10" t="n">
-        <v>0.0028</v>
+        <v>0.0026</v>
       </c>
       <c r="AM28" s="11" t="n">
         <v>0</v>
@@ -6761,10 +7069,10 @@
         <v>1995914</v>
       </c>
       <c r="AO28" s="9" t="n">
-        <v>38830.51</v>
+        <v>37762.69</v>
       </c>
       <c r="AP28" s="10" t="n">
-        <v>0.003</v>
+        <v>0.0028</v>
       </c>
       <c r="AQ28" s="11" t="n">
         <v>0</v>
@@ -6773,10 +7081,10 @@
         <v>1995914</v>
       </c>
       <c r="AS28" s="9" t="n">
-        <v>35076.19</v>
+        <v>38830.51</v>
       </c>
       <c r="AT28" s="10" t="n">
-        <v>0.0028</v>
+        <v>0.003</v>
       </c>
       <c r="AU28" s="11" t="n">
         <v>0</v>
@@ -6785,10 +7093,10 @@
         <v>1995914</v>
       </c>
       <c r="AW28" s="9" t="n">
-        <v>34681</v>
+        <v>35076.19</v>
       </c>
       <c r="AX28" s="10" t="n">
-        <v>0.0029</v>
+        <v>0.0028</v>
       </c>
       <c r="AY28" s="11" t="n">
         <v>0</v>
@@ -6797,10 +7105,10 @@
         <v>1995914</v>
       </c>
       <c r="BA28" s="9" t="n">
-        <v>35004.34</v>
+        <v>34681</v>
       </c>
       <c r="BB28" s="10" t="n">
-        <v>0.003</v>
+        <v>0.0029</v>
       </c>
       <c r="BC28" s="11" t="n">
         <v>0</v>
@@ -6809,10 +7117,10 @@
         <v>1995914</v>
       </c>
       <c r="BE28" s="9" t="n">
-        <v>38225.74</v>
+        <v>35004.34</v>
       </c>
       <c r="BF28" s="10" t="n">
-        <v>0.0034</v>
+        <v>0.003</v>
       </c>
       <c r="BG28" s="11" t="n">
         <v>0</v>
@@ -6821,10 +7129,10 @@
         <v>1995914</v>
       </c>
       <c r="BI28" s="9" t="n">
-        <v>43319.32</v>
+        <v>38225.74</v>
       </c>
       <c r="BJ28" s="10" t="n">
-        <v>0.0039</v>
+        <v>0.0034</v>
       </c>
       <c r="BK28" s="11" t="n">
         <v>0</v>
@@ -6833,10 +7141,10 @@
         <v>1995914</v>
       </c>
       <c r="BM28" s="9" t="n">
-        <v>34806.74</v>
+        <v>43319.32</v>
       </c>
       <c r="BN28" s="10" t="n">
-        <v>0.0034</v>
+        <v>0.0039</v>
       </c>
       <c r="BO28" s="11" t="n">
         <v>0</v>
@@ -6845,10 +7153,10 @@
         <v>1995914</v>
       </c>
       <c r="BQ28" s="9" t="n">
-        <v>35138.07</v>
+        <v>34806.74</v>
       </c>
       <c r="BR28" s="10" t="n">
-        <v>0.0036</v>
+        <v>0.0034</v>
       </c>
       <c r="BS28" s="11" t="n">
         <v>0</v>
@@ -6857,7 +7165,7 @@
         <v>1995914</v>
       </c>
       <c r="BU28" s="9" t="n">
-        <v>33771.86</v>
+        <v>35138.07</v>
       </c>
       <c r="BV28" s="10" t="n">
         <v>0.0036</v>
@@ -6869,10 +7177,10 @@
         <v>1995914</v>
       </c>
       <c r="BY28" s="9" t="n">
-        <v>28830.98</v>
+        <v>33771.86</v>
       </c>
       <c r="BZ28" s="10" t="n">
-        <v>0.0033</v>
+        <v>0.0036</v>
       </c>
       <c r="CA28" s="11" t="n">
         <v>0</v>
@@ -6881,12 +7189,24 @@
         <v>1995914</v>
       </c>
       <c r="CC28" s="9" t="n">
+        <v>28830.98</v>
+      </c>
+      <c r="CD28" s="10" t="n">
+        <v>0.0033</v>
+      </c>
+      <c r="CE28" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF28" s="8" t="n">
+        <v>1995914</v>
+      </c>
+      <c r="CG28" s="9" t="n">
         <v>27686.32</v>
       </c>
-      <c r="CD28" s="10" t="n">
+      <c r="CH28" s="10" t="n">
         <v>0.0031</v>
       </c>
-      <c r="CE28" s="11" t="n"/>
+      <c r="CI28" s="11" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -6980,10 +7300,10 @@
         <v>2264603</v>
       </c>
       <c r="AC29" s="9" t="n">
-        <v>28810.28</v>
+        <v>25349.97</v>
       </c>
       <c r="AD29" s="10" t="n">
-        <v>0.0021</v>
+        <v>0.002</v>
       </c>
       <c r="AE29" s="11" t="n">
         <v>0</v>
@@ -6992,10 +7312,10 @@
         <v>2264603</v>
       </c>
       <c r="AG29" s="9" t="n">
-        <v>29897.29</v>
+        <v>28810.28</v>
       </c>
       <c r="AH29" s="10" t="n">
-        <v>0.0022</v>
+        <v>0.0021</v>
       </c>
       <c r="AI29" s="11" t="n">
         <v>0</v>
@@ -7004,10 +7324,10 @@
         <v>2264603</v>
       </c>
       <c r="AK29" s="9" t="n">
-        <v>32691.81</v>
+        <v>29897.29</v>
       </c>
       <c r="AL29" s="10" t="n">
-        <v>0.0025</v>
+        <v>0.0022</v>
       </c>
       <c r="AM29" s="11" t="n">
         <v>0</v>
@@ -7016,10 +7336,10 @@
         <v>2264603</v>
       </c>
       <c r="AO29" s="9" t="n">
-        <v>36623.16</v>
+        <v>32691.81</v>
       </c>
       <c r="AP29" s="10" t="n">
-        <v>0.0028</v>
+        <v>0.0025</v>
       </c>
       <c r="AQ29" s="11" t="n">
         <v>0</v>
@@ -7028,10 +7348,10 @@
         <v>2264603</v>
       </c>
       <c r="AS29" s="9" t="n">
-        <v>35943.78</v>
+        <v>36623.16</v>
       </c>
       <c r="AT29" s="10" t="n">
-        <v>0.0029</v>
+        <v>0.0028</v>
       </c>
       <c r="AU29" s="11" t="n">
         <v>0</v>
@@ -7040,10 +7360,10 @@
         <v>2264603</v>
       </c>
       <c r="AW29" s="9" t="n">
-        <v>33031.5</v>
+        <v>35943.78</v>
       </c>
       <c r="AX29" s="10" t="n">
-        <v>0.0028</v>
+        <v>0.0029</v>
       </c>
       <c r="AY29" s="11" t="n">
         <v>0</v>
@@ -7052,7 +7372,7 @@
         <v>2264603</v>
       </c>
       <c r="BA29" s="9" t="n">
-        <v>32257.01</v>
+        <v>33031.5</v>
       </c>
       <c r="BB29" s="10" t="n">
         <v>0.0028</v>
@@ -7064,10 +7384,10 @@
         <v>2264603</v>
       </c>
       <c r="BE29" s="9" t="n">
-        <v>33534.24</v>
+        <v>32257.01</v>
       </c>
       <c r="BF29" s="10" t="n">
-        <v>0.003</v>
+        <v>0.0028</v>
       </c>
       <c r="BG29" s="11" t="n">
         <v>0</v>
@@ -7076,10 +7396,10 @@
         <v>2264603</v>
       </c>
       <c r="BI29" s="9" t="n">
-        <v>40626.98</v>
+        <v>33534.24</v>
       </c>
       <c r="BJ29" s="10" t="n">
-        <v>0.0037</v>
+        <v>0.003</v>
       </c>
       <c r="BK29" s="11" t="n">
         <v>0</v>
@@ -7088,10 +7408,10 @@
         <v>2264603</v>
       </c>
       <c r="BM29" s="9" t="n">
-        <v>34641.63</v>
+        <v>40626.98</v>
       </c>
       <c r="BN29" s="10" t="n">
-        <v>0.0033</v>
+        <v>0.0037</v>
       </c>
       <c r="BO29" s="11" t="n">
         <v>0</v>
@@ -7100,10 +7420,10 @@
         <v>2264603</v>
       </c>
       <c r="BQ29" s="9" t="n">
-        <v>29892.76</v>
+        <v>34641.63</v>
       </c>
       <c r="BR29" s="10" t="n">
-        <v>0.003</v>
+        <v>0.0033</v>
       </c>
       <c r="BS29" s="11" t="n">
         <v>0</v>
@@ -7112,7 +7432,7 @@
         <v>2264603</v>
       </c>
       <c r="BU29" s="9" t="n">
-        <v>27629.29</v>
+        <v>29892.76</v>
       </c>
       <c r="BV29" s="10" t="n">
         <v>0.003</v>
@@ -7124,10 +7444,10 @@
         <v>2264603</v>
       </c>
       <c r="BY29" s="9" t="n">
-        <v>25089.54</v>
+        <v>27629.29</v>
       </c>
       <c r="BZ29" s="10" t="n">
-        <v>0.0029</v>
+        <v>0.003</v>
       </c>
       <c r="CA29" s="11" t="n">
         <v>0</v>
@@ -7136,12 +7456,24 @@
         <v>2264603</v>
       </c>
       <c r="CC29" s="9" t="n">
+        <v>25089.54</v>
+      </c>
+      <c r="CD29" s="10" t="n">
+        <v>0.0029</v>
+      </c>
+      <c r="CE29" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF29" s="8" t="n">
+        <v>2264603</v>
+      </c>
+      <c r="CG29" s="9" t="n">
         <v>29659.51</v>
       </c>
-      <c r="CD29" s="10" t="n">
+      <c r="CH29" s="10" t="n">
         <v>0.0033</v>
       </c>
-      <c r="CE29" s="11" t="n"/>
+      <c r="CI29" s="11" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
@@ -7235,7 +7567,7 @@
         <v>710855</v>
       </c>
       <c r="AC30" s="9" t="n">
-        <v>3234.03</v>
+        <v>2972.44</v>
       </c>
       <c r="AD30" s="10" t="n">
         <v>0.0002</v>
@@ -7247,7 +7579,7 @@
         <v>710855</v>
       </c>
       <c r="AG30" s="9" t="n">
-        <v>3158.33</v>
+        <v>3234.03</v>
       </c>
       <c r="AH30" s="10" t="n">
         <v>0.0002</v>
@@ -7259,7 +7591,7 @@
         <v>710855</v>
       </c>
       <c r="AK30" s="9" t="n">
-        <v>2976.71</v>
+        <v>3158.33</v>
       </c>
       <c r="AL30" s="10" t="n">
         <v>0.0002</v>
@@ -7271,18 +7603,26 @@
         <v>710855</v>
       </c>
       <c r="AO30" s="9" t="n">
-        <v>2850.8839775</v>
+        <v>2976.71</v>
       </c>
       <c r="AP30" s="10" t="n">
         <v>0.0002</v>
       </c>
       <c r="AQ30" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR30" s="8" t="n">
+        <v>710855</v>
+      </c>
+      <c r="AS30" s="9" t="n">
+        <v>2850.8839775</v>
+      </c>
+      <c r="AT30" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="AU30" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="AR30" s="8" t="n"/>
-      <c r="AS30" s="9" t="n"/>
-      <c r="AT30" s="10" t="n"/>
-      <c r="AU30" s="11" t="n"/>
       <c r="AV30" s="8" t="n"/>
       <c r="AW30" s="9" t="n"/>
       <c r="AX30" s="10" t="n"/>
@@ -7319,6 +7659,10 @@
       <c r="CC30" s="9" t="n"/>
       <c r="CD30" s="10" t="n"/>
       <c r="CE30" s="11" t="n"/>
+      <c r="CF30" s="8" t="n"/>
+      <c r="CG30" s="9" t="n"/>
+      <c r="CH30" s="10" t="n"/>
+      <c r="CI30" s="11" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
@@ -7412,30 +7756,38 @@
         <v>464063</v>
       </c>
       <c r="AC31" s="9" t="n">
-        <v>2188.75</v>
+        <v>2065.08</v>
       </c>
       <c r="AD31" s="10" t="n">
         <v>0.0002</v>
       </c>
       <c r="AE31" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF31" s="8" t="n">
+        <v>464063</v>
+      </c>
+      <c r="AG31" s="9" t="n">
+        <v>2188.75</v>
+      </c>
+      <c r="AH31" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="AI31" s="11" t="n">
         <v>0.004302331872531515</v>
       </c>
-      <c r="AF31" s="8" t="n">
+      <c r="AJ31" s="8" t="n">
         <v>462075</v>
       </c>
-      <c r="AG31" s="9" t="n">
+      <c r="AK31" s="9" t="n">
         <v>1932.4</v>
       </c>
-      <c r="AH31" s="10" t="n">
+      <c r="AL31" s="10" t="n">
         <v>0.0001</v>
       </c>
-      <c r="AI31" s="11" t="n">
+      <c r="AM31" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="AJ31" s="8" t="n"/>
-      <c r="AK31" s="9" t="n"/>
-      <c r="AL31" s="10" t="n"/>
-      <c r="AM31" s="11" t="n"/>
       <c r="AN31" s="8" t="n"/>
       <c r="AO31" s="9" t="n"/>
       <c r="AP31" s="10" t="n"/>
@@ -7480,6 +7832,10 @@
       <c r="CC31" s="9" t="n"/>
       <c r="CD31" s="10" t="n"/>
       <c r="CE31" s="11" t="n"/>
+      <c r="CF31" s="8" t="n"/>
+      <c r="CG31" s="9" t="n"/>
+      <c r="CH31" s="10" t="n"/>
+      <c r="CI31" s="11" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
@@ -7567,36 +7923,44 @@
         <v>0.0014</v>
       </c>
       <c r="AA32" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="8" t="n">
+        <v>6957544</v>
+      </c>
+      <c r="AC32" s="9" t="n">
+        <v>18479.24</v>
+      </c>
+      <c r="AD32" s="10" t="n">
+        <v>0.0014</v>
+      </c>
+      <c r="AE32" s="11" t="n">
         <v>0.3678192645926667</v>
       </c>
-      <c r="AB32" s="8" t="n">
+      <c r="AF32" s="8" t="n">
         <v>5086596</v>
       </c>
-      <c r="AC32" s="9" t="n">
+      <c r="AG32" s="9" t="n">
         <v>15442.91</v>
       </c>
-      <c r="AD32" s="10" t="n">
+      <c r="AH32" s="10" t="n">
         <v>0.0012</v>
       </c>
-      <c r="AE32" s="11" t="n">
+      <c r="AI32" s="11" t="n">
         <v>24.46379118733668</v>
       </c>
-      <c r="AF32" s="8" t="n">
+      <c r="AJ32" s="8" t="n">
         <v>199758</v>
       </c>
-      <c r="AG32" s="9" t="n">
+      <c r="AK32" s="9" t="n">
         <v>629.9400000000001</v>
       </c>
-      <c r="AH32" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI32" s="11" t="n">
+      <c r="AL32" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM32" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="AJ32" s="8" t="n"/>
-      <c r="AK32" s="9" t="n"/>
-      <c r="AL32" s="10" t="n"/>
-      <c r="AM32" s="11" t="n"/>
       <c r="AN32" s="8" t="n"/>
       <c r="AO32" s="9" t="n"/>
       <c r="AP32" s="10" t="n"/>
@@ -7641,6 +8005,10 @@
       <c r="CC32" s="9" t="n"/>
       <c r="CD32" s="10" t="n"/>
       <c r="CE32" s="11" t="n"/>
+      <c r="CF32" s="8" t="n"/>
+      <c r="CG32" s="9" t="n"/>
+      <c r="CH32" s="10" t="n"/>
+      <c r="CI32" s="11" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
@@ -7734,43 +8102,43 @@
         <v>80565</v>
       </c>
       <c r="AC33" s="9" t="n">
+        <v>8949.969999999999</v>
+      </c>
+      <c r="AD33" s="10" t="n">
+        <v>0.0007</v>
+      </c>
+      <c r="AE33" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF33" s="8" t="n">
+        <v>80565</v>
+      </c>
+      <c r="AG33" s="9" t="n">
         <v>10682.11</v>
-      </c>
-      <c r="AD33" s="10" t="n">
-        <v>0.0008</v>
-      </c>
-      <c r="AE33" s="11" t="n">
-        <v>0.0001613864336081041</v>
-      </c>
-      <c r="AF33" s="8" t="n">
-        <v>80552</v>
-      </c>
-      <c r="AG33" s="9" t="n">
-        <v>10825.38</v>
       </c>
       <c r="AH33" s="10" t="n">
         <v>0.0008</v>
       </c>
       <c r="AI33" s="11" t="n">
+        <v>0.0001613864336081041</v>
+      </c>
+      <c r="AJ33" s="8" t="n">
+        <v>80552</v>
+      </c>
+      <c r="AK33" s="9" t="n">
+        <v>10825.38</v>
+      </c>
+      <c r="AL33" s="10" t="n">
+        <v>0.0008</v>
+      </c>
+      <c r="AM33" s="11" t="n">
         <v>0.004902755772901358</v>
-      </c>
-      <c r="AJ33" s="8" t="n">
-        <v>80159</v>
-      </c>
-      <c r="AK33" s="9" t="n">
-        <v>11401.01</v>
-      </c>
-      <c r="AL33" s="10" t="n">
-        <v>0.0009</v>
-      </c>
-      <c r="AM33" s="11" t="n">
-        <v>0</v>
       </c>
       <c r="AN33" s="8" t="n">
         <v>80159</v>
       </c>
       <c r="AO33" s="9" t="n">
-        <v>11787.38</v>
+        <v>11401.01</v>
       </c>
       <c r="AP33" s="10" t="n">
         <v>0.0009</v>
@@ -7782,10 +8150,10 @@
         <v>80159</v>
       </c>
       <c r="AS33" s="9" t="n">
-        <v>12110.42</v>
+        <v>11787.38</v>
       </c>
       <c r="AT33" s="10" t="n">
-        <v>0.001</v>
+        <v>0.0009</v>
       </c>
       <c r="AU33" s="11" t="n">
         <v>0</v>
@@ -7794,10 +8162,10 @@
         <v>80159</v>
       </c>
       <c r="AW33" s="9" t="n">
-        <v>13825.82</v>
+        <v>12110.42</v>
       </c>
       <c r="AX33" s="10" t="n">
-        <v>0.0012</v>
+        <v>0.001</v>
       </c>
       <c r="AY33" s="11" t="n">
         <v>0</v>
@@ -7806,10 +8174,10 @@
         <v>80159</v>
       </c>
       <c r="BA33" s="9" t="n">
-        <v>12726.04</v>
+        <v>13825.82</v>
       </c>
       <c r="BB33" s="10" t="n">
-        <v>0.0011</v>
+        <v>0.0012</v>
       </c>
       <c r="BC33" s="11" t="n">
         <v>0</v>
@@ -7818,7 +8186,7 @@
         <v>80159</v>
       </c>
       <c r="BE33" s="9" t="n">
-        <v>12868.73</v>
+        <v>12726.04</v>
       </c>
       <c r="BF33" s="10" t="n">
         <v>0.0011</v>
@@ -7830,7 +8198,7 @@
         <v>80159</v>
       </c>
       <c r="BI33" s="9" t="n">
-        <v>11621.45</v>
+        <v>12868.73</v>
       </c>
       <c r="BJ33" s="10" t="n">
         <v>0.0011</v>
@@ -7842,10 +8210,10 @@
         <v>80159</v>
       </c>
       <c r="BM33" s="9" t="n">
-        <v>10722.07</v>
+        <v>11621.45</v>
       </c>
       <c r="BN33" s="10" t="n">
-        <v>0.001</v>
+        <v>0.0011</v>
       </c>
       <c r="BO33" s="11" t="n">
         <v>0</v>
@@ -7854,10 +8222,10 @@
         <v>80159</v>
       </c>
       <c r="BQ33" s="9" t="n">
-        <v>9198.25</v>
+        <v>10722.07</v>
       </c>
       <c r="BR33" s="10" t="n">
-        <v>0.0009</v>
+        <v>0.001</v>
       </c>
       <c r="BS33" s="11" t="n">
         <v>0</v>
@@ -7866,10 +8234,10 @@
         <v>80159</v>
       </c>
       <c r="BU33" s="9" t="n">
-        <v>8997.450000000001</v>
+        <v>9198.25</v>
       </c>
       <c r="BV33" s="10" t="n">
-        <v>0.001</v>
+        <v>0.0009</v>
       </c>
       <c r="BW33" s="11" t="n">
         <v>0</v>
@@ -7878,10 +8246,10 @@
         <v>80159</v>
       </c>
       <c r="BY33" s="9" t="n">
-        <v>7401.52</v>
+        <v>8997.450000000001</v>
       </c>
       <c r="BZ33" s="10" t="n">
-        <v>0.0008</v>
+        <v>0.001</v>
       </c>
       <c r="CA33" s="11" t="n">
         <v>0</v>
@@ -7890,12 +8258,24 @@
         <v>80159</v>
       </c>
       <c r="CC33" s="9" t="n">
-        <v>7463.48</v>
+        <v>7401.52</v>
       </c>
       <c r="CD33" s="10" t="n">
         <v>0.0008</v>
       </c>
-      <c r="CE33" s="11" t="n"/>
+      <c r="CE33" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF33" s="8" t="n">
+        <v>80159</v>
+      </c>
+      <c r="CG33" s="9" t="n">
+        <v>7463.48</v>
+      </c>
+      <c r="CH33" s="10" t="n">
+        <v>0.0008</v>
+      </c>
+      <c r="CI33" s="11" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
@@ -7989,10 +8369,10 @@
         <v>287393</v>
       </c>
       <c r="AC34" s="9" t="n">
-        <v>15895.71</v>
+        <v>14378.27</v>
       </c>
       <c r="AD34" s="10" t="n">
-        <v>0.0012</v>
+        <v>0.0011</v>
       </c>
       <c r="AE34" s="11" t="n">
         <v>0</v>
@@ -8001,10 +8381,10 @@
         <v>287393</v>
       </c>
       <c r="AG34" s="9" t="n">
-        <v>18124.44</v>
+        <v>15895.71</v>
       </c>
       <c r="AH34" s="10" t="n">
-        <v>0.0014</v>
+        <v>0.0012</v>
       </c>
       <c r="AI34" s="11" t="n">
         <v>0</v>
@@ -8013,10 +8393,10 @@
         <v>287393</v>
       </c>
       <c r="AK34" s="9" t="n">
-        <v>17460.56</v>
+        <v>18124.44</v>
       </c>
       <c r="AL34" s="10" t="n">
-        <v>0.0013</v>
+        <v>0.0014</v>
       </c>
       <c r="AM34" s="11" t="n">
         <v>0</v>
@@ -8025,10 +8405,10 @@
         <v>287393</v>
       </c>
       <c r="AO34" s="9" t="n">
-        <v>17812.62</v>
+        <v>17460.56</v>
       </c>
       <c r="AP34" s="10" t="n">
-        <v>0.0014</v>
+        <v>0.0013</v>
       </c>
       <c r="AQ34" s="11" t="n">
         <v>0</v>
@@ -8037,10 +8417,10 @@
         <v>287393</v>
       </c>
       <c r="AS34" s="9" t="n">
-        <v>18463.56</v>
+        <v>17812.62</v>
       </c>
       <c r="AT34" s="10" t="n">
-        <v>0.0015</v>
+        <v>0.0014</v>
       </c>
       <c r="AU34" s="11" t="n">
         <v>0</v>
@@ -8049,7 +8429,7 @@
         <v>287393</v>
       </c>
       <c r="AW34" s="9" t="n">
-        <v>18243.71</v>
+        <v>18463.56</v>
       </c>
       <c r="AX34" s="10" t="n">
         <v>0.0015</v>
@@ -8061,10 +8441,10 @@
         <v>287393</v>
       </c>
       <c r="BA34" s="9" t="n">
-        <v>17962.06</v>
+        <v>18243.71</v>
       </c>
       <c r="BB34" s="10" t="n">
-        <v>0.0016</v>
+        <v>0.0015</v>
       </c>
       <c r="BC34" s="11" t="n">
         <v>0</v>
@@ -8073,10 +8453,10 @@
         <v>287393</v>
       </c>
       <c r="BE34" s="9" t="n">
-        <v>19048.41</v>
+        <v>17962.06</v>
       </c>
       <c r="BF34" s="10" t="n">
-        <v>0.0017</v>
+        <v>0.0016</v>
       </c>
       <c r="BG34" s="11" t="n">
         <v>0</v>
@@ -8085,10 +8465,10 @@
         <v>287393</v>
       </c>
       <c r="BI34" s="9" t="n">
-        <v>19453.63</v>
+        <v>19048.41</v>
       </c>
       <c r="BJ34" s="10" t="n">
-        <v>0.0018</v>
+        <v>0.0017</v>
       </c>
       <c r="BK34" s="11" t="n">
         <v>0</v>
@@ -8097,10 +8477,10 @@
         <v>287393</v>
       </c>
       <c r="BM34" s="9" t="n">
-        <v>19370.29</v>
+        <v>19453.63</v>
       </c>
       <c r="BN34" s="10" t="n">
-        <v>0.0019</v>
+        <v>0.0018</v>
       </c>
       <c r="BO34" s="11" t="n">
         <v>0</v>
@@ -8109,10 +8489,10 @@
         <v>287393</v>
       </c>
       <c r="BQ34" s="9" t="n">
-        <v>15976.18</v>
+        <v>19370.29</v>
       </c>
       <c r="BR34" s="10" t="n">
-        <v>0.0016</v>
+        <v>0.0019</v>
       </c>
       <c r="BS34" s="11" t="n">
         <v>0</v>
@@ -8121,10 +8501,10 @@
         <v>287393</v>
       </c>
       <c r="BU34" s="9" t="n">
-        <v>15821.13</v>
+        <v>15976.18</v>
       </c>
       <c r="BV34" s="10" t="n">
-        <v>0.0017</v>
+        <v>0.0016</v>
       </c>
       <c r="BW34" s="11" t="n">
         <v>0</v>
@@ -8133,24 +8513,36 @@
         <v>287393</v>
       </c>
       <c r="BY34" s="9" t="n">
-        <v>15273.64</v>
+        <v>15821.13</v>
       </c>
       <c r="BZ34" s="10" t="n">
         <v>0.0017</v>
       </c>
       <c r="CA34" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB34" s="8" t="n">
+        <v>287393</v>
+      </c>
+      <c r="CC34" s="9" t="n">
+        <v>15273.64</v>
+      </c>
+      <c r="CD34" s="10" t="n">
+        <v>0.0017</v>
+      </c>
+      <c r="CE34" s="11" t="n">
         <v>-0.03505968069568721</v>
       </c>
-      <c r="CB34" s="8" t="n">
+      <c r="CF34" s="8" t="n">
         <v>297835</v>
       </c>
-      <c r="CC34" s="9" t="n">
+      <c r="CG34" s="9" t="n">
         <v>18529.51</v>
       </c>
-      <c r="CD34" s="10" t="n">
+      <c r="CH34" s="10" t="n">
         <v>0.0021</v>
       </c>
-      <c r="CE34" s="11" t="n"/>
+      <c r="CI34" s="11" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
@@ -8244,7 +8636,7 @@
         <v>151687</v>
       </c>
       <c r="AC35" s="9" t="n">
-        <v>1704.36</v>
+        <v>1538.11</v>
       </c>
       <c r="AD35" s="10" t="n">
         <v>0.0001</v>
@@ -8256,7 +8648,7 @@
         <v>151687</v>
       </c>
       <c r="AG35" s="9" t="n">
-        <v>1728.63</v>
+        <v>1704.36</v>
       </c>
       <c r="AH35" s="10" t="n">
         <v>0.0001</v>
@@ -8268,7 +8660,7 @@
         <v>151687</v>
       </c>
       <c r="AK35" s="9" t="n">
-        <v>1858.32</v>
+        <v>1728.63</v>
       </c>
       <c r="AL35" s="10" t="n">
         <v>0.0001</v>
@@ -8280,10 +8672,10 @@
         <v>151687</v>
       </c>
       <c r="AO35" s="9" t="n">
-        <v>1947.66</v>
+        <v>1858.32</v>
       </c>
       <c r="AP35" s="10" t="n">
-        <v>0.0002</v>
+        <v>0.0001</v>
       </c>
       <c r="AQ35" s="11" t="n">
         <v>0</v>
@@ -8292,7 +8684,7 @@
         <v>151687</v>
       </c>
       <c r="AS35" s="9" t="n">
-        <v>2076.6</v>
+        <v>1947.66</v>
       </c>
       <c r="AT35" s="10" t="n">
         <v>0.0002</v>
@@ -8304,7 +8696,7 @@
         <v>151687</v>
       </c>
       <c r="AW35" s="9" t="n">
-        <v>1987.1</v>
+        <v>2076.6</v>
       </c>
       <c r="AX35" s="10" t="n">
         <v>0.0002</v>
@@ -8316,7 +8708,7 @@
         <v>151687</v>
       </c>
       <c r="BA35" s="9" t="n">
-        <v>2130.6</v>
+        <v>1987.1</v>
       </c>
       <c r="BB35" s="10" t="n">
         <v>0.0002</v>
@@ -8328,7 +8720,7 @@
         <v>151687</v>
       </c>
       <c r="BE35" s="9" t="n">
-        <v>2091.16</v>
+        <v>2130.6</v>
       </c>
       <c r="BF35" s="10" t="n">
         <v>0.0002</v>
@@ -8340,30 +8732,38 @@
         <v>151687</v>
       </c>
       <c r="BI35" s="9" t="n">
-        <v>1766.62</v>
+        <v>2091.16</v>
       </c>
       <c r="BJ35" s="10" t="n">
         <v>0.0002</v>
       </c>
       <c r="BK35" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL35" s="8" t="n">
+        <v>151687</v>
+      </c>
+      <c r="BM35" s="9" t="n">
+        <v>1766.62</v>
+      </c>
+      <c r="BN35" s="10" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="BO35" s="11" t="n">
         <v>0.6954140540298874</v>
       </c>
-      <c r="BL35" s="8" t="n">
+      <c r="BP35" s="8" t="n">
         <v>89469</v>
       </c>
-      <c r="BM35" s="9" t="n">
+      <c r="BQ35" s="9" t="n">
         <v>828.48</v>
       </c>
-      <c r="BN35" s="10" t="n">
+      <c r="BR35" s="10" t="n">
         <v>0.0001</v>
       </c>
-      <c r="BO35" s="11" t="n">
+      <c r="BS35" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="BP35" s="8" t="n"/>
-      <c r="BQ35" s="9" t="n"/>
-      <c r="BR35" s="10" t="n"/>
-      <c r="BS35" s="11" t="n"/>
       <c r="BT35" s="8" t="n"/>
       <c r="BU35" s="9" t="n"/>
       <c r="BV35" s="10" t="n"/>
@@ -8376,6 +8776,10 @@
       <c r="CC35" s="9" t="n"/>
       <c r="CD35" s="10" t="n"/>
       <c r="CE35" s="11" t="n"/>
+      <c r="CF35" s="8" t="n"/>
+      <c r="CG35" s="9" t="n"/>
+      <c r="CH35" s="10" t="n"/>
+      <c r="CI35" s="11" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
@@ -8469,7 +8873,7 @@
         <v>47293</v>
       </c>
       <c r="AC36" s="9" t="n">
-        <v>1700.33</v>
+        <v>1564.88</v>
       </c>
       <c r="AD36" s="10" t="n">
         <v>0.0001</v>
@@ -8481,7 +8885,7 @@
         <v>47293</v>
       </c>
       <c r="AG36" s="9" t="n">
-        <v>1637.61</v>
+        <v>1700.33</v>
       </c>
       <c r="AH36" s="10" t="n">
         <v>0.0001</v>
@@ -8493,7 +8897,7 @@
         <v>47293</v>
       </c>
       <c r="AK36" s="9" t="n">
-        <v>1691.91</v>
+        <v>1637.61</v>
       </c>
       <c r="AL36" s="10" t="n">
         <v>0.0001</v>
@@ -8505,7 +8909,7 @@
         <v>47293</v>
       </c>
       <c r="AO36" s="9" t="n">
-        <v>1764.08</v>
+        <v>1691.91</v>
       </c>
       <c r="AP36" s="10" t="n">
         <v>0.0001</v>
@@ -8517,10 +8921,10 @@
         <v>47293</v>
       </c>
       <c r="AS36" s="9" t="n">
-        <v>1892.15</v>
+        <v>1764.08</v>
       </c>
       <c r="AT36" s="10" t="n">
-        <v>0.0002</v>
+        <v>0.0001</v>
       </c>
       <c r="AU36" s="11" t="n">
         <v>0</v>
@@ -8529,7 +8933,7 @@
         <v>47293</v>
       </c>
       <c r="AW36" s="9" t="n">
-        <v>1955.38</v>
+        <v>1892.15</v>
       </c>
       <c r="AX36" s="10" t="n">
         <v>0.0002</v>
@@ -8541,7 +8945,7 @@
         <v>47293</v>
       </c>
       <c r="BA36" s="9" t="n">
-        <v>1897.21</v>
+        <v>1955.38</v>
       </c>
       <c r="BB36" s="10" t="n">
         <v>0.0002</v>
@@ -8553,7 +8957,7 @@
         <v>47293</v>
       </c>
       <c r="BE36" s="9" t="n">
-        <v>1983.66</v>
+        <v>1897.21</v>
       </c>
       <c r="BF36" s="10" t="n">
         <v>0.0002</v>
@@ -8565,7 +8969,7 @@
         <v>47293</v>
       </c>
       <c r="BI36" s="9" t="n">
-        <v>1867.41</v>
+        <v>1983.66</v>
       </c>
       <c r="BJ36" s="10" t="n">
         <v>0.0002</v>
@@ -8577,7 +8981,7 @@
         <v>47293</v>
       </c>
       <c r="BM36" s="9" t="n">
-        <v>1857.76</v>
+        <v>1867.41</v>
       </c>
       <c r="BN36" s="10" t="n">
         <v>0.0002</v>
@@ -8589,7 +8993,7 @@
         <v>47293</v>
       </c>
       <c r="BQ36" s="9" t="n">
-        <v>1925.39</v>
+        <v>1857.76</v>
       </c>
       <c r="BR36" s="10" t="n">
         <v>0.0002</v>
@@ -8601,7 +9005,7 @@
         <v>47293</v>
       </c>
       <c r="BU36" s="9" t="n">
-        <v>1844.17</v>
+        <v>1925.39</v>
       </c>
       <c r="BV36" s="10" t="n">
         <v>0.0002</v>
@@ -8613,10 +9017,10 @@
         <v>47293</v>
       </c>
       <c r="BY36" s="9" t="n">
-        <v>1236.83</v>
+        <v>1844.17</v>
       </c>
       <c r="BZ36" s="10" t="n">
-        <v>0.0001</v>
+        <v>0.0002</v>
       </c>
       <c r="CA36" s="11" t="n">
         <v>0</v>
@@ -8625,12 +9029,24 @@
         <v>47293</v>
       </c>
       <c r="CC36" s="9" t="n">
+        <v>1236.83</v>
+      </c>
+      <c r="CD36" s="10" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="CE36" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF36" s="8" t="n">
+        <v>47293</v>
+      </c>
+      <c r="CG36" s="9" t="n">
         <v>1612.64</v>
       </c>
-      <c r="CD36" s="10" t="n">
+      <c r="CH36" s="10" t="n">
         <v>0.0002</v>
       </c>
-      <c r="CE36" s="11" t="n"/>
+      <c r="CI36" s="11" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
@@ -8679,113 +9095,105 @@
       <c r="AF37" s="8" t="n"/>
       <c r="AG37" s="9" t="n"/>
       <c r="AH37" s="10" t="n"/>
-      <c r="AI37" s="11" t="n">
+      <c r="AI37" s="11" t="n"/>
+      <c r="AJ37" s="8" t="n"/>
+      <c r="AK37" s="9" t="n"/>
+      <c r="AL37" s="10" t="n"/>
+      <c r="AM37" s="11" t="n">
         <v>-1</v>
       </c>
-      <c r="AJ37" s="8" t="n">
+      <c r="AN37" s="8" t="n">
         <v>24621592</v>
       </c>
-      <c r="AK37" s="9" t="n">
+      <c r="AO37" s="9" t="n">
         <v>541945.86</v>
       </c>
-      <c r="AL37" s="10" t="n">
+      <c r="AP37" s="10" t="n">
         <v>0.0407</v>
       </c>
-      <c r="AM37" s="11" t="n">
+      <c r="AQ37" s="11" t="n">
         <v>0.01296144774839237</v>
       </c>
-      <c r="AN37" s="8" t="n">
+      <c r="AR37" s="8" t="n">
         <v>24306544</v>
       </c>
-      <c r="AO37" s="9" t="n">
+      <c r="AS37" s="9" t="n">
         <v>516368.22</v>
       </c>
-      <c r="AP37" s="10" t="n">
+      <c r="AT37" s="10" t="n">
         <v>0.0398</v>
       </c>
-      <c r="AQ37" s="11" t="n">
+      <c r="AU37" s="11" t="n">
         <v>0.004192884502844551</v>
-      </c>
-      <c r="AR37" s="8" t="n">
-        <v>24205055</v>
-      </c>
-      <c r="AS37" s="9" t="n">
-        <v>508838.67</v>
-      </c>
-      <c r="AT37" s="10" t="n">
-        <v>0.0404</v>
-      </c>
-      <c r="AU37" s="11" t="n">
-        <v>0</v>
       </c>
       <c r="AV37" s="8" t="n">
         <v>24205055</v>
       </c>
       <c r="AW37" s="9" t="n">
+        <v>508838.67</v>
+      </c>
+      <c r="AX37" s="10" t="n">
+        <v>0.0404</v>
+      </c>
+      <c r="AY37" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ37" s="8" t="n">
+        <v>24205055</v>
+      </c>
+      <c r="BA37" s="9" t="n">
         <v>482334.13</v>
       </c>
-      <c r="AX37" s="10" t="n">
+      <c r="BB37" s="10" t="n">
         <v>0.0403</v>
       </c>
-      <c r="AY37" s="11" t="n">
+      <c r="BC37" s="11" t="n">
         <v>0.03407788338216907</v>
       </c>
-      <c r="AZ37" s="8" t="n">
+      <c r="BD37" s="8" t="n">
         <v>23407381</v>
       </c>
-      <c r="BA37" s="9" t="n">
+      <c r="BE37" s="9" t="n">
         <v>458854.89</v>
       </c>
-      <c r="BB37" s="10" t="n">
+      <c r="BF37" s="10" t="n">
         <v>0.0399</v>
       </c>
-      <c r="BC37" s="11" t="n">
+      <c r="BG37" s="11" t="n">
         <v>0.06425892329321918</v>
       </c>
-      <c r="BD37" s="8" t="n">
+      <c r="BH37" s="8" t="n">
         <v>21994066</v>
       </c>
-      <c r="BE37" s="9" t="n">
+      <c r="BI37" s="9" t="n">
         <v>435174.59</v>
       </c>
-      <c r="BF37" s="10" t="n">
+      <c r="BJ37" s="10" t="n">
         <v>0.0384</v>
       </c>
-      <c r="BG37" s="11" t="n">
+      <c r="BK37" s="11" t="n">
         <v>0.07428402120388222</v>
       </c>
-      <c r="BH37" s="8" t="n">
+      <c r="BL37" s="8" t="n">
         <v>20473232</v>
       </c>
-      <c r="BI37" s="9" t="n">
+      <c r="BM37" s="9" t="n">
         <v>442938.37</v>
       </c>
-      <c r="BJ37" s="10" t="n">
+      <c r="BN37" s="10" t="n">
         <v>0.0401</v>
       </c>
-      <c r="BK37" s="11" t="n">
+      <c r="BO37" s="11" t="n">
         <v>0.03644973136547983</v>
-      </c>
-      <c r="BL37" s="8" t="n">
-        <v>19753232</v>
-      </c>
-      <c r="BM37" s="9" t="n">
-        <v>409820.3</v>
-      </c>
-      <c r="BN37" s="10" t="n">
-        <v>0.0395</v>
-      </c>
-      <c r="BO37" s="11" t="n">
-        <v>0</v>
       </c>
       <c r="BP37" s="8" t="n">
         <v>19753232</v>
       </c>
       <c r="BQ37" s="9" t="n">
-        <v>436171.12</v>
+        <v>409820.3</v>
       </c>
       <c r="BR37" s="10" t="n">
-        <v>0.0443</v>
+        <v>0.0395</v>
       </c>
       <c r="BS37" s="11" t="n">
         <v>0</v>
@@ -8794,10 +9202,10 @@
         <v>19753232</v>
       </c>
       <c r="BU37" s="9" t="n">
-        <v>428882.17</v>
+        <v>436171.12</v>
       </c>
       <c r="BV37" s="10" t="n">
-        <v>0.0459</v>
+        <v>0.0443</v>
       </c>
       <c r="BW37" s="11" t="n">
         <v>0</v>
@@ -8806,10 +9214,10 @@
         <v>19753232</v>
       </c>
       <c r="BY37" s="9" t="n">
-        <v>375894.13</v>
+        <v>428882.17</v>
       </c>
       <c r="BZ37" s="10" t="n">
-        <v>0.0427</v>
+        <v>0.0459</v>
       </c>
       <c r="CA37" s="11" t="n">
         <v>0</v>
@@ -8818,12 +9226,24 @@
         <v>19753232</v>
       </c>
       <c r="CC37" s="9" t="n">
+        <v>375894.13</v>
+      </c>
+      <c r="CD37" s="10" t="n">
+        <v>0.0427</v>
+      </c>
+      <c r="CE37" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF37" s="8" t="n">
+        <v>19753232</v>
+      </c>
+      <c r="CG37" s="9" t="n">
         <v>375568.2</v>
       </c>
-      <c r="CD37" s="10" t="n">
+      <c r="CH37" s="10" t="n">
         <v>0.0419</v>
       </c>
-      <c r="CE37" s="11" t="n"/>
+      <c r="CI37" s="11" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
@@ -8868,37 +9288,37 @@
         <v>-1</v>
       </c>
       <c r="AB38" s="8" t="n">
+        <v>2274074</v>
+      </c>
+      <c r="AC38" s="9" t="n">
+        <v>47368.96</v>
+      </c>
+      <c r="AD38" s="10" t="n">
+        <v>0.0037</v>
+      </c>
+      <c r="AE38" s="11" t="n">
+        <v>-0.2174731122669314</v>
+      </c>
+      <c r="AF38" s="8" t="n">
         <v>2906065</v>
       </c>
-      <c r="AC38" s="9" t="n">
+      <c r="AG38" s="9" t="n">
         <v>69277.67999999999</v>
       </c>
-      <c r="AD38" s="10" t="n">
+      <c r="AH38" s="10" t="n">
         <v>0.0052</v>
       </c>
-      <c r="AE38" s="11" t="n">
+      <c r="AI38" s="11" t="n">
         <v>-0.3062750860930125</v>
-      </c>
-      <c r="AF38" s="8" t="n">
-        <v>4189074</v>
-      </c>
-      <c r="AG38" s="9" t="n">
-        <v>96591.67</v>
-      </c>
-      <c r="AH38" s="10" t="n">
-        <v>0.0072</v>
-      </c>
-      <c r="AI38" s="11" t="n">
-        <v>0</v>
       </c>
       <c r="AJ38" s="8" t="n">
         <v>4189074</v>
       </c>
       <c r="AK38" s="9" t="n">
-        <v>97173.95</v>
+        <v>96591.67</v>
       </c>
       <c r="AL38" s="10" t="n">
-        <v>0.0073</v>
+        <v>0.0072</v>
       </c>
       <c r="AM38" s="11" t="n">
         <v>0</v>
@@ -8907,10 +9327,10 @@
         <v>4189074</v>
       </c>
       <c r="AO38" s="9" t="n">
-        <v>96721.53</v>
+        <v>97173.95</v>
       </c>
       <c r="AP38" s="10" t="n">
-        <v>0.0075</v>
+        <v>0.0073</v>
       </c>
       <c r="AQ38" s="11" t="n">
         <v>0</v>
@@ -8919,10 +9339,10 @@
         <v>4189074</v>
       </c>
       <c r="AS38" s="9" t="n">
-        <v>95502.50999999999</v>
+        <v>96721.53</v>
       </c>
       <c r="AT38" s="10" t="n">
-        <v>0.0076</v>
+        <v>0.0075</v>
       </c>
       <c r="AU38" s="11" t="n">
         <v>0</v>
@@ -8931,10 +9351,10 @@
         <v>4189074</v>
       </c>
       <c r="AW38" s="9" t="n">
-        <v>96130.87</v>
+        <v>95502.50999999999</v>
       </c>
       <c r="AX38" s="10" t="n">
-        <v>0.008</v>
+        <v>0.0076</v>
       </c>
       <c r="AY38" s="11" t="n">
         <v>0</v>
@@ -8943,10 +9363,10 @@
         <v>4189074</v>
       </c>
       <c r="BA38" s="9" t="n">
-        <v>95904.66</v>
+        <v>96130.87</v>
       </c>
       <c r="BB38" s="10" t="n">
-        <v>0.0083</v>
+        <v>0.008</v>
       </c>
       <c r="BC38" s="11" t="n">
         <v>0</v>
@@ -8955,10 +9375,10 @@
         <v>4189074</v>
       </c>
       <c r="BE38" s="9" t="n">
-        <v>112108</v>
+        <v>95904.66</v>
       </c>
       <c r="BF38" s="10" t="n">
-        <v>0.009900000000000001</v>
+        <v>0.0083</v>
       </c>
       <c r="BG38" s="11" t="n">
         <v>0</v>
@@ -8967,10 +9387,10 @@
         <v>4189074</v>
       </c>
       <c r="BI38" s="9" t="n">
-        <v>102435.43</v>
+        <v>112108</v>
       </c>
       <c r="BJ38" s="10" t="n">
-        <v>0.009299999999999999</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="BK38" s="11" t="n">
         <v>0</v>
@@ -8979,10 +9399,10 @@
         <v>4189074</v>
       </c>
       <c r="BM38" s="9" t="n">
-        <v>103562.29</v>
+        <v>102435.43</v>
       </c>
       <c r="BN38" s="10" t="n">
-        <v>0.01</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="BO38" s="11" t="n">
         <v>0</v>
@@ -8991,10 +9411,10 @@
         <v>4189074</v>
       </c>
       <c r="BQ38" s="9" t="n">
-        <v>112061.92</v>
+        <v>103562.29</v>
       </c>
       <c r="BR38" s="10" t="n">
-        <v>0.0114</v>
+        <v>0.01</v>
       </c>
       <c r="BS38" s="11" t="n">
         <v>0</v>
@@ -9003,10 +9423,10 @@
         <v>4189074</v>
       </c>
       <c r="BU38" s="9" t="n">
-        <v>107022.46</v>
+        <v>112061.92</v>
       </c>
       <c r="BV38" s="10" t="n">
-        <v>0.0115</v>
+        <v>0.0114</v>
       </c>
       <c r="BW38" s="11" t="n">
         <v>0</v>
@@ -9015,10 +9435,10 @@
         <v>4189074</v>
       </c>
       <c r="BY38" s="9" t="n">
-        <v>109571.51</v>
+        <v>107022.46</v>
       </c>
       <c r="BZ38" s="10" t="n">
-        <v>0.0125</v>
+        <v>0.0115</v>
       </c>
       <c r="CA38" s="11" t="n">
         <v>0</v>
@@ -9027,12 +9447,24 @@
         <v>4189074</v>
       </c>
       <c r="CC38" s="9" t="n">
+        <v>109571.51</v>
+      </c>
+      <c r="CD38" s="10" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="CE38" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF38" s="8" t="n">
+        <v>4189074</v>
+      </c>
+      <c r="CG38" s="9" t="n">
         <v>116089.71</v>
       </c>
-      <c r="CD38" s="10" t="n">
+      <c r="CH38" s="10" t="n">
         <v>0.0129</v>
       </c>
-      <c r="CE38" s="11" t="n"/>
+      <c r="CI38" s="11" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
@@ -9097,29 +9529,21 @@
       <c r="AV39" s="8" t="n"/>
       <c r="AW39" s="9" t="n"/>
       <c r="AX39" s="10" t="n"/>
-      <c r="AY39" s="11" t="n">
+      <c r="AY39" s="11" t="n"/>
+      <c r="AZ39" s="8" t="n"/>
+      <c r="BA39" s="9" t="n"/>
+      <c r="BB39" s="10" t="n"/>
+      <c r="BC39" s="11" t="n">
         <v>-1</v>
-      </c>
-      <c r="AZ39" s="8" t="n">
-        <v>4400000</v>
-      </c>
-      <c r="BA39" s="9" t="n">
-        <v>88822.8</v>
-      </c>
-      <c r="BB39" s="10" t="n">
-        <v>0.0077</v>
-      </c>
-      <c r="BC39" s="11" t="n">
-        <v>0</v>
       </c>
       <c r="BD39" s="8" t="n">
         <v>4400000</v>
       </c>
       <c r="BE39" s="9" t="n">
-        <v>89280.39999999999</v>
+        <v>88822.8</v>
       </c>
       <c r="BF39" s="10" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.0077</v>
       </c>
       <c r="BG39" s="11" t="n">
         <v>0</v>
@@ -9128,18 +9552,26 @@
         <v>4400000</v>
       </c>
       <c r="BI39" s="9" t="n">
+        <v>89280.39999999999</v>
+      </c>
+      <c r="BJ39" s="10" t="n">
+        <v>0.007900000000000001</v>
+      </c>
+      <c r="BK39" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL39" s="8" t="n">
+        <v>4400000</v>
+      </c>
+      <c r="BM39" s="9" t="n">
         <v>89020.8</v>
       </c>
-      <c r="BJ39" s="10" t="n">
+      <c r="BN39" s="10" t="n">
         <v>0.0081</v>
       </c>
-      <c r="BK39" s="11" t="n">
+      <c r="BO39" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="BL39" s="8" t="n"/>
-      <c r="BM39" s="9" t="n"/>
-      <c r="BN39" s="10" t="n"/>
-      <c r="BO39" s="11" t="n"/>
       <c r="BP39" s="8" t="n"/>
       <c r="BQ39" s="9" t="n"/>
       <c r="BR39" s="10" t="n"/>
@@ -9156,6 +9588,10 @@
       <c r="CC39" s="9" t="n"/>
       <c r="CD39" s="10" t="n"/>
       <c r="CE39" s="11" t="n"/>
+      <c r="CF39" s="8" t="n"/>
+      <c r="CG39" s="9" t="n"/>
+      <c r="CH39" s="10" t="n"/>
+      <c r="CI39" s="11" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
@@ -9204,29 +9640,21 @@
       <c r="AF40" s="8" t="n"/>
       <c r="AG40" s="9" t="n"/>
       <c r="AH40" s="10" t="n"/>
-      <c r="AI40" s="11" t="n">
+      <c r="AI40" s="11" t="n"/>
+      <c r="AJ40" s="8" t="n"/>
+      <c r="AK40" s="9" t="n"/>
+      <c r="AL40" s="10" t="n"/>
+      <c r="AM40" s="11" t="n">
         <v>-1</v>
-      </c>
-      <c r="AJ40" s="8" t="n">
-        <v>797719</v>
-      </c>
-      <c r="AK40" s="9" t="n">
-        <v>88833.99000000001</v>
-      </c>
-      <c r="AL40" s="10" t="n">
-        <v>0.0067</v>
-      </c>
-      <c r="AM40" s="11" t="n">
-        <v>0</v>
       </c>
       <c r="AN40" s="8" t="n">
         <v>797719</v>
       </c>
       <c r="AO40" s="9" t="n">
-        <v>80358.22</v>
+        <v>88833.99000000001</v>
       </c>
       <c r="AP40" s="10" t="n">
-        <v>0.0062</v>
+        <v>0.0067</v>
       </c>
       <c r="AQ40" s="11" t="n">
         <v>0</v>
@@ -9235,10 +9663,10 @@
         <v>797719</v>
       </c>
       <c r="AS40" s="9" t="n">
-        <v>73737.16</v>
+        <v>80358.22</v>
       </c>
       <c r="AT40" s="10" t="n">
-        <v>0.0059</v>
+        <v>0.0062</v>
       </c>
       <c r="AU40" s="11" t="n">
         <v>0</v>
@@ -9247,10 +9675,10 @@
         <v>797719</v>
       </c>
       <c r="AW40" s="9" t="n">
-        <v>62190.17</v>
+        <v>73737.16</v>
       </c>
       <c r="AX40" s="10" t="n">
-        <v>0.0052</v>
+        <v>0.0059</v>
       </c>
       <c r="AY40" s="11" t="n">
         <v>0</v>
@@ -9259,10 +9687,10 @@
         <v>797719</v>
       </c>
       <c r="BA40" s="9" t="n">
-        <v>58951.43</v>
+        <v>62190.17</v>
       </c>
       <c r="BB40" s="10" t="n">
-        <v>0.0051</v>
+        <v>0.0052</v>
       </c>
       <c r="BC40" s="11" t="n">
         <v>0</v>
@@ -9271,10 +9699,10 @@
         <v>797719</v>
       </c>
       <c r="BE40" s="9" t="n">
-        <v>61368.52</v>
+        <v>58951.43</v>
       </c>
       <c r="BF40" s="10" t="n">
-        <v>0.0054</v>
+        <v>0.0051</v>
       </c>
       <c r="BG40" s="11" t="n">
         <v>0</v>
@@ -9283,10 +9711,10 @@
         <v>797719</v>
       </c>
       <c r="BI40" s="9" t="n">
-        <v>71347.99000000001</v>
+        <v>61368.52</v>
       </c>
       <c r="BJ40" s="10" t="n">
-        <v>0.0065</v>
+        <v>0.0054</v>
       </c>
       <c r="BK40" s="11" t="n">
         <v>0</v>
@@ -9295,10 +9723,10 @@
         <v>797719</v>
       </c>
       <c r="BM40" s="9" t="n">
-        <v>52665.41</v>
+        <v>71347.99000000001</v>
       </c>
       <c r="BN40" s="10" t="n">
-        <v>0.0051</v>
+        <v>0.0065</v>
       </c>
       <c r="BO40" s="11" t="n">
         <v>0</v>
@@ -9307,10 +9735,10 @@
         <v>797719</v>
       </c>
       <c r="BQ40" s="9" t="n">
-        <v>48884.22</v>
+        <v>52665.41</v>
       </c>
       <c r="BR40" s="10" t="n">
-        <v>0.005</v>
+        <v>0.0051</v>
       </c>
       <c r="BS40" s="11" t="n">
         <v>0</v>
@@ -9319,10 +9747,10 @@
         <v>797719</v>
       </c>
       <c r="BU40" s="9" t="n">
-        <v>42372.84</v>
+        <v>48884.22</v>
       </c>
       <c r="BV40" s="10" t="n">
-        <v>0.0045</v>
+        <v>0.005</v>
       </c>
       <c r="BW40" s="11" t="n">
         <v>0</v>
@@ -9331,24 +9759,36 @@
         <v>797719</v>
       </c>
       <c r="BY40" s="9" t="n">
-        <v>39819.34</v>
+        <v>42372.84</v>
       </c>
       <c r="BZ40" s="10" t="n">
         <v>0.0045</v>
       </c>
       <c r="CA40" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB40" s="8" t="n">
+        <v>797719</v>
+      </c>
+      <c r="CC40" s="9" t="n">
+        <v>39819.34</v>
+      </c>
+      <c r="CD40" s="10" t="n">
+        <v>0.0045</v>
+      </c>
+      <c r="CE40" s="11" t="n">
         <v>-0.09569612848812428</v>
       </c>
-      <c r="CB40" s="8" t="n">
+      <c r="CF40" s="8" t="n">
         <v>882136</v>
       </c>
-      <c r="CC40" s="9" t="n">
+      <c r="CG40" s="9" t="n">
         <v>50572.42</v>
       </c>
-      <c r="CD40" s="10" t="n">
+      <c r="CH40" s="10" t="n">
         <v>0.0056</v>
       </c>
-      <c r="CE40" s="11" t="n"/>
+      <c r="CI40" s="11" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
@@ -9413,103 +9853,107 @@
       <c r="AV41" s="8" t="n"/>
       <c r="AW41" s="9" t="n"/>
       <c r="AX41" s="10" t="n"/>
-      <c r="AY41" s="11" t="n">
+      <c r="AY41" s="11" t="n"/>
+      <c r="AZ41" s="8" t="n"/>
+      <c r="BA41" s="9" t="n"/>
+      <c r="BB41" s="10" t="n"/>
+      <c r="BC41" s="11" t="n">
         <v>-1</v>
       </c>
-      <c r="AZ41" s="8" t="n">
+      <c r="BD41" s="8" t="n">
         <v>218075</v>
       </c>
-      <c r="BA41" s="9" t="n">
+      <c r="BE41" s="9" t="n">
         <v>3019.03</v>
       </c>
-      <c r="BB41" s="10" t="n">
+      <c r="BF41" s="10" t="n">
         <v>0.0003</v>
       </c>
-      <c r="BC41" s="11" t="n">
+      <c r="BG41" s="11" t="n">
         <v>-0.6148554615199853</v>
       </c>
-      <c r="BD41" s="8" t="n">
+      <c r="BH41" s="8" t="n">
         <v>566216</v>
       </c>
-      <c r="BE41" s="9" t="n">
+      <c r="BI41" s="9" t="n">
         <v>8345.459999999999</v>
       </c>
-      <c r="BF41" s="10" t="n">
+      <c r="BJ41" s="10" t="n">
         <v>0.0007</v>
       </c>
-      <c r="BG41" s="11" t="n">
+      <c r="BK41" s="11" t="n">
         <v>-0.5682871579351869</v>
       </c>
-      <c r="BH41" s="8" t="n">
+      <c r="BL41" s="8" t="n">
         <v>1311557</v>
       </c>
-      <c r="BI41" s="9" t="n">
+      <c r="BM41" s="9" t="n">
         <v>18228.02</v>
       </c>
-      <c r="BJ41" s="10" t="n">
+      <c r="BN41" s="10" t="n">
         <v>0.0017</v>
       </c>
-      <c r="BK41" s="11" t="n">
+      <c r="BO41" s="11" t="n">
         <v>-0.2008037316547793</v>
       </c>
-      <c r="BL41" s="8" t="n">
+      <c r="BP41" s="8" t="n">
         <v>1641095</v>
       </c>
-      <c r="BM41" s="9" t="n">
+      <c r="BQ41" s="9" t="n">
         <v>23382.32</v>
       </c>
-      <c r="BN41" s="10" t="n">
+      <c r="BR41" s="10" t="n">
         <v>0.0023</v>
       </c>
-      <c r="BO41" s="11" t="n">
+      <c r="BS41" s="11" t="n">
         <v>-0.1163687388172734</v>
       </c>
-      <c r="BP41" s="8" t="n">
+      <c r="BT41" s="8" t="n">
         <v>1857217</v>
       </c>
-      <c r="BQ41" s="9" t="n">
+      <c r="BU41" s="9" t="n">
         <v>26023.32</v>
       </c>
-      <c r="BR41" s="10" t="n">
+      <c r="BV41" s="10" t="n">
         <v>0.0026</v>
       </c>
-      <c r="BS41" s="11" t="n">
+      <c r="BW41" s="11" t="n">
         <v>-0.03620728307597141</v>
-      </c>
-      <c r="BT41" s="8" t="n">
-        <v>1926988</v>
-      </c>
-      <c r="BU41" s="9" t="n">
-        <v>28941.43</v>
-      </c>
-      <c r="BV41" s="10" t="n">
-        <v>0.0031</v>
-      </c>
-      <c r="BW41" s="11" t="n">
-        <v>0</v>
       </c>
       <c r="BX41" s="8" t="n">
         <v>1926988</v>
       </c>
       <c r="BY41" s="9" t="n">
+        <v>28941.43</v>
+      </c>
+      <c r="BZ41" s="10" t="n">
+        <v>0.0031</v>
+      </c>
+      <c r="CA41" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB41" s="8" t="n">
+        <v>1926988</v>
+      </c>
+      <c r="CC41" s="9" t="n">
         <v>26117.43</v>
       </c>
-      <c r="BZ41" s="10" t="n">
+      <c r="CD41" s="10" t="n">
         <v>0.003</v>
       </c>
-      <c r="CA41" s="11" t="n">
+      <c r="CE41" s="11" t="n">
         <v>-0.1421734974921662</v>
       </c>
-      <c r="CB41" s="8" t="n">
+      <c r="CF41" s="8" t="n">
         <v>2246361</v>
       </c>
-      <c r="CC41" s="9" t="n">
+      <c r="CG41" s="9" t="n">
         <v>32421.73</v>
       </c>
-      <c r="CD41" s="10" t="n">
+      <c r="CH41" s="10" t="n">
         <v>0.0036</v>
       </c>
-      <c r="CE41" s="11" t="n"/>
+      <c r="CI41" s="11" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
@@ -9582,79 +10026,83 @@
       <c r="BD42" s="8" t="n"/>
       <c r="BE42" s="9" t="n"/>
       <c r="BF42" s="10" t="n"/>
-      <c r="BG42" s="11" t="n">
+      <c r="BG42" s="11" t="n"/>
+      <c r="BH42" s="8" t="n"/>
+      <c r="BI42" s="9" t="n"/>
+      <c r="BJ42" s="10" t="n"/>
+      <c r="BK42" s="11" t="n">
         <v>-1</v>
       </c>
-      <c r="BH42" s="8" t="n">
+      <c r="BL42" s="8" t="n">
         <v>591805</v>
       </c>
-      <c r="BI42" s="9" t="n">
+      <c r="BM42" s="9" t="n">
         <v>5149</v>
       </c>
-      <c r="BJ42" s="10" t="n">
+      <c r="BN42" s="10" t="n">
         <v>0.0005</v>
       </c>
-      <c r="BK42" s="11" t="n">
+      <c r="BO42" s="11" t="n">
         <v>-0.8902567225534253</v>
       </c>
-      <c r="BL42" s="8" t="n">
+      <c r="BP42" s="8" t="n">
         <v>5392631</v>
       </c>
-      <c r="BM42" s="9" t="n">
+      <c r="BQ42" s="9" t="n">
         <v>43674.92</v>
       </c>
-      <c r="BN42" s="10" t="n">
+      <c r="BR42" s="10" t="n">
         <v>0.0042</v>
       </c>
-      <c r="BO42" s="11" t="n">
+      <c r="BS42" s="11" t="n">
         <v>-0.3719237093069153</v>
       </c>
-      <c r="BP42" s="8" t="n">
+      <c r="BT42" s="8" t="n">
         <v>8585949</v>
       </c>
-      <c r="BQ42" s="9" t="n">
+      <c r="BU42" s="9" t="n">
         <v>56044.78</v>
       </c>
-      <c r="BR42" s="10" t="n">
+      <c r="BV42" s="10" t="n">
         <v>0.0057</v>
       </c>
-      <c r="BS42" s="11" t="n">
+      <c r="BW42" s="11" t="n">
         <v>-0.2132577936597328</v>
       </c>
-      <c r="BT42" s="8" t="n">
+      <c r="BX42" s="8" t="n">
         <v>10913294</v>
       </c>
-      <c r="BU42" s="9" t="n">
+      <c r="BY42" s="9" t="n">
         <v>67154.95</v>
       </c>
-      <c r="BV42" s="10" t="n">
+      <c r="BZ42" s="10" t="n">
         <v>0.0072</v>
       </c>
-      <c r="BW42" s="11" t="n">
+      <c r="CA42" s="11" t="n">
         <v>-0.09462389658963724</v>
-      </c>
-      <c r="BX42" s="8" t="n">
-        <v>12053879</v>
-      </c>
-      <c r="BY42" s="9" t="n">
-        <v>70937.08</v>
-      </c>
-      <c r="BZ42" s="10" t="n">
-        <v>0.0081</v>
-      </c>
-      <c r="CA42" s="11" t="n">
-        <v>0</v>
       </c>
       <c r="CB42" s="8" t="n">
         <v>12053879</v>
       </c>
       <c r="CC42" s="9" t="n">
+        <v>70937.08</v>
+      </c>
+      <c r="CD42" s="10" t="n">
+        <v>0.0081</v>
+      </c>
+      <c r="CE42" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF42" s="8" t="n">
+        <v>12053879</v>
+      </c>
+      <c r="CG42" s="9" t="n">
         <v>76801.28999999999</v>
       </c>
-      <c r="CD42" s="10" t="n">
+      <c r="CH42" s="10" t="n">
         <v>0.0086</v>
       </c>
-      <c r="CE42" s="11" t="n"/>
+      <c r="CI42" s="11" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
@@ -9742,10 +10190,10 @@
         <v>2205298</v>
       </c>
       <c r="AC43" s="9" t="n">
-        <v>29526.73</v>
+        <v>31198.35</v>
       </c>
       <c r="AD43" s="10" t="n">
-        <v>0.0022</v>
+        <v>0.0024</v>
       </c>
       <c r="AE43" s="11" t="n">
         <v>0</v>
@@ -9754,30 +10202,38 @@
         <v>2205298</v>
       </c>
       <c r="AG43" s="9" t="n">
+        <v>29526.73</v>
+      </c>
+      <c r="AH43" s="10" t="n">
+        <v>0.0022</v>
+      </c>
+      <c r="AI43" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ43" s="8" t="n">
+        <v>2205298</v>
+      </c>
+      <c r="AK43" s="9" t="n">
         <v>26516.5</v>
       </c>
-      <c r="AH43" s="10" t="n">
+      <c r="AL43" s="10" t="n">
         <v>0.002</v>
       </c>
-      <c r="AI43" s="11" t="n">
+      <c r="AM43" s="11" t="n">
         <v>0.3305575398932319</v>
       </c>
-      <c r="AJ43" s="8" t="n">
+      <c r="AN43" s="8" t="n">
         <v>1657424</v>
       </c>
-      <c r="AK43" s="9" t="n">
+      <c r="AO43" s="9" t="n">
         <v>18712.32</v>
       </c>
-      <c r="AL43" s="10" t="n">
+      <c r="AP43" s="10" t="n">
         <v>0.0014</v>
       </c>
-      <c r="AM43" s="11" t="n">
+      <c r="AQ43" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="AN43" s="8" t="n"/>
-      <c r="AO43" s="9" t="n"/>
-      <c r="AP43" s="10" t="n"/>
-      <c r="AQ43" s="11" t="n"/>
       <c r="AR43" s="8" t="n"/>
       <c r="AS43" s="9" t="n"/>
       <c r="AT43" s="10" t="n"/>
@@ -9818,6 +10274,10 @@
       <c r="CC43" s="9" t="n"/>
       <c r="CD43" s="10" t="n"/>
       <c r="CE43" s="11" t="n"/>
+      <c r="CF43" s="8" t="n"/>
+      <c r="CG43" s="9" t="n"/>
+      <c r="CH43" s="10" t="n"/>
+      <c r="CI43" s="11" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
@@ -9902,29 +10362,21 @@
       <c r="BP44" s="8" t="n"/>
       <c r="BQ44" s="9" t="n"/>
       <c r="BR44" s="10" t="n"/>
-      <c r="BS44" s="11" t="n">
+      <c r="BS44" s="11" t="n"/>
+      <c r="BT44" s="8" t="n"/>
+      <c r="BU44" s="9" t="n"/>
+      <c r="BV44" s="10" t="n"/>
+      <c r="BW44" s="11" t="n">
         <v>-1</v>
-      </c>
-      <c r="BT44" s="8" t="n">
-        <v>9899412</v>
-      </c>
-      <c r="BU44" s="9" t="n">
-        <v>19552.33</v>
-      </c>
-      <c r="BV44" s="10" t="n">
-        <v>0.0021</v>
-      </c>
-      <c r="BW44" s="11" t="n">
-        <v>0</v>
       </c>
       <c r="BX44" s="8" t="n">
         <v>9899412</v>
       </c>
       <c r="BY44" s="9" t="n">
-        <v>16216.23</v>
+        <v>19552.33</v>
       </c>
       <c r="BZ44" s="10" t="n">
-        <v>0.0018</v>
+        <v>0.0021</v>
       </c>
       <c r="CA44" s="11" t="n">
         <v>0</v>
@@ -9933,12 +10385,24 @@
         <v>9899412</v>
       </c>
       <c r="CC44" s="9" t="n">
-        <v>16131.09</v>
+        <v>16216.23</v>
       </c>
       <c r="CD44" s="10" t="n">
         <v>0.0018</v>
       </c>
-      <c r="CE44" s="11" t="n"/>
+      <c r="CE44" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF44" s="8" t="n">
+        <v>9899412</v>
+      </c>
+      <c r="CG44" s="9" t="n">
+        <v>16131.09</v>
+      </c>
+      <c r="CH44" s="10" t="n">
+        <v>0.0018</v>
+      </c>
+      <c r="CI44" s="11" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
@@ -9983,25 +10447,25 @@
       <c r="AB45" s="8" t="n"/>
       <c r="AC45" s="9" t="n"/>
       <c r="AD45" s="10" t="n"/>
-      <c r="AE45" s="11" t="n">
+      <c r="AE45" s="11" t="n"/>
+      <c r="AF45" s="8" t="n"/>
+      <c r="AG45" s="9" t="n"/>
+      <c r="AH45" s="10" t="n"/>
+      <c r="AI45" s="11" t="n">
         <v>-1</v>
       </c>
-      <c r="AF45" s="8" t="n">
+      <c r="AJ45" s="8" t="n">
         <v>795472</v>
       </c>
-      <c r="AG45" s="9" t="n">
+      <c r="AK45" s="9" t="n">
         <v>20109.53</v>
       </c>
-      <c r="AH45" s="10" t="n">
+      <c r="AL45" s="10" t="n">
         <v>0.0015</v>
       </c>
-      <c r="AI45" s="11" t="n">
+      <c r="AM45" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="AJ45" s="8" t="n"/>
-      <c r="AK45" s="9" t="n"/>
-      <c r="AL45" s="10" t="n"/>
-      <c r="AM45" s="11" t="n"/>
       <c r="AN45" s="8" t="n"/>
       <c r="AO45" s="9" t="n"/>
       <c r="AP45" s="10" t="n"/>
@@ -10046,6 +10510,10 @@
       <c r="CC45" s="9" t="n"/>
       <c r="CD45" s="10" t="n"/>
       <c r="CE45" s="11" t="n"/>
+      <c r="CF45" s="8" t="n"/>
+      <c r="CG45" s="9" t="n"/>
+      <c r="CH45" s="10" t="n"/>
+      <c r="CI45" s="11" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="12" t="inlineStr">
@@ -10116,157 +10584,168 @@
       </c>
       <c r="AA46" s="17" t="n"/>
       <c r="AB46" s="14" t="n">
-        <v>1285817925</v>
+        <v>1373201700</v>
       </c>
       <c r="AC46" s="15" t="n">
-        <v>8857498.139999999</v>
+        <v>8608487.040000001</v>
       </c>
       <c r="AD46" s="16" t="n">
-        <v>0.6597999999999999</v>
+        <v>0.6675</v>
       </c>
       <c r="AE46" s="17" t="n"/>
       <c r="AF46" s="14" t="n">
-        <v>1265994824</v>
+        <v>1285817925</v>
       </c>
       <c r="AG46" s="15" t="n">
-        <v>8789059.288358001</v>
+        <v>8857498.139999999</v>
       </c>
       <c r="AH46" s="16" t="n">
-        <v>0.6559051731198605</v>
+        <v>0.6597999999999999</v>
       </c>
       <c r="AI46" s="17" t="n"/>
       <c r="AJ46" s="14" t="n">
-        <v>1079845116</v>
+        <v>1265994824</v>
       </c>
       <c r="AK46" s="15" t="n">
-        <v>8588270.84</v>
+        <v>8789059.288358001</v>
       </c>
       <c r="AL46" s="16" t="n">
-        <v>0.6443999999999998</v>
+        <v>0.6559051731198605</v>
       </c>
       <c r="AM46" s="17" t="n"/>
       <c r="AN46" s="14" t="n">
-        <v>1039629309</v>
+        <v>1079845116</v>
       </c>
       <c r="AO46" s="15" t="n">
-        <v>8271351.1939775</v>
+        <v>8588270.84</v>
       </c>
       <c r="AP46" s="16" t="n">
-        <v>0.6373999999999999</v>
+        <v>0.6443999999999998</v>
       </c>
       <c r="AQ46" s="17" t="n"/>
       <c r="AR46" s="14" t="n">
-        <v>991416407</v>
+        <v>1039629309</v>
       </c>
       <c r="AS46" s="15" t="n">
-        <v>7865128.239999999</v>
+        <v>8271351.1939775</v>
       </c>
       <c r="AT46" s="16" t="n">
-        <v>0.6254999999999999</v>
+        <v>0.6373999999999999</v>
       </c>
       <c r="AU46" s="17" t="n"/>
       <c r="AV46" s="14" t="n">
-        <v>979359723</v>
+        <v>991416407</v>
       </c>
       <c r="AW46" s="15" t="n">
-        <v>7559180.720000002</v>
+        <v>7865128.239999999</v>
       </c>
       <c r="AX46" s="16" t="n">
-        <v>0.6313999999999996</v>
+        <v>0.6254999999999999</v>
       </c>
       <c r="AY46" s="17" t="n"/>
       <c r="AZ46" s="14" t="n">
-        <v>927478800</v>
+        <v>979359723</v>
       </c>
       <c r="BA46" s="15" t="n">
-        <v>7320811.489999999</v>
+        <v>7559180.720000002</v>
       </c>
       <c r="BB46" s="16" t="n">
-        <v>0.6364000000000001</v>
+        <v>0.6313999999999996</v>
       </c>
       <c r="BC46" s="17" t="n"/>
       <c r="BD46" s="14" t="n">
-        <v>819556049</v>
+        <v>927478800</v>
       </c>
       <c r="BE46" s="15" t="n">
-        <v>7290583.900000002</v>
+        <v>7320811.489999999</v>
       </c>
       <c r="BF46" s="16" t="n">
-        <v>0.6436999999999999</v>
+        <v>0.6364000000000001</v>
       </c>
       <c r="BG46" s="17" t="n"/>
       <c r="BH46" s="14" t="n">
-        <v>799425942</v>
+        <v>819556049</v>
       </c>
       <c r="BI46" s="15" t="n">
-        <v>7347454.07</v>
+        <v>7290583.900000002</v>
       </c>
       <c r="BJ46" s="16" t="n">
-        <v>0.6658000000000001</v>
+        <v>0.6436999999999999</v>
       </c>
       <c r="BK46" s="17" t="n"/>
       <c r="BL46" s="14" t="n">
-        <v>756845974</v>
+        <v>799425942</v>
       </c>
       <c r="BM46" s="15" t="n">
-        <v>6714757.130000002</v>
+        <v>7347454.07</v>
       </c>
       <c r="BN46" s="16" t="n">
-        <v>0.6467999999999997</v>
+        <v>0.6658000000000001</v>
       </c>
       <c r="BO46" s="17" t="n"/>
       <c r="BP46" s="14" t="n">
-        <v>719050337</v>
+        <v>756845974</v>
       </c>
       <c r="BQ46" s="15" t="n">
-        <v>6275568.75</v>
+        <v>6714757.130000002</v>
       </c>
       <c r="BR46" s="16" t="n">
-        <v>0.6369999999999999</v>
+        <v>0.6467999999999997</v>
       </c>
       <c r="BS46" s="17" t="n"/>
       <c r="BT46" s="14" t="n">
-        <v>717176528</v>
+        <v>719050337</v>
       </c>
       <c r="BU46" s="15" t="n">
-        <v>6051937.579999999</v>
+        <v>6275568.75</v>
       </c>
       <c r="BV46" s="16" t="n">
-        <v>0.6476999999999998</v>
+        <v>0.6369999999999999</v>
       </c>
       <c r="BW46" s="17" t="n"/>
       <c r="BX46" s="14" t="n">
-        <v>718063829</v>
+        <v>717176528</v>
       </c>
       <c r="BY46" s="15" t="n">
-        <v>5662977.75</v>
+        <v>6051937.579999999</v>
       </c>
       <c r="BZ46" s="16" t="n">
-        <v>0.6436999999999999</v>
+        <v>0.6476999999999998</v>
       </c>
       <c r="CA46" s="17" t="n"/>
       <c r="CB46" s="14" t="n">
+        <v>718063829</v>
+      </c>
+      <c r="CC46" s="15" t="n">
+        <v>5662977.75</v>
+      </c>
+      <c r="CD46" s="16" t="n">
+        <v>0.6436999999999999</v>
+      </c>
+      <c r="CE46" s="17" t="n"/>
+      <c r="CF46" s="14" t="n">
         <v>697292654</v>
       </c>
-      <c r="CC46" s="15" t="n">
+      <c r="CG46" s="15" t="n">
         <v>5868142.6</v>
       </c>
-      <c r="CD46" s="16" t="n">
+      <c r="CH46" s="16" t="n">
         <v>0.6543000000000003</v>
       </c>
-      <c r="CE46" s="17" t="n"/>
+      <c r="CI46" s="17" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="21">
+  <mergeCells count="22">
     <mergeCell ref="BX2:CA2"/>
     <mergeCell ref="AR2:AU2"/>
     <mergeCell ref="AZ2:BC2"/>
     <mergeCell ref="BL2:BO2"/>
+    <mergeCell ref="A1:CI1"/>
     <mergeCell ref="L2:O2"/>
     <mergeCell ref="X2:AA2"/>
     <mergeCell ref="AJ2:AM2"/>
     <mergeCell ref="CB2:CE2"/>
-    <mergeCell ref="A1:CE1"/>
+    <mergeCell ref="CF2:CI2"/>
     <mergeCell ref="AV2:AY2"/>
     <mergeCell ref="D2:G2"/>
     <mergeCell ref="P2:S2"/>

--- a/PPFAS_Equity_Analysis.xlsx
+++ b/PPFAS_Equity_Analysis.xlsx
@@ -6522,7 +6522,7 @@
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>Food Products</t>
+          <t>Fertilizers &amp; Agrochemicals</t>
         </is>
       </c>
       <c r="D26" s="8" t="n">
@@ -9469,17 +9469,17 @@
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>Zydus Wellness Limited</t>
+          <t>Motilal Oswal Financial Services Limited</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>INE768C01010</t>
+          <t>INE338I01027</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>Food Products</t>
+          <t>Capital Markets</t>
         </is>
       </c>
       <c r="D39" s="8" t="n"/>
@@ -9533,64 +9533,86 @@
       <c r="AZ39" s="8" t="n"/>
       <c r="BA39" s="9" t="n"/>
       <c r="BB39" s="10" t="n"/>
-      <c r="BC39" s="11" t="n">
+      <c r="BC39" s="11" t="n"/>
+      <c r="BD39" s="8" t="n"/>
+      <c r="BE39" s="9" t="n"/>
+      <c r="BF39" s="10" t="n"/>
+      <c r="BG39" s="11" t="n"/>
+      <c r="BH39" s="8" t="n"/>
+      <c r="BI39" s="9" t="n"/>
+      <c r="BJ39" s="10" t="n"/>
+      <c r="BK39" s="11" t="n">
         <v>-1</v>
       </c>
-      <c r="BD39" s="8" t="n">
-        <v>4400000</v>
-      </c>
-      <c r="BE39" s="9" t="n">
-        <v>88822.8</v>
-      </c>
-      <c r="BF39" s="10" t="n">
-        <v>0.0077</v>
-      </c>
-      <c r="BG39" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH39" s="8" t="n">
-        <v>4400000</v>
-      </c>
-      <c r="BI39" s="9" t="n">
-        <v>89280.39999999999</v>
-      </c>
-      <c r="BJ39" s="10" t="n">
-        <v>0.007900000000000001</v>
-      </c>
-      <c r="BK39" s="11" t="n">
-        <v>0</v>
-      </c>
       <c r="BL39" s="8" t="n">
-        <v>4400000</v>
+        <v>591805</v>
       </c>
       <c r="BM39" s="9" t="n">
-        <v>89020.8</v>
+        <v>5149</v>
       </c>
       <c r="BN39" s="10" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="BO39" s="11" t="n">
+        <v>-0.8902567225534253</v>
+      </c>
+      <c r="BP39" s="8" t="n">
+        <v>5392631</v>
+      </c>
+      <c r="BQ39" s="9" t="n">
+        <v>43674.92</v>
+      </c>
+      <c r="BR39" s="10" t="n">
+        <v>0.0042</v>
+      </c>
+      <c r="BS39" s="11" t="n">
+        <v>-0.3719237093069153</v>
+      </c>
+      <c r="BT39" s="8" t="n">
+        <v>8585949</v>
+      </c>
+      <c r="BU39" s="9" t="n">
+        <v>56044.78</v>
+      </c>
+      <c r="BV39" s="10" t="n">
+        <v>0.0057</v>
+      </c>
+      <c r="BW39" s="11" t="n">
+        <v>-0.2132577936597328</v>
+      </c>
+      <c r="BX39" s="8" t="n">
+        <v>10913294</v>
+      </c>
+      <c r="BY39" s="9" t="n">
+        <v>67154.95</v>
+      </c>
+      <c r="BZ39" s="10" t="n">
+        <v>0.0072</v>
+      </c>
+      <c r="CA39" s="11" t="n">
+        <v>-0.09462389658963724</v>
+      </c>
+      <c r="CB39" s="8" t="n">
+        <v>12053879</v>
+      </c>
+      <c r="CC39" s="9" t="n">
+        <v>70937.08</v>
+      </c>
+      <c r="CD39" s="10" t="n">
         <v>0.0081</v>
       </c>
-      <c r="BO39" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP39" s="8" t="n"/>
-      <c r="BQ39" s="9" t="n"/>
-      <c r="BR39" s="10" t="n"/>
-      <c r="BS39" s="11" t="n"/>
-      <c r="BT39" s="8" t="n"/>
-      <c r="BU39" s="9" t="n"/>
-      <c r="BV39" s="10" t="n"/>
-      <c r="BW39" s="11" t="n"/>
-      <c r="BX39" s="8" t="n"/>
-      <c r="BY39" s="9" t="n"/>
-      <c r="BZ39" s="10" t="n"/>
-      <c r="CA39" s="11" t="n"/>
-      <c r="CB39" s="8" t="n"/>
-      <c r="CC39" s="9" t="n"/>
-      <c r="CD39" s="10" t="n"/>
-      <c r="CE39" s="11" t="n"/>
-      <c r="CF39" s="8" t="n"/>
-      <c r="CG39" s="9" t="n"/>
-      <c r="CH39" s="10" t="n"/>
+      <c r="CE39" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF39" s="8" t="n">
+        <v>12053879</v>
+      </c>
+      <c r="CG39" s="9" t="n">
+        <v>76801.28999999999</v>
+      </c>
+      <c r="CH39" s="10" t="n">
+        <v>0.0086</v>
+      </c>
       <c r="CI39" s="11" t="n"/>
     </row>
     <row r="40">
@@ -9958,17 +9980,17 @@
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>Motilal Oswal Financial Services Limited</t>
+          <t>ITC Hotels Limited</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>INE338I01027</t>
+          <t>INE379A01028</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>Capital Markets</t>
+          <t>Leisure Services</t>
         </is>
       </c>
       <c r="D42" s="8" t="n"/>
@@ -10030,77 +10052,53 @@
       <c r="BH42" s="8" t="n"/>
       <c r="BI42" s="9" t="n"/>
       <c r="BJ42" s="10" t="n"/>
-      <c r="BK42" s="11" t="n">
+      <c r="BK42" s="11" t="n"/>
+      <c r="BL42" s="8" t="n"/>
+      <c r="BM42" s="9" t="n"/>
+      <c r="BN42" s="10" t="n"/>
+      <c r="BO42" s="11" t="n"/>
+      <c r="BP42" s="8" t="n"/>
+      <c r="BQ42" s="9" t="n"/>
+      <c r="BR42" s="10" t="n"/>
+      <c r="BS42" s="11" t="n"/>
+      <c r="BT42" s="8" t="n"/>
+      <c r="BU42" s="9" t="n"/>
+      <c r="BV42" s="10" t="n"/>
+      <c r="BW42" s="11" t="n">
         <v>-1</v>
       </c>
-      <c r="BL42" s="8" t="n">
-        <v>591805</v>
-      </c>
-      <c r="BM42" s="9" t="n">
-        <v>5149</v>
-      </c>
-      <c r="BN42" s="10" t="n">
-        <v>0.0005</v>
-      </c>
-      <c r="BO42" s="11" t="n">
-        <v>-0.8902567225534253</v>
-      </c>
-      <c r="BP42" s="8" t="n">
-        <v>5392631</v>
-      </c>
-      <c r="BQ42" s="9" t="n">
-        <v>43674.92</v>
-      </c>
-      <c r="BR42" s="10" t="n">
-        <v>0.0042</v>
-      </c>
-      <c r="BS42" s="11" t="n">
-        <v>-0.3719237093069153</v>
-      </c>
-      <c r="BT42" s="8" t="n">
-        <v>8585949</v>
-      </c>
-      <c r="BU42" s="9" t="n">
-        <v>56044.78</v>
-      </c>
-      <c r="BV42" s="10" t="n">
-        <v>0.0057</v>
-      </c>
-      <c r="BW42" s="11" t="n">
-        <v>-0.2132577936597328</v>
-      </c>
       <c r="BX42" s="8" t="n">
-        <v>10913294</v>
+        <v>9899412</v>
       </c>
       <c r="BY42" s="9" t="n">
-        <v>67154.95</v>
+        <v>19552.33</v>
       </c>
       <c r="BZ42" s="10" t="n">
-        <v>0.0072</v>
+        <v>0.0021</v>
       </c>
       <c r="CA42" s="11" t="n">
-        <v>-0.09462389658963724</v>
+        <v>0</v>
       </c>
       <c r="CB42" s="8" t="n">
-        <v>12053879</v>
+        <v>9899412</v>
       </c>
       <c r="CC42" s="9" t="n">
-        <v>70937.08</v>
+        <v>16216.23</v>
       </c>
       <c r="CD42" s="10" t="n">
-        <v>0.0081</v>
+        <v>0.0018</v>
       </c>
       <c r="CE42" s="11" t="n">
         <v>0</v>
       </c>
       <c r="CF42" s="8" t="n">
-        <v>12053879</v>
+        <v>9899412</v>
       </c>
       <c r="CG42" s="9" t="n">
-        <v>76801.28999999999</v>
+        <v>16131.09</v>
       </c>
       <c r="CH42" s="10" t="n">
-        <v>0.0086</v>
+        <v>0.0018</v>
       </c>
       <c r="CI42" s="11" t="n"/>
     </row>
@@ -10282,17 +10280,17 @@
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>ITC Hotels Limited</t>
+          <t>Multi Commodity Exchange of India Limited</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>INE379A01028</t>
+          <t>INE745G01043</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>Leisure Services</t>
+          <t>Capital Markets</t>
         </is>
       </c>
       <c r="D44" s="8" t="n"/>
@@ -10326,11 +10324,21 @@
       <c r="AF44" s="8" t="n"/>
       <c r="AG44" s="9" t="n"/>
       <c r="AH44" s="10" t="n"/>
-      <c r="AI44" s="11" t="n"/>
-      <c r="AJ44" s="8" t="n"/>
-      <c r="AK44" s="9" t="n"/>
-      <c r="AL44" s="10" t="n"/>
-      <c r="AM44" s="11" t="n"/>
+      <c r="AI44" s="11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AJ44" s="8" t="n">
+        <v>795472</v>
+      </c>
+      <c r="AK44" s="9" t="n">
+        <v>20109.53</v>
+      </c>
+      <c r="AL44" s="10" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="AM44" s="11" t="n">
+        <v>1</v>
+      </c>
       <c r="AN44" s="8" t="n"/>
       <c r="AO44" s="9" t="n"/>
       <c r="AP44" s="10" t="n"/>
@@ -10366,58 +10374,34 @@
       <c r="BT44" s="8" t="n"/>
       <c r="BU44" s="9" t="n"/>
       <c r="BV44" s="10" t="n"/>
-      <c r="BW44" s="11" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BX44" s="8" t="n">
-        <v>9899412</v>
-      </c>
-      <c r="BY44" s="9" t="n">
-        <v>19552.33</v>
-      </c>
-      <c r="BZ44" s="10" t="n">
-        <v>0.0021</v>
-      </c>
-      <c r="CA44" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB44" s="8" t="n">
-        <v>9899412</v>
-      </c>
-      <c r="CC44" s="9" t="n">
-        <v>16216.23</v>
-      </c>
-      <c r="CD44" s="10" t="n">
-        <v>0.0018</v>
-      </c>
-      <c r="CE44" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF44" s="8" t="n">
-        <v>9899412</v>
-      </c>
-      <c r="CG44" s="9" t="n">
-        <v>16131.09</v>
-      </c>
-      <c r="CH44" s="10" t="n">
-        <v>0.0018</v>
-      </c>
+      <c r="BW44" s="11" t="n"/>
+      <c r="BX44" s="8" t="n"/>
+      <c r="BY44" s="9" t="n"/>
+      <c r="BZ44" s="10" t="n"/>
+      <c r="CA44" s="11" t="n"/>
+      <c r="CB44" s="8" t="n"/>
+      <c r="CC44" s="9" t="n"/>
+      <c r="CD44" s="10" t="n"/>
+      <c r="CE44" s="11" t="n"/>
+      <c r="CF44" s="8" t="n"/>
+      <c r="CG44" s="9" t="n"/>
+      <c r="CH44" s="10" t="n"/>
       <c r="CI44" s="11" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>Multi Commodity Exchange of India Limited</t>
+          <t>Zydus Wellness Limited</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>INE745G01043</t>
+          <t>INE768C01010</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>Capital Markets</t>
+          <t>Food Products</t>
         </is>
       </c>
       <c r="D45" s="8" t="n"/>
@@ -10451,21 +10435,11 @@
       <c r="AF45" s="8" t="n"/>
       <c r="AG45" s="9" t="n"/>
       <c r="AH45" s="10" t="n"/>
-      <c r="AI45" s="11" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AJ45" s="8" t="n">
-        <v>795472</v>
-      </c>
-      <c r="AK45" s="9" t="n">
-        <v>20109.53</v>
-      </c>
-      <c r="AL45" s="10" t="n">
-        <v>0.0015</v>
-      </c>
-      <c r="AM45" s="11" t="n">
-        <v>1</v>
-      </c>
+      <c r="AI45" s="11" t="n"/>
+      <c r="AJ45" s="8" t="n"/>
+      <c r="AK45" s="9" t="n"/>
+      <c r="AL45" s="10" t="n"/>
+      <c r="AM45" s="11" t="n"/>
       <c r="AN45" s="8" t="n"/>
       <c r="AO45" s="9" t="n"/>
       <c r="AP45" s="10" t="n"/>
@@ -10481,19 +10455,45 @@
       <c r="AZ45" s="8" t="n"/>
       <c r="BA45" s="9" t="n"/>
       <c r="BB45" s="10" t="n"/>
-      <c r="BC45" s="11" t="n"/>
-      <c r="BD45" s="8" t="n"/>
-      <c r="BE45" s="9" t="n"/>
-      <c r="BF45" s="10" t="n"/>
-      <c r="BG45" s="11" t="n"/>
-      <c r="BH45" s="8" t="n"/>
-      <c r="BI45" s="9" t="n"/>
-      <c r="BJ45" s="10" t="n"/>
-      <c r="BK45" s="11" t="n"/>
-      <c r="BL45" s="8" t="n"/>
-      <c r="BM45" s="9" t="n"/>
-      <c r="BN45" s="10" t="n"/>
-      <c r="BO45" s="11" t="n"/>
+      <c r="BC45" s="11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BD45" s="8" t="n">
+        <v>4400000</v>
+      </c>
+      <c r="BE45" s="9" t="n">
+        <v>88822.8</v>
+      </c>
+      <c r="BF45" s="10" t="n">
+        <v>0.0077</v>
+      </c>
+      <c r="BG45" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH45" s="8" t="n">
+        <v>4400000</v>
+      </c>
+      <c r="BI45" s="9" t="n">
+        <v>89280.39999999999</v>
+      </c>
+      <c r="BJ45" s="10" t="n">
+        <v>0.007900000000000001</v>
+      </c>
+      <c r="BK45" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL45" s="8" t="n">
+        <v>4400000</v>
+      </c>
+      <c r="BM45" s="9" t="n">
+        <v>89020.8</v>
+      </c>
+      <c r="BN45" s="10" t="n">
+        <v>0.0081</v>
+      </c>
+      <c r="BO45" s="11" t="n">
+        <v>1</v>
+      </c>
       <c r="BP45" s="8" t="n"/>
       <c r="BQ45" s="9" t="n"/>
       <c r="BR45" s="10" t="n"/>

--- a/PPFAS_Equity_Analysis.xlsx
+++ b/PPFAS_Equity_Analysis.xlsx
@@ -6522,7 +6522,7 @@
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>Fertilizers &amp; Agrochemicals</t>
+          <t>Food Products</t>
         </is>
       </c>
       <c r="D26" s="8" t="n">
@@ -9469,17 +9469,17 @@
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>Motilal Oswal Financial Services Limited</t>
+          <t>Zydus Wellness Limited</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>INE338I01027</t>
+          <t>INE768C01010</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>Capital Markets</t>
+          <t>Food Products</t>
         </is>
       </c>
       <c r="D39" s="8" t="n"/>
@@ -9533,86 +9533,64 @@
       <c r="AZ39" s="8" t="n"/>
       <c r="BA39" s="9" t="n"/>
       <c r="BB39" s="10" t="n"/>
-      <c r="BC39" s="11" t="n"/>
-      <c r="BD39" s="8" t="n"/>
-      <c r="BE39" s="9" t="n"/>
-      <c r="BF39" s="10" t="n"/>
-      <c r="BG39" s="11" t="n"/>
-      <c r="BH39" s="8" t="n"/>
-      <c r="BI39" s="9" t="n"/>
-      <c r="BJ39" s="10" t="n"/>
+      <c r="BC39" s="11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BD39" s="8" t="n">
+        <v>4400000</v>
+      </c>
+      <c r="BE39" s="9" t="n">
+        <v>88822.8</v>
+      </c>
+      <c r="BF39" s="10" t="n">
+        <v>0.0077</v>
+      </c>
+      <c r="BG39" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH39" s="8" t="n">
+        <v>4400000</v>
+      </c>
+      <c r="BI39" s="9" t="n">
+        <v>89280.39999999999</v>
+      </c>
+      <c r="BJ39" s="10" t="n">
+        <v>0.007900000000000001</v>
+      </c>
       <c r="BK39" s="11" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="BL39" s="8" t="n">
-        <v>591805</v>
+        <v>4400000</v>
       </c>
       <c r="BM39" s="9" t="n">
-        <v>5149</v>
+        <v>89020.8</v>
       </c>
       <c r="BN39" s="10" t="n">
-        <v>0.0005</v>
+        <v>0.0081</v>
       </c>
       <c r="BO39" s="11" t="n">
-        <v>-0.8902567225534253</v>
-      </c>
-      <c r="BP39" s="8" t="n">
-        <v>5392631</v>
-      </c>
-      <c r="BQ39" s="9" t="n">
-        <v>43674.92</v>
-      </c>
-      <c r="BR39" s="10" t="n">
-        <v>0.0042</v>
-      </c>
-      <c r="BS39" s="11" t="n">
-        <v>-0.3719237093069153</v>
-      </c>
-      <c r="BT39" s="8" t="n">
-        <v>8585949</v>
-      </c>
-      <c r="BU39" s="9" t="n">
-        <v>56044.78</v>
-      </c>
-      <c r="BV39" s="10" t="n">
-        <v>0.0057</v>
-      </c>
-      <c r="BW39" s="11" t="n">
-        <v>-0.2132577936597328</v>
-      </c>
-      <c r="BX39" s="8" t="n">
-        <v>10913294</v>
-      </c>
-      <c r="BY39" s="9" t="n">
-        <v>67154.95</v>
-      </c>
-      <c r="BZ39" s="10" t="n">
-        <v>0.0072</v>
-      </c>
-      <c r="CA39" s="11" t="n">
-        <v>-0.09462389658963724</v>
-      </c>
-      <c r="CB39" s="8" t="n">
-        <v>12053879</v>
-      </c>
-      <c r="CC39" s="9" t="n">
-        <v>70937.08</v>
-      </c>
-      <c r="CD39" s="10" t="n">
-        <v>0.0081</v>
-      </c>
-      <c r="CE39" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF39" s="8" t="n">
-        <v>12053879</v>
-      </c>
-      <c r="CG39" s="9" t="n">
-        <v>76801.28999999999</v>
-      </c>
-      <c r="CH39" s="10" t="n">
-        <v>0.0086</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="BP39" s="8" t="n"/>
+      <c r="BQ39" s="9" t="n"/>
+      <c r="BR39" s="10" t="n"/>
+      <c r="BS39" s="11" t="n"/>
+      <c r="BT39" s="8" t="n"/>
+      <c r="BU39" s="9" t="n"/>
+      <c r="BV39" s="10" t="n"/>
+      <c r="BW39" s="11" t="n"/>
+      <c r="BX39" s="8" t="n"/>
+      <c r="BY39" s="9" t="n"/>
+      <c r="BZ39" s="10" t="n"/>
+      <c r="CA39" s="11" t="n"/>
+      <c r="CB39" s="8" t="n"/>
+      <c r="CC39" s="9" t="n"/>
+      <c r="CD39" s="10" t="n"/>
+      <c r="CE39" s="11" t="n"/>
+      <c r="CF39" s="8" t="n"/>
+      <c r="CG39" s="9" t="n"/>
+      <c r="CH39" s="10" t="n"/>
       <c r="CI39" s="11" t="n"/>
     </row>
     <row r="40">
@@ -9980,17 +9958,17 @@
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>ITC Hotels Limited</t>
+          <t>Motilal Oswal Financial Services Limited</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>INE379A01028</t>
+          <t>INE338I01027</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>Leisure Services</t>
+          <t>Capital Markets</t>
         </is>
       </c>
       <c r="D42" s="8" t="n"/>
@@ -10052,53 +10030,77 @@
       <c r="BH42" s="8" t="n"/>
       <c r="BI42" s="9" t="n"/>
       <c r="BJ42" s="10" t="n"/>
-      <c r="BK42" s="11" t="n"/>
-      <c r="BL42" s="8" t="n"/>
-      <c r="BM42" s="9" t="n"/>
-      <c r="BN42" s="10" t="n"/>
-      <c r="BO42" s="11" t="n"/>
-      <c r="BP42" s="8" t="n"/>
-      <c r="BQ42" s="9" t="n"/>
-      <c r="BR42" s="10" t="n"/>
-      <c r="BS42" s="11" t="n"/>
-      <c r="BT42" s="8" t="n"/>
-      <c r="BU42" s="9" t="n"/>
-      <c r="BV42" s="10" t="n"/>
+      <c r="BK42" s="11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL42" s="8" t="n">
+        <v>591805</v>
+      </c>
+      <c r="BM42" s="9" t="n">
+        <v>5149</v>
+      </c>
+      <c r="BN42" s="10" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="BO42" s="11" t="n">
+        <v>-0.8902567225534253</v>
+      </c>
+      <c r="BP42" s="8" t="n">
+        <v>5392631</v>
+      </c>
+      <c r="BQ42" s="9" t="n">
+        <v>43674.92</v>
+      </c>
+      <c r="BR42" s="10" t="n">
+        <v>0.0042</v>
+      </c>
+      <c r="BS42" s="11" t="n">
+        <v>-0.3719237093069153</v>
+      </c>
+      <c r="BT42" s="8" t="n">
+        <v>8585949</v>
+      </c>
+      <c r="BU42" s="9" t="n">
+        <v>56044.78</v>
+      </c>
+      <c r="BV42" s="10" t="n">
+        <v>0.0057</v>
+      </c>
       <c r="BW42" s="11" t="n">
-        <v>-1</v>
+        <v>-0.2132577936597328</v>
       </c>
       <c r="BX42" s="8" t="n">
-        <v>9899412</v>
+        <v>10913294</v>
       </c>
       <c r="BY42" s="9" t="n">
-        <v>19552.33</v>
+        <v>67154.95</v>
       </c>
       <c r="BZ42" s="10" t="n">
-        <v>0.0021</v>
+        <v>0.0072</v>
       </c>
       <c r="CA42" s="11" t="n">
-        <v>0</v>
+        <v>-0.09462389658963724</v>
       </c>
       <c r="CB42" s="8" t="n">
-        <v>9899412</v>
+        <v>12053879</v>
       </c>
       <c r="CC42" s="9" t="n">
-        <v>16216.23</v>
+        <v>70937.08</v>
       </c>
       <c r="CD42" s="10" t="n">
-        <v>0.0018</v>
+        <v>0.0081</v>
       </c>
       <c r="CE42" s="11" t="n">
         <v>0</v>
       </c>
       <c r="CF42" s="8" t="n">
-        <v>9899412</v>
+        <v>12053879</v>
       </c>
       <c r="CG42" s="9" t="n">
-        <v>16131.09</v>
+        <v>76801.28999999999</v>
       </c>
       <c r="CH42" s="10" t="n">
-        <v>0.0018</v>
+        <v>0.0086</v>
       </c>
       <c r="CI42" s="11" t="n"/>
     </row>
@@ -10280,17 +10282,17 @@
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>Multi Commodity Exchange of India Limited</t>
+          <t>ITC Hotels Limited</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>INE745G01043</t>
+          <t>INE379A01028</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>Capital Markets</t>
+          <t>Leisure Services</t>
         </is>
       </c>
       <c r="D44" s="8" t="n"/>
@@ -10324,21 +10326,11 @@
       <c r="AF44" s="8" t="n"/>
       <c r="AG44" s="9" t="n"/>
       <c r="AH44" s="10" t="n"/>
-      <c r="AI44" s="11" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AJ44" s="8" t="n">
-        <v>795472</v>
-      </c>
-      <c r="AK44" s="9" t="n">
-        <v>20109.53</v>
-      </c>
-      <c r="AL44" s="10" t="n">
-        <v>0.0015</v>
-      </c>
-      <c r="AM44" s="11" t="n">
-        <v>1</v>
-      </c>
+      <c r="AI44" s="11" t="n"/>
+      <c r="AJ44" s="8" t="n"/>
+      <c r="AK44" s="9" t="n"/>
+      <c r="AL44" s="10" t="n"/>
+      <c r="AM44" s="11" t="n"/>
       <c r="AN44" s="8" t="n"/>
       <c r="AO44" s="9" t="n"/>
       <c r="AP44" s="10" t="n"/>
@@ -10374,34 +10366,58 @@
       <c r="BT44" s="8" t="n"/>
       <c r="BU44" s="9" t="n"/>
       <c r="BV44" s="10" t="n"/>
-      <c r="BW44" s="11" t="n"/>
-      <c r="BX44" s="8" t="n"/>
-      <c r="BY44" s="9" t="n"/>
-      <c r="BZ44" s="10" t="n"/>
-      <c r="CA44" s="11" t="n"/>
-      <c r="CB44" s="8" t="n"/>
-      <c r="CC44" s="9" t="n"/>
-      <c r="CD44" s="10" t="n"/>
-      <c r="CE44" s="11" t="n"/>
-      <c r="CF44" s="8" t="n"/>
-      <c r="CG44" s="9" t="n"/>
-      <c r="CH44" s="10" t="n"/>
+      <c r="BW44" s="11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BX44" s="8" t="n">
+        <v>9899412</v>
+      </c>
+      <c r="BY44" s="9" t="n">
+        <v>19552.33</v>
+      </c>
+      <c r="BZ44" s="10" t="n">
+        <v>0.0021</v>
+      </c>
+      <c r="CA44" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB44" s="8" t="n">
+        <v>9899412</v>
+      </c>
+      <c r="CC44" s="9" t="n">
+        <v>16216.23</v>
+      </c>
+      <c r="CD44" s="10" t="n">
+        <v>0.0018</v>
+      </c>
+      <c r="CE44" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF44" s="8" t="n">
+        <v>9899412</v>
+      </c>
+      <c r="CG44" s="9" t="n">
+        <v>16131.09</v>
+      </c>
+      <c r="CH44" s="10" t="n">
+        <v>0.0018</v>
+      </c>
       <c r="CI44" s="11" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>Zydus Wellness Limited</t>
+          <t>Multi Commodity Exchange of India Limited</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>INE768C01010</t>
+          <t>INE745G01043</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>Food Products</t>
+          <t>Capital Markets</t>
         </is>
       </c>
       <c r="D45" s="8" t="n"/>
@@ -10435,11 +10451,21 @@
       <c r="AF45" s="8" t="n"/>
       <c r="AG45" s="9" t="n"/>
       <c r="AH45" s="10" t="n"/>
-      <c r="AI45" s="11" t="n"/>
-      <c r="AJ45" s="8" t="n"/>
-      <c r="AK45" s="9" t="n"/>
-      <c r="AL45" s="10" t="n"/>
-      <c r="AM45" s="11" t="n"/>
+      <c r="AI45" s="11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AJ45" s="8" t="n">
+        <v>795472</v>
+      </c>
+      <c r="AK45" s="9" t="n">
+        <v>20109.53</v>
+      </c>
+      <c r="AL45" s="10" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="AM45" s="11" t="n">
+        <v>1</v>
+      </c>
       <c r="AN45" s="8" t="n"/>
       <c r="AO45" s="9" t="n"/>
       <c r="AP45" s="10" t="n"/>
@@ -10455,45 +10481,19 @@
       <c r="AZ45" s="8" t="n"/>
       <c r="BA45" s="9" t="n"/>
       <c r="BB45" s="10" t="n"/>
-      <c r="BC45" s="11" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BD45" s="8" t="n">
-        <v>4400000</v>
-      </c>
-      <c r="BE45" s="9" t="n">
-        <v>88822.8</v>
-      </c>
-      <c r="BF45" s="10" t="n">
-        <v>0.0077</v>
-      </c>
-      <c r="BG45" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH45" s="8" t="n">
-        <v>4400000</v>
-      </c>
-      <c r="BI45" s="9" t="n">
-        <v>89280.39999999999</v>
-      </c>
-      <c r="BJ45" s="10" t="n">
-        <v>0.007900000000000001</v>
-      </c>
-      <c r="BK45" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL45" s="8" t="n">
-        <v>4400000</v>
-      </c>
-      <c r="BM45" s="9" t="n">
-        <v>89020.8</v>
-      </c>
-      <c r="BN45" s="10" t="n">
-        <v>0.0081</v>
-      </c>
-      <c r="BO45" s="11" t="n">
-        <v>1</v>
-      </c>
+      <c r="BC45" s="11" t="n"/>
+      <c r="BD45" s="8" t="n"/>
+      <c r="BE45" s="9" t="n"/>
+      <c r="BF45" s="10" t="n"/>
+      <c r="BG45" s="11" t="n"/>
+      <c r="BH45" s="8" t="n"/>
+      <c r="BI45" s="9" t="n"/>
+      <c r="BJ45" s="10" t="n"/>
+      <c r="BK45" s="11" t="n"/>
+      <c r="BL45" s="8" t="n"/>
+      <c r="BM45" s="9" t="n"/>
+      <c r="BN45" s="10" t="n"/>
+      <c r="BO45" s="11" t="n"/>
       <c r="BP45" s="8" t="n"/>
       <c r="BQ45" s="9" t="n"/>
       <c r="BR45" s="10" t="n"/>

--- a/PPFAS_Equity_Analysis.xlsx
+++ b/PPFAS_Equity_Analysis.xlsx
@@ -9051,214 +9051,192 @@
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>Kotak Mahindra Bank Limited</t>
+          <t>The Great Eastern Shipping Company Limited</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>INE237A01028</t>
+          <t>INE017A01032</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>Banks</t>
+          <t>Transport Services</t>
         </is>
       </c>
       <c r="D37" s="8" t="n"/>
       <c r="E37" s="9" t="n"/>
       <c r="F37" s="10" t="n"/>
-      <c r="G37" s="11" t="n"/>
-      <c r="H37" s="8" t="n"/>
-      <c r="I37" s="9" t="n"/>
-      <c r="J37" s="10" t="n"/>
-      <c r="K37" s="11" t="n"/>
-      <c r="L37" s="8" t="n"/>
-      <c r="M37" s="9" t="n"/>
-      <c r="N37" s="10" t="n"/>
-      <c r="O37" s="11" t="n"/>
-      <c r="P37" s="8" t="n"/>
-      <c r="Q37" s="9" t="n"/>
-      <c r="R37" s="10" t="n"/>
-      <c r="S37" s="11" t="n"/>
-      <c r="T37" s="8" t="n"/>
-      <c r="U37" s="9" t="n"/>
-      <c r="V37" s="10" t="n"/>
-      <c r="W37" s="11" t="n"/>
-      <c r="X37" s="8" t="n"/>
-      <c r="Y37" s="9" t="n"/>
-      <c r="Z37" s="10" t="n"/>
-      <c r="AA37" s="11" t="n"/>
-      <c r="AB37" s="8" t="n"/>
-      <c r="AC37" s="9" t="n"/>
-      <c r="AD37" s="10" t="n"/>
-      <c r="AE37" s="11" t="n"/>
-      <c r="AF37" s="8" t="n"/>
-      <c r="AG37" s="9" t="n"/>
-      <c r="AH37" s="10" t="n"/>
-      <c r="AI37" s="11" t="n"/>
-      <c r="AJ37" s="8" t="n"/>
-      <c r="AK37" s="9" t="n"/>
-      <c r="AL37" s="10" t="n"/>
+      <c r="G37" s="11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H37" s="8" t="n">
+        <v>1273951</v>
+      </c>
+      <c r="I37" s="9" t="n">
+        <v>16584.29</v>
+      </c>
+      <c r="J37" s="10" t="n">
+        <v>0.0011</v>
+      </c>
+      <c r="K37" s="11" t="n">
+        <v>-0.4223225160499851</v>
+      </c>
+      <c r="L37" s="8" t="n">
+        <v>2205298</v>
+      </c>
+      <c r="M37" s="9" t="n">
+        <v>29780.34</v>
+      </c>
+      <c r="N37" s="10" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="O37" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" s="8" t="n">
+        <v>2205298</v>
+      </c>
+      <c r="Q37" s="9" t="n">
+        <v>32706.77</v>
+      </c>
+      <c r="R37" s="10" t="n">
+        <v>0.0023</v>
+      </c>
+      <c r="S37" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" s="8" t="n">
+        <v>2205298</v>
+      </c>
+      <c r="U37" s="9" t="n">
+        <v>31290.97</v>
+      </c>
+      <c r="V37" s="10" t="n">
+        <v>0.0022</v>
+      </c>
+      <c r="W37" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X37" s="8" t="n">
+        <v>2205298</v>
+      </c>
+      <c r="Y37" s="9" t="n">
+        <v>34773.14</v>
+      </c>
+      <c r="Z37" s="10" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="AA37" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB37" s="8" t="n">
+        <v>2205298</v>
+      </c>
+      <c r="AC37" s="9" t="n">
+        <v>31198.35</v>
+      </c>
+      <c r="AD37" s="10" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="AE37" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF37" s="8" t="n">
+        <v>2205298</v>
+      </c>
+      <c r="AG37" s="9" t="n">
+        <v>29526.73</v>
+      </c>
+      <c r="AH37" s="10" t="n">
+        <v>0.0022</v>
+      </c>
+      <c r="AI37" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ37" s="8" t="n">
+        <v>2205298</v>
+      </c>
+      <c r="AK37" s="9" t="n">
+        <v>26516.5</v>
+      </c>
+      <c r="AL37" s="10" t="n">
+        <v>0.002</v>
+      </c>
       <c r="AM37" s="11" t="n">
-        <v>-1</v>
+        <v>0.3305575398932319</v>
       </c>
       <c r="AN37" s="8" t="n">
-        <v>24621592</v>
+        <v>1657424</v>
       </c>
       <c r="AO37" s="9" t="n">
-        <v>541945.86</v>
+        <v>18712.32</v>
       </c>
       <c r="AP37" s="10" t="n">
-        <v>0.0407</v>
+        <v>0.0014</v>
       </c>
       <c r="AQ37" s="11" t="n">
-        <v>0.01296144774839237</v>
-      </c>
-      <c r="AR37" s="8" t="n">
-        <v>24306544</v>
-      </c>
-      <c r="AS37" s="9" t="n">
-        <v>516368.22</v>
-      </c>
-      <c r="AT37" s="10" t="n">
-        <v>0.0398</v>
-      </c>
-      <c r="AU37" s="11" t="n">
-        <v>0.004192884502844551</v>
-      </c>
-      <c r="AV37" s="8" t="n">
-        <v>24205055</v>
-      </c>
-      <c r="AW37" s="9" t="n">
-        <v>508838.67</v>
-      </c>
-      <c r="AX37" s="10" t="n">
-        <v>0.0404</v>
-      </c>
-      <c r="AY37" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ37" s="8" t="n">
-        <v>24205055</v>
-      </c>
-      <c r="BA37" s="9" t="n">
-        <v>482334.13</v>
-      </c>
-      <c r="BB37" s="10" t="n">
-        <v>0.0403</v>
-      </c>
-      <c r="BC37" s="11" t="n">
-        <v>0.03407788338216907</v>
-      </c>
-      <c r="BD37" s="8" t="n">
-        <v>23407381</v>
-      </c>
-      <c r="BE37" s="9" t="n">
-        <v>458854.89</v>
-      </c>
-      <c r="BF37" s="10" t="n">
-        <v>0.0399</v>
-      </c>
-      <c r="BG37" s="11" t="n">
-        <v>0.06425892329321918</v>
-      </c>
-      <c r="BH37" s="8" t="n">
-        <v>21994066</v>
-      </c>
-      <c r="BI37" s="9" t="n">
-        <v>435174.59</v>
-      </c>
-      <c r="BJ37" s="10" t="n">
-        <v>0.0384</v>
-      </c>
-      <c r="BK37" s="11" t="n">
-        <v>0.07428402120388222</v>
-      </c>
-      <c r="BL37" s="8" t="n">
-        <v>20473232</v>
-      </c>
-      <c r="BM37" s="9" t="n">
-        <v>442938.37</v>
-      </c>
-      <c r="BN37" s="10" t="n">
-        <v>0.0401</v>
-      </c>
-      <c r="BO37" s="11" t="n">
-        <v>0.03644973136547983</v>
-      </c>
-      <c r="BP37" s="8" t="n">
-        <v>19753232</v>
-      </c>
-      <c r="BQ37" s="9" t="n">
-        <v>409820.3</v>
-      </c>
-      <c r="BR37" s="10" t="n">
-        <v>0.0395</v>
-      </c>
-      <c r="BS37" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT37" s="8" t="n">
-        <v>19753232</v>
-      </c>
-      <c r="BU37" s="9" t="n">
-        <v>436171.12</v>
-      </c>
-      <c r="BV37" s="10" t="n">
-        <v>0.0443</v>
-      </c>
-      <c r="BW37" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX37" s="8" t="n">
-        <v>19753232</v>
-      </c>
-      <c r="BY37" s="9" t="n">
-        <v>428882.17</v>
-      </c>
-      <c r="BZ37" s="10" t="n">
-        <v>0.0459</v>
-      </c>
-      <c r="CA37" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB37" s="8" t="n">
-        <v>19753232</v>
-      </c>
-      <c r="CC37" s="9" t="n">
-        <v>375894.13</v>
-      </c>
-      <c r="CD37" s="10" t="n">
-        <v>0.0427</v>
-      </c>
-      <c r="CE37" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF37" s="8" t="n">
-        <v>19753232</v>
-      </c>
-      <c r="CG37" s="9" t="n">
-        <v>375568.2</v>
-      </c>
-      <c r="CH37" s="10" t="n">
-        <v>0.0419</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AR37" s="8" t="n"/>
+      <c r="AS37" s="9" t="n"/>
+      <c r="AT37" s="10" t="n"/>
+      <c r="AU37" s="11" t="n"/>
+      <c r="AV37" s="8" t="n"/>
+      <c r="AW37" s="9" t="n"/>
+      <c r="AX37" s="10" t="n"/>
+      <c r="AY37" s="11" t="n"/>
+      <c r="AZ37" s="8" t="n"/>
+      <c r="BA37" s="9" t="n"/>
+      <c r="BB37" s="10" t="n"/>
+      <c r="BC37" s="11" t="n"/>
+      <c r="BD37" s="8" t="n"/>
+      <c r="BE37" s="9" t="n"/>
+      <c r="BF37" s="10" t="n"/>
+      <c r="BG37" s="11" t="n"/>
+      <c r="BH37" s="8" t="n"/>
+      <c r="BI37" s="9" t="n"/>
+      <c r="BJ37" s="10" t="n"/>
+      <c r="BK37" s="11" t="n"/>
+      <c r="BL37" s="8" t="n"/>
+      <c r="BM37" s="9" t="n"/>
+      <c r="BN37" s="10" t="n"/>
+      <c r="BO37" s="11" t="n"/>
+      <c r="BP37" s="8" t="n"/>
+      <c r="BQ37" s="9" t="n"/>
+      <c r="BR37" s="10" t="n"/>
+      <c r="BS37" s="11" t="n"/>
+      <c r="BT37" s="8" t="n"/>
+      <c r="BU37" s="9" t="n"/>
+      <c r="BV37" s="10" t="n"/>
+      <c r="BW37" s="11" t="n"/>
+      <c r="BX37" s="8" t="n"/>
+      <c r="BY37" s="9" t="n"/>
+      <c r="BZ37" s="10" t="n"/>
+      <c r="CA37" s="11" t="n"/>
+      <c r="CB37" s="8" t="n"/>
+      <c r="CC37" s="9" t="n"/>
+      <c r="CD37" s="10" t="n"/>
+      <c r="CE37" s="11" t="n"/>
+      <c r="CF37" s="8" t="n"/>
+      <c r="CG37" s="9" t="n"/>
+      <c r="CH37" s="10" t="n"/>
       <c r="CI37" s="11" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>Balkrishna Industries Limited</t>
+          <t>Kotak Mahindra Bank Limited</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>INE787D01026</t>
+          <t>INE237A01028</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>Auto Components</t>
+          <t>Banks</t>
         </is>
       </c>
       <c r="D38" s="8" t="n"/>
@@ -9284,202 +9262,178 @@
       <c r="X38" s="8" t="n"/>
       <c r="Y38" s="9" t="n"/>
       <c r="Z38" s="10" t="n"/>
-      <c r="AA38" s="11" t="n">
+      <c r="AA38" s="11" t="n"/>
+      <c r="AB38" s="8" t="n"/>
+      <c r="AC38" s="9" t="n"/>
+      <c r="AD38" s="10" t="n"/>
+      <c r="AE38" s="11" t="n"/>
+      <c r="AF38" s="8" t="n"/>
+      <c r="AG38" s="9" t="n"/>
+      <c r="AH38" s="10" t="n"/>
+      <c r="AI38" s="11" t="n"/>
+      <c r="AJ38" s="8" t="n"/>
+      <c r="AK38" s="9" t="n"/>
+      <c r="AL38" s="10" t="n"/>
+      <c r="AM38" s="11" t="n">
         <v>-1</v>
       </c>
-      <c r="AB38" s="8" t="n">
-        <v>2274074</v>
-      </c>
-      <c r="AC38" s="9" t="n">
-        <v>47368.96</v>
-      </c>
-      <c r="AD38" s="10" t="n">
-        <v>0.0037</v>
-      </c>
-      <c r="AE38" s="11" t="n">
-        <v>-0.2174731122669314</v>
-      </c>
-      <c r="AF38" s="8" t="n">
-        <v>2906065</v>
-      </c>
-      <c r="AG38" s="9" t="n">
-        <v>69277.67999999999</v>
-      </c>
-      <c r="AH38" s="10" t="n">
-        <v>0.0052</v>
-      </c>
-      <c r="AI38" s="11" t="n">
-        <v>-0.3062750860930125</v>
-      </c>
-      <c r="AJ38" s="8" t="n">
-        <v>4189074</v>
-      </c>
-      <c r="AK38" s="9" t="n">
-        <v>96591.67</v>
-      </c>
-      <c r="AL38" s="10" t="n">
-        <v>0.0072</v>
-      </c>
-      <c r="AM38" s="11" t="n">
-        <v>0</v>
-      </c>
       <c r="AN38" s="8" t="n">
-        <v>4189074</v>
+        <v>24621592</v>
       </c>
       <c r="AO38" s="9" t="n">
-        <v>97173.95</v>
+        <v>541945.86</v>
       </c>
       <c r="AP38" s="10" t="n">
-        <v>0.0073</v>
+        <v>0.0407</v>
       </c>
       <c r="AQ38" s="11" t="n">
-        <v>0</v>
+        <v>0.01296144774839237</v>
       </c>
       <c r="AR38" s="8" t="n">
-        <v>4189074</v>
+        <v>24306544</v>
       </c>
       <c r="AS38" s="9" t="n">
-        <v>96721.53</v>
+        <v>516368.22</v>
       </c>
       <c r="AT38" s="10" t="n">
-        <v>0.0075</v>
+        <v>0.0398</v>
       </c>
       <c r="AU38" s="11" t="n">
-        <v>0</v>
+        <v>0.004192884502844551</v>
       </c>
       <c r="AV38" s="8" t="n">
-        <v>4189074</v>
+        <v>24205055</v>
       </c>
       <c r="AW38" s="9" t="n">
-        <v>95502.50999999999</v>
+        <v>508838.67</v>
       </c>
       <c r="AX38" s="10" t="n">
-        <v>0.0076</v>
+        <v>0.0404</v>
       </c>
       <c r="AY38" s="11" t="n">
         <v>0</v>
       </c>
       <c r="AZ38" s="8" t="n">
-        <v>4189074</v>
+        <v>24205055</v>
       </c>
       <c r="BA38" s="9" t="n">
-        <v>96130.87</v>
+        <v>482334.13</v>
       </c>
       <c r="BB38" s="10" t="n">
-        <v>0.008</v>
+        <v>0.0403</v>
       </c>
       <c r="BC38" s="11" t="n">
-        <v>0</v>
+        <v>0.03407788338216907</v>
       </c>
       <c r="BD38" s="8" t="n">
-        <v>4189074</v>
+        <v>23407381</v>
       </c>
       <c r="BE38" s="9" t="n">
-        <v>95904.66</v>
+        <v>458854.89</v>
       </c>
       <c r="BF38" s="10" t="n">
-        <v>0.0083</v>
+        <v>0.0399</v>
       </c>
       <c r="BG38" s="11" t="n">
-        <v>0</v>
+        <v>0.06425892329321918</v>
       </c>
       <c r="BH38" s="8" t="n">
-        <v>4189074</v>
+        <v>21994066</v>
       </c>
       <c r="BI38" s="9" t="n">
-        <v>112108</v>
+        <v>435174.59</v>
       </c>
       <c r="BJ38" s="10" t="n">
-        <v>0.009900000000000001</v>
+        <v>0.0384</v>
       </c>
       <c r="BK38" s="11" t="n">
-        <v>0</v>
+        <v>0.07428402120388222</v>
       </c>
       <c r="BL38" s="8" t="n">
-        <v>4189074</v>
+        <v>20473232</v>
       </c>
       <c r="BM38" s="9" t="n">
-        <v>102435.43</v>
+        <v>442938.37</v>
       </c>
       <c r="BN38" s="10" t="n">
-        <v>0.009299999999999999</v>
+        <v>0.0401</v>
       </c>
       <c r="BO38" s="11" t="n">
-        <v>0</v>
+        <v>0.03644973136547983</v>
       </c>
       <c r="BP38" s="8" t="n">
-        <v>4189074</v>
+        <v>19753232</v>
       </c>
       <c r="BQ38" s="9" t="n">
-        <v>103562.29</v>
+        <v>409820.3</v>
       </c>
       <c r="BR38" s="10" t="n">
-        <v>0.01</v>
+        <v>0.0395</v>
       </c>
       <c r="BS38" s="11" t="n">
         <v>0</v>
       </c>
       <c r="BT38" s="8" t="n">
-        <v>4189074</v>
+        <v>19753232</v>
       </c>
       <c r="BU38" s="9" t="n">
-        <v>112061.92</v>
+        <v>436171.12</v>
       </c>
       <c r="BV38" s="10" t="n">
-        <v>0.0114</v>
+        <v>0.0443</v>
       </c>
       <c r="BW38" s="11" t="n">
         <v>0</v>
       </c>
       <c r="BX38" s="8" t="n">
-        <v>4189074</v>
+        <v>19753232</v>
       </c>
       <c r="BY38" s="9" t="n">
-        <v>107022.46</v>
+        <v>428882.17</v>
       </c>
       <c r="BZ38" s="10" t="n">
-        <v>0.0115</v>
+        <v>0.0459</v>
       </c>
       <c r="CA38" s="11" t="n">
         <v>0</v>
       </c>
       <c r="CB38" s="8" t="n">
-        <v>4189074</v>
+        <v>19753232</v>
       </c>
       <c r="CC38" s="9" t="n">
-        <v>109571.51</v>
+        <v>375894.13</v>
       </c>
       <c r="CD38" s="10" t="n">
-        <v>0.0125</v>
+        <v>0.0427</v>
       </c>
       <c r="CE38" s="11" t="n">
         <v>0</v>
       </c>
       <c r="CF38" s="8" t="n">
-        <v>4189074</v>
+        <v>19753232</v>
       </c>
       <c r="CG38" s="9" t="n">
-        <v>116089.71</v>
+        <v>375568.2</v>
       </c>
       <c r="CH38" s="10" t="n">
-        <v>0.0129</v>
+        <v>0.0419</v>
       </c>
       <c r="CI38" s="11" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>Zydus Wellness Limited</t>
+          <t>Balkrishna Industries Limited</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>INE768C01010</t>
+          <t>INE787D01026</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>Food Products</t>
+          <t>Auto Components</t>
         </is>
       </c>
       <c r="D39" s="8" t="n"/>
@@ -9505,92 +9459,186 @@
       <c r="X39" s="8" t="n"/>
       <c r="Y39" s="9" t="n"/>
       <c r="Z39" s="10" t="n"/>
-      <c r="AA39" s="11" t="n"/>
-      <c r="AB39" s="8" t="n"/>
-      <c r="AC39" s="9" t="n"/>
-      <c r="AD39" s="10" t="n"/>
-      <c r="AE39" s="11" t="n"/>
-      <c r="AF39" s="8" t="n"/>
-      <c r="AG39" s="9" t="n"/>
-      <c r="AH39" s="10" t="n"/>
-      <c r="AI39" s="11" t="n"/>
-      <c r="AJ39" s="8" t="n"/>
-      <c r="AK39" s="9" t="n"/>
-      <c r="AL39" s="10" t="n"/>
-      <c r="AM39" s="11" t="n"/>
-      <c r="AN39" s="8" t="n"/>
-      <c r="AO39" s="9" t="n"/>
-      <c r="AP39" s="10" t="n"/>
-      <c r="AQ39" s="11" t="n"/>
-      <c r="AR39" s="8" t="n"/>
-      <c r="AS39" s="9" t="n"/>
-      <c r="AT39" s="10" t="n"/>
-      <c r="AU39" s="11" t="n"/>
-      <c r="AV39" s="8" t="n"/>
-      <c r="AW39" s="9" t="n"/>
-      <c r="AX39" s="10" t="n"/>
-      <c r="AY39" s="11" t="n"/>
-      <c r="AZ39" s="8" t="n"/>
-      <c r="BA39" s="9" t="n"/>
-      <c r="BB39" s="10" t="n"/>
+      <c r="AA39" s="11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AB39" s="8" t="n">
+        <v>2274074</v>
+      </c>
+      <c r="AC39" s="9" t="n">
+        <v>47368.96</v>
+      </c>
+      <c r="AD39" s="10" t="n">
+        <v>0.0037</v>
+      </c>
+      <c r="AE39" s="11" t="n">
+        <v>-0.2174731122669314</v>
+      </c>
+      <c r="AF39" s="8" t="n">
+        <v>2906065</v>
+      </c>
+      <c r="AG39" s="9" t="n">
+        <v>69277.67999999999</v>
+      </c>
+      <c r="AH39" s="10" t="n">
+        <v>0.0052</v>
+      </c>
+      <c r="AI39" s="11" t="n">
+        <v>-0.3062750860930125</v>
+      </c>
+      <c r="AJ39" s="8" t="n">
+        <v>4189074</v>
+      </c>
+      <c r="AK39" s="9" t="n">
+        <v>96591.67</v>
+      </c>
+      <c r="AL39" s="10" t="n">
+        <v>0.0072</v>
+      </c>
+      <c r="AM39" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN39" s="8" t="n">
+        <v>4189074</v>
+      </c>
+      <c r="AO39" s="9" t="n">
+        <v>97173.95</v>
+      </c>
+      <c r="AP39" s="10" t="n">
+        <v>0.0073</v>
+      </c>
+      <c r="AQ39" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR39" s="8" t="n">
+        <v>4189074</v>
+      </c>
+      <c r="AS39" s="9" t="n">
+        <v>96721.53</v>
+      </c>
+      <c r="AT39" s="10" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="AU39" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV39" s="8" t="n">
+        <v>4189074</v>
+      </c>
+      <c r="AW39" s="9" t="n">
+        <v>95502.50999999999</v>
+      </c>
+      <c r="AX39" s="10" t="n">
+        <v>0.0076</v>
+      </c>
+      <c r="AY39" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ39" s="8" t="n">
+        <v>4189074</v>
+      </c>
+      <c r="BA39" s="9" t="n">
+        <v>96130.87</v>
+      </c>
+      <c r="BB39" s="10" t="n">
+        <v>0.008</v>
+      </c>
       <c r="BC39" s="11" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="BD39" s="8" t="n">
-        <v>4400000</v>
+        <v>4189074</v>
       </c>
       <c r="BE39" s="9" t="n">
-        <v>88822.8</v>
+        <v>95904.66</v>
       </c>
       <c r="BF39" s="10" t="n">
-        <v>0.0077</v>
+        <v>0.0083</v>
       </c>
       <c r="BG39" s="11" t="n">
         <v>0</v>
       </c>
       <c r="BH39" s="8" t="n">
-        <v>4400000</v>
+        <v>4189074</v>
       </c>
       <c r="BI39" s="9" t="n">
-        <v>89280.39999999999</v>
+        <v>112108</v>
       </c>
       <c r="BJ39" s="10" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="BK39" s="11" t="n">
         <v>0</v>
       </c>
       <c r="BL39" s="8" t="n">
-        <v>4400000</v>
+        <v>4189074</v>
       </c>
       <c r="BM39" s="9" t="n">
-        <v>89020.8</v>
+        <v>102435.43</v>
       </c>
       <c r="BN39" s="10" t="n">
-        <v>0.0081</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="BO39" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP39" s="8" t="n"/>
-      <c r="BQ39" s="9" t="n"/>
-      <c r="BR39" s="10" t="n"/>
-      <c r="BS39" s="11" t="n"/>
-      <c r="BT39" s="8" t="n"/>
-      <c r="BU39" s="9" t="n"/>
-      <c r="BV39" s="10" t="n"/>
-      <c r="BW39" s="11" t="n"/>
-      <c r="BX39" s="8" t="n"/>
-      <c r="BY39" s="9" t="n"/>
-      <c r="BZ39" s="10" t="n"/>
-      <c r="CA39" s="11" t="n"/>
-      <c r="CB39" s="8" t="n"/>
-      <c r="CC39" s="9" t="n"/>
-      <c r="CD39" s="10" t="n"/>
-      <c r="CE39" s="11" t="n"/>
-      <c r="CF39" s="8" t="n"/>
-      <c r="CG39" s="9" t="n"/>
-      <c r="CH39" s="10" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="BP39" s="8" t="n">
+        <v>4189074</v>
+      </c>
+      <c r="BQ39" s="9" t="n">
+        <v>103562.29</v>
+      </c>
+      <c r="BR39" s="10" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="BS39" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT39" s="8" t="n">
+        <v>4189074</v>
+      </c>
+      <c r="BU39" s="9" t="n">
+        <v>112061.92</v>
+      </c>
+      <c r="BV39" s="10" t="n">
+        <v>0.0114</v>
+      </c>
+      <c r="BW39" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX39" s="8" t="n">
+        <v>4189074</v>
+      </c>
+      <c r="BY39" s="9" t="n">
+        <v>107022.46</v>
+      </c>
+      <c r="BZ39" s="10" t="n">
+        <v>0.0115</v>
+      </c>
+      <c r="CA39" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB39" s="8" t="n">
+        <v>4189074</v>
+      </c>
+      <c r="CC39" s="9" t="n">
+        <v>109571.51</v>
+      </c>
+      <c r="CD39" s="10" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="CE39" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF39" s="8" t="n">
+        <v>4189074</v>
+      </c>
+      <c r="CG39" s="9" t="n">
+        <v>116089.71</v>
+      </c>
+      <c r="CH39" s="10" t="n">
+        <v>0.0129</v>
+      </c>
       <c r="CI39" s="11" t="n"/>
     </row>
     <row r="40">
@@ -9793,17 +9841,17 @@
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>IPCA Laboratories Limited</t>
+          <t>Motilal Oswal Financial Services Limited</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>INE571A01038</t>
+          <t>INE338I01027</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>Pharmaceuticals &amp; Biotechnology</t>
+          <t>Capital Markets</t>
         </is>
       </c>
       <c r="D41" s="8" t="n"/>
@@ -9857,118 +9905,102 @@
       <c r="AZ41" s="8" t="n"/>
       <c r="BA41" s="9" t="n"/>
       <c r="BB41" s="10" t="n"/>
-      <c r="BC41" s="11" t="n">
+      <c r="BC41" s="11" t="n"/>
+      <c r="BD41" s="8" t="n"/>
+      <c r="BE41" s="9" t="n"/>
+      <c r="BF41" s="10" t="n"/>
+      <c r="BG41" s="11" t="n"/>
+      <c r="BH41" s="8" t="n"/>
+      <c r="BI41" s="9" t="n"/>
+      <c r="BJ41" s="10" t="n"/>
+      <c r="BK41" s="11" t="n">
         <v>-1</v>
       </c>
-      <c r="BD41" s="8" t="n">
-        <v>218075</v>
-      </c>
-      <c r="BE41" s="9" t="n">
-        <v>3019.03</v>
-      </c>
-      <c r="BF41" s="10" t="n">
-        <v>0.0003</v>
-      </c>
-      <c r="BG41" s="11" t="n">
-        <v>-0.6148554615199853</v>
-      </c>
-      <c r="BH41" s="8" t="n">
-        <v>566216</v>
-      </c>
-      <c r="BI41" s="9" t="n">
-        <v>8345.459999999999</v>
-      </c>
-      <c r="BJ41" s="10" t="n">
-        <v>0.0007</v>
-      </c>
-      <c r="BK41" s="11" t="n">
-        <v>-0.5682871579351869</v>
-      </c>
       <c r="BL41" s="8" t="n">
-        <v>1311557</v>
+        <v>591805</v>
       </c>
       <c r="BM41" s="9" t="n">
-        <v>18228.02</v>
+        <v>5149</v>
       </c>
       <c r="BN41" s="10" t="n">
-        <v>0.0017</v>
+        <v>0.0005</v>
       </c>
       <c r="BO41" s="11" t="n">
-        <v>-0.2008037316547793</v>
+        <v>-0.8902567225534253</v>
       </c>
       <c r="BP41" s="8" t="n">
-        <v>1641095</v>
+        <v>5392631</v>
       </c>
       <c r="BQ41" s="9" t="n">
-        <v>23382.32</v>
+        <v>43674.92</v>
       </c>
       <c r="BR41" s="10" t="n">
-        <v>0.0023</v>
+        <v>0.0042</v>
       </c>
       <c r="BS41" s="11" t="n">
-        <v>-0.1163687388172734</v>
+        <v>-0.3719237093069153</v>
       </c>
       <c r="BT41" s="8" t="n">
-        <v>1857217</v>
+        <v>8585949</v>
       </c>
       <c r="BU41" s="9" t="n">
-        <v>26023.32</v>
+        <v>56044.78</v>
       </c>
       <c r="BV41" s="10" t="n">
-        <v>0.0026</v>
+        <v>0.0057</v>
       </c>
       <c r="BW41" s="11" t="n">
-        <v>-0.03620728307597141</v>
+        <v>-0.2132577936597328</v>
       </c>
       <c r="BX41" s="8" t="n">
-        <v>1926988</v>
+        <v>10913294</v>
       </c>
       <c r="BY41" s="9" t="n">
-        <v>28941.43</v>
+        <v>67154.95</v>
       </c>
       <c r="BZ41" s="10" t="n">
-        <v>0.0031</v>
+        <v>0.0072</v>
       </c>
       <c r="CA41" s="11" t="n">
-        <v>0</v>
+        <v>-0.09462389658963724</v>
       </c>
       <c r="CB41" s="8" t="n">
-        <v>1926988</v>
+        <v>12053879</v>
       </c>
       <c r="CC41" s="9" t="n">
-        <v>26117.43</v>
+        <v>70937.08</v>
       </c>
       <c r="CD41" s="10" t="n">
-        <v>0.003</v>
+        <v>0.0081</v>
       </c>
       <c r="CE41" s="11" t="n">
-        <v>-0.1421734974921662</v>
+        <v>0</v>
       </c>
       <c r="CF41" s="8" t="n">
-        <v>2246361</v>
+        <v>12053879</v>
       </c>
       <c r="CG41" s="9" t="n">
-        <v>32421.73</v>
+        <v>76801.28999999999</v>
       </c>
       <c r="CH41" s="10" t="n">
-        <v>0.0036</v>
+        <v>0.0086</v>
       </c>
       <c r="CI41" s="11" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>Motilal Oswal Financial Services Limited</t>
+          <t>IPCA Laboratories Limited</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>INE338I01027</t>
+          <t>INE571A01038</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>Capital Markets</t>
+          <t>Pharmaceuticals &amp; Biotechnology</t>
         </is>
       </c>
       <c r="D42" s="8" t="n"/>
@@ -10022,218 +10054,160 @@
       <c r="AZ42" s="8" t="n"/>
       <c r="BA42" s="9" t="n"/>
       <c r="BB42" s="10" t="n"/>
-      <c r="BC42" s="11" t="n"/>
-      <c r="BD42" s="8" t="n"/>
-      <c r="BE42" s="9" t="n"/>
-      <c r="BF42" s="10" t="n"/>
-      <c r="BG42" s="11" t="n"/>
-      <c r="BH42" s="8" t="n"/>
-      <c r="BI42" s="9" t="n"/>
-      <c r="BJ42" s="10" t="n"/>
+      <c r="BC42" s="11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BD42" s="8" t="n">
+        <v>218075</v>
+      </c>
+      <c r="BE42" s="9" t="n">
+        <v>3019.03</v>
+      </c>
+      <c r="BF42" s="10" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="BG42" s="11" t="n">
+        <v>-0.6148554615199853</v>
+      </c>
+      <c r="BH42" s="8" t="n">
+        <v>566216</v>
+      </c>
+      <c r="BI42" s="9" t="n">
+        <v>8345.459999999999</v>
+      </c>
+      <c r="BJ42" s="10" t="n">
+        <v>0.0007</v>
+      </c>
       <c r="BK42" s="11" t="n">
-        <v>-1</v>
+        <v>-0.5682871579351869</v>
       </c>
       <c r="BL42" s="8" t="n">
-        <v>591805</v>
+        <v>1311557</v>
       </c>
       <c r="BM42" s="9" t="n">
-        <v>5149</v>
+        <v>18228.02</v>
       </c>
       <c r="BN42" s="10" t="n">
-        <v>0.0005</v>
+        <v>0.0017</v>
       </c>
       <c r="BO42" s="11" t="n">
-        <v>-0.8902567225534253</v>
+        <v>-0.2008037316547793</v>
       </c>
       <c r="BP42" s="8" t="n">
-        <v>5392631</v>
+        <v>1641095</v>
       </c>
       <c r="BQ42" s="9" t="n">
-        <v>43674.92</v>
+        <v>23382.32</v>
       </c>
       <c r="BR42" s="10" t="n">
-        <v>0.0042</v>
+        <v>0.0023</v>
       </c>
       <c r="BS42" s="11" t="n">
-        <v>-0.3719237093069153</v>
+        <v>-0.1163687388172734</v>
       </c>
       <c r="BT42" s="8" t="n">
-        <v>8585949</v>
+        <v>1857217</v>
       </c>
       <c r="BU42" s="9" t="n">
-        <v>56044.78</v>
+        <v>26023.32</v>
       </c>
       <c r="BV42" s="10" t="n">
-        <v>0.0057</v>
+        <v>0.0026</v>
       </c>
       <c r="BW42" s="11" t="n">
-        <v>-0.2132577936597328</v>
+        <v>-0.03620728307597141</v>
       </c>
       <c r="BX42" s="8" t="n">
-        <v>10913294</v>
+        <v>1926988</v>
       </c>
       <c r="BY42" s="9" t="n">
-        <v>67154.95</v>
+        <v>28941.43</v>
       </c>
       <c r="BZ42" s="10" t="n">
-        <v>0.0072</v>
+        <v>0.0031</v>
       </c>
       <c r="CA42" s="11" t="n">
-        <v>-0.09462389658963724</v>
+        <v>0</v>
       </c>
       <c r="CB42" s="8" t="n">
-        <v>12053879</v>
+        <v>1926988</v>
       </c>
       <c r="CC42" s="9" t="n">
-        <v>70937.08</v>
+        <v>26117.43</v>
       </c>
       <c r="CD42" s="10" t="n">
-        <v>0.0081</v>
+        <v>0.003</v>
       </c>
       <c r="CE42" s="11" t="n">
-        <v>0</v>
+        <v>-0.1421734974921662</v>
       </c>
       <c r="CF42" s="8" t="n">
-        <v>12053879</v>
+        <v>2246361</v>
       </c>
       <c r="CG42" s="9" t="n">
-        <v>76801.28999999999</v>
+        <v>32421.73</v>
       </c>
       <c r="CH42" s="10" t="n">
-        <v>0.0086</v>
+        <v>0.0036</v>
       </c>
       <c r="CI42" s="11" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>The Great Eastern Shipping Company Limited</t>
+          <t>ITC Hotels Limited</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>INE017A01032</t>
+          <t>INE379A01028</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>Transport Services</t>
+          <t>Leisure Services</t>
         </is>
       </c>
       <c r="D43" s="8" t="n"/>
       <c r="E43" s="9" t="n"/>
       <c r="F43" s="10" t="n"/>
-      <c r="G43" s="11" t="n">
-        <v>-1</v>
-      </c>
-      <c r="H43" s="8" t="n">
-        <v>1273951</v>
-      </c>
-      <c r="I43" s="9" t="n">
-        <v>16584.29</v>
-      </c>
-      <c r="J43" s="10" t="n">
-        <v>0.0011</v>
-      </c>
-      <c r="K43" s="11" t="n">
-        <v>-0.4223225160499851</v>
-      </c>
-      <c r="L43" s="8" t="n">
-        <v>2205298</v>
-      </c>
-      <c r="M43" s="9" t="n">
-        <v>29780.34</v>
-      </c>
-      <c r="N43" s="10" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="O43" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P43" s="8" t="n">
-        <v>2205298</v>
-      </c>
-      <c r="Q43" s="9" t="n">
-        <v>32706.77</v>
-      </c>
-      <c r="R43" s="10" t="n">
-        <v>0.0023</v>
-      </c>
-      <c r="S43" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T43" s="8" t="n">
-        <v>2205298</v>
-      </c>
-      <c r="U43" s="9" t="n">
-        <v>31290.97</v>
-      </c>
-      <c r="V43" s="10" t="n">
-        <v>0.0022</v>
-      </c>
-      <c r="W43" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X43" s="8" t="n">
-        <v>2205298</v>
-      </c>
-      <c r="Y43" s="9" t="n">
-        <v>34773.14</v>
-      </c>
-      <c r="Z43" s="10" t="n">
-        <v>0.0025</v>
-      </c>
-      <c r="AA43" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB43" s="8" t="n">
-        <v>2205298</v>
-      </c>
-      <c r="AC43" s="9" t="n">
-        <v>31198.35</v>
-      </c>
-      <c r="AD43" s="10" t="n">
-        <v>0.0024</v>
-      </c>
-      <c r="AE43" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF43" s="8" t="n">
-        <v>2205298</v>
-      </c>
-      <c r="AG43" s="9" t="n">
-        <v>29526.73</v>
-      </c>
-      <c r="AH43" s="10" t="n">
-        <v>0.0022</v>
-      </c>
-      <c r="AI43" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ43" s="8" t="n">
-        <v>2205298</v>
-      </c>
-      <c r="AK43" s="9" t="n">
-        <v>26516.5</v>
-      </c>
-      <c r="AL43" s="10" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="AM43" s="11" t="n">
-        <v>0.3305575398932319</v>
-      </c>
-      <c r="AN43" s="8" t="n">
-        <v>1657424</v>
-      </c>
-      <c r="AO43" s="9" t="n">
-        <v>18712.32</v>
-      </c>
-      <c r="AP43" s="10" t="n">
-        <v>0.0014</v>
-      </c>
-      <c r="AQ43" s="11" t="n">
-        <v>1</v>
-      </c>
+      <c r="G43" s="11" t="n"/>
+      <c r="H43" s="8" t="n"/>
+      <c r="I43" s="9" t="n"/>
+      <c r="J43" s="10" t="n"/>
+      <c r="K43" s="11" t="n"/>
+      <c r="L43" s="8" t="n"/>
+      <c r="M43" s="9" t="n"/>
+      <c r="N43" s="10" t="n"/>
+      <c r="O43" s="11" t="n"/>
+      <c r="P43" s="8" t="n"/>
+      <c r="Q43" s="9" t="n"/>
+      <c r="R43" s="10" t="n"/>
+      <c r="S43" s="11" t="n"/>
+      <c r="T43" s="8" t="n"/>
+      <c r="U43" s="9" t="n"/>
+      <c r="V43" s="10" t="n"/>
+      <c r="W43" s="11" t="n"/>
+      <c r="X43" s="8" t="n"/>
+      <c r="Y43" s="9" t="n"/>
+      <c r="Z43" s="10" t="n"/>
+      <c r="AA43" s="11" t="n"/>
+      <c r="AB43" s="8" t="n"/>
+      <c r="AC43" s="9" t="n"/>
+      <c r="AD43" s="10" t="n"/>
+      <c r="AE43" s="11" t="n"/>
+      <c r="AF43" s="8" t="n"/>
+      <c r="AG43" s="9" t="n"/>
+      <c r="AH43" s="10" t="n"/>
+      <c r="AI43" s="11" t="n"/>
+      <c r="AJ43" s="8" t="n"/>
+      <c r="AK43" s="9" t="n"/>
+      <c r="AL43" s="10" t="n"/>
+      <c r="AM43" s="11" t="n"/>
+      <c r="AN43" s="8" t="n"/>
+      <c r="AO43" s="9" t="n"/>
+      <c r="AP43" s="10" t="n"/>
+      <c r="AQ43" s="11" t="n"/>
       <c r="AR43" s="8" t="n"/>
       <c r="AS43" s="9" t="n"/>
       <c r="AT43" s="10" t="n"/>
@@ -10265,34 +10239,58 @@
       <c r="BT43" s="8" t="n"/>
       <c r="BU43" s="9" t="n"/>
       <c r="BV43" s="10" t="n"/>
-      <c r="BW43" s="11" t="n"/>
-      <c r="BX43" s="8" t="n"/>
-      <c r="BY43" s="9" t="n"/>
-      <c r="BZ43" s="10" t="n"/>
-      <c r="CA43" s="11" t="n"/>
-      <c r="CB43" s="8" t="n"/>
-      <c r="CC43" s="9" t="n"/>
-      <c r="CD43" s="10" t="n"/>
-      <c r="CE43" s="11" t="n"/>
-      <c r="CF43" s="8" t="n"/>
-      <c r="CG43" s="9" t="n"/>
-      <c r="CH43" s="10" t="n"/>
+      <c r="BW43" s="11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BX43" s="8" t="n">
+        <v>9899412</v>
+      </c>
+      <c r="BY43" s="9" t="n">
+        <v>19552.33</v>
+      </c>
+      <c r="BZ43" s="10" t="n">
+        <v>0.0021</v>
+      </c>
+      <c r="CA43" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB43" s="8" t="n">
+        <v>9899412</v>
+      </c>
+      <c r="CC43" s="9" t="n">
+        <v>16216.23</v>
+      </c>
+      <c r="CD43" s="10" t="n">
+        <v>0.0018</v>
+      </c>
+      <c r="CE43" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF43" s="8" t="n">
+        <v>9899412</v>
+      </c>
+      <c r="CG43" s="9" t="n">
+        <v>16131.09</v>
+      </c>
+      <c r="CH43" s="10" t="n">
+        <v>0.0018</v>
+      </c>
       <c r="CI43" s="11" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>ITC Hotels Limited</t>
+          <t>Multi Commodity Exchange of India Limited</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>INE379A01028</t>
+          <t>INE745G01043</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>Leisure Services</t>
+          <t>Capital Markets</t>
         </is>
       </c>
       <c r="D44" s="8" t="n"/>
@@ -10326,11 +10324,21 @@
       <c r="AF44" s="8" t="n"/>
       <c r="AG44" s="9" t="n"/>
       <c r="AH44" s="10" t="n"/>
-      <c r="AI44" s="11" t="n"/>
-      <c r="AJ44" s="8" t="n"/>
-      <c r="AK44" s="9" t="n"/>
-      <c r="AL44" s="10" t="n"/>
-      <c r="AM44" s="11" t="n"/>
+      <c r="AI44" s="11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AJ44" s="8" t="n">
+        <v>795472</v>
+      </c>
+      <c r="AK44" s="9" t="n">
+        <v>20109.53</v>
+      </c>
+      <c r="AL44" s="10" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="AM44" s="11" t="n">
+        <v>1</v>
+      </c>
       <c r="AN44" s="8" t="n"/>
       <c r="AO44" s="9" t="n"/>
       <c r="AP44" s="10" t="n"/>
@@ -10366,58 +10374,34 @@
       <c r="BT44" s="8" t="n"/>
       <c r="BU44" s="9" t="n"/>
       <c r="BV44" s="10" t="n"/>
-      <c r="BW44" s="11" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BX44" s="8" t="n">
-        <v>9899412</v>
-      </c>
-      <c r="BY44" s="9" t="n">
-        <v>19552.33</v>
-      </c>
-      <c r="BZ44" s="10" t="n">
-        <v>0.0021</v>
-      </c>
-      <c r="CA44" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB44" s="8" t="n">
-        <v>9899412</v>
-      </c>
-      <c r="CC44" s="9" t="n">
-        <v>16216.23</v>
-      </c>
-      <c r="CD44" s="10" t="n">
-        <v>0.0018</v>
-      </c>
-      <c r="CE44" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF44" s="8" t="n">
-        <v>9899412</v>
-      </c>
-      <c r="CG44" s="9" t="n">
-        <v>16131.09</v>
-      </c>
-      <c r="CH44" s="10" t="n">
-        <v>0.0018</v>
-      </c>
+      <c r="BW44" s="11" t="n"/>
+      <c r="BX44" s="8" t="n"/>
+      <c r="BY44" s="9" t="n"/>
+      <c r="BZ44" s="10" t="n"/>
+      <c r="CA44" s="11" t="n"/>
+      <c r="CB44" s="8" t="n"/>
+      <c r="CC44" s="9" t="n"/>
+      <c r="CD44" s="10" t="n"/>
+      <c r="CE44" s="11" t="n"/>
+      <c r="CF44" s="8" t="n"/>
+      <c r="CG44" s="9" t="n"/>
+      <c r="CH44" s="10" t="n"/>
       <c r="CI44" s="11" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>Multi Commodity Exchange of India Limited</t>
+          <t>Zydus Wellness Limited</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>INE745G01043</t>
+          <t>INE768C01010</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>Capital Markets</t>
+          <t>Food Products</t>
         </is>
       </c>
       <c r="D45" s="8" t="n"/>
@@ -10451,21 +10435,11 @@
       <c r="AF45" s="8" t="n"/>
       <c r="AG45" s="9" t="n"/>
       <c r="AH45" s="10" t="n"/>
-      <c r="AI45" s="11" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AJ45" s="8" t="n">
-        <v>795472</v>
-      </c>
-      <c r="AK45" s="9" t="n">
-        <v>20109.53</v>
-      </c>
-      <c r="AL45" s="10" t="n">
-        <v>0.0015</v>
-      </c>
-      <c r="AM45" s="11" t="n">
-        <v>1</v>
-      </c>
+      <c r="AI45" s="11" t="n"/>
+      <c r="AJ45" s="8" t="n"/>
+      <c r="AK45" s="9" t="n"/>
+      <c r="AL45" s="10" t="n"/>
+      <c r="AM45" s="11" t="n"/>
       <c r="AN45" s="8" t="n"/>
       <c r="AO45" s="9" t="n"/>
       <c r="AP45" s="10" t="n"/>
@@ -10481,19 +10455,45 @@
       <c r="AZ45" s="8" t="n"/>
       <c r="BA45" s="9" t="n"/>
       <c r="BB45" s="10" t="n"/>
-      <c r="BC45" s="11" t="n"/>
-      <c r="BD45" s="8" t="n"/>
-      <c r="BE45" s="9" t="n"/>
-      <c r="BF45" s="10" t="n"/>
-      <c r="BG45" s="11" t="n"/>
-      <c r="BH45" s="8" t="n"/>
-      <c r="BI45" s="9" t="n"/>
-      <c r="BJ45" s="10" t="n"/>
-      <c r="BK45" s="11" t="n"/>
-      <c r="BL45" s="8" t="n"/>
-      <c r="BM45" s="9" t="n"/>
-      <c r="BN45" s="10" t="n"/>
-      <c r="BO45" s="11" t="n"/>
+      <c r="BC45" s="11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BD45" s="8" t="n">
+        <v>4400000</v>
+      </c>
+      <c r="BE45" s="9" t="n">
+        <v>88822.8</v>
+      </c>
+      <c r="BF45" s="10" t="n">
+        <v>0.0077</v>
+      </c>
+      <c r="BG45" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH45" s="8" t="n">
+        <v>4400000</v>
+      </c>
+      <c r="BI45" s="9" t="n">
+        <v>89280.39999999999</v>
+      </c>
+      <c r="BJ45" s="10" t="n">
+        <v>0.007900000000000001</v>
+      </c>
+      <c r="BK45" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL45" s="8" t="n">
+        <v>4400000</v>
+      </c>
+      <c r="BM45" s="9" t="n">
+        <v>89020.8</v>
+      </c>
+      <c r="BN45" s="10" t="n">
+        <v>0.0081</v>
+      </c>
+      <c r="BO45" s="11" t="n">
+        <v>1</v>
+      </c>
       <c r="BP45" s="8" t="n"/>
       <c r="BQ45" s="9" t="n"/>
       <c r="BR45" s="10" t="n"/>
@@ -10617,7 +10617,7 @@
         <v>1079845116</v>
       </c>
       <c r="AO46" s="15" t="n">
-        <v>8588270.84</v>
+        <v>8588270.839999998</v>
       </c>
       <c r="AP46" s="16" t="n">
         <v>0.6443999999999998</v>
